--- a/Final Execution SKU wise.xlsx
+++ b/Final Execution SKU wise.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDEFF30C-FEE6-4598-8EC1-2EB2B66DE0D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F925AB3-0FE4-4242-9ACE-4E8DCA6A65CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" activeTab="11" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
   </bookViews>
   <sheets>
     <sheet name="last month" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="37">
   <si>
     <t>Gate Pass</t>
   </si>
@@ -159,12 +159,21 @@
   <si>
     <t xml:space="preserve">Last Month </t>
   </si>
+  <si>
+    <t>Mubeen</t>
+  </si>
+  <si>
+    <t>shops</t>
+  </si>
+  <si>
+    <t>ctns</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -193,6 +202,14 @@
       <color theme="1"/>
       <name val="Arial Black"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -562,7 +579,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
@@ -674,6 +691,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2202,7 +2225,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E52CB744-359B-4545-85D0-01C9D0099EAF}">
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:R19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.90625" bestFit="1" customWidth="1"/>
@@ -2216,7 +2239,7 @@
     <col min="11" max="11" width="5.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2229,7 +2252,7 @@
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="34" t="s">
         <v>0</v>
@@ -2244,7 +2267,7 @@
       <c r="J2" s="35"/>
       <c r="K2" s="36"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="37"/>
       <c r="C3" s="38"/>
@@ -2257,7 +2280,7 @@
       <c r="J3" s="38"/>
       <c r="K3" s="39"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" s="37"/>
       <c r="C4" s="38"/>
@@ -2270,7 +2293,7 @@
       <c r="J4" s="38"/>
       <c r="K4" s="39"/>
     </row>
-    <row r="5" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
       <c r="B5" s="40"/>
       <c r="C5" s="41"/>
@@ -2283,7 +2306,7 @@
       <c r="J5" s="41"/>
       <c r="K5" s="42"/>
     </row>
-    <row r="6" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="1"/>
       <c r="B6" s="2"/>
       <c r="C6" s="3" t="s">
@@ -2301,8 +2324,14 @@
       <c r="I6" s="44"/>
       <c r="J6" s="44"/>
       <c r="K6" s="45"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="Q6" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="R6" s="47" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>4</v>
       </c>
@@ -2336,53 +2365,138 @@
       <c r="K7" s="8" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P7" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q7" s="46">
+        <v>10</v>
+      </c>
+      <c r="R7" s="46">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A8" s="27"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
+      <c r="B8" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="12">
+        <v>28</v>
+      </c>
+      <c r="D8" s="12">
+        <v>10</v>
+      </c>
+      <c r="E8" s="12">
+        <v>10</v>
+      </c>
+      <c r="F8" s="12">
+        <v>6</v>
+      </c>
       <c r="G8" s="28">
         <f>SUM(D8:F8)/20</f>
-        <v>0</v>
-      </c>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="12"/>
+        <v>1.3</v>
+      </c>
+      <c r="H8" s="12">
+        <v>36</v>
+      </c>
+      <c r="I8" s="12">
+        <v>10</v>
+      </c>
+      <c r="J8" s="12">
+        <v>30</v>
+      </c>
       <c r="K8" s="28">
         <f>SUM(H8:J8)/20</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+        <v>3.8</v>
+      </c>
+      <c r="P8" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q8" s="46">
+        <v>10</v>
+      </c>
+      <c r="R8" s="46">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A9" s="27"/>
-      <c r="B9" s="10"/>
+      <c r="B9" s="10" t="s">
+        <v>34</v>
+      </c>
       <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12"/>
-      <c r="K9" s="28"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="D9" s="12">
+        <v>15</v>
+      </c>
+      <c r="E9" s="12">
+        <v>30</v>
+      </c>
+      <c r="F9" s="12">
+        <v>35</v>
+      </c>
+      <c r="G9" s="28">
+        <f t="shared" ref="G9:G10" si="0">SUM(D9:F9)/20</f>
+        <v>4</v>
+      </c>
+      <c r="H9" s="12">
+        <v>70</v>
+      </c>
+      <c r="I9" s="12">
+        <v>80</v>
+      </c>
+      <c r="J9" s="12">
+        <v>90</v>
+      </c>
+      <c r="K9" s="28">
+        <f t="shared" ref="K9:K10" si="1">SUM(H9:J9)/20</f>
+        <v>12</v>
+      </c>
+      <c r="P9" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q9" s="46">
+        <v>10</v>
+      </c>
+      <c r="R9" s="46">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="28"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="28"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B10" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="12">
+        <v>172</v>
+      </c>
+      <c r="D10" s="12">
+        <v>90</v>
+      </c>
+      <c r="E10" s="12">
+        <v>90</v>
+      </c>
+      <c r="F10" s="12">
+        <v>80</v>
+      </c>
+      <c r="G10" s="28">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="H10" s="12">
+        <v>307</v>
+      </c>
+      <c r="I10" s="12">
+        <v>256</v>
+      </c>
+      <c r="J10" s="12">
+        <v>335</v>
+      </c>
+      <c r="K10" s="28">
+        <f t="shared" si="1"/>
+        <v>44.9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11"/>
       <c r="C11" s="12"/>
@@ -2395,7 +2509,7 @@
       <c r="J11" s="12"/>
       <c r="K11" s="12"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
       <c r="B12" s="11"/>
       <c r="C12" s="12"/>
@@ -2408,7 +2522,7 @@
       <c r="J12" s="12"/>
       <c r="K12" s="12"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
       <c r="B13" s="11"/>
       <c r="C13" s="12"/>
@@ -2421,47 +2535,47 @@
       <c r="J13" s="12"/>
       <c r="K13" s="12"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:K14" si="0">SUM(C8:C13)</f>
-        <v>0</v>
+        <f t="shared" ref="C14:K14" si="2">SUM(C8:C13)</f>
+        <v>200</v>
       </c>
       <c r="D14" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>115</v>
       </c>
       <c r="E14" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>130</v>
       </c>
       <c r="F14" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>121</v>
       </c>
       <c r="G14" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>18.3</v>
       </c>
       <c r="H14" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>413</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>346</v>
       </c>
       <c r="J14" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>455</v>
       </c>
       <c r="K14" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v>60.7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A15" s="1"/>
       <c r="B15" s="15"/>
       <c r="C15" s="16"/>
@@ -2474,11 +2588,11 @@
       <c r="J15" s="18"/>
       <c r="K15" s="19"/>
     </row>
-    <row r="16" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="1"/>
       <c r="B16" s="15">
         <f>SUM(C8:F13,H8:J13)/40</f>
-        <v>0</v>
+        <v>44.5</v>
       </c>
       <c r="C16" s="21"/>
       <c r="D16" s="22"/>
@@ -2495,39 +2609,39 @@
       <c r="B17" s="1"/>
       <c r="C17" s="26">
         <f>C14/40</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D17" s="26">
-        <f t="shared" ref="D17:K17" si="1">D14/40</f>
-        <v>0</v>
+        <f t="shared" ref="D17:K17" si="3">D14/40</f>
+        <v>2.875</v>
       </c>
       <c r="E17" s="26">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>3.25</v>
       </c>
       <c r="F17" s="26">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>3.0249999999999999</v>
       </c>
       <c r="G17" s="26">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>0.45750000000000002</v>
       </c>
       <c r="H17" s="26">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>10.324999999999999</v>
       </c>
       <c r="I17" s="26">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>8.65</v>
       </c>
       <c r="J17" s="26">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>11.375</v>
       </c>
       <c r="K17" s="26">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1.5175000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.35">

--- a/Final Execution SKU wise.xlsx
+++ b/Final Execution SKU wise.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B257BD2A-9A0B-4FF8-95FC-C040ACBA3F1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56B72B0F-F77A-4022-B276-8E0E4D57523F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" activeTab="4" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" activeTab="13" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
   </bookViews>
   <sheets>
     <sheet name="last month" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="58">
   <si>
     <t>Gate Pass</t>
   </si>
@@ -183,6 +183,54 @@
   <si>
     <t>SKU Wise</t>
   </si>
+  <si>
+    <t xml:space="preserve">Pcs </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ctns </t>
+  </si>
+  <si>
+    <t>Gourmet</t>
+  </si>
+  <si>
+    <t>Meat 70</t>
+  </si>
+  <si>
+    <t>Lemon 70</t>
+  </si>
+  <si>
+    <t>Masala 70</t>
+  </si>
+  <si>
+    <t>Meat 120</t>
+  </si>
+  <si>
+    <t>Lemon 120</t>
+  </si>
+  <si>
+    <t>Chk 120</t>
+  </si>
+  <si>
+    <t>Zahoore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Link Road </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C Block </t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Block </t>
+  </si>
+  <si>
+    <t>Naseera Abad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Firdos </t>
+  </si>
+  <si>
+    <t>Nbeel</t>
+  </si>
 </sst>
 </file>
 
@@ -243,7 +291,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -271,6 +319,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -601,7 +655,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
@@ -678,6 +732,35 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -713,32 +796,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1085,57 +1142,57 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="36"/>
+      <c r="B2" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="49"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="37"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="39"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="52"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
-      <c r="K4" s="39"/>
+      <c r="B4" s="50"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="52"/>
     </row>
     <row r="5" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="40"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
-      <c r="J5" s="41"/>
-      <c r="K5" s="42"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
+      <c r="K5" s="55"/>
     </row>
     <row r="6" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="1"/>
@@ -1143,18 +1200,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="43" t="s">
+      <c r="D6" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="44" t="s">
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
-      <c r="K6" s="45"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="57"/>
+      <c r="K6" s="58"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
@@ -1455,57 +1512,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="36"/>
+      <c r="B2" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="49"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="37"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="39"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="52"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
-      <c r="K4" s="39"/>
+      <c r="B4" s="50"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="52"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="40"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
-      <c r="J5" s="41"/>
-      <c r="K5" s="42"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
+      <c r="K5" s="55"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -1513,18 +1570,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="43" t="s">
+      <c r="D6" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="44" t="s">
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
-      <c r="K6" s="45"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="57"/>
+      <c r="K6" s="58"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -1533,7 +1590,7 @@
       <c r="B7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="50" t="s">
+      <c r="C7" s="38" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="12" t="s">
@@ -1790,7 +1847,7 @@
         <f t="shared" si="1"/>
         <v>21.4</v>
       </c>
-      <c r="L14" s="48">
+      <c r="L14" s="36">
         <f>C14+D14+E14+F14+H14+I14+J14</f>
         <v>1176</v>
       </c>
@@ -1806,7 +1863,7 @@
         <v>6.9</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:K15" si="3">E14/20</f>
+        <f t="shared" ref="E15:J15" si="3">E14/20</f>
         <v>7.85</v>
       </c>
       <c r="F15" s="13">
@@ -1833,79 +1890,79 @@
       <c r="B16" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="49">
+      <c r="C16" s="37">
         <f>C15+C14</f>
         <v>248</v>
       </c>
-      <c r="D16" s="49">
-        <f t="shared" ref="D16:K16" si="4">D15+D14</f>
+      <c r="D16" s="37">
+        <f t="shared" ref="D16:J16" si="4">D15+D14</f>
         <v>144.9</v>
       </c>
-      <c r="E16" s="49">
+      <c r="E16" s="37">
         <f t="shared" si="4"/>
         <v>164.85</v>
       </c>
-      <c r="F16" s="49">
+      <c r="F16" s="37">
         <f t="shared" si="4"/>
         <v>215.25</v>
       </c>
-      <c r="G16" s="49"/>
-      <c r="H16" s="49">
+      <c r="G16" s="37"/>
+      <c r="H16" s="37">
         <f t="shared" si="4"/>
         <v>156.44999999999999</v>
       </c>
-      <c r="I16" s="49">
+      <c r="I16" s="37">
         <f t="shared" si="4"/>
         <v>130.19999999999999</v>
       </c>
-      <c r="J16" s="49">
+      <c r="J16" s="37">
         <f t="shared" si="4"/>
         <v>162.75</v>
       </c>
-      <c r="K16" s="49"/>
+      <c r="K16" s="37"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" s="13"/>
-      <c r="B17" s="52" t="s">
+      <c r="B17" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="49">
+      <c r="C17" s="37">
         <f>C14/40</f>
         <v>6.2</v>
       </c>
-      <c r="D17" s="49">
-        <f t="shared" ref="D17:K17" si="5">D14/40</f>
+      <c r="D17" s="37">
+        <f t="shared" ref="D17:J17" si="5">D14/40</f>
         <v>3.45</v>
       </c>
-      <c r="E17" s="49">
+      <c r="E17" s="37">
         <f t="shared" si="5"/>
         <v>3.9249999999999998</v>
       </c>
-      <c r="F17" s="49">
+      <c r="F17" s="37">
         <f t="shared" si="5"/>
         <v>5.125</v>
       </c>
-      <c r="G17" s="49"/>
-      <c r="H17" s="49">
+      <c r="G17" s="37"/>
+      <c r="H17" s="37">
         <f t="shared" si="5"/>
         <v>3.7250000000000001</v>
       </c>
-      <c r="I17" s="49">
+      <c r="I17" s="37">
         <f t="shared" si="5"/>
         <v>3.1</v>
       </c>
-      <c r="J17" s="49">
+      <c r="J17" s="37">
         <f t="shared" si="5"/>
         <v>3.875</v>
       </c>
-      <c r="K17" s="49"/>
-      <c r="L17" s="48">
+      <c r="K17" s="37"/>
+      <c r="L17" s="36">
         <f>SUM(C17:J17)</f>
         <v>29.400000000000002</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="C18" s="54"/>
+      <c r="C18" s="32"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
@@ -1962,57 +2019,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="36"/>
+      <c r="B2" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="49"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="37"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="39"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="52"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
-      <c r="K4" s="39"/>
+      <c r="B4" s="50"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="52"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="40"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
-      <c r="J5" s="41"/>
-      <c r="K5" s="42"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
+      <c r="K5" s="55"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -2020,18 +2077,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="43" t="s">
+      <c r="D6" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="44" t="s">
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
-      <c r="K6" s="45"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="57"/>
+      <c r="K6" s="58"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -2040,7 +2097,7 @@
       <c r="B7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="50" t="s">
+      <c r="C7" s="38" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="12" t="s">
@@ -2221,7 +2278,7 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="L14" s="48">
+      <c r="L14" s="36">
         <f>C14+D14+E14+F14+H14+I14+J14</f>
         <v>811</v>
       </c>
@@ -2237,7 +2294,7 @@
         <v>5.75</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:K15" si="1">E14/20</f>
+        <f t="shared" ref="E15:J15" si="1">E14/20</f>
         <v>6.1</v>
       </c>
       <c r="F15" s="13">
@@ -2264,79 +2321,79 @@
       <c r="B16" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="49">
+      <c r="C16" s="37">
         <f>C15+C14</f>
         <v>80</v>
       </c>
-      <c r="D16" s="49">
-        <f t="shared" ref="D16:K16" si="2">D15+D14</f>
+      <c r="D16" s="37">
+        <f t="shared" ref="D16:J16" si="2">D15+D14</f>
         <v>120.75</v>
       </c>
-      <c r="E16" s="49">
+      <c r="E16" s="37">
         <f t="shared" si="2"/>
         <v>128.1</v>
       </c>
-      <c r="F16" s="49">
+      <c r="F16" s="37">
         <f t="shared" si="2"/>
         <v>99.75</v>
       </c>
-      <c r="G16" s="49"/>
-      <c r="H16" s="49">
+      <c r="G16" s="37"/>
+      <c r="H16" s="37">
         <f t="shared" si="2"/>
         <v>168</v>
       </c>
-      <c r="I16" s="49">
+      <c r="I16" s="37">
         <f t="shared" si="2"/>
         <v>219.45</v>
       </c>
-      <c r="J16" s="49">
+      <c r="J16" s="37">
         <f t="shared" si="2"/>
         <v>31.5</v>
       </c>
-      <c r="K16" s="49"/>
+      <c r="K16" s="37"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" s="13"/>
-      <c r="B17" s="52" t="s">
+      <c r="B17" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="49">
+      <c r="C17" s="37">
         <f>C14/40</f>
         <v>2</v>
       </c>
-      <c r="D17" s="49">
-        <f t="shared" ref="D17:K17" si="3">D14/40</f>
+      <c r="D17" s="37">
+        <f t="shared" ref="D17:J17" si="3">D14/40</f>
         <v>2.875</v>
       </c>
-      <c r="E17" s="49">
+      <c r="E17" s="37">
         <f t="shared" si="3"/>
         <v>3.05</v>
       </c>
-      <c r="F17" s="49">
+      <c r="F17" s="37">
         <f t="shared" si="3"/>
         <v>2.375</v>
       </c>
-      <c r="G17" s="49"/>
-      <c r="H17" s="49">
+      <c r="G17" s="37"/>
+      <c r="H17" s="37">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="I17" s="49">
+      <c r="I17" s="37">
         <f t="shared" si="3"/>
         <v>5.2249999999999996</v>
       </c>
-      <c r="J17" s="49">
+      <c r="J17" s="37">
         <f t="shared" si="3"/>
         <v>0.75</v>
       </c>
-      <c r="K17" s="49"/>
-      <c r="L17" s="48">
+      <c r="K17" s="37"/>
+      <c r="L17" s="36">
         <f>SUM(C17:J17)</f>
         <v>20.274999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="C18" s="54"/>
+      <c r="C18" s="32"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
@@ -2393,57 +2450,57 @@
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="36"/>
+      <c r="B2" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="49"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="37"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="39"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="52"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
-      <c r="K4" s="39"/>
+      <c r="B4" s="50"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="52"/>
     </row>
     <row r="5" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="40"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
-      <c r="J5" s="41"/>
-      <c r="K5" s="42"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
+      <c r="K5" s="55"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -2451,18 +2508,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="43" t="s">
+      <c r="D6" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="44" t="s">
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
-      <c r="K6" s="45"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="57"/>
+      <c r="K6" s="58"/>
       <c r="Q6" s="33" t="s">
         <v>35</v>
       </c>
@@ -2477,7 +2534,7 @@
       <c r="B7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="50" t="s">
+      <c r="C7" s="38" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="12" t="s">
@@ -2713,7 +2770,7 @@
         <f t="shared" si="2"/>
         <v>60.7</v>
       </c>
-      <c r="L14" s="48">
+      <c r="L14" s="36">
         <f>C14+D14+E14+F14+H14+I14+J14</f>
         <v>1780</v>
       </c>
@@ -2729,7 +2786,7 @@
         <v>5.75</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:K15" si="3">E14/20</f>
+        <f t="shared" ref="E15:J15" si="3">E14/20</f>
         <v>6.5</v>
       </c>
       <c r="F15" s="13">
@@ -2756,79 +2813,79 @@
       <c r="B16" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="49">
+      <c r="C16" s="37">
         <f>C15+C14</f>
         <v>200</v>
       </c>
-      <c r="D16" s="49">
-        <f t="shared" ref="D16:K16" si="4">D15+D14</f>
+      <c r="D16" s="37">
+        <f t="shared" ref="D16:J16" si="4">D15+D14</f>
         <v>120.75</v>
       </c>
-      <c r="E16" s="49">
+      <c r="E16" s="37">
         <f t="shared" si="4"/>
         <v>136.5</v>
       </c>
-      <c r="F16" s="49">
+      <c r="F16" s="37">
         <f t="shared" si="4"/>
         <v>127.05</v>
       </c>
-      <c r="G16" s="49"/>
-      <c r="H16" s="49">
+      <c r="G16" s="37"/>
+      <c r="H16" s="37">
         <f t="shared" si="4"/>
         <v>433.65</v>
       </c>
-      <c r="I16" s="49">
+      <c r="I16" s="37">
         <f t="shared" si="4"/>
         <v>363.3</v>
       </c>
-      <c r="J16" s="49">
+      <c r="J16" s="37">
         <f t="shared" si="4"/>
         <v>477.75</v>
       </c>
-      <c r="K16" s="49"/>
+      <c r="K16" s="37"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" s="13"/>
-      <c r="B17" s="52" t="s">
+      <c r="B17" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="49">
+      <c r="C17" s="37">
         <f>C14/40</f>
         <v>5</v>
       </c>
-      <c r="D17" s="49">
-        <f t="shared" ref="D17:K17" si="5">D14/40</f>
+      <c r="D17" s="37">
+        <f t="shared" ref="D17:J17" si="5">D14/40</f>
         <v>2.875</v>
       </c>
-      <c r="E17" s="49">
+      <c r="E17" s="37">
         <f t="shared" si="5"/>
         <v>3.25</v>
       </c>
-      <c r="F17" s="49">
+      <c r="F17" s="37">
         <f t="shared" si="5"/>
         <v>3.0249999999999999</v>
       </c>
-      <c r="G17" s="49"/>
-      <c r="H17" s="49">
+      <c r="G17" s="37"/>
+      <c r="H17" s="37">
         <f t="shared" si="5"/>
         <v>10.324999999999999</v>
       </c>
-      <c r="I17" s="49">
+      <c r="I17" s="37">
         <f t="shared" si="5"/>
         <v>8.65</v>
       </c>
-      <c r="J17" s="49">
+      <c r="J17" s="37">
         <f t="shared" si="5"/>
         <v>11.375</v>
       </c>
-      <c r="K17" s="49"/>
-      <c r="L17" s="48">
+      <c r="K17" s="37"/>
+      <c r="L17" s="36">
         <f>SUM(C17:J17)</f>
         <v>44.5</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="C18" s="54"/>
+      <c r="C18" s="32"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
@@ -2888,57 +2945,57 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="36"/>
+      <c r="B2" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="49"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="37"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="39"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="52"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
-      <c r="K4" s="39"/>
+      <c r="B4" s="50"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="52"/>
     </row>
     <row r="5" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="40"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
-      <c r="J5" s="41"/>
-      <c r="K5" s="42"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
+      <c r="K5" s="55"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -2946,18 +3003,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="43" t="s">
+      <c r="D6" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="44" t="s">
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
-      <c r="K6" s="45"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="57"/>
+      <c r="K6" s="58"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -2966,7 +3023,7 @@
       <c r="B7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="50" t="s">
+      <c r="C7" s="38" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="12" t="s">
@@ -3147,43 +3204,43 @@
       <c r="B14" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="46">
+      <c r="C14" s="34">
         <f t="shared" ref="C14:K14" si="0">SUM(C8:C13)</f>
         <v>102</v>
       </c>
-      <c r="D14" s="46">
+      <c r="D14" s="34">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="E14" s="46">
+      <c r="E14" s="34">
         <f t="shared" si="0"/>
         <v>120</v>
       </c>
-      <c r="F14" s="46">
+      <c r="F14" s="34">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="G14" s="46">
+      <c r="G14" s="34">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="H14" s="46">
+      <c r="H14" s="34">
         <f t="shared" si="0"/>
         <v>273</v>
       </c>
-      <c r="I14" s="46">
+      <c r="I14" s="34">
         <f t="shared" si="0"/>
         <v>231</v>
       </c>
-      <c r="J14" s="46">
+      <c r="J14" s="34">
         <f t="shared" si="0"/>
         <v>242</v>
       </c>
-      <c r="K14" s="46">
+      <c r="K14" s="34">
         <f t="shared" si="0"/>
         <v>37.299999999999997</v>
       </c>
-      <c r="L14" s="47">
+      <c r="L14" s="35">
         <f>C14+D14+E14+F14+H14+I14+J14</f>
         <v>1128</v>
       </c>
@@ -3199,7 +3256,7 @@
         <v>5</v>
       </c>
       <c r="E15" s="30">
-        <f t="shared" ref="E15:K15" si="1">E14/20</f>
+        <f t="shared" ref="E15:J15" si="1">E14/20</f>
         <v>6</v>
       </c>
       <c r="F15" s="30">
@@ -3226,79 +3283,79 @@
       <c r="B16" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="51">
+      <c r="C16" s="39">
         <f>C15+C14</f>
         <v>102</v>
       </c>
-      <c r="D16" s="51">
-        <f t="shared" ref="D16:K16" si="2">D15+D14</f>
+      <c r="D16" s="39">
+        <f t="shared" ref="D16:J16" si="2">D15+D14</f>
         <v>105</v>
       </c>
-      <c r="E16" s="51">
+      <c r="E16" s="39">
         <f t="shared" si="2"/>
         <v>126</v>
       </c>
-      <c r="F16" s="51">
+      <c r="F16" s="39">
         <f t="shared" si="2"/>
         <v>63</v>
       </c>
-      <c r="G16" s="51"/>
-      <c r="H16" s="51">
+      <c r="G16" s="39"/>
+      <c r="H16" s="39">
         <f t="shared" si="2"/>
         <v>286.64999999999998</v>
       </c>
-      <c r="I16" s="51">
+      <c r="I16" s="39">
         <f t="shared" si="2"/>
         <v>242.55</v>
       </c>
-      <c r="J16" s="51">
+      <c r="J16" s="39">
         <f t="shared" si="2"/>
         <v>254.1</v>
       </c>
-      <c r="K16" s="51"/>
+      <c r="K16" s="39"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" s="13"/>
       <c r="B17" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="49">
+      <c r="C17" s="37">
         <f>C14/40</f>
         <v>2.5499999999999998</v>
       </c>
-      <c r="D17" s="49">
-        <f t="shared" ref="D17:K17" si="3">D14/40</f>
+      <c r="D17" s="37">
+        <f t="shared" ref="D17:J17" si="3">D14/40</f>
         <v>2.5</v>
       </c>
-      <c r="E17" s="49">
+      <c r="E17" s="37">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="F17" s="49">
+      <c r="F17" s="37">
         <f t="shared" si="3"/>
         <v>1.5</v>
       </c>
-      <c r="G17" s="49"/>
-      <c r="H17" s="49">
+      <c r="G17" s="37"/>
+      <c r="H17" s="37">
         <f t="shared" si="3"/>
         <v>6.8250000000000002</v>
       </c>
-      <c r="I17" s="49">
+      <c r="I17" s="37">
         <f t="shared" si="3"/>
         <v>5.7750000000000004</v>
       </c>
-      <c r="J17" s="49">
+      <c r="J17" s="37">
         <f t="shared" si="3"/>
         <v>6.05</v>
       </c>
-      <c r="K17" s="49"/>
-      <c r="L17" s="47">
+      <c r="K17" s="37"/>
+      <c r="L17" s="35">
         <f>SUM(C17:J17)</f>
         <v>28.2</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="C18" s="54"/>
+      <c r="C18" s="32"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
@@ -3325,22 +3382,22 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{400FD42A-C002-41E3-80E9-BA0AAA04C4EB}">
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:T19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.90625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.08984375" customWidth="1"/>
-    <col min="5" max="5" width="4.26953125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="3.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.36328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="3.90625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="5.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="4.26953125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="3.54296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="4.36328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="3.90625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="5.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3353,87 +3410,87 @@
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="36"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B2" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="49"/>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="37"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="39"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B3" s="50"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="52"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
-      <c r="K4" s="39"/>
-    </row>
-    <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B4" s="50"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="52"/>
+    </row>
+    <row r="5" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="40"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
-      <c r="J5" s="41"/>
-      <c r="K5" s="42"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B5" s="53"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
+      <c r="K5" s="55"/>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
       <c r="B6" s="2"/>
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="43" t="s">
+      <c r="D6" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="44" t="s">
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
-      <c r="K6" s="45"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="I6" s="57"/>
+      <c r="J6" s="57"/>
+      <c r="K6" s="58"/>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
         <v>4</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="50" t="s">
+      <c r="C7" s="38" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="12" t="s">
@@ -3461,65 +3518,210 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A8" s="27"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
+      <c r="B8" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="12">
+        <v>40</v>
+      </c>
+      <c r="D8" s="12">
+        <v>60</v>
+      </c>
+      <c r="E8" s="12">
+        <v>100</v>
+      </c>
+      <c r="F8" s="12">
+        <v>80</v>
+      </c>
       <c r="G8" s="28">
         <f>SUM(D8:F8)/20</f>
-        <v>0</v>
-      </c>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="H8" s="12">
+        <v>135</v>
+      </c>
+      <c r="I8" s="12">
+        <v>110</v>
+      </c>
+      <c r="J8" s="12">
+        <v>115</v>
+      </c>
       <c r="K8" s="28">
         <f>SUM(H8:J8)/20</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="O8" s="44" t="s">
+        <v>45</v>
+      </c>
+      <c r="P8" s="44" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q8" s="44" t="s">
+        <v>47</v>
+      </c>
+      <c r="R8" s="44" t="s">
+        <v>48</v>
+      </c>
+      <c r="S8" s="44" t="s">
+        <v>49</v>
+      </c>
+      <c r="T8" s="44" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A9" s="27"/>
-      <c r="B9" s="10"/>
+      <c r="B9" s="10" t="s">
+        <v>11</v>
+      </c>
       <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12"/>
-      <c r="K9" s="28"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="D9" s="12">
+        <v>27</v>
+      </c>
+      <c r="E9" s="12">
+        <v>22</v>
+      </c>
+      <c r="F9" s="12">
+        <v>27</v>
+      </c>
+      <c r="G9" s="28">
+        <f t="shared" ref="G9:G11" si="0">SUM(D9:F9)/20</f>
+        <v>3.8</v>
+      </c>
+      <c r="H9" s="12">
+        <v>22</v>
+      </c>
+      <c r="I9" s="12">
+        <v>52</v>
+      </c>
+      <c r="J9" s="12">
+        <v>42</v>
+      </c>
+      <c r="K9" s="28">
+        <f t="shared" ref="K9:K11" si="1">SUM(H9:J9)/20</f>
+        <v>5.8</v>
+      </c>
+      <c r="N9" s="45" t="s">
+        <v>51</v>
+      </c>
+      <c r="O9" s="45">
+        <v>80</v>
+      </c>
+      <c r="P9" s="45">
+        <v>80</v>
+      </c>
+      <c r="Q9" s="45">
+        <v>80</v>
+      </c>
+      <c r="R9" s="45">
+        <v>80</v>
+      </c>
+      <c r="S9" s="45">
+        <v>80</v>
+      </c>
+      <c r="T9" s="45">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
-      <c r="B10" s="10"/>
+      <c r="B10" s="10" t="s">
+        <v>44</v>
+      </c>
       <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="28"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="28"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="D10" s="12">
+        <v>300</v>
+      </c>
+      <c r="E10" s="12">
+        <v>300</v>
+      </c>
+      <c r="F10" s="12">
+        <v>300</v>
+      </c>
+      <c r="G10" s="28">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="H10" s="12">
+        <v>300</v>
+      </c>
+      <c r="I10" s="12">
+        <v>300</v>
+      </c>
+      <c r="J10" s="12">
+        <v>300</v>
+      </c>
+      <c r="K10" s="28">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="N10" s="45" t="s">
+        <v>52</v>
+      </c>
+      <c r="O10" s="45">
+        <v>20</v>
+      </c>
+      <c r="P10" s="45">
+        <v>20</v>
+      </c>
+      <c r="Q10" s="45">
+        <v>20</v>
+      </c>
+      <c r="R10" s="45">
+        <v>20</v>
+      </c>
+      <c r="S10" s="45">
+        <v>20</v>
+      </c>
+      <c r="T10" s="45">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
-      <c r="B11" s="11"/>
+      <c r="B11" s="11" t="s">
+        <v>57</v>
+      </c>
       <c r="C11" s="12"/>
       <c r="D11" s="12"/>
       <c r="E11" s="12"/>
       <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
+      <c r="G11" s="28">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="H11" s="12"/>
       <c r="I11" s="12"/>
       <c r="J11" s="12"/>
-      <c r="K11" s="12"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="K11" s="28">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N11" s="45" t="s">
+        <v>53</v>
+      </c>
+      <c r="O11" s="45">
+        <v>40</v>
+      </c>
+      <c r="P11" s="45">
+        <v>40</v>
+      </c>
+      <c r="Q11" s="45">
+        <v>40</v>
+      </c>
+      <c r="R11" s="45">
+        <v>40</v>
+      </c>
+      <c r="S11" s="45">
+        <v>40</v>
+      </c>
+      <c r="T11" s="45">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
       <c r="B12" s="11"/>
       <c r="C12" s="12"/>
@@ -3531,8 +3733,29 @@
       <c r="I12" s="12"/>
       <c r="J12" s="12"/>
       <c r="K12" s="12"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N12" s="45" t="s">
+        <v>54</v>
+      </c>
+      <c r="O12" s="45">
+        <v>40</v>
+      </c>
+      <c r="P12" s="45">
+        <v>40</v>
+      </c>
+      <c r="Q12" s="45">
+        <v>40</v>
+      </c>
+      <c r="R12" s="45">
+        <v>40</v>
+      </c>
+      <c r="S12" s="45">
+        <v>40</v>
+      </c>
+      <c r="T12" s="45">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
       <c r="B13" s="11"/>
       <c r="C13" s="12"/>
@@ -3544,52 +3767,99 @@
       <c r="I13" s="12"/>
       <c r="J13" s="12"/>
       <c r="K13" s="12"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="L13" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="N13" s="45" t="s">
+        <v>55</v>
+      </c>
+      <c r="O13" s="45">
+        <v>80</v>
+      </c>
+      <c r="P13" s="45">
+        <v>80</v>
+      </c>
+      <c r="Q13" s="45">
+        <v>80</v>
+      </c>
+      <c r="R13" s="45">
+        <v>80</v>
+      </c>
+      <c r="S13" s="45">
+        <v>80</v>
+      </c>
+      <c r="T13" s="45">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
-      <c r="B14" s="10"/>
+      <c r="B14" s="10" t="s">
+        <v>31</v>
+      </c>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:K14" si="0">SUM(C8:C13)</f>
-        <v>0</v>
+        <f t="shared" ref="C14:K14" si="2">SUM(C8:C13)</f>
+        <v>40</v>
       </c>
       <c r="D14" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>387</v>
       </c>
       <c r="E14" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>422</v>
       </c>
       <c r="F14" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>407</v>
       </c>
       <c r="G14" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>60.8</v>
       </c>
       <c r="H14" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>457</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>462</v>
       </c>
       <c r="J14" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>457</v>
       </c>
       <c r="K14" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L14" s="48">
+        <f t="shared" si="2"/>
+        <v>68.8</v>
+      </c>
+      <c r="L14" s="36">
         <f>C14+D14+E14+F14+H14+I14+J14</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+        <v>2632</v>
+      </c>
+      <c r="N14" s="45" t="s">
+        <v>56</v>
+      </c>
+      <c r="O14" s="45">
+        <v>40</v>
+      </c>
+      <c r="P14" s="45">
+        <v>40</v>
+      </c>
+      <c r="Q14" s="45">
+        <v>40</v>
+      </c>
+      <c r="R14" s="45">
+        <v>40</v>
+      </c>
+      <c r="S14" s="45">
+        <v>40</v>
+      </c>
+      <c r="T14" s="45">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A15" s="13"/>
       <c r="B15" s="10" t="s">
         <v>40</v>
@@ -3597,109 +3867,139 @@
       <c r="C15" s="13"/>
       <c r="D15" s="13">
         <f>D14/20</f>
-        <v>0</v>
+        <v>19.350000000000001</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:K15" si="1">E14/20</f>
-        <v>0</v>
+        <f t="shared" ref="E15:J15" si="3">E14/20</f>
+        <v>21.1</v>
       </c>
       <c r="F15" s="13">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>20.350000000000001</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>22.85</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>23.1</v>
       </c>
       <c r="J15" s="13">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>22.85</v>
       </c>
       <c r="K15" s="13"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N15" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="O15" s="46">
+        <f>SUM(O9:O14)</f>
+        <v>300</v>
+      </c>
+      <c r="P15" s="46">
+        <f t="shared" ref="P15:T15" si="4">SUM(P9:P14)</f>
+        <v>300</v>
+      </c>
+      <c r="Q15" s="46">
+        <f t="shared" si="4"/>
+        <v>300</v>
+      </c>
+      <c r="R15" s="46">
+        <f t="shared" si="4"/>
+        <v>300</v>
+      </c>
+      <c r="S15" s="46">
+        <f t="shared" si="4"/>
+        <v>300</v>
+      </c>
+      <c r="T15" s="46">
+        <f t="shared" si="4"/>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A16" s="13"/>
       <c r="B16" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="49">
+      <c r="C16" s="37">
         <f>C15+C14</f>
-        <v>0</v>
-      </c>
-      <c r="D16" s="49">
-        <f t="shared" ref="D16:K16" si="2">D15+D14</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G16" s="49"/>
-      <c r="H16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K16" s="49"/>
+        <v>40</v>
+      </c>
+      <c r="D16" s="39">
+        <f t="shared" ref="D16:J16" si="5">D15+D14</f>
+        <v>406.35</v>
+      </c>
+      <c r="E16" s="39">
+        <f t="shared" si="5"/>
+        <v>443.1</v>
+      </c>
+      <c r="F16" s="39">
+        <f t="shared" si="5"/>
+        <v>427.35</v>
+      </c>
+      <c r="G16" s="39"/>
+      <c r="H16" s="39">
+        <f t="shared" si="5"/>
+        <v>479.85</v>
+      </c>
+      <c r="I16" s="39">
+        <f t="shared" si="5"/>
+        <v>485.1</v>
+      </c>
+      <c r="J16" s="39">
+        <f t="shared" si="5"/>
+        <v>479.85</v>
+      </c>
+      <c r="K16" s="37"/>
+      <c r="L16" s="43" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" s="13"/>
-      <c r="B17" s="52" t="s">
+      <c r="B17" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="49">
+      <c r="C17" s="37">
         <f>C14/40</f>
-        <v>0</v>
-      </c>
-      <c r="D17" s="49">
-        <f t="shared" ref="D17:K17" si="3">D14/40</f>
-        <v>0</v>
-      </c>
-      <c r="E17" s="49">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F17" s="49">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G17" s="49"/>
-      <c r="H17" s="49">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I17" s="49">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J17" s="49">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K17" s="49"/>
-      <c r="L17" s="48">
+        <v>1</v>
+      </c>
+      <c r="D17" s="37">
+        <f t="shared" ref="D17:J17" si="6">D14/40</f>
+        <v>9.6750000000000007</v>
+      </c>
+      <c r="E17" s="37">
+        <f t="shared" si="6"/>
+        <v>10.55</v>
+      </c>
+      <c r="F17" s="37">
+        <f t="shared" si="6"/>
+        <v>10.175000000000001</v>
+      </c>
+      <c r="G17" s="37"/>
+      <c r="H17" s="37">
+        <f t="shared" si="6"/>
+        <v>11.425000000000001</v>
+      </c>
+      <c r="I17" s="37">
+        <f t="shared" si="6"/>
+        <v>11.55</v>
+      </c>
+      <c r="J17" s="37">
+        <f t="shared" si="6"/>
+        <v>11.425000000000001</v>
+      </c>
+      <c r="K17" s="37"/>
+      <c r="L17" s="36">
         <f>SUM(C17:J17)</f>
-        <v>0</v>
+        <v>65.8</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="C18" s="54"/>
+      <c r="C18" s="32"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
@@ -3756,57 +4056,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="36"/>
+      <c r="B2" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="49"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="37"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="39"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="52"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
-      <c r="K4" s="39"/>
+      <c r="B4" s="50"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="52"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="40"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
-      <c r="J5" s="41"/>
-      <c r="K5" s="42"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
+      <c r="K5" s="55"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -3814,18 +4114,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="43" t="s">
+      <c r="D6" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="44" t="s">
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
-      <c r="K6" s="45"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="57"/>
+      <c r="K6" s="58"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -3834,7 +4134,7 @@
       <c r="B7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="50" t="s">
+      <c r="C7" s="38" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="12" t="s">
@@ -3985,7 +4285,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L14" s="48">
+      <c r="L14" s="36">
         <f>C14+D14+E14+F14+H14+I14+J14</f>
         <v>0</v>
       </c>
@@ -4001,7 +4301,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:K15" si="1">E14/20</f>
+        <f t="shared" ref="E15:J15" si="1">E14/20</f>
         <v>0</v>
       </c>
       <c r="F15" s="13">
@@ -4028,79 +4328,79 @@
       <c r="B16" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="49">
+      <c r="C16" s="37">
         <f>C15+C14</f>
         <v>0</v>
       </c>
-      <c r="D16" s="49">
-        <f t="shared" ref="D16:K16" si="2">D15+D14</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G16" s="49"/>
-      <c r="H16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K16" s="49"/>
+      <c r="D16" s="37">
+        <f t="shared" ref="D16:J16" si="2">D15+D14</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="37"/>
+      <c r="H16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="37"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" s="13"/>
-      <c r="B17" s="52" t="s">
+      <c r="B17" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="49">
+      <c r="C17" s="37">
         <f>C14/40</f>
         <v>0</v>
       </c>
-      <c r="D17" s="49">
-        <f t="shared" ref="D17:K17" si="3">D14/40</f>
-        <v>0</v>
-      </c>
-      <c r="E17" s="49">
+      <c r="D17" s="37">
+        <f t="shared" ref="D17:J17" si="3">D14/40</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F17" s="49">
+      <c r="F17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G17" s="49"/>
-      <c r="H17" s="49">
+      <c r="G17" s="37"/>
+      <c r="H17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I17" s="49">
+      <c r="I17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J17" s="49">
+      <c r="J17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K17" s="49"/>
-      <c r="L17" s="48">
+      <c r="K17" s="37"/>
+      <c r="L17" s="36">
         <f>SUM(C17:J17)</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="C18" s="54"/>
+      <c r="C18" s="32"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
@@ -4157,57 +4457,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="36"/>
+      <c r="B2" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="49"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="37"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="39"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="52"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
-      <c r="K4" s="39"/>
+      <c r="B4" s="50"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="52"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="40"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
-      <c r="J5" s="41"/>
-      <c r="K5" s="42"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
+      <c r="K5" s="55"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -4215,18 +4515,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="43" t="s">
+      <c r="D6" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="44" t="s">
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
-      <c r="K6" s="45"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="57"/>
+      <c r="K6" s="58"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -4235,7 +4535,7 @@
       <c r="B7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="50" t="s">
+      <c r="C7" s="38" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="12" t="s">
@@ -4386,7 +4686,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L14" s="48">
+      <c r="L14" s="36">
         <f>C14+D14+E14+F14+H14+I14+J14</f>
         <v>0</v>
       </c>
@@ -4402,7 +4702,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:K15" si="1">E14/20</f>
+        <f t="shared" ref="E15:J15" si="1">E14/20</f>
         <v>0</v>
       </c>
       <c r="F15" s="13">
@@ -4429,79 +4729,79 @@
       <c r="B16" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="49">
+      <c r="C16" s="37">
         <f>C15+C14</f>
         <v>0</v>
       </c>
-      <c r="D16" s="49">
-        <f t="shared" ref="D16:K16" si="2">D15+D14</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G16" s="49"/>
-      <c r="H16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K16" s="49"/>
+      <c r="D16" s="37">
+        <f t="shared" ref="D16:J16" si="2">D15+D14</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="37"/>
+      <c r="H16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="37"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" s="13"/>
-      <c r="B17" s="52" t="s">
+      <c r="B17" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="49">
+      <c r="C17" s="37">
         <f>C14/40</f>
         <v>0</v>
       </c>
-      <c r="D17" s="49">
-        <f t="shared" ref="D17:K17" si="3">D14/40</f>
-        <v>0</v>
-      </c>
-      <c r="E17" s="49">
+      <c r="D17" s="37">
+        <f t="shared" ref="D17:J17" si="3">D14/40</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F17" s="49">
+      <c r="F17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G17" s="49"/>
-      <c r="H17" s="49">
+      <c r="G17" s="37"/>
+      <c r="H17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I17" s="49">
+      <c r="I17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J17" s="49">
+      <c r="J17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K17" s="49"/>
-      <c r="L17" s="48">
+      <c r="K17" s="37"/>
+      <c r="L17" s="36">
         <f>SUM(C17:J17)</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="C18" s="54"/>
+      <c r="C18" s="32"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
@@ -4558,57 +4858,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="36"/>
+      <c r="B2" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="49"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="37"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="39"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="52"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
-      <c r="K4" s="39"/>
+      <c r="B4" s="50"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="52"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="40"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
-      <c r="J5" s="41"/>
-      <c r="K5" s="42"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
+      <c r="K5" s="55"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -4616,18 +4916,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="43" t="s">
+      <c r="D6" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="44" t="s">
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
-      <c r="K6" s="45"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="57"/>
+      <c r="K6" s="58"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -4636,7 +4936,7 @@
       <c r="B7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="50" t="s">
+      <c r="C7" s="38" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="12" t="s">
@@ -4787,7 +5087,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L14" s="48">
+      <c r="L14" s="36">
         <f>C14+D14+E14+F14+H14+I14+J14</f>
         <v>0</v>
       </c>
@@ -4803,7 +5103,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:K15" si="1">E14/20</f>
+        <f t="shared" ref="E15:J15" si="1">E14/20</f>
         <v>0</v>
       </c>
       <c r="F15" s="13">
@@ -4830,79 +5130,79 @@
       <c r="B16" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="49">
+      <c r="C16" s="37">
         <f>C15+C14</f>
         <v>0</v>
       </c>
-      <c r="D16" s="49">
-        <f t="shared" ref="D16:K16" si="2">D15+D14</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G16" s="49"/>
-      <c r="H16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K16" s="49"/>
+      <c r="D16" s="37">
+        <f t="shared" ref="D16:J16" si="2">D15+D14</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="37"/>
+      <c r="H16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="37"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" s="13"/>
-      <c r="B17" s="52" t="s">
+      <c r="B17" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="49">
+      <c r="C17" s="37">
         <f>C14/40</f>
         <v>0</v>
       </c>
-      <c r="D17" s="49">
-        <f t="shared" ref="D17:K17" si="3">D14/40</f>
-        <v>0</v>
-      </c>
-      <c r="E17" s="49">
+      <c r="D17" s="37">
+        <f t="shared" ref="D17:J17" si="3">D14/40</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F17" s="49">
+      <c r="F17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G17" s="49"/>
-      <c r="H17" s="49">
+      <c r="G17" s="37"/>
+      <c r="H17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I17" s="49">
+      <c r="I17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J17" s="49">
+      <c r="J17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K17" s="49"/>
-      <c r="L17" s="48">
+      <c r="K17" s="37"/>
+      <c r="L17" s="36">
         <f>SUM(C17:J17)</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="C18" s="54"/>
+      <c r="C18" s="32"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
@@ -4959,57 +5259,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="36"/>
+      <c r="B2" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="49"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="37"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="39"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="52"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
-      <c r="K4" s="39"/>
+      <c r="B4" s="50"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="52"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="40"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
-      <c r="J5" s="41"/>
-      <c r="K5" s="42"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
+      <c r="K5" s="55"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -5017,18 +5317,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="43" t="s">
+      <c r="D6" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="44" t="s">
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
-      <c r="K6" s="45"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="57"/>
+      <c r="K6" s="58"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -5037,7 +5337,7 @@
       <c r="B7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="50" t="s">
+      <c r="C7" s="38" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="12" t="s">
@@ -5188,7 +5488,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L14" s="48">
+      <c r="L14" s="36">
         <f>C14+D14+E14+F14+H14+I14+J14</f>
         <v>0</v>
       </c>
@@ -5204,7 +5504,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:K15" si="1">E14/20</f>
+        <f t="shared" ref="E15:J15" si="1">E14/20</f>
         <v>0</v>
       </c>
       <c r="F15" s="13">
@@ -5231,79 +5531,79 @@
       <c r="B16" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="49">
+      <c r="C16" s="37">
         <f>C15+C14</f>
         <v>0</v>
       </c>
-      <c r="D16" s="49">
-        <f t="shared" ref="D16:K16" si="2">D15+D14</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G16" s="49"/>
-      <c r="H16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K16" s="49"/>
+      <c r="D16" s="37">
+        <f t="shared" ref="D16:J16" si="2">D15+D14</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="37"/>
+      <c r="H16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="37"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" s="13"/>
-      <c r="B17" s="52" t="s">
+      <c r="B17" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="49">
+      <c r="C17" s="37">
         <f>C14/40</f>
         <v>0</v>
       </c>
-      <c r="D17" s="49">
-        <f t="shared" ref="D17:K17" si="3">D14/40</f>
-        <v>0</v>
-      </c>
-      <c r="E17" s="49">
+      <c r="D17" s="37">
+        <f t="shared" ref="D17:J17" si="3">D14/40</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F17" s="49">
+      <c r="F17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G17" s="49"/>
-      <c r="H17" s="49">
+      <c r="G17" s="37"/>
+      <c r="H17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I17" s="49">
+      <c r="I17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J17" s="49">
+      <c r="J17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K17" s="49"/>
-      <c r="L17" s="48">
+      <c r="K17" s="37"/>
+      <c r="L17" s="36">
         <f>SUM(C17:J17)</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="C18" s="54"/>
+      <c r="C18" s="32"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
@@ -5360,57 +5660,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="36"/>
+      <c r="B2" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="49"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="37"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="39"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="52"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
-      <c r="K4" s="39"/>
+      <c r="B4" s="50"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="52"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="40"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
-      <c r="J5" s="41"/>
-      <c r="K5" s="42"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
+      <c r="K5" s="55"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -5418,18 +5718,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="43" t="s">
+      <c r="D6" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="44" t="s">
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
-      <c r="K6" s="45"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="57"/>
+      <c r="K6" s="58"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -5438,7 +5738,7 @@
       <c r="B7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="50" t="s">
+      <c r="C7" s="38" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="12" t="s">
@@ -5589,7 +5889,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L14" s="48">
+      <c r="L14" s="36">
         <f>C14+D14+E14+F14+H14+I14+J14</f>
         <v>0</v>
       </c>
@@ -5605,7 +5905,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:K15" si="1">E14/20</f>
+        <f t="shared" ref="E15:J15" si="1">E14/20</f>
         <v>0</v>
       </c>
       <c r="F15" s="13">
@@ -5632,79 +5932,79 @@
       <c r="B16" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="49">
+      <c r="C16" s="37">
         <f>C15+C14</f>
         <v>0</v>
       </c>
-      <c r="D16" s="49">
-        <f t="shared" ref="D16:K16" si="2">D15+D14</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G16" s="49"/>
-      <c r="H16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K16" s="49"/>
+      <c r="D16" s="37">
+        <f t="shared" ref="D16:J16" si="2">D15+D14</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="37"/>
+      <c r="H16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="37"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" s="13"/>
-      <c r="B17" s="52" t="s">
+      <c r="B17" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="49">
+      <c r="C17" s="37">
         <f>C14/40</f>
         <v>0</v>
       </c>
-      <c r="D17" s="49">
-        <f t="shared" ref="D17:K17" si="3">D14/40</f>
-        <v>0</v>
-      </c>
-      <c r="E17" s="49">
+      <c r="D17" s="37">
+        <f t="shared" ref="D17:J17" si="3">D14/40</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F17" s="49">
+      <c r="F17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G17" s="49"/>
-      <c r="H17" s="49">
+      <c r="G17" s="37"/>
+      <c r="H17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I17" s="49">
+      <c r="I17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J17" s="49">
+      <c r="J17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K17" s="49"/>
-      <c r="L17" s="48">
+      <c r="K17" s="37"/>
+      <c r="L17" s="36">
         <f>SUM(C17:J17)</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="C18" s="54"/>
+      <c r="C18" s="32"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
@@ -5761,57 +6061,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="36"/>
+      <c r="B2" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="49"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="37"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="39"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="52"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
-      <c r="K4" s="39"/>
+      <c r="B4" s="50"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="52"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="40"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
-      <c r="J5" s="41"/>
-      <c r="K5" s="42"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
+      <c r="K5" s="55"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -5819,18 +6119,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="43" t="s">
+      <c r="D6" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="44" t="s">
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
-      <c r="K6" s="45"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="57"/>
+      <c r="K6" s="58"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -5839,7 +6139,7 @@
       <c r="B7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="50" t="s">
+      <c r="C7" s="38" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="12" t="s">
@@ -6038,7 +6338,7 @@
         <f t="shared" si="0"/>
         <v>6.25</v>
       </c>
-      <c r="L14" s="48">
+      <c r="L14" s="36">
         <f>C14+D14+E14+F14+H14+I14+J14</f>
         <v>387</v>
       </c>
@@ -6054,7 +6354,7 @@
         <v>1.6</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:K15" si="1">E14/20</f>
+        <f t="shared" ref="E15:J15" si="1">E14/20</f>
         <v>1</v>
       </c>
       <c r="F15" s="13">
@@ -6081,79 +6381,79 @@
       <c r="B16" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="49">
+      <c r="C16" s="37">
         <f>C15+C14</f>
         <v>190</v>
       </c>
-      <c r="D16" s="49">
-        <f t="shared" ref="D16:K16" si="2">D15+D14</f>
+      <c r="D16" s="37">
+        <f t="shared" ref="D16:J16" si="2">D15+D14</f>
         <v>33.6</v>
       </c>
-      <c r="E16" s="49">
+      <c r="E16" s="37">
         <f t="shared" si="2"/>
         <v>21</v>
       </c>
-      <c r="F16" s="49">
+      <c r="F16" s="37">
         <f t="shared" si="2"/>
         <v>21</v>
       </c>
-      <c r="G16" s="49"/>
-      <c r="H16" s="49">
+      <c r="G16" s="37"/>
+      <c r="H16" s="37">
         <f t="shared" si="2"/>
         <v>52.5</v>
       </c>
-      <c r="I16" s="49">
+      <c r="I16" s="37">
         <f t="shared" si="2"/>
         <v>35.700000000000003</v>
       </c>
-      <c r="J16" s="49">
+      <c r="J16" s="37">
         <f t="shared" si="2"/>
         <v>43.05</v>
       </c>
-      <c r="K16" s="49"/>
+      <c r="K16" s="37"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" s="13"/>
-      <c r="B17" s="52" t="s">
+      <c r="B17" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="49">
+      <c r="C17" s="37">
         <f>C14/40</f>
         <v>4.75</v>
       </c>
-      <c r="D17" s="49">
-        <f t="shared" ref="D17:K17" si="3">D14/40</f>
+      <c r="D17" s="37">
+        <f t="shared" ref="D17:J17" si="3">D14/40</f>
         <v>0.8</v>
       </c>
-      <c r="E17" s="49">
+      <c r="E17" s="37">
         <f t="shared" si="3"/>
         <v>0.5</v>
       </c>
-      <c r="F17" s="49">
+      <c r="F17" s="37">
         <f t="shared" si="3"/>
         <v>0.5</v>
       </c>
-      <c r="G17" s="49"/>
-      <c r="H17" s="49">
+      <c r="G17" s="37"/>
+      <c r="H17" s="37">
         <f t="shared" si="3"/>
         <v>1.25</v>
       </c>
-      <c r="I17" s="49">
+      <c r="I17" s="37">
         <f t="shared" si="3"/>
         <v>0.85</v>
       </c>
-      <c r="J17" s="49">
+      <c r="J17" s="37">
         <f t="shared" si="3"/>
         <v>1.0249999999999999</v>
       </c>
-      <c r="K17" s="49"/>
-      <c r="L17" s="48">
+      <c r="K17" s="37"/>
+      <c r="L17" s="36">
         <f>SUM(C17:J17)</f>
         <v>9.6750000000000007</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="C18" s="54"/>
+      <c r="C18" s="32"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
@@ -6210,57 +6510,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="36"/>
+      <c r="B2" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="49"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="37"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="39"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="52"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
-      <c r="K4" s="39"/>
+      <c r="B4" s="50"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="52"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="40"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
-      <c r="J5" s="41"/>
-      <c r="K5" s="42"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
+      <c r="K5" s="55"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -6268,18 +6568,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="43" t="s">
+      <c r="D6" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="44" t="s">
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
-      <c r="K6" s="45"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="57"/>
+      <c r="K6" s="58"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -6288,7 +6588,7 @@
       <c r="B7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="50" t="s">
+      <c r="C7" s="38" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="12" t="s">
@@ -6439,7 +6739,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L14" s="48">
+      <c r="L14" s="36">
         <f>C14+D14+E14+F14+H14+I14+J14</f>
         <v>0</v>
       </c>
@@ -6455,7 +6755,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:K15" si="1">E14/20</f>
+        <f t="shared" ref="E15:J15" si="1">E14/20</f>
         <v>0</v>
       </c>
       <c r="F15" s="13">
@@ -6482,79 +6782,79 @@
       <c r="B16" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="49">
+      <c r="C16" s="37">
         <f>C15+C14</f>
         <v>0</v>
       </c>
-      <c r="D16" s="49">
-        <f t="shared" ref="D16:K16" si="2">D15+D14</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G16" s="49"/>
-      <c r="H16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K16" s="49"/>
+      <c r="D16" s="37">
+        <f t="shared" ref="D16:J16" si="2">D15+D14</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="37"/>
+      <c r="H16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="37"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" s="13"/>
-      <c r="B17" s="52" t="s">
+      <c r="B17" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="49">
+      <c r="C17" s="37">
         <f>C14/40</f>
         <v>0</v>
       </c>
-      <c r="D17" s="49">
-        <f t="shared" ref="D17:K17" si="3">D14/40</f>
-        <v>0</v>
-      </c>
-      <c r="E17" s="49">
+      <c r="D17" s="37">
+        <f t="shared" ref="D17:J17" si="3">D14/40</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F17" s="49">
+      <c r="F17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G17" s="49"/>
-      <c r="H17" s="49">
+      <c r="G17" s="37"/>
+      <c r="H17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I17" s="49">
+      <c r="I17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J17" s="49">
+      <c r="J17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K17" s="49"/>
-      <c r="L17" s="48">
+      <c r="K17" s="37"/>
+      <c r="L17" s="36">
         <f>SUM(C17:J17)</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="C18" s="54"/>
+      <c r="C18" s="32"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
@@ -6611,57 +6911,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="36"/>
+      <c r="B2" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="49"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="37"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="39"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="52"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
-      <c r="K4" s="39"/>
+      <c r="B4" s="50"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="52"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="40"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
-      <c r="J5" s="41"/>
-      <c r="K5" s="42"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
+      <c r="K5" s="55"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -6669,18 +6969,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="43" t="s">
+      <c r="D6" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="44" t="s">
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
-      <c r="K6" s="45"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="57"/>
+      <c r="K6" s="58"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -6689,7 +6989,7 @@
       <c r="B7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="50" t="s">
+      <c r="C7" s="38" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="12" t="s">
@@ -6840,7 +7140,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L14" s="48">
+      <c r="L14" s="36">
         <f>C14+D14+E14+F14+H14+I14+J14</f>
         <v>0</v>
       </c>
@@ -6856,7 +7156,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:K15" si="1">E14/20</f>
+        <f t="shared" ref="E15:J15" si="1">E14/20</f>
         <v>0</v>
       </c>
       <c r="F15" s="13">
@@ -6883,79 +7183,79 @@
       <c r="B16" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="49">
+      <c r="C16" s="37">
         <f>C15+C14</f>
         <v>0</v>
       </c>
-      <c r="D16" s="49">
-        <f t="shared" ref="D16:K16" si="2">D15+D14</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G16" s="49"/>
-      <c r="H16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K16" s="49"/>
+      <c r="D16" s="37">
+        <f t="shared" ref="D16:J16" si="2">D15+D14</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="37"/>
+      <c r="H16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="37"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" s="13"/>
-      <c r="B17" s="52" t="s">
+      <c r="B17" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="49">
+      <c r="C17" s="37">
         <f>C14/40</f>
         <v>0</v>
       </c>
-      <c r="D17" s="49">
-        <f t="shared" ref="D17:K17" si="3">D14/40</f>
-        <v>0</v>
-      </c>
-      <c r="E17" s="49">
+      <c r="D17" s="37">
+        <f t="shared" ref="D17:J17" si="3">D14/40</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F17" s="49">
+      <c r="F17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G17" s="49"/>
-      <c r="H17" s="49">
+      <c r="G17" s="37"/>
+      <c r="H17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I17" s="49">
+      <c r="I17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J17" s="49">
+      <c r="J17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K17" s="49"/>
-      <c r="L17" s="48">
+      <c r="K17" s="37"/>
+      <c r="L17" s="36">
         <f>SUM(C17:J17)</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="C18" s="54"/>
+      <c r="C18" s="32"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
@@ -7012,57 +7312,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="36"/>
+      <c r="B2" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="49"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="37"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="39"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="52"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
-      <c r="K4" s="39"/>
+      <c r="B4" s="50"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="52"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="40"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
-      <c r="J5" s="41"/>
-      <c r="K5" s="42"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
+      <c r="K5" s="55"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -7070,18 +7370,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="43" t="s">
+      <c r="D6" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="44" t="s">
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
-      <c r="K6" s="45"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="57"/>
+      <c r="K6" s="58"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -7090,7 +7390,7 @@
       <c r="B7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="50" t="s">
+      <c r="C7" s="38" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="12" t="s">
@@ -7241,7 +7541,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L14" s="48">
+      <c r="L14" s="36">
         <f>C14+D14+E14+F14+H14+I14+J14</f>
         <v>0</v>
       </c>
@@ -7257,7 +7557,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:K15" si="1">E14/20</f>
+        <f t="shared" ref="E15:J15" si="1">E14/20</f>
         <v>0</v>
       </c>
       <c r="F15" s="13">
@@ -7284,79 +7584,79 @@
       <c r="B16" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="49">
+      <c r="C16" s="37">
         <f>C15+C14</f>
         <v>0</v>
       </c>
-      <c r="D16" s="49">
-        <f t="shared" ref="D16:K16" si="2">D15+D14</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G16" s="49"/>
-      <c r="H16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K16" s="49"/>
+      <c r="D16" s="37">
+        <f t="shared" ref="D16:J16" si="2">D15+D14</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="37"/>
+      <c r="H16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="37"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" s="13"/>
-      <c r="B17" s="52" t="s">
+      <c r="B17" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="49">
+      <c r="C17" s="37">
         <f>C14/40</f>
         <v>0</v>
       </c>
-      <c r="D17" s="49">
-        <f t="shared" ref="D17:K17" si="3">D14/40</f>
-        <v>0</v>
-      </c>
-      <c r="E17" s="49">
+      <c r="D17" s="37">
+        <f t="shared" ref="D17:J17" si="3">D14/40</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F17" s="49">
+      <c r="F17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G17" s="49"/>
-      <c r="H17" s="49">
+      <c r="G17" s="37"/>
+      <c r="H17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I17" s="49">
+      <c r="I17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J17" s="49">
+      <c r="J17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K17" s="49"/>
-      <c r="L17" s="48">
+      <c r="K17" s="37"/>
+      <c r="L17" s="36">
         <f>SUM(C17:J17)</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="C18" s="54"/>
+      <c r="C18" s="32"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
@@ -7413,57 +7713,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="36"/>
+      <c r="B2" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="49"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="37"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="39"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="52"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
-      <c r="K4" s="39"/>
+      <c r="B4" s="50"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="52"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="40"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
-      <c r="J5" s="41"/>
-      <c r="K5" s="42"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
+      <c r="K5" s="55"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -7471,18 +7771,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="43" t="s">
+      <c r="D6" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="44" t="s">
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
-      <c r="K6" s="45"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="57"/>
+      <c r="K6" s="58"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -7491,7 +7791,7 @@
       <c r="B7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="50" t="s">
+      <c r="C7" s="38" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="12" t="s">
@@ -7642,7 +7942,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L14" s="48">
+      <c r="L14" s="36">
         <f>C14+D14+E14+F14+H14+I14+J14</f>
         <v>0</v>
       </c>
@@ -7658,7 +7958,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:K15" si="1">E14/20</f>
+        <f t="shared" ref="E15:J15" si="1">E14/20</f>
         <v>0</v>
       </c>
       <c r="F15" s="13">
@@ -7685,79 +7985,79 @@
       <c r="B16" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="49">
+      <c r="C16" s="37">
         <f>C15+C14</f>
         <v>0</v>
       </c>
-      <c r="D16" s="49">
-        <f t="shared" ref="D16:K16" si="2">D15+D14</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G16" s="49"/>
-      <c r="H16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K16" s="49"/>
+      <c r="D16" s="37">
+        <f t="shared" ref="D16:J16" si="2">D15+D14</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="37"/>
+      <c r="H16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="37"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" s="13"/>
-      <c r="B17" s="52" t="s">
+      <c r="B17" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="49">
+      <c r="C17" s="37">
         <f>C14/40</f>
         <v>0</v>
       </c>
-      <c r="D17" s="49">
-        <f t="shared" ref="D17:K17" si="3">D14/40</f>
-        <v>0</v>
-      </c>
-      <c r="E17" s="49">
+      <c r="D17" s="37">
+        <f t="shared" ref="D17:J17" si="3">D14/40</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F17" s="49">
+      <c r="F17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G17" s="49"/>
-      <c r="H17" s="49">
+      <c r="G17" s="37"/>
+      <c r="H17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I17" s="49">
+      <c r="I17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J17" s="49">
+      <c r="J17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K17" s="49"/>
-      <c r="L17" s="48">
+      <c r="K17" s="37"/>
+      <c r="L17" s="36">
         <f>SUM(C17:J17)</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="C18" s="54"/>
+      <c r="C18" s="32"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
@@ -7814,57 +8114,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="36"/>
+      <c r="B2" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="49"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="37"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="39"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="52"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
-      <c r="K4" s="39"/>
+      <c r="B4" s="50"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="52"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="40"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
-      <c r="J5" s="41"/>
-      <c r="K5" s="42"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
+      <c r="K5" s="55"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -7872,18 +8172,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="43" t="s">
+      <c r="D6" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="44" t="s">
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
-      <c r="K6" s="45"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="57"/>
+      <c r="K6" s="58"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -7892,7 +8192,7 @@
       <c r="B7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="50" t="s">
+      <c r="C7" s="38" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="12" t="s">
@@ -8043,7 +8343,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L14" s="48">
+      <c r="L14" s="36">
         <f>C14+D14+E14+F14+H14+I14+J14</f>
         <v>0</v>
       </c>
@@ -8059,7 +8359,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:K15" si="1">E14/20</f>
+        <f t="shared" ref="E15:J15" si="1">E14/20</f>
         <v>0</v>
       </c>
       <c r="F15" s="13">
@@ -8086,79 +8386,79 @@
       <c r="B16" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="49">
+      <c r="C16" s="37">
         <f>C15+C14</f>
         <v>0</v>
       </c>
-      <c r="D16" s="49">
-        <f t="shared" ref="D16:K16" si="2">D15+D14</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G16" s="49"/>
-      <c r="H16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K16" s="49"/>
+      <c r="D16" s="37">
+        <f t="shared" ref="D16:J16" si="2">D15+D14</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="37"/>
+      <c r="H16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="37"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" s="13"/>
-      <c r="B17" s="52" t="s">
+      <c r="B17" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="49">
+      <c r="C17" s="37">
         <f>C14/40</f>
         <v>0</v>
       </c>
-      <c r="D17" s="49">
-        <f t="shared" ref="D17:K17" si="3">D14/40</f>
-        <v>0</v>
-      </c>
-      <c r="E17" s="49">
+      <c r="D17" s="37">
+        <f t="shared" ref="D17:J17" si="3">D14/40</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F17" s="49">
+      <c r="F17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G17" s="49"/>
-      <c r="H17" s="49">
+      <c r="G17" s="37"/>
+      <c r="H17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I17" s="49">
+      <c r="I17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J17" s="49">
+      <c r="J17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K17" s="49"/>
-      <c r="L17" s="48">
+      <c r="K17" s="37"/>
+      <c r="L17" s="36">
         <f>SUM(C17:J17)</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="C18" s="54"/>
+      <c r="C18" s="32"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
@@ -8215,57 +8515,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="36"/>
+      <c r="B2" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="49"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="37"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="39"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="52"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
-      <c r="K4" s="39"/>
+      <c r="B4" s="50"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="52"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="40"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
-      <c r="J5" s="41"/>
-      <c r="K5" s="42"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
+      <c r="K5" s="55"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -8273,18 +8573,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="43" t="s">
+      <c r="D6" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="44" t="s">
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
-      <c r="K6" s="45"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="57"/>
+      <c r="K6" s="58"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -8293,7 +8593,7 @@
       <c r="B7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="50" t="s">
+      <c r="C7" s="38" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="12" t="s">
@@ -8444,7 +8744,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L14" s="48">
+      <c r="L14" s="36">
         <f>C14+D14+E14+F14+H14+I14+J14</f>
         <v>0</v>
       </c>
@@ -8460,7 +8760,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:K15" si="1">E14/20</f>
+        <f t="shared" ref="E15:J15" si="1">E14/20</f>
         <v>0</v>
       </c>
       <c r="F15" s="13">
@@ -8487,79 +8787,79 @@
       <c r="B16" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="49">
+      <c r="C16" s="37">
         <f>C15+C14</f>
         <v>0</v>
       </c>
-      <c r="D16" s="49">
-        <f t="shared" ref="D16:K16" si="2">D15+D14</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G16" s="49"/>
-      <c r="H16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K16" s="49"/>
+      <c r="D16" s="37">
+        <f t="shared" ref="D16:J16" si="2">D15+D14</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="37"/>
+      <c r="H16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="37"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" s="13"/>
-      <c r="B17" s="52" t="s">
+      <c r="B17" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="49">
+      <c r="C17" s="37">
         <f>C14/40</f>
         <v>0</v>
       </c>
-      <c r="D17" s="49">
-        <f t="shared" ref="D17:K17" si="3">D14/40</f>
-        <v>0</v>
-      </c>
-      <c r="E17" s="49">
+      <c r="D17" s="37">
+        <f t="shared" ref="D17:J17" si="3">D14/40</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F17" s="49">
+      <c r="F17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G17" s="49"/>
-      <c r="H17" s="49">
+      <c r="G17" s="37"/>
+      <c r="H17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I17" s="49">
+      <c r="I17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J17" s="49">
+      <c r="J17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K17" s="49"/>
-      <c r="L17" s="48">
+      <c r="K17" s="37"/>
+      <c r="L17" s="36">
         <f>SUM(C17:J17)</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="C18" s="54"/>
+      <c r="C18" s="32"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
@@ -8616,57 +8916,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="36"/>
+      <c r="B2" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="49"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="37"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="39"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="52"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
-      <c r="K4" s="39"/>
+      <c r="B4" s="50"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="52"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="40"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
-      <c r="J5" s="41"/>
-      <c r="K5" s="42"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
+      <c r="K5" s="55"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -8674,18 +8974,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="43" t="s">
+      <c r="D6" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="44" t="s">
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
-      <c r="K6" s="45"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="57"/>
+      <c r="K6" s="58"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -8694,7 +8994,7 @@
       <c r="B7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="50" t="s">
+      <c r="C7" s="38" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="12" t="s">
@@ -8845,7 +9145,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L14" s="48">
+      <c r="L14" s="36">
         <f>C14+D14+E14+F14+H14+I14+J14</f>
         <v>0</v>
       </c>
@@ -8861,7 +9161,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:K15" si="1">E14/20</f>
+        <f t="shared" ref="E15:J15" si="1">E14/20</f>
         <v>0</v>
       </c>
       <c r="F15" s="13">
@@ -8888,79 +9188,79 @@
       <c r="B16" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="49">
+      <c r="C16" s="37">
         <f>C15+C14</f>
         <v>0</v>
       </c>
-      <c r="D16" s="49">
-        <f t="shared" ref="D16:K16" si="2">D15+D14</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G16" s="49"/>
-      <c r="H16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K16" s="49"/>
+      <c r="D16" s="37">
+        <f t="shared" ref="D16:J16" si="2">D15+D14</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="37"/>
+      <c r="H16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="37"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" s="13"/>
-      <c r="B17" s="52" t="s">
+      <c r="B17" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="49">
+      <c r="C17" s="37">
         <f>C14/40</f>
         <v>0</v>
       </c>
-      <c r="D17" s="49">
-        <f t="shared" ref="D17:K17" si="3">D14/40</f>
-        <v>0</v>
-      </c>
-      <c r="E17" s="49">
+      <c r="D17" s="37">
+        <f t="shared" ref="D17:J17" si="3">D14/40</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F17" s="49">
+      <c r="F17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G17" s="49"/>
-      <c r="H17" s="49">
+      <c r="G17" s="37"/>
+      <c r="H17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I17" s="49">
+      <c r="I17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J17" s="49">
+      <c r="J17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K17" s="49"/>
-      <c r="L17" s="48">
+      <c r="K17" s="37"/>
+      <c r="L17" s="36">
         <f>SUM(C17:J17)</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="C18" s="54"/>
+      <c r="C18" s="32"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
@@ -9017,57 +9317,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="36"/>
+      <c r="B2" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="49"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="37"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="39"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="52"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
-      <c r="K4" s="39"/>
+      <c r="B4" s="50"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="52"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="40"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
-      <c r="J5" s="41"/>
-      <c r="K5" s="42"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
+      <c r="K5" s="55"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -9075,18 +9375,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="43" t="s">
+      <c r="D6" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="44" t="s">
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
-      <c r="K6" s="45"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="57"/>
+      <c r="K6" s="58"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -9095,7 +9395,7 @@
       <c r="B7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="50" t="s">
+      <c r="C7" s="38" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="12" t="s">
@@ -9246,7 +9546,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L14" s="48">
+      <c r="L14" s="36">
         <f>C14+D14+E14+F14+H14+I14+J14</f>
         <v>0</v>
       </c>
@@ -9262,7 +9562,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:K15" si="1">E14/20</f>
+        <f t="shared" ref="E15:J15" si="1">E14/20</f>
         <v>0</v>
       </c>
       <c r="F15" s="13">
@@ -9289,79 +9589,79 @@
       <c r="B16" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="49">
+      <c r="C16" s="37">
         <f>C15+C14</f>
         <v>0</v>
       </c>
-      <c r="D16" s="49">
-        <f t="shared" ref="D16:K16" si="2">D15+D14</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G16" s="49"/>
-      <c r="H16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K16" s="49"/>
+      <c r="D16" s="37">
+        <f t="shared" ref="D16:J16" si="2">D15+D14</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="37"/>
+      <c r="H16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="37"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" s="13"/>
-      <c r="B17" s="52" t="s">
+      <c r="B17" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="49">
+      <c r="C17" s="37">
         <f>C14/40</f>
         <v>0</v>
       </c>
-      <c r="D17" s="49">
-        <f t="shared" ref="D17:K17" si="3">D14/40</f>
-        <v>0</v>
-      </c>
-      <c r="E17" s="49">
+      <c r="D17" s="37">
+        <f t="shared" ref="D17:J17" si="3">D14/40</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F17" s="49">
+      <c r="F17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G17" s="49"/>
-      <c r="H17" s="49">
+      <c r="G17" s="37"/>
+      <c r="H17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I17" s="49">
+      <c r="I17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J17" s="49">
+      <c r="J17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K17" s="49"/>
-      <c r="L17" s="48">
+      <c r="K17" s="37"/>
+      <c r="L17" s="36">
         <f>SUM(C17:J17)</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="C18" s="54"/>
+      <c r="C18" s="32"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
@@ -9418,57 +9718,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="36"/>
+      <c r="B2" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="49"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="37"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="39"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="52"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
-      <c r="K4" s="39"/>
+      <c r="B4" s="50"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="52"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="40"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
-      <c r="J5" s="41"/>
-      <c r="K5" s="42"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
+      <c r="K5" s="55"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -9476,18 +9776,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="43" t="s">
+      <c r="D6" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="44" t="s">
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
-      <c r="K6" s="45"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="57"/>
+      <c r="K6" s="58"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -9496,7 +9796,7 @@
       <c r="B7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="50" t="s">
+      <c r="C7" s="38" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="12" t="s">
@@ -9647,7 +9947,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L14" s="48">
+      <c r="L14" s="36">
         <f>C14+D14+E14+F14+H14+I14+J14</f>
         <v>0</v>
       </c>
@@ -9663,7 +9963,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:K15" si="1">E14/20</f>
+        <f t="shared" ref="E15:J15" si="1">E14/20</f>
         <v>0</v>
       </c>
       <c r="F15" s="13">
@@ -9690,79 +9990,79 @@
       <c r="B16" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="49">
+      <c r="C16" s="37">
         <f>C15+C14</f>
         <v>0</v>
       </c>
-      <c r="D16" s="49">
-        <f t="shared" ref="D16:K16" si="2">D15+D14</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G16" s="49"/>
-      <c r="H16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K16" s="49"/>
+      <c r="D16" s="37">
+        <f t="shared" ref="D16:J16" si="2">D15+D14</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="37"/>
+      <c r="H16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="37"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" s="13"/>
-      <c r="B17" s="52" t="s">
+      <c r="B17" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="49">
+      <c r="C17" s="37">
         <f>C14/40</f>
         <v>0</v>
       </c>
-      <c r="D17" s="49">
-        <f t="shared" ref="D17:K17" si="3">D14/40</f>
-        <v>0</v>
-      </c>
-      <c r="E17" s="49">
+      <c r="D17" s="37">
+        <f t="shared" ref="D17:J17" si="3">D14/40</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F17" s="49">
+      <c r="F17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G17" s="49"/>
-      <c r="H17" s="49">
+      <c r="G17" s="37"/>
+      <c r="H17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I17" s="49">
+      <c r="I17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J17" s="49">
+      <c r="J17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K17" s="49"/>
-      <c r="L17" s="48">
+      <c r="K17" s="37"/>
+      <c r="L17" s="36">
         <f>SUM(C17:J17)</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="C18" s="54"/>
+      <c r="C18" s="32"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
@@ -9819,57 +10119,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="36"/>
+      <c r="B2" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="49"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="37"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="39"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="52"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
-      <c r="K4" s="39"/>
+      <c r="B4" s="50"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="52"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="40"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
-      <c r="J5" s="41"/>
-      <c r="K5" s="42"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
+      <c r="K5" s="55"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -9877,18 +10177,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="43" t="s">
+      <c r="D6" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="44" t="s">
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
-      <c r="K6" s="45"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="57"/>
+      <c r="K6" s="58"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -9897,7 +10197,7 @@
       <c r="B7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="50" t="s">
+      <c r="C7" s="38" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="12" t="s">
@@ -10048,7 +10348,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L14" s="48">
+      <c r="L14" s="36">
         <f>C14+D14+E14+F14+H14+I14+J14</f>
         <v>0</v>
       </c>
@@ -10064,7 +10364,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:K15" si="1">E14/20</f>
+        <f t="shared" ref="E15:J15" si="1">E14/20</f>
         <v>0</v>
       </c>
       <c r="F15" s="13">
@@ -10091,79 +10391,79 @@
       <c r="B16" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="49">
+      <c r="C16" s="37">
         <f>C15+C14</f>
         <v>0</v>
       </c>
-      <c r="D16" s="49">
-        <f t="shared" ref="D16:K16" si="2">D15+D14</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G16" s="49"/>
-      <c r="H16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K16" s="49"/>
+      <c r="D16" s="37">
+        <f t="shared" ref="D16:J16" si="2">D15+D14</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="37"/>
+      <c r="H16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="37"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" s="13"/>
-      <c r="B17" s="52" t="s">
+      <c r="B17" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="49">
+      <c r="C17" s="37">
         <f>C14/40</f>
         <v>0</v>
       </c>
-      <c r="D17" s="49">
-        <f t="shared" ref="D17:K17" si="3">D14/40</f>
-        <v>0</v>
-      </c>
-      <c r="E17" s="49">
+      <c r="D17" s="37">
+        <f t="shared" ref="D17:J17" si="3">D14/40</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F17" s="49">
+      <c r="F17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G17" s="49"/>
-      <c r="H17" s="49">
+      <c r="G17" s="37"/>
+      <c r="H17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I17" s="49">
+      <c r="I17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J17" s="49">
+      <c r="J17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K17" s="49"/>
-      <c r="L17" s="48">
+      <c r="K17" s="37"/>
+      <c r="L17" s="36">
         <f>SUM(C17:J17)</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="C18" s="54"/>
+      <c r="C18" s="32"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
@@ -10220,57 +10520,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="36"/>
+      <c r="B2" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="49"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="37"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="39"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="52"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
-      <c r="K4" s="39"/>
+      <c r="B4" s="50"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="52"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="40"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
-      <c r="J5" s="41"/>
-      <c r="K5" s="42"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
+      <c r="K5" s="55"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -10278,18 +10578,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="43" t="s">
+      <c r="D6" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="44" t="s">
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
-      <c r="K6" s="45"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="57"/>
+      <c r="K6" s="58"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -10298,7 +10598,7 @@
       <c r="B7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="50" t="s">
+      <c r="C7" s="38" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="12" t="s">
@@ -10511,7 +10811,7 @@
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
-      <c r="L14" s="48">
+      <c r="L14" s="36">
         <f>C14+D14+E14+F14+H14+I14+J14</f>
         <v>430</v>
       </c>
@@ -10527,7 +10827,7 @@
         <v>4.2</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:K15" si="3">E14/20</f>
+        <f t="shared" ref="E15:J15" si="3">E14/20</f>
         <v>4.2</v>
       </c>
       <c r="F15" s="13">
@@ -10554,79 +10854,79 @@
       <c r="B16" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="49">
+      <c r="C16" s="37">
         <f>C15+C14</f>
         <v>40</v>
       </c>
-      <c r="D16" s="49">
-        <f t="shared" ref="D16:K16" si="4">D15+D14</f>
+      <c r="D16" s="37">
+        <f t="shared" ref="D16:J16" si="4">D15+D14</f>
         <v>88.2</v>
       </c>
-      <c r="E16" s="49">
+      <c r="E16" s="37">
         <f t="shared" si="4"/>
         <v>88.2</v>
       </c>
-      <c r="F16" s="49">
+      <c r="F16" s="37">
         <f t="shared" si="4"/>
         <v>44.1</v>
       </c>
-      <c r="G16" s="49"/>
-      <c r="H16" s="49">
+      <c r="G16" s="37"/>
+      <c r="H16" s="37">
         <f t="shared" si="4"/>
         <v>59.85</v>
       </c>
-      <c r="I16" s="49">
+      <c r="I16" s="37">
         <f t="shared" si="4"/>
         <v>54.6</v>
       </c>
-      <c r="J16" s="49">
+      <c r="J16" s="37">
         <f t="shared" si="4"/>
         <v>74.55</v>
       </c>
-      <c r="K16" s="49"/>
+      <c r="K16" s="37"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" s="13"/>
-      <c r="B17" s="52" t="s">
+      <c r="B17" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="49">
+      <c r="C17" s="37">
         <f>C14/40</f>
         <v>1</v>
       </c>
-      <c r="D17" s="49">
-        <f t="shared" ref="D17:K17" si="5">D14/40</f>
+      <c r="D17" s="37">
+        <f t="shared" ref="D17:J17" si="5">D14/40</f>
         <v>2.1</v>
       </c>
-      <c r="E17" s="49">
+      <c r="E17" s="37">
         <f t="shared" si="5"/>
         <v>2.1</v>
       </c>
-      <c r="F17" s="49">
+      <c r="F17" s="37">
         <f t="shared" si="5"/>
         <v>1.05</v>
       </c>
-      <c r="G17" s="49"/>
-      <c r="H17" s="49">
+      <c r="G17" s="37"/>
+      <c r="H17" s="37">
         <f t="shared" si="5"/>
         <v>1.425</v>
       </c>
-      <c r="I17" s="49">
+      <c r="I17" s="37">
         <f t="shared" si="5"/>
         <v>1.3</v>
       </c>
-      <c r="J17" s="49">
+      <c r="J17" s="37">
         <f t="shared" si="5"/>
         <v>1.7749999999999999</v>
       </c>
-      <c r="K17" s="49"/>
-      <c r="L17" s="48">
+      <c r="K17" s="37"/>
+      <c r="L17" s="36">
         <f>SUM(C17:J17)</f>
         <v>10.75</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="C18" s="54"/>
+      <c r="C18" s="32"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
@@ -10683,57 +10983,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="36"/>
+      <c r="B2" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="49"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="37"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="39"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="52"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
-      <c r="K4" s="39"/>
+      <c r="B4" s="50"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="52"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="40"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
-      <c r="J5" s="41"/>
-      <c r="K5" s="42"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
+      <c r="K5" s="55"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -10741,18 +11041,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="43" t="s">
+      <c r="D6" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="44" t="s">
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
-      <c r="K6" s="45"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="57"/>
+      <c r="K6" s="58"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -10761,7 +11061,7 @@
       <c r="B7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="50" t="s">
+      <c r="C7" s="38" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="12" t="s">
@@ -10912,7 +11212,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L14" s="48">
+      <c r="L14" s="36">
         <f>C14+D14+E14+F14+H14+I14+J14</f>
         <v>0</v>
       </c>
@@ -10928,7 +11228,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:K15" si="1">E14/20</f>
+        <f t="shared" ref="E15:J15" si="1">E14/20</f>
         <v>0</v>
       </c>
       <c r="F15" s="13">
@@ -10955,79 +11255,79 @@
       <c r="B16" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="49">
+      <c r="C16" s="37">
         <f>C15+C14</f>
         <v>0</v>
       </c>
-      <c r="D16" s="49">
-        <f t="shared" ref="D16:K16" si="2">D15+D14</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G16" s="49"/>
-      <c r="H16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K16" s="49"/>
+      <c r="D16" s="37">
+        <f t="shared" ref="D16:J16" si="2">D15+D14</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="37"/>
+      <c r="H16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="37"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" s="13"/>
-      <c r="B17" s="52" t="s">
+      <c r="B17" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="49">
+      <c r="C17" s="37">
         <f>C14/40</f>
         <v>0</v>
       </c>
-      <c r="D17" s="49">
-        <f t="shared" ref="D17:K17" si="3">D14/40</f>
-        <v>0</v>
-      </c>
-      <c r="E17" s="49">
+      <c r="D17" s="37">
+        <f t="shared" ref="D17:J17" si="3">D14/40</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F17" s="49">
+      <c r="F17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G17" s="49"/>
-      <c r="H17" s="49">
+      <c r="G17" s="37"/>
+      <c r="H17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I17" s="49">
+      <c r="I17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J17" s="49">
+      <c r="J17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K17" s="49"/>
-      <c r="L17" s="48">
+      <c r="K17" s="37"/>
+      <c r="L17" s="36">
         <f>SUM(C17:J17)</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="C18" s="54"/>
+      <c r="C18" s="32"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
@@ -11084,57 +11384,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="36"/>
+      <c r="B2" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="49"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="37"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="39"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="52"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
-      <c r="K4" s="39"/>
+      <c r="B4" s="50"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="52"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="40"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
-      <c r="J5" s="41"/>
-      <c r="K5" s="42"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
+      <c r="K5" s="55"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -11142,18 +11442,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="43" t="s">
+      <c r="D6" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="44" t="s">
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
-      <c r="K6" s="45"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="57"/>
+      <c r="K6" s="58"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -11162,7 +11462,7 @@
       <c r="B7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="50" t="s">
+      <c r="C7" s="38" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="12" t="s">
@@ -11313,7 +11613,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L14" s="48">
+      <c r="L14" s="36">
         <f>C14+D14+E14+F14+H14+I14+J14</f>
         <v>0</v>
       </c>
@@ -11329,7 +11629,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:K15" si="1">E14/20</f>
+        <f t="shared" ref="E15:J15" si="1">E14/20</f>
         <v>0</v>
       </c>
       <c r="F15" s="13">
@@ -11356,79 +11656,79 @@
       <c r="B16" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="49">
+      <c r="C16" s="37">
         <f>C15+C14</f>
         <v>0</v>
       </c>
-      <c r="D16" s="49">
-        <f t="shared" ref="D16:K16" si="2">D15+D14</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G16" s="49"/>
-      <c r="H16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K16" s="49"/>
+      <c r="D16" s="37">
+        <f t="shared" ref="D16:J16" si="2">D15+D14</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="37"/>
+      <c r="H16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="37"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" s="13"/>
-      <c r="B17" s="52" t="s">
+      <c r="B17" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="49">
+      <c r="C17" s="37">
         <f>C14/40</f>
         <v>0</v>
       </c>
-      <c r="D17" s="49">
-        <f t="shared" ref="D17:K17" si="3">D14/40</f>
-        <v>0</v>
-      </c>
-      <c r="E17" s="49">
+      <c r="D17" s="37">
+        <f t="shared" ref="D17:J17" si="3">D14/40</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F17" s="49">
+      <c r="F17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G17" s="49"/>
-      <c r="H17" s="49">
+      <c r="G17" s="37"/>
+      <c r="H17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I17" s="49">
+      <c r="I17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J17" s="49">
+      <c r="J17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K17" s="49"/>
-      <c r="L17" s="48">
+      <c r="K17" s="37"/>
+      <c r="L17" s="36">
         <f>SUM(C17:J17)</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="C18" s="54"/>
+      <c r="C18" s="32"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
@@ -11486,57 +11786,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="36"/>
+      <c r="B2" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="49"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="37"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="39"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="52"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
-      <c r="K4" s="39"/>
+      <c r="B4" s="50"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="52"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="40"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
-      <c r="J5" s="41"/>
-      <c r="K5" s="42"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
+      <c r="K5" s="55"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -11544,18 +11844,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="43" t="s">
+      <c r="D6" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="44" t="s">
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
-      <c r="K6" s="45"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="57"/>
+      <c r="K6" s="58"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -11564,7 +11864,7 @@
       <c r="B7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="50" t="s">
+      <c r="C7" s="38" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="12" t="s">
@@ -11715,7 +12015,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L14" s="48">
+      <c r="L14" s="36">
         <f>C14+D14+E14+F14+H14+I14+J14</f>
         <v>0</v>
       </c>
@@ -11731,7 +12031,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:K15" si="1">E14/20</f>
+        <f t="shared" ref="E15:J15" si="1">E14/20</f>
         <v>0</v>
       </c>
       <c r="F15" s="13">
@@ -11758,79 +12058,79 @@
       <c r="B16" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="49">
+      <c r="C16" s="37">
         <f>C15+C14</f>
         <v>0</v>
       </c>
-      <c r="D16" s="49">
-        <f t="shared" ref="D16:K16" si="2">D15+D14</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G16" s="49"/>
-      <c r="H16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K16" s="49"/>
+      <c r="D16" s="37">
+        <f t="shared" ref="D16:J16" si="2">D15+D14</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="37"/>
+      <c r="H16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="37"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" s="13"/>
-      <c r="B17" s="52" t="s">
+      <c r="B17" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="49">
+      <c r="C17" s="37">
         <f>C14/40</f>
         <v>0</v>
       </c>
-      <c r="D17" s="49">
-        <f t="shared" ref="D17:K17" si="3">D14/40</f>
-        <v>0</v>
-      </c>
-      <c r="E17" s="49">
+      <c r="D17" s="37">
+        <f t="shared" ref="D17:J17" si="3">D14/40</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F17" s="49">
+      <c r="F17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G17" s="49"/>
-      <c r="H17" s="49">
+      <c r="G17" s="37"/>
+      <c r="H17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I17" s="49">
+      <c r="I17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J17" s="49">
+      <c r="J17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K17" s="49"/>
-      <c r="L17" s="48">
+      <c r="K17" s="37"/>
+      <c r="L17" s="36">
         <f>SUM(C17:J17)</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="C18" s="54"/>
+      <c r="C18" s="32"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
@@ -11887,57 +12187,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="36"/>
+      <c r="B2" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="49"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="37"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="39"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="52"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
-      <c r="K4" s="39"/>
+      <c r="B4" s="50"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="52"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="40"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
-      <c r="J5" s="41"/>
-      <c r="K5" s="42"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
+      <c r="K5" s="55"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -11945,18 +12245,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="43" t="s">
+      <c r="D6" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="44" t="s">
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
-      <c r="K6" s="45"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="57"/>
+      <c r="K6" s="58"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -11965,7 +12265,7 @@
       <c r="B7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="50" t="s">
+      <c r="C7" s="38" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="12" t="s">
@@ -12230,7 +12530,7 @@
         <f t="shared" si="2"/>
         <v>49.1</v>
       </c>
-      <c r="L14" s="48">
+      <c r="L14" s="36">
         <f>C14+D14+E14+F14+H14+I14+J14</f>
         <v>1425</v>
       </c>
@@ -12246,7 +12546,7 @@
         <v>2.4</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:K15" si="3">E14/20</f>
+        <f t="shared" ref="E15:J15" si="3">E14/20</f>
         <v>5.55</v>
       </c>
       <c r="F15" s="13">
@@ -12273,79 +12573,79 @@
       <c r="B16" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="49">
+      <c r="C16" s="37">
         <f>C15+C14</f>
         <v>200</v>
       </c>
-      <c r="D16" s="49">
-        <f t="shared" ref="D16:K16" si="4">D15+D14</f>
+      <c r="D16" s="37">
+        <f t="shared" ref="D16:J16" si="4">D15+D14</f>
         <v>50.4</v>
       </c>
-      <c r="E16" s="49">
+      <c r="E16" s="37">
         <f t="shared" si="4"/>
         <v>116.55</v>
       </c>
-      <c r="F16" s="49">
+      <c r="F16" s="37">
         <f t="shared" si="4"/>
         <v>88.2</v>
       </c>
-      <c r="G16" s="49"/>
-      <c r="H16" s="49">
+      <c r="G16" s="37"/>
+      <c r="H16" s="37">
         <f t="shared" si="4"/>
         <v>340.2</v>
       </c>
-      <c r="I16" s="49">
+      <c r="I16" s="37">
         <f t="shared" si="4"/>
         <v>302.39999999999998</v>
       </c>
-      <c r="J16" s="49">
+      <c r="J16" s="37">
         <f t="shared" si="4"/>
         <v>388.5</v>
       </c>
-      <c r="K16" s="49"/>
+      <c r="K16" s="37"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" s="13"/>
-      <c r="B17" s="52" t="s">
+      <c r="B17" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="49">
+      <c r="C17" s="37">
         <f>C14/40</f>
         <v>5</v>
       </c>
-      <c r="D17" s="49">
-        <f t="shared" ref="D17:K17" si="5">D14/40</f>
+      <c r="D17" s="37">
+        <f t="shared" ref="D17:J17" si="5">D14/40</f>
         <v>1.2</v>
       </c>
-      <c r="E17" s="49">
+      <c r="E17" s="37">
         <f t="shared" si="5"/>
         <v>2.7749999999999999</v>
       </c>
-      <c r="F17" s="49">
+      <c r="F17" s="37">
         <f t="shared" si="5"/>
         <v>2.1</v>
       </c>
-      <c r="G17" s="49"/>
-      <c r="H17" s="49">
+      <c r="G17" s="37"/>
+      <c r="H17" s="37">
         <f t="shared" si="5"/>
         <v>8.1</v>
       </c>
-      <c r="I17" s="49">
+      <c r="I17" s="37">
         <f t="shared" si="5"/>
         <v>7.2</v>
       </c>
-      <c r="J17" s="49">
+      <c r="J17" s="37">
         <f t="shared" si="5"/>
         <v>9.25</v>
       </c>
-      <c r="K17" s="49"/>
-      <c r="L17" s="48">
+      <c r="K17" s="37"/>
+      <c r="L17" s="36">
         <f>SUM(C17:J17)</f>
         <v>35.625</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="C18" s="54"/>
+      <c r="C18" s="32"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
@@ -12403,57 +12703,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="36"/>
+      <c r="B2" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="49"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="37"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="39"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="52"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
-      <c r="K4" s="39"/>
+      <c r="B4" s="50"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="52"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="40"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
-      <c r="J5" s="41"/>
-      <c r="K5" s="42"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
+      <c r="K5" s="55"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -12461,18 +12761,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="43" t="s">
+      <c r="D6" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="44" t="s">
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
-      <c r="K6" s="45"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="57"/>
+      <c r="K6" s="58"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -12481,7 +12781,7 @@
       <c r="B7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="50" t="s">
+      <c r="C7" s="38" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="12" t="s">
@@ -12718,7 +13018,7 @@
         <f t="shared" si="2"/>
         <v>46.1</v>
       </c>
-      <c r="L14" s="48">
+      <c r="L14" s="36">
         <f>C14+D14+E14+F14+H14+I14+J14</f>
         <v>2093</v>
       </c>
@@ -12734,7 +13034,7 @@
         <v>14.9</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:K15" si="3">E14/20</f>
+        <f t="shared" ref="E15:J15" si="3">E14/20</f>
         <v>10.5</v>
       </c>
       <c r="F15" s="13">
@@ -12761,79 +13061,79 @@
       <c r="B16" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="49">
+      <c r="C16" s="37">
         <f>C15+C14</f>
         <v>399</v>
       </c>
-      <c r="D16" s="49">
-        <f t="shared" ref="D16:K16" si="4">D15+D14</f>
+      <c r="D16" s="37">
+        <f t="shared" ref="D16:J16" si="4">D15+D14</f>
         <v>312.89999999999998</v>
       </c>
-      <c r="E16" s="49">
+      <c r="E16" s="37">
         <f t="shared" si="4"/>
         <v>220.5</v>
       </c>
-      <c r="F16" s="49">
+      <c r="F16" s="37">
         <f t="shared" si="4"/>
         <v>277.2</v>
       </c>
-      <c r="G16" s="49"/>
-      <c r="H16" s="49">
+      <c r="G16" s="37"/>
+      <c r="H16" s="37">
         <f t="shared" si="4"/>
         <v>247.8</v>
       </c>
-      <c r="I16" s="49">
+      <c r="I16" s="37">
         <f t="shared" si="4"/>
         <v>346.5</v>
       </c>
-      <c r="J16" s="49">
+      <c r="J16" s="37">
         <f t="shared" si="4"/>
         <v>373.8</v>
       </c>
-      <c r="K16" s="49"/>
+      <c r="K16" s="37"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" s="13"/>
-      <c r="B17" s="52" t="s">
+      <c r="B17" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="49">
+      <c r="C17" s="37">
         <f>C14/40</f>
         <v>9.9749999999999996</v>
       </c>
-      <c r="D17" s="49">
-        <f t="shared" ref="D17:K17" si="5">D14/40</f>
+      <c r="D17" s="37">
+        <f t="shared" ref="D17:J17" si="5">D14/40</f>
         <v>7.45</v>
       </c>
-      <c r="E17" s="49">
+      <c r="E17" s="37">
         <f t="shared" si="5"/>
         <v>5.25</v>
       </c>
-      <c r="F17" s="49">
+      <c r="F17" s="37">
         <f t="shared" si="5"/>
         <v>6.6</v>
       </c>
-      <c r="G17" s="49"/>
-      <c r="H17" s="49">
+      <c r="G17" s="37"/>
+      <c r="H17" s="37">
         <f t="shared" si="5"/>
         <v>5.9</v>
       </c>
-      <c r="I17" s="49">
+      <c r="I17" s="37">
         <f t="shared" si="5"/>
         <v>8.25</v>
       </c>
-      <c r="J17" s="49">
+      <c r="J17" s="37">
         <f t="shared" si="5"/>
         <v>8.9</v>
       </c>
-      <c r="K17" s="49"/>
-      <c r="L17" s="48">
+      <c r="K17" s="37"/>
+      <c r="L17" s="36">
         <f>SUM(C17:J17)</f>
         <v>52.324999999999996</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="C18" s="54"/>
+      <c r="C18" s="32"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
@@ -12891,57 +13191,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="36"/>
+      <c r="B2" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="49"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="37"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="39"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="52"/>
     </row>
     <row r="4" spans="1:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
-      <c r="K4" s="39"/>
+      <c r="B4" s="50"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="52"/>
     </row>
     <row r="5" spans="1:12" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="40"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
-      <c r="J5" s="41"/>
-      <c r="K5" s="42"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
+      <c r="K5" s="55"/>
     </row>
     <row r="6" spans="1:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -12949,18 +13249,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="43" t="s">
+      <c r="D6" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="44" t="s">
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
-      <c r="K6" s="45"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="57"/>
+      <c r="K6" s="58"/>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -12969,7 +13269,7 @@
       <c r="B7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="50" t="s">
+      <c r="C7" s="38" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="12" t="s">
@@ -13156,7 +13456,7 @@
       <c r="I14" s="12"/>
       <c r="J14" s="12"/>
       <c r="K14" s="12"/>
-      <c r="L14" s="48">
+      <c r="L14" s="36">
         <f>C14+D14+E14+F14+H14+I14+J14</f>
         <v>0</v>
       </c>
@@ -13167,7 +13467,7 @@
         <v>40</v>
       </c>
       <c r="C15" s="14">
-        <f t="shared" ref="C15:K15" si="0">SUM(C8:C14)</f>
+        <f t="shared" ref="C15" si="0">SUM(C8:C14)</f>
         <v>178</v>
       </c>
       <c r="D15" s="14">
@@ -13175,7 +13475,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="14">
-        <f t="shared" ref="E15:K15" si="1">E14/20</f>
+        <f t="shared" ref="E15:J15" si="1">E14/20</f>
         <v>0</v>
       </c>
       <c r="F15" s="14">
@@ -13207,7 +13507,7 @@
         <v>178</v>
       </c>
       <c r="D16" s="13">
-        <f t="shared" ref="D16:K16" si="2">D15+D14</f>
+        <f t="shared" ref="D16:J16" si="2">D15+D14</f>
         <v>0</v>
       </c>
       <c r="E16" s="13">
@@ -13235,19 +13535,19 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" s="13"/>
-      <c r="B17" s="52" t="s">
+      <c r="B17" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="49"/>
-      <c r="D17" s="49"/>
-      <c r="E17" s="49"/>
-      <c r="F17" s="49"/>
-      <c r="G17" s="49"/>
-      <c r="H17" s="49"/>
-      <c r="I17" s="49"/>
-      <c r="J17" s="49"/>
-      <c r="K17" s="49"/>
-      <c r="L17" s="48">
+      <c r="C17" s="37"/>
+      <c r="D17" s="37"/>
+      <c r="E17" s="37"/>
+      <c r="F17" s="37"/>
+      <c r="G17" s="37"/>
+      <c r="H17" s="37"/>
+      <c r="I17" s="37"/>
+      <c r="J17" s="37"/>
+      <c r="K17" s="37"/>
+      <c r="L17" s="36">
         <f>SUM(C17:J17)</f>
         <v>0</v>
       </c>
@@ -13255,7 +13555,7 @@
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
-      <c r="C18" s="55"/>
+      <c r="C18" s="42"/>
       <c r="D18" s="26">
         <f t="shared" ref="D18:K18" si="3">D15/40</f>
         <v>0</v>
@@ -13344,57 +13644,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="36"/>
+      <c r="B2" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="49"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="37"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="39"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="52"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
-      <c r="K4" s="39"/>
+      <c r="B4" s="50"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="52"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="40"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
-      <c r="J5" s="41"/>
-      <c r="K5" s="42"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
+      <c r="K5" s="55"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -13402,18 +13702,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="43" t="s">
+      <c r="D6" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="44" t="s">
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
-      <c r="K6" s="45"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="57"/>
+      <c r="K6" s="58"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -13422,7 +13722,7 @@
       <c r="B7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="50" t="s">
+      <c r="C7" s="38" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="12" t="s">
@@ -13611,7 +13911,7 @@
       <c r="I14" s="13"/>
       <c r="J14" s="13"/>
       <c r="K14" s="13"/>
-      <c r="L14" s="48">
+      <c r="L14" s="36">
         <f>C14+D14+E14+F14+H14+I14+J14</f>
         <v>0</v>
       </c>
@@ -13621,91 +13921,91 @@
       <c r="B15" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="C15" s="49"/>
-      <c r="D15" s="49">
+      <c r="C15" s="37"/>
+      <c r="D15" s="37">
         <f>D14/20</f>
         <v>0</v>
       </c>
-      <c r="E15" s="49">
-        <f t="shared" ref="E15:K15" si="1">E14/20</f>
-        <v>0</v>
-      </c>
-      <c r="F15" s="49">
+      <c r="E15" s="37">
+        <f t="shared" ref="E15:J15" si="1">E14/20</f>
+        <v>0</v>
+      </c>
+      <c r="F15" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G15" s="49"/>
-      <c r="H15" s="49">
+      <c r="G15" s="37"/>
+      <c r="H15" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I15" s="49">
+      <c r="I15" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J15" s="49">
+      <c r="J15" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K15" s="49"/>
+      <c r="K15" s="37"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" s="13"/>
       <c r="B16" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="49">
+      <c r="C16" s="37">
         <f>C15+C14</f>
         <v>0</v>
       </c>
-      <c r="D16" s="49">
-        <f t="shared" ref="D16:K16" si="2">D15+D14</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G16" s="49"/>
-      <c r="H16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K16" s="49"/>
+      <c r="D16" s="37">
+        <f t="shared" ref="D16:J16" si="2">D15+D14</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="37"/>
+      <c r="H16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="37"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A17" s="53"/>
-      <c r="B17" s="52" t="s">
+      <c r="A17" s="41"/>
+      <c r="B17" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="53"/>
-      <c r="D17" s="53"/>
-      <c r="E17" s="53"/>
-      <c r="F17" s="53"/>
-      <c r="G17" s="53"/>
-      <c r="H17" s="53"/>
-      <c r="I17" s="53"/>
-      <c r="J17" s="53"/>
-      <c r="K17" s="53"/>
-      <c r="L17" s="48">
+      <c r="C17" s="41"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="41"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="41"/>
+      <c r="H17" s="41"/>
+      <c r="I17" s="41"/>
+      <c r="J17" s="41"/>
+      <c r="K17" s="41"/>
+      <c r="L17" s="36">
         <f>SUM(C17:J17)</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="C18" s="54"/>
+      <c r="C18" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -13749,57 +14049,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="36"/>
+      <c r="B2" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="49"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="37"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="39"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="52"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
-      <c r="K4" s="39"/>
+      <c r="B4" s="50"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="52"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="40"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
-      <c r="J5" s="41"/>
-      <c r="K5" s="42"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
+      <c r="K5" s="55"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -13807,18 +14107,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="43" t="s">
+      <c r="D6" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="44" t="s">
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
-      <c r="K6" s="45"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="57"/>
+      <c r="K6" s="58"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -13827,7 +14127,7 @@
       <c r="B7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="50" t="s">
+      <c r="C7" s="38" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="12" t="s">
@@ -13972,7 +14272,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L14" s="48">
+      <c r="L14" s="36">
         <f>C14+D14+E14+F14+H14+I14+J14</f>
         <v>0</v>
       </c>
@@ -13988,7 +14288,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:K15" si="1">E14/20</f>
+        <f t="shared" ref="E15:J15" si="1">E14/20</f>
         <v>0</v>
       </c>
       <c r="F15" s="13">
@@ -14015,79 +14315,79 @@
       <c r="B16" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="49">
+      <c r="C16" s="37">
         <f>C15+C14</f>
         <v>0</v>
       </c>
-      <c r="D16" s="49">
-        <f t="shared" ref="D16:K16" si="2">D15+D14</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G16" s="49"/>
-      <c r="H16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J16" s="49">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K16" s="49"/>
+      <c r="D16" s="37">
+        <f t="shared" ref="D16:J16" si="2">D15+D14</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="37"/>
+      <c r="H16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="37"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" s="13"/>
-      <c r="B17" s="52" t="s">
+      <c r="B17" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="49">
+      <c r="C17" s="37">
         <f>C14/40</f>
         <v>0</v>
       </c>
-      <c r="D17" s="49">
-        <f t="shared" ref="D17:K17" si="3">D14/40</f>
-        <v>0</v>
-      </c>
-      <c r="E17" s="49">
+      <c r="D17" s="37">
+        <f t="shared" ref="D17:J17" si="3">D14/40</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F17" s="49">
+      <c r="F17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G17" s="49"/>
-      <c r="H17" s="49">
+      <c r="G17" s="37"/>
+      <c r="H17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I17" s="49">
+      <c r="I17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J17" s="49">
+      <c r="J17" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K17" s="49"/>
-      <c r="L17" s="48">
+      <c r="K17" s="37"/>
+      <c r="L17" s="36">
         <f>SUM(C17:J17)</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="C18" s="54"/>
+      <c r="C18" s="32"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
@@ -14144,57 +14444,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="36"/>
+      <c r="B2" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="49"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="37"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="39"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="52"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
-      <c r="K4" s="39"/>
+      <c r="B4" s="50"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="52"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="40"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
-      <c r="J5" s="41"/>
-      <c r="K5" s="42"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
+      <c r="K5" s="55"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -14202,18 +14502,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="43" t="s">
+      <c r="D6" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="44" t="s">
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
-      <c r="K6" s="45"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="57"/>
+      <c r="K6" s="58"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -14222,7 +14522,7 @@
       <c r="B7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="50" t="s">
+      <c r="C7" s="38" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="12" t="s">
@@ -14431,7 +14731,7 @@
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="L14" s="48">
+      <c r="L14" s="36">
         <f>C14+D14+E14+F14+H14+I14+J14</f>
         <v>2054</v>
       </c>
@@ -14447,7 +14747,7 @@
         <v>20.55</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:K15" si="1">E14/20</f>
+        <f t="shared" ref="E15:J15" si="1">E14/20</f>
         <v>14</v>
       </c>
       <c r="F15" s="13">
@@ -14474,79 +14774,79 @@
       <c r="B16" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="49">
+      <c r="C16" s="37">
         <f>C15+C14</f>
         <v>172</v>
       </c>
-      <c r="D16" s="49">
-        <f t="shared" ref="D16:K16" si="2">D15+D14</f>
+      <c r="D16" s="37">
+        <f t="shared" ref="D16:J16" si="2">D15+D14</f>
         <v>431.55</v>
       </c>
-      <c r="E16" s="49">
+      <c r="E16" s="37">
         <f t="shared" si="2"/>
         <v>294</v>
       </c>
-      <c r="F16" s="49">
+      <c r="F16" s="37">
         <f t="shared" si="2"/>
         <v>271.95</v>
       </c>
-      <c r="G16" s="49"/>
-      <c r="H16" s="49">
+      <c r="G16" s="37"/>
+      <c r="H16" s="37">
         <f t="shared" si="2"/>
         <v>323.39999999999998</v>
       </c>
-      <c r="I16" s="49">
+      <c r="I16" s="37">
         <f t="shared" si="2"/>
         <v>241.5</v>
       </c>
-      <c r="J16" s="49">
+      <c r="J16" s="37">
         <f t="shared" si="2"/>
         <v>413.7</v>
       </c>
-      <c r="K16" s="49"/>
+      <c r="K16" s="37"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" s="13"/>
-      <c r="B17" s="52" t="s">
+      <c r="B17" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="49">
+      <c r="C17" s="37">
         <f>C14/40</f>
         <v>4.3</v>
       </c>
-      <c r="D17" s="49">
-        <f t="shared" ref="D17:K17" si="3">D14/40</f>
+      <c r="D17" s="37">
+        <f t="shared" ref="D17:J17" si="3">D14/40</f>
         <v>10.275</v>
       </c>
-      <c r="E17" s="49">
+      <c r="E17" s="37">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
-      <c r="F17" s="49">
+      <c r="F17" s="37">
         <f t="shared" si="3"/>
         <v>6.4749999999999996</v>
       </c>
-      <c r="G17" s="49"/>
-      <c r="H17" s="49">
+      <c r="G17" s="37"/>
+      <c r="H17" s="37">
         <f t="shared" si="3"/>
         <v>7.7</v>
       </c>
-      <c r="I17" s="49">
+      <c r="I17" s="37">
         <f t="shared" si="3"/>
         <v>5.75</v>
       </c>
-      <c r="J17" s="49">
+      <c r="J17" s="37">
         <f t="shared" si="3"/>
         <v>9.85</v>
       </c>
-      <c r="K17" s="49"/>
-      <c r="L17" s="48">
+      <c r="K17" s="37"/>
+      <c r="L17" s="36">
         <f>SUM(C17:J17)</f>
         <v>51.35</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="C18" s="54"/>
+      <c r="C18" s="32"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>

--- a/Final Execution SKU wise.xlsx
+++ b/Final Execution SKU wise.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56B72B0F-F77A-4022-B276-8E0E4D57523F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05A20FBA-256D-497A-93DA-C6B3DA5703FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" activeTab="13" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" activeTab="14" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
   </bookViews>
   <sheets>
     <sheet name="last month" sheetId="1" r:id="rId1"/>

--- a/Final Execution SKU wise.xlsx
+++ b/Final Execution SKU wise.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05A20FBA-256D-497A-93DA-C6B3DA5703FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81233A15-C6E9-49CF-85DC-B233163C042E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" activeTab="14" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
   </bookViews>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="61">
   <si>
     <t>Gate Pass</t>
   </si>
@@ -231,6 +231,15 @@
   <si>
     <t>Nbeel</t>
   </si>
+  <si>
+    <t>Shops</t>
+  </si>
+  <si>
+    <t>Ctns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Furqan </t>
+  </si>
 </sst>
 </file>
 
@@ -329,7 +338,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="27">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -651,11 +660,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
@@ -797,6 +817,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1617,6 +1641,9 @@
       <c r="K7" s="12" t="s">
         <v>8</v>
       </c>
+      <c r="L7" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="27"/>
@@ -1644,6 +1671,10 @@
         <f>SUM(H8:J8)/20</f>
         <v>1</v>
       </c>
+      <c r="L8">
+        <f>SUM(C8:F8,H8,I8,J8)/40</f>
+        <v>0.5</v>
+      </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" s="27"/>
@@ -1679,6 +1710,10 @@
         <f t="shared" ref="K9:K14" si="1">SUM(H9:J9)/20</f>
         <v>1.25</v>
       </c>
+      <c r="L9">
+        <f t="shared" ref="L9:L12" si="2">SUM(C9:F9,H9,I9,J9)/40</f>
+        <v>3.7250000000000001</v>
+      </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
@@ -1714,6 +1749,10 @@
         <f t="shared" si="1"/>
         <v>1.05</v>
       </c>
+      <c r="L10">
+        <f t="shared" si="2"/>
+        <v>6.7750000000000004</v>
+      </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
@@ -1748,6 +1787,10 @@
       <c r="K11" s="30">
         <f t="shared" si="1"/>
         <v>14</v>
+      </c>
+      <c r="L11">
+        <f t="shared" si="2"/>
+        <v>11.6</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
@@ -1770,6 +1813,10 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
+      <c r="L12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
@@ -1812,35 +1859,35 @@
         <v>31</v>
       </c>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:J14" si="2">SUM(C8:C13)</f>
+        <f t="shared" ref="C14:J14" si="3">SUM(C8:C13)</f>
         <v>248</v>
       </c>
       <c r="D14" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>138</v>
       </c>
       <c r="E14" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>157</v>
       </c>
       <c r="F14" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>205</v>
       </c>
       <c r="G14" s="31">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>25</v>
       </c>
       <c r="H14" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>149</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>124</v>
       </c>
       <c r="J14" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>155</v>
       </c>
       <c r="K14" s="30">
@@ -1863,24 +1910,24 @@
         <v>6.9</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:J15" si="3">E14/20</f>
+        <f t="shared" ref="E15:J15" si="4">E14/20</f>
         <v>7.85</v>
       </c>
       <c r="F15" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>10.25</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>7.45</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>6.2</v>
       </c>
       <c r="J15" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>7.75</v>
       </c>
       <c r="K15" s="13"/>
@@ -1895,28 +1942,28 @@
         <v>248</v>
       </c>
       <c r="D16" s="37">
-        <f t="shared" ref="D16:J16" si="4">D15+D14</f>
+        <f t="shared" ref="D16:J16" si="5">D15+D14</f>
         <v>144.9</v>
       </c>
       <c r="E16" s="37">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>164.85</v>
       </c>
       <c r="F16" s="37">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>215.25</v>
       </c>
       <c r="G16" s="37"/>
       <c r="H16" s="37">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>156.44999999999999</v>
       </c>
       <c r="I16" s="37">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>130.19999999999999</v>
       </c>
       <c r="J16" s="37">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>162.75</v>
       </c>
       <c r="K16" s="37"/>
@@ -1931,28 +1978,28 @@
         <v>6.2</v>
       </c>
       <c r="D17" s="37">
-        <f t="shared" ref="D17:J17" si="5">D14/40</f>
+        <f t="shared" ref="D17:J17" si="6">D14/40</f>
         <v>3.45</v>
       </c>
       <c r="E17" s="37">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3.9249999999999998</v>
       </c>
       <c r="F17" s="37">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>5.125</v>
       </c>
       <c r="G17" s="37"/>
       <c r="H17" s="37">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3.7250000000000001</v>
       </c>
       <c r="I17" s="37">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3.1</v>
       </c>
       <c r="J17" s="37">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3.875</v>
       </c>
       <c r="K17" s="37"/>
@@ -2124,6 +2171,9 @@
       <c r="K7" s="12" t="s">
         <v>8</v>
       </c>
+      <c r="L7" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="27"/>
@@ -2157,6 +2207,10 @@
         <f>SUM(H8:J8)/20</f>
         <v>8</v>
       </c>
+      <c r="L8">
+        <f>SUM(C8:F8,H8,I8,J8)/40</f>
+        <v>7</v>
+      </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" s="27"/>
@@ -2186,6 +2240,10 @@
         <v>0</v>
       </c>
       <c r="K9" s="28"/>
+      <c r="L9">
+        <f t="shared" ref="L9:L12" si="0">SUM(C9:F9,H9,I9,J9)/40</f>
+        <v>13.275</v>
+      </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
@@ -2199,6 +2257,10 @@
       <c r="I10" s="12"/>
       <c r="J10" s="12"/>
       <c r="K10" s="28"/>
+      <c r="L10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
@@ -2212,6 +2274,10 @@
       <c r="I11" s="12"/>
       <c r="J11" s="12"/>
       <c r="K11" s="12"/>
+      <c r="L11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
@@ -2225,6 +2291,10 @@
       <c r="I12" s="12"/>
       <c r="J12" s="12"/>
       <c r="K12" s="12"/>
+      <c r="L12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
@@ -2243,39 +2313,39 @@
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:K14" si="0">SUM(C8:C13)</f>
+        <f t="shared" ref="C14:K14" si="1">SUM(C8:C13)</f>
         <v>80</v>
       </c>
       <c r="D14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>115</v>
       </c>
       <c r="E14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>122</v>
       </c>
       <c r="F14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>95</v>
       </c>
       <c r="G14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="H14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>160</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>209</v>
       </c>
       <c r="J14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>30</v>
       </c>
       <c r="K14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="L14" s="36">
@@ -2294,24 +2364,24 @@
         <v>5.75</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:J15" si="1">E14/20</f>
+        <f t="shared" ref="E15:J15" si="2">E14/20</f>
         <v>6.1</v>
       </c>
       <c r="F15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4.75</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>10.45</v>
       </c>
       <c r="J15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.5</v>
       </c>
       <c r="K15" s="13"/>
@@ -2326,28 +2396,28 @@
         <v>80</v>
       </c>
       <c r="D16" s="37">
-        <f t="shared" ref="D16:J16" si="2">D15+D14</f>
+        <f t="shared" ref="D16:J16" si="3">D15+D14</f>
         <v>120.75</v>
       </c>
       <c r="E16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>128.1</v>
       </c>
       <c r="F16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>99.75</v>
       </c>
       <c r="G16" s="37"/>
       <c r="H16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>168</v>
       </c>
       <c r="I16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>219.45</v>
       </c>
       <c r="J16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>31.5</v>
       </c>
       <c r="K16" s="37"/>
@@ -2362,28 +2432,28 @@
         <v>2</v>
       </c>
       <c r="D17" s="37">
-        <f t="shared" ref="D17:J17" si="3">D14/40</f>
+        <f t="shared" ref="D17:J17" si="4">D14/40</f>
         <v>2.875</v>
       </c>
       <c r="E17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3.05</v>
       </c>
       <c r="F17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.375</v>
       </c>
       <c r="G17" s="37"/>
       <c r="H17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4</v>
       </c>
       <c r="I17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5.2249999999999996</v>
       </c>
       <c r="J17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.75</v>
       </c>
       <c r="K17" s="37"/>
@@ -2561,6 +2631,9 @@
       <c r="K7" s="12" t="s">
         <v>8</v>
       </c>
+      <c r="L7" t="s">
+        <v>59</v>
+      </c>
       <c r="P7" t="s">
         <v>16</v>
       </c>
@@ -2605,6 +2678,10 @@
         <f>SUM(H8:J8)/20</f>
         <v>3.8</v>
       </c>
+      <c r="L8">
+        <f>SUM(C8:F8,H8,I8,J8)/40</f>
+        <v>3.25</v>
+      </c>
       <c r="P8" t="s">
         <v>17</v>
       </c>
@@ -2647,6 +2724,10 @@
         <f t="shared" ref="K9:K10" si="1">SUM(H9:J9)/20</f>
         <v>12</v>
       </c>
+      <c r="L9">
+        <f t="shared" ref="L9:L12" si="2">SUM(C9:F9,H9,I9,J9)/40</f>
+        <v>8</v>
+      </c>
       <c r="P9" t="s">
         <v>34</v>
       </c>
@@ -2690,6 +2771,10 @@
       <c r="K10" s="28">
         <f t="shared" si="1"/>
         <v>44.9</v>
+      </c>
+      <c r="L10">
+        <f t="shared" si="2"/>
+        <v>33.25</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.35">
@@ -2704,6 +2789,10 @@
       <c r="I11" s="12"/>
       <c r="J11" s="12"/>
       <c r="K11" s="12"/>
+      <c r="L11">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
@@ -2717,6 +2806,10 @@
       <c r="I12" s="12"/>
       <c r="J12" s="12"/>
       <c r="K12" s="12"/>
+      <c r="L12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
@@ -2735,39 +2828,39 @@
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:K14" si="2">SUM(C8:C13)</f>
+        <f t="shared" ref="C14:K14" si="3">SUM(C8:C13)</f>
         <v>200</v>
       </c>
       <c r="D14" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>115</v>
       </c>
       <c r="E14" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>130</v>
       </c>
       <c r="F14" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>121</v>
       </c>
       <c r="G14" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>18.3</v>
       </c>
       <c r="H14" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>413</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>346</v>
       </c>
       <c r="J14" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>455</v>
       </c>
       <c r="K14" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>60.7</v>
       </c>
       <c r="L14" s="36">
@@ -2786,24 +2879,24 @@
         <v>5.75</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:J15" si="3">E14/20</f>
+        <f t="shared" ref="E15:J15" si="4">E14/20</f>
         <v>6.5</v>
       </c>
       <c r="F15" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>6.05</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>20.65</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>17.3</v>
       </c>
       <c r="J15" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>22.75</v>
       </c>
       <c r="K15" s="13"/>
@@ -2818,28 +2911,28 @@
         <v>200</v>
       </c>
       <c r="D16" s="37">
-        <f t="shared" ref="D16:J16" si="4">D15+D14</f>
+        <f t="shared" ref="D16:J16" si="5">D15+D14</f>
         <v>120.75</v>
       </c>
       <c r="E16" s="37">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>136.5</v>
       </c>
       <c r="F16" s="37">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>127.05</v>
       </c>
       <c r="G16" s="37"/>
       <c r="H16" s="37">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>433.65</v>
       </c>
       <c r="I16" s="37">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>363.3</v>
       </c>
       <c r="J16" s="37">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>477.75</v>
       </c>
       <c r="K16" s="37"/>
@@ -2854,28 +2947,28 @@
         <v>5</v>
       </c>
       <c r="D17" s="37">
-        <f t="shared" ref="D17:J17" si="5">D14/40</f>
+        <f t="shared" ref="D17:J17" si="6">D14/40</f>
         <v>2.875</v>
       </c>
       <c r="E17" s="37">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3.25</v>
       </c>
       <c r="F17" s="37">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3.0249999999999999</v>
       </c>
       <c r="G17" s="37"/>
       <c r="H17" s="37">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>10.324999999999999</v>
       </c>
       <c r="I17" s="37">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>8.65</v>
       </c>
       <c r="J17" s="37">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>11.375</v>
       </c>
       <c r="K17" s="37"/>
@@ -3050,6 +3143,9 @@
       <c r="K7" s="12" t="s">
         <v>8</v>
       </c>
+      <c r="L7" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" s="27"/>
@@ -3085,6 +3181,10 @@
         <f>SUM(H8:J8)/20</f>
         <v>8</v>
       </c>
+      <c r="L8">
+        <f>SUM(C8:F8,H8,I8,J8)/40</f>
+        <v>8.3000000000000007</v>
+      </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" s="27"/>
@@ -3118,6 +3218,10 @@
         <f>SUM(H9:J9)/20</f>
         <v>18.3</v>
       </c>
+      <c r="L9">
+        <f t="shared" ref="L9:L12" si="0">SUM(C9:F9,H9,I9,J9)/40</f>
+        <v>10.15</v>
+      </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
@@ -3152,6 +3256,10 @@
       <c r="K10" s="28">
         <f>SUM(H10:J10)/20</f>
         <v>11</v>
+      </c>
+      <c r="L10">
+        <f t="shared" si="0"/>
+        <v>9.75</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.35">
@@ -3170,6 +3278,10 @@
       <c r="J11" s="12"/>
       <c r="K11" s="28">
         <f>SUM(H11:J11)/20</f>
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -3185,6 +3297,10 @@
       <c r="I12" s="12"/>
       <c r="J12" s="12"/>
       <c r="K12" s="12"/>
+      <c r="L12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
@@ -3205,39 +3321,39 @@
         <v>31</v>
       </c>
       <c r="C14" s="34">
-        <f t="shared" ref="C14:K14" si="0">SUM(C8:C13)</f>
+        <f t="shared" ref="C14:K14" si="1">SUM(C8:C13)</f>
         <v>102</v>
       </c>
       <c r="D14" s="34">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="E14" s="34">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>120</v>
       </c>
       <c r="F14" s="34">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>60</v>
       </c>
       <c r="G14" s="34">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="H14" s="34">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>273</v>
       </c>
       <c r="I14" s="34">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>231</v>
       </c>
       <c r="J14" s="34">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>242</v>
       </c>
       <c r="K14" s="34">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>37.299999999999997</v>
       </c>
       <c r="L14" s="35">
@@ -3256,24 +3372,24 @@
         <v>5</v>
       </c>
       <c r="E15" s="30">
-        <f t="shared" ref="E15:J15" si="1">E14/20</f>
+        <f t="shared" ref="E15:J15" si="2">E14/20</f>
         <v>6</v>
       </c>
       <c r="F15" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="G15" s="30"/>
       <c r="H15" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>13.65</v>
       </c>
       <c r="I15" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>11.55</v>
       </c>
       <c r="J15" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>12.1</v>
       </c>
       <c r="K15" s="30"/>
@@ -3288,28 +3404,28 @@
         <v>102</v>
       </c>
       <c r="D16" s="39">
-        <f t="shared" ref="D16:J16" si="2">D15+D14</f>
+        <f t="shared" ref="D16:J16" si="3">D15+D14</f>
         <v>105</v>
       </c>
       <c r="E16" s="39">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>126</v>
       </c>
       <c r="F16" s="39">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>63</v>
       </c>
       <c r="G16" s="39"/>
       <c r="H16" s="39">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>286.64999999999998</v>
       </c>
       <c r="I16" s="39">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>242.55</v>
       </c>
       <c r="J16" s="39">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>254.1</v>
       </c>
       <c r="K16" s="39"/>
@@ -3324,28 +3440,28 @@
         <v>2.5499999999999998</v>
       </c>
       <c r="D17" s="37">
-        <f t="shared" ref="D17:J17" si="3">D14/40</f>
+        <f t="shared" ref="D17:J17" si="4">D14/40</f>
         <v>2.5</v>
       </c>
       <c r="E17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="F17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.5</v>
       </c>
       <c r="G17" s="37"/>
       <c r="H17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>6.8250000000000002</v>
       </c>
       <c r="I17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5.7750000000000004</v>
       </c>
       <c r="J17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>6.05</v>
       </c>
       <c r="K17" s="37"/>
@@ -3517,6 +3633,9 @@
       <c r="K7" s="12" t="s">
         <v>8</v>
       </c>
+      <c r="L7" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A8" s="27"/>
@@ -3552,6 +3671,10 @@
         <f>SUM(H8:J8)/20</f>
         <v>18</v>
       </c>
+      <c r="L8">
+        <f>SUM(C8:F8,H8,I8,J8)/40</f>
+        <v>16</v>
+      </c>
       <c r="O8" s="44" t="s">
         <v>45</v>
       </c>
@@ -3603,6 +3726,10 @@
         <f t="shared" ref="K9:K11" si="1">SUM(H9:J9)/20</f>
         <v>5.8</v>
       </c>
+      <c r="L9">
+        <f t="shared" ref="L9:L12" si="2">SUM(C9:F9,H9,I9,J9)/40</f>
+        <v>4.8</v>
+      </c>
       <c r="N9" s="45" t="s">
         <v>51</v>
       </c>
@@ -3655,6 +3782,10 @@
       </c>
       <c r="K10" s="28">
         <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="L10">
+        <f t="shared" si="2"/>
         <v>45</v>
       </c>
       <c r="N10" s="45" t="s">
@@ -3697,6 +3828,10 @@
       <c r="J11" s="12"/>
       <c r="K11" s="28">
         <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N11" s="45" t="s">
@@ -3733,6 +3868,10 @@
       <c r="I12" s="12"/>
       <c r="J12" s="12"/>
       <c r="K12" s="12"/>
+      <c r="L12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="N12" s="45" t="s">
         <v>54</v>
       </c>
@@ -3798,39 +3937,39 @@
         <v>31</v>
       </c>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:K14" si="2">SUM(C8:C13)</f>
+        <f t="shared" ref="C14:K14" si="3">SUM(C8:C13)</f>
         <v>40</v>
       </c>
       <c r="D14" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>387</v>
       </c>
       <c r="E14" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>422</v>
       </c>
       <c r="F14" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>407</v>
       </c>
       <c r="G14" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>60.8</v>
       </c>
       <c r="H14" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>457</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>462</v>
       </c>
       <c r="J14" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>457</v>
       </c>
       <c r="K14" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>68.8</v>
       </c>
       <c r="L14" s="36">
@@ -3870,24 +4009,24 @@
         <v>19.350000000000001</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:J15" si="3">E14/20</f>
+        <f t="shared" ref="E15:J15" si="4">E14/20</f>
         <v>21.1</v>
       </c>
       <c r="F15" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>20.350000000000001</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>22.85</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>23.1</v>
       </c>
       <c r="J15" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>22.85</v>
       </c>
       <c r="K15" s="13"/>
@@ -3899,23 +4038,23 @@
         <v>300</v>
       </c>
       <c r="P15" s="46">
-        <f t="shared" ref="P15:T15" si="4">SUM(P9:P14)</f>
+        <f t="shared" ref="P15:T15" si="5">SUM(P9:P14)</f>
         <v>300</v>
       </c>
       <c r="Q15" s="46">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>300</v>
       </c>
       <c r="R15" s="46">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>300</v>
       </c>
       <c r="S15" s="46">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>300</v>
       </c>
       <c r="T15" s="46">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>300</v>
       </c>
     </row>
@@ -3929,28 +4068,28 @@
         <v>40</v>
       </c>
       <c r="D16" s="39">
-        <f t="shared" ref="D16:J16" si="5">D15+D14</f>
+        <f t="shared" ref="D16:J16" si="6">D15+D14</f>
         <v>406.35</v>
       </c>
       <c r="E16" s="39">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>443.1</v>
       </c>
       <c r="F16" s="39">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>427.35</v>
       </c>
       <c r="G16" s="39"/>
       <c r="H16" s="39">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>479.85</v>
       </c>
       <c r="I16" s="39">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>485.1</v>
       </c>
       <c r="J16" s="39">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>479.85</v>
       </c>
       <c r="K16" s="37"/>
@@ -3968,28 +4107,28 @@
         <v>1</v>
       </c>
       <c r="D17" s="37">
-        <f t="shared" ref="D17:J17" si="6">D14/40</f>
+        <f t="shared" ref="D17:J17" si="7">D14/40</f>
         <v>9.6750000000000007</v>
       </c>
       <c r="E17" s="37">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>10.55</v>
       </c>
       <c r="F17" s="37">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>10.175000000000001</v>
       </c>
       <c r="G17" s="37"/>
       <c r="H17" s="37">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>11.425000000000001</v>
       </c>
       <c r="I17" s="37">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>11.55</v>
       </c>
       <c r="J17" s="37">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>11.425000000000001</v>
       </c>
       <c r="K17" s="37"/>
@@ -4161,51 +4300,66 @@
       <c r="K7" s="12" t="s">
         <v>8</v>
       </c>
+      <c r="L7" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="27"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
+      <c r="B8" s="60"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
       <c r="G8" s="28">
         <f>SUM(D8:F8)/20</f>
         <v>0</v>
       </c>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="12"/>
+      <c r="H8" s="29"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="29"/>
       <c r="K8" s="28">
         <f>SUM(H8:J8)/20</f>
         <v>0</v>
       </c>
+      <c r="L8">
+        <f>SUM(C8:F8,H8,I8,J8)/40</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" s="27"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
+      <c r="B9" s="60"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="29"/>
       <c r="G9" s="28"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12"/>
+      <c r="H9" s="29"/>
+      <c r="I9" s="29"/>
+      <c r="J9" s="29"/>
       <c r="K9" s="28"/>
+      <c r="L9">
+        <f t="shared" ref="L9:L12" si="0">SUM(C9:F9,H9,I9,J9)/40</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
+      <c r="B10" s="60"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="29"/>
       <c r="G10" s="28"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="12"/>
+      <c r="H10" s="29"/>
+      <c r="I10" s="29"/>
+      <c r="J10" s="29"/>
       <c r="K10" s="28"/>
+      <c r="L10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
@@ -4219,6 +4373,10 @@
       <c r="I11" s="12"/>
       <c r="J11" s="12"/>
       <c r="K11" s="12"/>
+      <c r="L11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
@@ -4232,6 +4390,10 @@
       <c r="I12" s="12"/>
       <c r="J12" s="12"/>
       <c r="K12" s="12"/>
+      <c r="L12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
@@ -4250,39 +4412,39 @@
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:K14" si="0">SUM(C8:C13)</f>
+        <f t="shared" ref="C14:K14" si="1">SUM(C8:C13)</f>
         <v>0</v>
       </c>
       <c r="D14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="E14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L14" s="36">
@@ -4301,24 +4463,24 @@
         <v>0</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:J15" si="1">E14/20</f>
+        <f t="shared" ref="E15:J15" si="2">E14/20</f>
         <v>0</v>
       </c>
       <c r="F15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K15" s="13"/>
@@ -4333,28 +4495,28 @@
         <v>0</v>
       </c>
       <c r="D16" s="37">
-        <f t="shared" ref="D16:J16" si="2">D15+D14</f>
+        <f t="shared" ref="D16:J16" si="3">D15+D14</f>
         <v>0</v>
       </c>
       <c r="E16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G16" s="37"/>
       <c r="H16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K16" s="37"/>
@@ -4369,28 +4531,28 @@
         <v>0</v>
       </c>
       <c r="D17" s="37">
-        <f t="shared" ref="D17:J17" si="3">D14/40</f>
+        <f t="shared" ref="D17:J17" si="4">D14/40</f>
         <v>0</v>
       </c>
       <c r="E17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G17" s="37"/>
       <c r="H17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K17" s="37"/>
@@ -4562,38 +4724,85 @@
       <c r="K7" s="12" t="s">
         <v>8</v>
       </c>
+      <c r="L7" s="59" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="27"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
+      <c r="B8" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="12">
+        <v>36</v>
+      </c>
+      <c r="D8" s="12">
+        <v>12</v>
+      </c>
+      <c r="E8" s="12">
+        <v>0</v>
+      </c>
+      <c r="F8" s="12">
+        <v>0</v>
+      </c>
       <c r="G8" s="28">
         <f>SUM(D8:F8)/20</f>
-        <v>0</v>
-      </c>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="12"/>
+        <v>0.6</v>
+      </c>
+      <c r="H8" s="12">
+        <v>27</v>
+      </c>
+      <c r="I8" s="12">
+        <v>27</v>
+      </c>
+      <c r="J8" s="12">
+        <v>27</v>
+      </c>
       <c r="K8" s="28">
         <f>SUM(H8:J8)/20</f>
-        <v>0</v>
+        <v>4.05</v>
+      </c>
+      <c r="L8">
+        <f>SUM(C8:F8,H8,I8,J8)/40</f>
+        <v>3.2250000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" s="27"/>
-      <c r="B9" s="10"/>
+      <c r="B9" s="10" t="s">
+        <v>11</v>
+      </c>
       <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12"/>
-      <c r="K9" s="28"/>
+      <c r="D9" s="12">
+        <v>15</v>
+      </c>
+      <c r="E9" s="12">
+        <v>10</v>
+      </c>
+      <c r="F9" s="12">
+        <v>15</v>
+      </c>
+      <c r="G9" s="28">
+        <f>SUM(D9:F9)/20</f>
+        <v>2</v>
+      </c>
+      <c r="H9" s="12">
+        <v>109</v>
+      </c>
+      <c r="I9" s="12">
+        <v>51</v>
+      </c>
+      <c r="J9" s="12">
+        <v>160</v>
+      </c>
+      <c r="K9" s="28">
+        <f>SUM(H9:J9)/20</f>
+        <v>16</v>
+      </c>
+      <c r="L9">
+        <f t="shared" ref="L9:L12" si="0">SUM(C9:F9,H9,I9,J9)/40</f>
+        <v>9</v>
+      </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
@@ -4602,11 +4811,21 @@
       <c r="D10" s="12"/>
       <c r="E10" s="12"/>
       <c r="F10" s="12"/>
-      <c r="G10" s="28"/>
+      <c r="G10" s="28">
+        <f>SUM(D10:F10)/20</f>
+        <v>0</v>
+      </c>
       <c r="H10" s="12"/>
       <c r="I10" s="12"/>
       <c r="J10" s="12"/>
-      <c r="K10" s="28"/>
+      <c r="K10" s="28">
+        <f>SUM(H10:J10)/20</f>
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
@@ -4620,6 +4839,10 @@
       <c r="I11" s="12"/>
       <c r="J11" s="12"/>
       <c r="K11" s="12"/>
+      <c r="L11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
@@ -4633,6 +4856,10 @@
       <c r="I12" s="12"/>
       <c r="J12" s="12"/>
       <c r="K12" s="12"/>
+      <c r="L12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
@@ -4651,44 +4878,44 @@
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:K14" si="0">SUM(C8:C13)</f>
-        <v>0</v>
+        <f t="shared" ref="C14:K14" si="1">SUM(C8:C13)</f>
+        <v>36</v>
       </c>
       <c r="D14" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>27</v>
       </c>
       <c r="E14" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>10</v>
       </c>
       <c r="F14" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>15</v>
       </c>
       <c r="G14" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>2.6</v>
       </c>
       <c r="H14" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>136</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>78</v>
       </c>
       <c r="J14" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>187</v>
       </c>
       <c r="K14" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>20.05</v>
       </c>
       <c r="L14" s="36">
         <f>C14+D14+E14+F14+H14+I14+J14</f>
-        <v>0</v>
+        <v>489</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.35">
@@ -4699,28 +4926,28 @@
       <c r="C15" s="13"/>
       <c r="D15" s="13">
         <f>D14/20</f>
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:J15" si="1">E14/20</f>
-        <v>0</v>
+        <f t="shared" ref="E15:J15" si="2">E14/20</f>
+        <v>0.5</v>
       </c>
       <c r="F15" s="13">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>0.75</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>6.8</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>3.9</v>
       </c>
       <c r="J15" s="13">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>9.35</v>
       </c>
       <c r="K15" s="13"/>
     </row>
@@ -4731,32 +4958,32 @@
       </c>
       <c r="C16" s="37">
         <f>C15+C14</f>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="D16" s="37">
-        <f t="shared" ref="D16:J16" si="2">D15+D14</f>
-        <v>0</v>
+        <f t="shared" ref="D16:J16" si="3">D15+D14</f>
+        <v>28.35</v>
       </c>
       <c r="E16" s="37">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>10.5</v>
       </c>
       <c r="F16" s="37">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>15.75</v>
       </c>
       <c r="G16" s="37"/>
       <c r="H16" s="37">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>142.80000000000001</v>
       </c>
       <c r="I16" s="37">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>81.900000000000006</v>
       </c>
       <c r="J16" s="37">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>196.35</v>
       </c>
       <c r="K16" s="37"/>
     </row>
@@ -4767,37 +4994,37 @@
       </c>
       <c r="C17" s="37">
         <f>C14/40</f>
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="D17" s="37">
-        <f t="shared" ref="D17:J17" si="3">D14/40</f>
-        <v>0</v>
+        <f t="shared" ref="D17:J17" si="4">D14/40</f>
+        <v>0.67500000000000004</v>
       </c>
       <c r="E17" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>0.25</v>
       </c>
       <c r="F17" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>0.375</v>
       </c>
       <c r="G17" s="37"/>
       <c r="H17" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>3.4</v>
       </c>
       <c r="I17" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>1.95</v>
       </c>
       <c r="J17" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>4.6749999999999998</v>
       </c>
       <c r="K17" s="37"/>
       <c r="L17" s="36">
         <f>SUM(C17:J17)</f>
-        <v>0</v>
+        <v>12.225</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">
@@ -4828,7 +5055,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7A2FBED-8856-42CC-977B-5977D4F16323}">
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.90625" bestFit="1" customWidth="1"/>
@@ -4843,7 +5070,7 @@
     <col min="11" max="11" width="5.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4856,7 +5083,7 @@
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="47" t="s">
         <v>0</v>
@@ -4871,7 +5098,7 @@
       <c r="J2" s="48"/>
       <c r="K2" s="49"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="50"/>
       <c r="C3" s="51"/>
@@ -4884,7 +5111,7 @@
       <c r="J3" s="51"/>
       <c r="K3" s="52"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" s="50"/>
       <c r="C4" s="51"/>
@@ -4897,7 +5124,7 @@
       <c r="J4" s="51"/>
       <c r="K4" s="52"/>
     </row>
-    <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
       <c r="B5" s="53"/>
       <c r="C5" s="54"/>
@@ -4910,7 +5137,7 @@
       <c r="J5" s="54"/>
       <c r="K5" s="55"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
       <c r="B6" s="2"/>
       <c r="C6" s="3" t="s">
@@ -4929,7 +5156,7 @@
       <c r="J6" s="57"/>
       <c r="K6" s="58"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
         <v>4</v>
       </c>
@@ -4963,53 +5190,162 @@
       <c r="K7" s="12" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="L7" t="s">
+        <v>59</v>
+      </c>
+      <c r="O7" s="41"/>
+      <c r="P7" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q7" s="41" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8" s="27"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
+      <c r="B8" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="12">
+        <v>144</v>
+      </c>
+      <c r="D8" s="12">
+        <v>70</v>
+      </c>
+      <c r="E8" s="12">
+        <v>70</v>
+      </c>
+      <c r="F8" s="12">
+        <v>20</v>
+      </c>
       <c r="G8" s="28">
         <f>SUM(D8:F8)/20</f>
-        <v>0</v>
-      </c>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="12"/>
+        <v>8</v>
+      </c>
+      <c r="H8" s="12">
+        <v>95</v>
+      </c>
+      <c r="I8" s="12">
+        <v>70</v>
+      </c>
+      <c r="J8" s="12">
+        <v>75</v>
+      </c>
       <c r="K8" s="28">
         <f>SUM(H8:J8)/20</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+        <v>12</v>
+      </c>
+      <c r="L8">
+        <f>SUM(C8:F8,H8,I8,J8)/40</f>
+        <v>13.6</v>
+      </c>
+      <c r="O8" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="P8" s="41">
+        <v>5</v>
+      </c>
+      <c r="Q8" s="41">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9" s="27"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12"/>
-      <c r="K9" s="28"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B9" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="12">
+        <v>24</v>
+      </c>
+      <c r="D9" s="12">
+        <v>52</v>
+      </c>
+      <c r="E9" s="12">
+        <v>62</v>
+      </c>
+      <c r="F9" s="12">
+        <v>62</v>
+      </c>
+      <c r="G9" s="28">
+        <f t="shared" ref="G9:G10" si="0">SUM(D9:F9)/20</f>
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="H9" s="12">
+        <v>22</v>
+      </c>
+      <c r="I9" s="12">
+        <v>43</v>
+      </c>
+      <c r="J9" s="12">
+        <v>91</v>
+      </c>
+      <c r="K9" s="28">
+        <f t="shared" ref="K9:K10" si="1">SUM(H9:J9)/20</f>
+        <v>7.8</v>
+      </c>
+      <c r="L9">
+        <f t="shared" ref="L9:L12" si="2">SUM(C9:F9,H9,I9,J9)/40</f>
+        <v>8.9</v>
+      </c>
+      <c r="O9" s="41" t="s">
+        <v>11</v>
+      </c>
+      <c r="P9" s="41">
+        <v>9</v>
+      </c>
+      <c r="Q9" s="41">
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="28"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="28"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B10" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="C10" s="12">
+        <v>30</v>
+      </c>
+      <c r="D10" s="12">
+        <v>66</v>
+      </c>
+      <c r="E10" s="12">
+        <v>66</v>
+      </c>
+      <c r="F10" s="12">
+        <v>40</v>
+      </c>
+      <c r="G10" s="28">
+        <f t="shared" si="0"/>
+        <v>8.6</v>
+      </c>
+      <c r="H10" s="12">
+        <v>48</v>
+      </c>
+      <c r="I10" s="12">
+        <v>5</v>
+      </c>
+      <c r="J10" s="12">
+        <v>47</v>
+      </c>
+      <c r="K10" s="28">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="L10">
+        <f t="shared" si="2"/>
+        <v>7.55</v>
+      </c>
+      <c r="O10" s="41" t="s">
+        <v>60</v>
+      </c>
+      <c r="P10" s="41">
+        <v>6</v>
+      </c>
+      <c r="Q10" s="41">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11"/>
       <c r="C11" s="12"/>
@@ -5021,8 +5357,12 @@
       <c r="I11" s="12"/>
       <c r="J11" s="12"/>
       <c r="K11" s="12"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="L11">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
       <c r="B12" s="11"/>
       <c r="C12" s="12"/>
@@ -5034,8 +5374,12 @@
       <c r="I12" s="12"/>
       <c r="J12" s="12"/>
       <c r="K12" s="12"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="L12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
       <c r="B13" s="11"/>
       <c r="C13" s="12"/>
@@ -5048,51 +5392,51 @@
       <c r="J13" s="12"/>
       <c r="K13" s="12"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:K14" si="0">SUM(C8:C13)</f>
-        <v>0</v>
+        <f t="shared" ref="C14:K14" si="3">SUM(C8:C13)</f>
+        <v>198</v>
       </c>
       <c r="D14" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>188</v>
       </c>
       <c r="E14" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>198</v>
       </c>
       <c r="F14" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>122</v>
       </c>
       <c r="G14" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>25.4</v>
       </c>
       <c r="H14" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>165</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>118</v>
       </c>
       <c r="J14" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>213</v>
       </c>
       <c r="K14" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>24.8</v>
       </c>
       <c r="L14" s="36">
         <f>C14+D14+E14+F14+H14+I14+J14</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15" s="13"/>
       <c r="B15" s="10" t="s">
         <v>40</v>
@@ -5100,64 +5444,64 @@
       <c r="C15" s="13"/>
       <c r="D15" s="13">
         <f>D14/20</f>
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:J15" si="1">E14/20</f>
-        <v>0</v>
+        <f t="shared" ref="E15:J15" si="4">E14/20</f>
+        <v>9.9</v>
       </c>
       <c r="F15" s="13">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>6.1</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>8.25</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>5.9</v>
       </c>
       <c r="J15" s="13">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>10.65</v>
       </c>
       <c r="K15" s="13"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16" s="13"/>
       <c r="B16" s="10" t="s">
         <v>39</v>
       </c>
       <c r="C16" s="37">
         <f>C15+C14</f>
-        <v>0</v>
+        <v>198</v>
       </c>
       <c r="D16" s="37">
-        <f t="shared" ref="D16:J16" si="2">D15+D14</f>
-        <v>0</v>
+        <f t="shared" ref="D16:J16" si="5">D15+D14</f>
+        <v>197.4</v>
       </c>
       <c r="E16" s="37">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>207.9</v>
       </c>
       <c r="F16" s="37">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>128.1</v>
       </c>
       <c r="G16" s="37"/>
       <c r="H16" s="37">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>173.25</v>
       </c>
       <c r="I16" s="37">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>123.9</v>
       </c>
       <c r="J16" s="37">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>223.65</v>
       </c>
       <c r="K16" s="37"/>
     </row>
@@ -5168,37 +5512,37 @@
       </c>
       <c r="C17" s="37">
         <f>C14/40</f>
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="D17" s="37">
-        <f t="shared" ref="D17:J17" si="3">D14/40</f>
-        <v>0</v>
+        <f t="shared" ref="D17:J17" si="6">D14/40</f>
+        <v>4.7</v>
       </c>
       <c r="E17" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>4.95</v>
       </c>
       <c r="F17" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>3.05</v>
       </c>
       <c r="G17" s="37"/>
       <c r="H17" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>4.125</v>
       </c>
       <c r="I17" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>2.95</v>
       </c>
       <c r="J17" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>5.3250000000000002</v>
       </c>
       <c r="K17" s="37"/>
       <c r="L17" s="36">
         <f>SUM(C17:J17)</f>
-        <v>0</v>
+        <v>30.05</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">
@@ -5364,6 +5708,9 @@
       <c r="K7" s="12" t="s">
         <v>8</v>
       </c>
+      <c r="L7" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="27"/>
@@ -5381,6 +5728,10 @@
       <c r="J8" s="12"/>
       <c r="K8" s="28">
         <f>SUM(H8:J8)/20</f>
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <f>SUM(C8:F8,H8,I8,J8)/40</f>
         <v>0</v>
       </c>
     </row>
@@ -5396,6 +5747,10 @@
       <c r="I9" s="12"/>
       <c r="J9" s="12"/>
       <c r="K9" s="28"/>
+      <c r="L9">
+        <f t="shared" ref="L9:L12" si="0">SUM(C9:F9,H9,I9,J9)/40</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
@@ -5409,6 +5764,10 @@
       <c r="I10" s="12"/>
       <c r="J10" s="12"/>
       <c r="K10" s="28"/>
+      <c r="L10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
@@ -5422,6 +5781,10 @@
       <c r="I11" s="12"/>
       <c r="J11" s="12"/>
       <c r="K11" s="12"/>
+      <c r="L11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
@@ -5435,6 +5798,10 @@
       <c r="I12" s="12"/>
       <c r="J12" s="12"/>
       <c r="K12" s="12"/>
+      <c r="L12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
@@ -5453,39 +5820,39 @@
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:K14" si="0">SUM(C8:C13)</f>
+        <f t="shared" ref="C14:K14" si="1">SUM(C8:C13)</f>
         <v>0</v>
       </c>
       <c r="D14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="E14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L14" s="36">
@@ -5504,24 +5871,24 @@
         <v>0</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:J15" si="1">E14/20</f>
+        <f t="shared" ref="E15:J15" si="2">E14/20</f>
         <v>0</v>
       </c>
       <c r="F15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K15" s="13"/>
@@ -5536,28 +5903,28 @@
         <v>0</v>
       </c>
       <c r="D16" s="37">
-        <f t="shared" ref="D16:J16" si="2">D15+D14</f>
+        <f t="shared" ref="D16:J16" si="3">D15+D14</f>
         <v>0</v>
       </c>
       <c r="E16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G16" s="37"/>
       <c r="H16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K16" s="37"/>
@@ -5572,28 +5939,28 @@
         <v>0</v>
       </c>
       <c r="D17" s="37">
-        <f t="shared" ref="D17:J17" si="3">D14/40</f>
+        <f t="shared" ref="D17:J17" si="4">D14/40</f>
         <v>0</v>
       </c>
       <c r="E17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G17" s="37"/>
       <c r="H17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K17" s="37"/>
@@ -5765,6 +6132,9 @@
       <c r="K7" s="12" t="s">
         <v>8</v>
       </c>
+      <c r="L7" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="27"/>
@@ -5782,6 +6152,10 @@
       <c r="J8" s="12"/>
       <c r="K8" s="28">
         <f>SUM(H8:J8)/20</f>
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <f>SUM(C8:F8,H8,I8,J8)/40</f>
         <v>0</v>
       </c>
     </row>
@@ -5797,6 +6171,10 @@
       <c r="I9" s="12"/>
       <c r="J9" s="12"/>
       <c r="K9" s="28"/>
+      <c r="L9">
+        <f t="shared" ref="L9:L12" si="0">SUM(C9:F9,H9,I9,J9)/40</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
@@ -5810,6 +6188,10 @@
       <c r="I10" s="12"/>
       <c r="J10" s="12"/>
       <c r="K10" s="28"/>
+      <c r="L10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
@@ -5823,6 +6205,10 @@
       <c r="I11" s="12"/>
       <c r="J11" s="12"/>
       <c r="K11" s="12"/>
+      <c r="L11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
@@ -5836,6 +6222,10 @@
       <c r="I12" s="12"/>
       <c r="J12" s="12"/>
       <c r="K12" s="12"/>
+      <c r="L12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
@@ -5854,39 +6244,39 @@
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:K14" si="0">SUM(C8:C13)</f>
+        <f t="shared" ref="C14:K14" si="1">SUM(C8:C13)</f>
         <v>0</v>
       </c>
       <c r="D14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="E14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L14" s="36">
@@ -5905,24 +6295,24 @@
         <v>0</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:J15" si="1">E14/20</f>
+        <f t="shared" ref="E15:J15" si="2">E14/20</f>
         <v>0</v>
       </c>
       <c r="F15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K15" s="13"/>
@@ -5937,28 +6327,28 @@
         <v>0</v>
       </c>
       <c r="D16" s="37">
-        <f t="shared" ref="D16:J16" si="2">D15+D14</f>
+        <f t="shared" ref="D16:J16" si="3">D15+D14</f>
         <v>0</v>
       </c>
       <c r="E16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G16" s="37"/>
       <c r="H16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K16" s="37"/>
@@ -5973,28 +6363,28 @@
         <v>0</v>
       </c>
       <c r="D17" s="37">
-        <f t="shared" ref="D17:J17" si="3">D14/40</f>
+        <f t="shared" ref="D17:J17" si="4">D14/40</f>
         <v>0</v>
       </c>
       <c r="E17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G17" s="37"/>
       <c r="H17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K17" s="37"/>
@@ -6166,6 +6556,9 @@
       <c r="K7" s="12" t="s">
         <v>8</v>
       </c>
+      <c r="L7" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="27">
@@ -6203,6 +6596,10 @@
         <f>SUM(H8:J8)/20</f>
         <v>3.15</v>
       </c>
+      <c r="L8">
+        <f>SUM(C8:F8,H8,I8,J8)/40</f>
+        <v>5.2249999999999996</v>
+      </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" s="27">
@@ -6239,6 +6636,10 @@
       <c r="K9" s="28">
         <f>SUM(H9:J9)/20</f>
         <v>3.1</v>
+      </c>
+      <c r="L9">
+        <f t="shared" ref="L9:L12" si="0">SUM(C9:F9,H9,I9,J9)/40</f>
+        <v>4.45</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.35">
@@ -6257,6 +6658,10 @@
       <c r="J10" s="12"/>
       <c r="K10" s="28">
         <f>SUM(H10:J10)/20</f>
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -6272,6 +6677,10 @@
       <c r="I11" s="12"/>
       <c r="J11" s="12"/>
       <c r="K11" s="12"/>
+      <c r="L11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
@@ -6285,6 +6694,10 @@
       <c r="I12" s="12"/>
       <c r="J12" s="12"/>
       <c r="K12" s="12"/>
+      <c r="L12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
@@ -6303,39 +6716,39 @@
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:K14" si="0">SUM(C8:C13)</f>
+        <f t="shared" ref="C14:K14" si="1">SUM(C8:C13)</f>
         <v>190</v>
       </c>
       <c r="D14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>32</v>
       </c>
       <c r="E14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="F14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="G14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3.6</v>
       </c>
       <c r="H14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>50</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>34</v>
       </c>
       <c r="J14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>41</v>
       </c>
       <c r="K14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6.25</v>
       </c>
       <c r="L14" s="36">
@@ -6354,24 +6767,24 @@
         <v>1.6</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:J15" si="1">E14/20</f>
+        <f t="shared" ref="E15:J15" si="2">E14/20</f>
         <v>1</v>
       </c>
       <c r="F15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.5</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.7</v>
       </c>
       <c r="J15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.0499999999999998</v>
       </c>
       <c r="K15" s="13"/>
@@ -6386,28 +6799,28 @@
         <v>190</v>
       </c>
       <c r="D16" s="37">
-        <f t="shared" ref="D16:J16" si="2">D15+D14</f>
+        <f t="shared" ref="D16:J16" si="3">D15+D14</f>
         <v>33.6</v>
       </c>
       <c r="E16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>21</v>
       </c>
       <c r="F16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>21</v>
       </c>
       <c r="G16" s="37"/>
       <c r="H16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>52.5</v>
       </c>
       <c r="I16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>35.700000000000003</v>
       </c>
       <c r="J16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>43.05</v>
       </c>
       <c r="K16" s="37"/>
@@ -6422,28 +6835,28 @@
         <v>4.75</v>
       </c>
       <c r="D17" s="37">
-        <f t="shared" ref="D17:J17" si="3">D14/40</f>
+        <f t="shared" ref="D17:J17" si="4">D14/40</f>
         <v>0.8</v>
       </c>
       <c r="E17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.5</v>
       </c>
       <c r="F17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.5</v>
       </c>
       <c r="G17" s="37"/>
       <c r="H17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.25</v>
       </c>
       <c r="I17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.85</v>
       </c>
       <c r="J17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.0249999999999999</v>
       </c>
       <c r="K17" s="37"/>
@@ -6615,6 +7028,9 @@
       <c r="K7" s="12" t="s">
         <v>8</v>
       </c>
+      <c r="L7" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="27"/>
@@ -6632,6 +7048,10 @@
       <c r="J8" s="12"/>
       <c r="K8" s="28">
         <f>SUM(H8:J8)/20</f>
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <f>SUM(C8:F8,H8,I8,J8)/40</f>
         <v>0</v>
       </c>
     </row>
@@ -6647,6 +7067,10 @@
       <c r="I9" s="12"/>
       <c r="J9" s="12"/>
       <c r="K9" s="28"/>
+      <c r="L9">
+        <f t="shared" ref="L9:L12" si="0">SUM(C9:F9,H9,I9,J9)/40</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
@@ -6660,6 +7084,10 @@
       <c r="I10" s="12"/>
       <c r="J10" s="12"/>
       <c r="K10" s="28"/>
+      <c r="L10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
@@ -6673,6 +7101,10 @@
       <c r="I11" s="12"/>
       <c r="J11" s="12"/>
       <c r="K11" s="12"/>
+      <c r="L11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
@@ -6686,6 +7118,10 @@
       <c r="I12" s="12"/>
       <c r="J12" s="12"/>
       <c r="K12" s="12"/>
+      <c r="L12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
@@ -6704,39 +7140,39 @@
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:K14" si="0">SUM(C8:C13)</f>
+        <f t="shared" ref="C14:K14" si="1">SUM(C8:C13)</f>
         <v>0</v>
       </c>
       <c r="D14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="E14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L14" s="36">
@@ -6755,24 +7191,24 @@
         <v>0</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:J15" si="1">E14/20</f>
+        <f t="shared" ref="E15:J15" si="2">E14/20</f>
         <v>0</v>
       </c>
       <c r="F15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K15" s="13"/>
@@ -6787,28 +7223,28 @@
         <v>0</v>
       </c>
       <c r="D16" s="37">
-        <f t="shared" ref="D16:J16" si="2">D15+D14</f>
+        <f t="shared" ref="D16:J16" si="3">D15+D14</f>
         <v>0</v>
       </c>
       <c r="E16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G16" s="37"/>
       <c r="H16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K16" s="37"/>
@@ -6823,28 +7259,28 @@
         <v>0</v>
       </c>
       <c r="D17" s="37">
-        <f t="shared" ref="D17:J17" si="3">D14/40</f>
+        <f t="shared" ref="D17:J17" si="4">D14/40</f>
         <v>0</v>
       </c>
       <c r="E17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G17" s="37"/>
       <c r="H17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K17" s="37"/>
@@ -7016,6 +7452,9 @@
       <c r="K7" s="12" t="s">
         <v>8</v>
       </c>
+      <c r="L7" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="27"/>
@@ -7033,6 +7472,10 @@
       <c r="J8" s="12"/>
       <c r="K8" s="28">
         <f>SUM(H8:J8)/20</f>
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <f>SUM(C8:F8,H8,I8,J8)/40</f>
         <v>0</v>
       </c>
     </row>
@@ -7048,6 +7491,10 @@
       <c r="I9" s="12"/>
       <c r="J9" s="12"/>
       <c r="K9" s="28"/>
+      <c r="L9">
+        <f t="shared" ref="L9:L12" si="0">SUM(C9:F9,H9,I9,J9)/40</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
@@ -7061,6 +7508,10 @@
       <c r="I10" s="12"/>
       <c r="J10" s="12"/>
       <c r="K10" s="28"/>
+      <c r="L10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
@@ -7074,6 +7525,10 @@
       <c r="I11" s="12"/>
       <c r="J11" s="12"/>
       <c r="K11" s="12"/>
+      <c r="L11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
@@ -7087,6 +7542,10 @@
       <c r="I12" s="12"/>
       <c r="J12" s="12"/>
       <c r="K12" s="12"/>
+      <c r="L12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
@@ -7105,39 +7564,39 @@
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:K14" si="0">SUM(C8:C13)</f>
+        <f t="shared" ref="C14:K14" si="1">SUM(C8:C13)</f>
         <v>0</v>
       </c>
       <c r="D14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="E14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L14" s="36">
@@ -7156,24 +7615,24 @@
         <v>0</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:J15" si="1">E14/20</f>
+        <f t="shared" ref="E15:J15" si="2">E14/20</f>
         <v>0</v>
       </c>
       <c r="F15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K15" s="13"/>
@@ -7188,28 +7647,28 @@
         <v>0</v>
       </c>
       <c r="D16" s="37">
-        <f t="shared" ref="D16:J16" si="2">D15+D14</f>
+        <f t="shared" ref="D16:J16" si="3">D15+D14</f>
         <v>0</v>
       </c>
       <c r="E16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G16" s="37"/>
       <c r="H16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K16" s="37"/>
@@ -7224,28 +7683,28 @@
         <v>0</v>
       </c>
       <c r="D17" s="37">
-        <f t="shared" ref="D17:J17" si="3">D14/40</f>
+        <f t="shared" ref="D17:J17" si="4">D14/40</f>
         <v>0</v>
       </c>
       <c r="E17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G17" s="37"/>
       <c r="H17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K17" s="37"/>
@@ -7417,6 +7876,9 @@
       <c r="K7" s="12" t="s">
         <v>8</v>
       </c>
+      <c r="L7" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="27"/>
@@ -7434,6 +7896,10 @@
       <c r="J8" s="12"/>
       <c r="K8" s="28">
         <f>SUM(H8:J8)/20</f>
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <f>SUM(C8:F8,H8,I8,J8)/40</f>
         <v>0</v>
       </c>
     </row>
@@ -7449,6 +7915,10 @@
       <c r="I9" s="12"/>
       <c r="J9" s="12"/>
       <c r="K9" s="28"/>
+      <c r="L9">
+        <f t="shared" ref="L9:L12" si="0">SUM(C9:F9,H9,I9,J9)/40</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
@@ -7462,6 +7932,10 @@
       <c r="I10" s="12"/>
       <c r="J10" s="12"/>
       <c r="K10" s="28"/>
+      <c r="L10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
@@ -7475,6 +7949,10 @@
       <c r="I11" s="12"/>
       <c r="J11" s="12"/>
       <c r="K11" s="12"/>
+      <c r="L11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
@@ -7488,6 +7966,10 @@
       <c r="I12" s="12"/>
       <c r="J12" s="12"/>
       <c r="K12" s="12"/>
+      <c r="L12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
@@ -7506,39 +7988,39 @@
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:K14" si="0">SUM(C8:C13)</f>
+        <f t="shared" ref="C14:K14" si="1">SUM(C8:C13)</f>
         <v>0</v>
       </c>
       <c r="D14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="E14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L14" s="36">
@@ -7557,24 +8039,24 @@
         <v>0</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:J15" si="1">E14/20</f>
+        <f t="shared" ref="E15:J15" si="2">E14/20</f>
         <v>0</v>
       </c>
       <c r="F15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K15" s="13"/>
@@ -7589,28 +8071,28 @@
         <v>0</v>
       </c>
       <c r="D16" s="37">
-        <f t="shared" ref="D16:J16" si="2">D15+D14</f>
+        <f t="shared" ref="D16:J16" si="3">D15+D14</f>
         <v>0</v>
       </c>
       <c r="E16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G16" s="37"/>
       <c r="H16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K16" s="37"/>
@@ -7625,28 +8107,28 @@
         <v>0</v>
       </c>
       <c r="D17" s="37">
-        <f t="shared" ref="D17:J17" si="3">D14/40</f>
+        <f t="shared" ref="D17:J17" si="4">D14/40</f>
         <v>0</v>
       </c>
       <c r="E17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G17" s="37"/>
       <c r="H17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K17" s="37"/>
@@ -7818,6 +8300,9 @@
       <c r="K7" s="12" t="s">
         <v>8</v>
       </c>
+      <c r="L7" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="27"/>
@@ -7835,6 +8320,10 @@
       <c r="J8" s="12"/>
       <c r="K8" s="28">
         <f>SUM(H8:J8)/20</f>
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <f>SUM(C8:F8,H8,I8,J8)/40</f>
         <v>0</v>
       </c>
     </row>
@@ -7850,6 +8339,10 @@
       <c r="I9" s="12"/>
       <c r="J9" s="12"/>
       <c r="K9" s="28"/>
+      <c r="L9">
+        <f t="shared" ref="L9:L12" si="0">SUM(C9:F9,H9,I9,J9)/40</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
@@ -7863,6 +8356,10 @@
       <c r="I10" s="12"/>
       <c r="J10" s="12"/>
       <c r="K10" s="28"/>
+      <c r="L10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
@@ -7876,6 +8373,10 @@
       <c r="I11" s="12"/>
       <c r="J11" s="12"/>
       <c r="K11" s="12"/>
+      <c r="L11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
@@ -7889,6 +8390,10 @@
       <c r="I12" s="12"/>
       <c r="J12" s="12"/>
       <c r="K12" s="12"/>
+      <c r="L12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
@@ -7907,39 +8412,39 @@
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:K14" si="0">SUM(C8:C13)</f>
+        <f t="shared" ref="C14:K14" si="1">SUM(C8:C13)</f>
         <v>0</v>
       </c>
       <c r="D14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="E14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L14" s="36">
@@ -7958,24 +8463,24 @@
         <v>0</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:J15" si="1">E14/20</f>
+        <f t="shared" ref="E15:J15" si="2">E14/20</f>
         <v>0</v>
       </c>
       <c r="F15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K15" s="13"/>
@@ -7990,28 +8495,28 @@
         <v>0</v>
       </c>
       <c r="D16" s="37">
-        <f t="shared" ref="D16:J16" si="2">D15+D14</f>
+        <f t="shared" ref="D16:J16" si="3">D15+D14</f>
         <v>0</v>
       </c>
       <c r="E16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G16" s="37"/>
       <c r="H16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K16" s="37"/>
@@ -8026,28 +8531,28 @@
         <v>0</v>
       </c>
       <c r="D17" s="37">
-        <f t="shared" ref="D17:J17" si="3">D14/40</f>
+        <f t="shared" ref="D17:J17" si="4">D14/40</f>
         <v>0</v>
       </c>
       <c r="E17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G17" s="37"/>
       <c r="H17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K17" s="37"/>
@@ -8219,6 +8724,9 @@
       <c r="K7" s="12" t="s">
         <v>8</v>
       </c>
+      <c r="L7" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="27"/>
@@ -8236,6 +8744,10 @@
       <c r="J8" s="12"/>
       <c r="K8" s="28">
         <f>SUM(H8:J8)/20</f>
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <f>SUM(C8:F8,H8,I8,J8)/40</f>
         <v>0</v>
       </c>
     </row>
@@ -8251,6 +8763,10 @@
       <c r="I9" s="12"/>
       <c r="J9" s="12"/>
       <c r="K9" s="28"/>
+      <c r="L9">
+        <f t="shared" ref="L9:L12" si="0">SUM(C9:F9,H9,I9,J9)/40</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
@@ -8264,6 +8780,10 @@
       <c r="I10" s="12"/>
       <c r="J10" s="12"/>
       <c r="K10" s="28"/>
+      <c r="L10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
@@ -8277,6 +8797,10 @@
       <c r="I11" s="12"/>
       <c r="J11" s="12"/>
       <c r="K11" s="12"/>
+      <c r="L11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
@@ -8290,6 +8814,10 @@
       <c r="I12" s="12"/>
       <c r="J12" s="12"/>
       <c r="K12" s="12"/>
+      <c r="L12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
@@ -8308,39 +8836,39 @@
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:K14" si="0">SUM(C8:C13)</f>
+        <f t="shared" ref="C14:K14" si="1">SUM(C8:C13)</f>
         <v>0</v>
       </c>
       <c r="D14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="E14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L14" s="36">
@@ -8359,24 +8887,24 @@
         <v>0</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:J15" si="1">E14/20</f>
+        <f t="shared" ref="E15:J15" si="2">E14/20</f>
         <v>0</v>
       </c>
       <c r="F15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K15" s="13"/>
@@ -8391,28 +8919,28 @@
         <v>0</v>
       </c>
       <c r="D16" s="37">
-        <f t="shared" ref="D16:J16" si="2">D15+D14</f>
+        <f t="shared" ref="D16:J16" si="3">D15+D14</f>
         <v>0</v>
       </c>
       <c r="E16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G16" s="37"/>
       <c r="H16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K16" s="37"/>
@@ -8427,28 +8955,28 @@
         <v>0</v>
       </c>
       <c r="D17" s="37">
-        <f t="shared" ref="D17:J17" si="3">D14/40</f>
+        <f t="shared" ref="D17:J17" si="4">D14/40</f>
         <v>0</v>
       </c>
       <c r="E17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G17" s="37"/>
       <c r="H17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K17" s="37"/>
@@ -8620,6 +9148,9 @@
       <c r="K7" s="12" t="s">
         <v>8</v>
       </c>
+      <c r="L7" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="27"/>
@@ -8637,6 +9168,10 @@
       <c r="J8" s="12"/>
       <c r="K8" s="28">
         <f>SUM(H8:J8)/20</f>
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <f>SUM(C8:F8,H8,I8,J8)/40</f>
         <v>0</v>
       </c>
     </row>
@@ -8652,6 +9187,10 @@
       <c r="I9" s="12"/>
       <c r="J9" s="12"/>
       <c r="K9" s="28"/>
+      <c r="L9">
+        <f t="shared" ref="L9:L12" si="0">SUM(C9:F9,H9,I9,J9)/40</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
@@ -8665,6 +9204,10 @@
       <c r="I10" s="12"/>
       <c r="J10" s="12"/>
       <c r="K10" s="28"/>
+      <c r="L10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
@@ -8678,6 +9221,10 @@
       <c r="I11" s="12"/>
       <c r="J11" s="12"/>
       <c r="K11" s="12"/>
+      <c r="L11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
@@ -8691,6 +9238,10 @@
       <c r="I12" s="12"/>
       <c r="J12" s="12"/>
       <c r="K12" s="12"/>
+      <c r="L12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
@@ -8709,39 +9260,39 @@
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:K14" si="0">SUM(C8:C13)</f>
+        <f t="shared" ref="C14:K14" si="1">SUM(C8:C13)</f>
         <v>0</v>
       </c>
       <c r="D14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="E14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L14" s="36">
@@ -8760,24 +9311,24 @@
         <v>0</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:J15" si="1">E14/20</f>
+        <f t="shared" ref="E15:J15" si="2">E14/20</f>
         <v>0</v>
       </c>
       <c r="F15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K15" s="13"/>
@@ -8792,28 +9343,28 @@
         <v>0</v>
       </c>
       <c r="D16" s="37">
-        <f t="shared" ref="D16:J16" si="2">D15+D14</f>
+        <f t="shared" ref="D16:J16" si="3">D15+D14</f>
         <v>0</v>
       </c>
       <c r="E16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G16" s="37"/>
       <c r="H16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K16" s="37"/>
@@ -8828,28 +9379,28 @@
         <v>0</v>
       </c>
       <c r="D17" s="37">
-        <f t="shared" ref="D17:J17" si="3">D14/40</f>
+        <f t="shared" ref="D17:J17" si="4">D14/40</f>
         <v>0</v>
       </c>
       <c r="E17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G17" s="37"/>
       <c r="H17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K17" s="37"/>
@@ -9021,6 +9572,9 @@
       <c r="K7" s="12" t="s">
         <v>8</v>
       </c>
+      <c r="L7" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="27"/>
@@ -9038,6 +9592,10 @@
       <c r="J8" s="12"/>
       <c r="K8" s="28">
         <f>SUM(H8:J8)/20</f>
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <f>SUM(C8:F8,H8,I8,J8)/40</f>
         <v>0</v>
       </c>
     </row>
@@ -9053,6 +9611,10 @@
       <c r="I9" s="12"/>
       <c r="J9" s="12"/>
       <c r="K9" s="28"/>
+      <c r="L9">
+        <f t="shared" ref="L9:L12" si="0">SUM(C9:F9,H9,I9,J9)/40</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
@@ -9066,6 +9628,10 @@
       <c r="I10" s="12"/>
       <c r="J10" s="12"/>
       <c r="K10" s="28"/>
+      <c r="L10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
@@ -9079,6 +9645,10 @@
       <c r="I11" s="12"/>
       <c r="J11" s="12"/>
       <c r="K11" s="12"/>
+      <c r="L11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
@@ -9092,6 +9662,10 @@
       <c r="I12" s="12"/>
       <c r="J12" s="12"/>
       <c r="K12" s="12"/>
+      <c r="L12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
@@ -9110,39 +9684,39 @@
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:K14" si="0">SUM(C8:C13)</f>
+        <f t="shared" ref="C14:K14" si="1">SUM(C8:C13)</f>
         <v>0</v>
       </c>
       <c r="D14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="E14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L14" s="36">
@@ -9161,24 +9735,24 @@
         <v>0</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:J15" si="1">E14/20</f>
+        <f t="shared" ref="E15:J15" si="2">E14/20</f>
         <v>0</v>
       </c>
       <c r="F15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K15" s="13"/>
@@ -9193,28 +9767,28 @@
         <v>0</v>
       </c>
       <c r="D16" s="37">
-        <f t="shared" ref="D16:J16" si="2">D15+D14</f>
+        <f t="shared" ref="D16:J16" si="3">D15+D14</f>
         <v>0</v>
       </c>
       <c r="E16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G16" s="37"/>
       <c r="H16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K16" s="37"/>
@@ -9229,28 +9803,28 @@
         <v>0</v>
       </c>
       <c r="D17" s="37">
-        <f t="shared" ref="D17:J17" si="3">D14/40</f>
+        <f t="shared" ref="D17:J17" si="4">D14/40</f>
         <v>0</v>
       </c>
       <c r="E17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G17" s="37"/>
       <c r="H17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K17" s="37"/>
@@ -9422,6 +9996,9 @@
       <c r="K7" s="12" t="s">
         <v>8</v>
       </c>
+      <c r="L7" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="27"/>
@@ -9439,6 +10016,10 @@
       <c r="J8" s="12"/>
       <c r="K8" s="28">
         <f>SUM(H8:J8)/20</f>
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <f>SUM(C8:F8,H8,I8,J8)/40</f>
         <v>0</v>
       </c>
     </row>
@@ -9454,6 +10035,10 @@
       <c r="I9" s="12"/>
       <c r="J9" s="12"/>
       <c r="K9" s="28"/>
+      <c r="L9">
+        <f t="shared" ref="L9:L12" si="0">SUM(C9:F9,H9,I9,J9)/40</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
@@ -9467,6 +10052,10 @@
       <c r="I10" s="12"/>
       <c r="J10" s="12"/>
       <c r="K10" s="28"/>
+      <c r="L10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
@@ -9480,6 +10069,10 @@
       <c r="I11" s="12"/>
       <c r="J11" s="12"/>
       <c r="K11" s="12"/>
+      <c r="L11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
@@ -9493,6 +10086,10 @@
       <c r="I12" s="12"/>
       <c r="J12" s="12"/>
       <c r="K12" s="12"/>
+      <c r="L12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
@@ -9511,39 +10108,39 @@
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:K14" si="0">SUM(C8:C13)</f>
+        <f t="shared" ref="C14:K14" si="1">SUM(C8:C13)</f>
         <v>0</v>
       </c>
       <c r="D14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="E14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L14" s="36">
@@ -9562,24 +10159,24 @@
         <v>0</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:J15" si="1">E14/20</f>
+        <f t="shared" ref="E15:J15" si="2">E14/20</f>
         <v>0</v>
       </c>
       <c r="F15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K15" s="13"/>
@@ -9594,28 +10191,28 @@
         <v>0</v>
       </c>
       <c r="D16" s="37">
-        <f t="shared" ref="D16:J16" si="2">D15+D14</f>
+        <f t="shared" ref="D16:J16" si="3">D15+D14</f>
         <v>0</v>
       </c>
       <c r="E16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G16" s="37"/>
       <c r="H16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K16" s="37"/>
@@ -9630,28 +10227,28 @@
         <v>0</v>
       </c>
       <c r="D17" s="37">
-        <f t="shared" ref="D17:J17" si="3">D14/40</f>
+        <f t="shared" ref="D17:J17" si="4">D14/40</f>
         <v>0</v>
       </c>
       <c r="E17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G17" s="37"/>
       <c r="H17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K17" s="37"/>
@@ -9823,6 +10420,9 @@
       <c r="K7" s="12" t="s">
         <v>8</v>
       </c>
+      <c r="L7" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="27"/>
@@ -9840,6 +10440,10 @@
       <c r="J8" s="12"/>
       <c r="K8" s="28">
         <f>SUM(H8:J8)/20</f>
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <f>SUM(C8:F8,H8,I8,J8)/40</f>
         <v>0</v>
       </c>
     </row>
@@ -9855,6 +10459,10 @@
       <c r="I9" s="12"/>
       <c r="J9" s="12"/>
       <c r="K9" s="28"/>
+      <c r="L9">
+        <f t="shared" ref="L9:L12" si="0">SUM(C9:F9,H9,I9,J9)/40</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
@@ -9868,6 +10476,10 @@
       <c r="I10" s="12"/>
       <c r="J10" s="12"/>
       <c r="K10" s="28"/>
+      <c r="L10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
@@ -9881,6 +10493,10 @@
       <c r="I11" s="12"/>
       <c r="J11" s="12"/>
       <c r="K11" s="12"/>
+      <c r="L11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
@@ -9894,6 +10510,10 @@
       <c r="I12" s="12"/>
       <c r="J12" s="12"/>
       <c r="K12" s="12"/>
+      <c r="L12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
@@ -9912,39 +10532,39 @@
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:K14" si="0">SUM(C8:C13)</f>
+        <f t="shared" ref="C14:K14" si="1">SUM(C8:C13)</f>
         <v>0</v>
       </c>
       <c r="D14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="E14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L14" s="36">
@@ -9963,24 +10583,24 @@
         <v>0</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:J15" si="1">E14/20</f>
+        <f t="shared" ref="E15:J15" si="2">E14/20</f>
         <v>0</v>
       </c>
       <c r="F15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K15" s="13"/>
@@ -9995,28 +10615,28 @@
         <v>0</v>
       </c>
       <c r="D16" s="37">
-        <f t="shared" ref="D16:J16" si="2">D15+D14</f>
+        <f t="shared" ref="D16:J16" si="3">D15+D14</f>
         <v>0</v>
       </c>
       <c r="E16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G16" s="37"/>
       <c r="H16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K16" s="37"/>
@@ -10031,28 +10651,28 @@
         <v>0</v>
       </c>
       <c r="D17" s="37">
-        <f t="shared" ref="D17:J17" si="3">D14/40</f>
+        <f t="shared" ref="D17:J17" si="4">D14/40</f>
         <v>0</v>
       </c>
       <c r="E17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G17" s="37"/>
       <c r="H17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K17" s="37"/>
@@ -10224,6 +10844,9 @@
       <c r="K7" s="12" t="s">
         <v>8</v>
       </c>
+      <c r="L7" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="27"/>
@@ -10241,6 +10864,10 @@
       <c r="J8" s="12"/>
       <c r="K8" s="28">
         <f>SUM(H8:J8)/20</f>
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <f>SUM(C8:F8,H8,I8,J8)/40</f>
         <v>0</v>
       </c>
     </row>
@@ -10256,6 +10883,10 @@
       <c r="I9" s="12"/>
       <c r="J9" s="12"/>
       <c r="K9" s="28"/>
+      <c r="L9">
+        <f t="shared" ref="L9:L12" si="0">SUM(C9:F9,H9,I9,J9)/40</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
@@ -10269,6 +10900,10 @@
       <c r="I10" s="12"/>
       <c r="J10" s="12"/>
       <c r="K10" s="28"/>
+      <c r="L10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
@@ -10282,6 +10917,10 @@
       <c r="I11" s="12"/>
       <c r="J11" s="12"/>
       <c r="K11" s="12"/>
+      <c r="L11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
@@ -10295,6 +10934,10 @@
       <c r="I12" s="12"/>
       <c r="J12" s="12"/>
       <c r="K12" s="12"/>
+      <c r="L12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
@@ -10313,39 +10956,39 @@
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:K14" si="0">SUM(C8:C13)</f>
+        <f t="shared" ref="C14:K14" si="1">SUM(C8:C13)</f>
         <v>0</v>
       </c>
       <c r="D14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="E14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L14" s="36">
@@ -10364,24 +11007,24 @@
         <v>0</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:J15" si="1">E14/20</f>
+        <f t="shared" ref="E15:J15" si="2">E14/20</f>
         <v>0</v>
       </c>
       <c r="F15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K15" s="13"/>
@@ -10396,28 +11039,28 @@
         <v>0</v>
       </c>
       <c r="D16" s="37">
-        <f t="shared" ref="D16:J16" si="2">D15+D14</f>
+        <f t="shared" ref="D16:J16" si="3">D15+D14</f>
         <v>0</v>
       </c>
       <c r="E16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G16" s="37"/>
       <c r="H16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K16" s="37"/>
@@ -10432,28 +11075,28 @@
         <v>0</v>
       </c>
       <c r="D17" s="37">
-        <f t="shared" ref="D17:J17" si="3">D14/40</f>
+        <f t="shared" ref="D17:J17" si="4">D14/40</f>
         <v>0</v>
       </c>
       <c r="E17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G17" s="37"/>
       <c r="H17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K17" s="37"/>
@@ -10625,6 +11268,9 @@
       <c r="K7" s="12" t="s">
         <v>8</v>
       </c>
+      <c r="L7" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="27">
@@ -10662,6 +11308,10 @@
         <f>SUM(H8:J8)/20</f>
         <v>4.8499999999999996</v>
       </c>
+      <c r="L8">
+        <f>SUM(C8:F8,H8,I8,J8)/40</f>
+        <v>6.0750000000000002</v>
+      </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" s="27">
@@ -10698,6 +11348,10 @@
       <c r="K9" s="28">
         <f t="shared" ref="K9:K10" si="1">SUM(H9:J9)/20</f>
         <v>2.25</v>
+      </c>
+      <c r="L9">
+        <f t="shared" ref="L9:L12" si="2">SUM(C9:F9,H9,I9,J9)/40</f>
+        <v>2.4750000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.35">
@@ -10731,6 +11385,10 @@
       <c r="K10" s="28">
         <f t="shared" si="1"/>
         <v>1.9</v>
+      </c>
+      <c r="L10">
+        <f t="shared" si="2"/>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
@@ -10745,6 +11403,10 @@
       <c r="I11" s="12"/>
       <c r="J11" s="12"/>
       <c r="K11" s="12"/>
+      <c r="L11">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
@@ -10758,6 +11420,10 @@
       <c r="I12" s="12"/>
       <c r="J12" s="12"/>
       <c r="K12" s="12"/>
+      <c r="L12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
@@ -10776,39 +11442,39 @@
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:K14" si="2">SUM(C8:C13)</f>
+        <f t="shared" ref="C14:K14" si="3">SUM(C8:C13)</f>
         <v>40</v>
       </c>
       <c r="D14" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>84</v>
       </c>
       <c r="E14" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>84</v>
       </c>
       <c r="F14" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>42</v>
       </c>
       <c r="G14" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>10.5</v>
       </c>
       <c r="H14" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>57</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>52</v>
       </c>
       <c r="J14" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>71</v>
       </c>
       <c r="K14" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>9</v>
       </c>
       <c r="L14" s="36">
@@ -10827,24 +11493,24 @@
         <v>4.2</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:J15" si="3">E14/20</f>
+        <f t="shared" ref="E15:J15" si="4">E14/20</f>
         <v>4.2</v>
       </c>
       <c r="F15" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.1</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.85</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.6</v>
       </c>
       <c r="J15" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3.55</v>
       </c>
       <c r="K15" s="13"/>
@@ -10859,28 +11525,28 @@
         <v>40</v>
       </c>
       <c r="D16" s="37">
-        <f t="shared" ref="D16:J16" si="4">D15+D14</f>
+        <f t="shared" ref="D16:J16" si="5">D15+D14</f>
         <v>88.2</v>
       </c>
       <c r="E16" s="37">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>88.2</v>
       </c>
       <c r="F16" s="37">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>44.1</v>
       </c>
       <c r="G16" s="37"/>
       <c r="H16" s="37">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>59.85</v>
       </c>
       <c r="I16" s="37">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>54.6</v>
       </c>
       <c r="J16" s="37">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>74.55</v>
       </c>
       <c r="K16" s="37"/>
@@ -10895,28 +11561,28 @@
         <v>1</v>
       </c>
       <c r="D17" s="37">
-        <f t="shared" ref="D17:J17" si="5">D14/40</f>
+        <f t="shared" ref="D17:J17" si="6">D14/40</f>
         <v>2.1</v>
       </c>
       <c r="E17" s="37">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2.1</v>
       </c>
       <c r="F17" s="37">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.05</v>
       </c>
       <c r="G17" s="37"/>
       <c r="H17" s="37">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.425</v>
       </c>
       <c r="I17" s="37">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.3</v>
       </c>
       <c r="J17" s="37">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.7749999999999999</v>
       </c>
       <c r="K17" s="37"/>
@@ -11088,6 +11754,9 @@
       <c r="K7" s="12" t="s">
         <v>8</v>
       </c>
+      <c r="L7" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="27"/>
@@ -11105,6 +11774,10 @@
       <c r="J8" s="12"/>
       <c r="K8" s="28">
         <f>SUM(H8:J8)/20</f>
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <f>SUM(C8:F8,H8,I8,J8)/40</f>
         <v>0</v>
       </c>
     </row>
@@ -11120,6 +11793,10 @@
       <c r="I9" s="12"/>
       <c r="J9" s="12"/>
       <c r="K9" s="28"/>
+      <c r="L9">
+        <f t="shared" ref="L9:L12" si="0">SUM(C9:F9,H9,I9,J9)/40</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
@@ -11133,6 +11810,10 @@
       <c r="I10" s="12"/>
       <c r="J10" s="12"/>
       <c r="K10" s="28"/>
+      <c r="L10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
@@ -11146,6 +11827,10 @@
       <c r="I11" s="12"/>
       <c r="J11" s="12"/>
       <c r="K11" s="12"/>
+      <c r="L11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
@@ -11159,6 +11844,10 @@
       <c r="I12" s="12"/>
       <c r="J12" s="12"/>
       <c r="K12" s="12"/>
+      <c r="L12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
@@ -11177,39 +11866,39 @@
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:K14" si="0">SUM(C8:C13)</f>
+        <f t="shared" ref="C14:K14" si="1">SUM(C8:C13)</f>
         <v>0</v>
       </c>
       <c r="D14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="E14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L14" s="36">
@@ -11228,24 +11917,24 @@
         <v>0</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:J15" si="1">E14/20</f>
+        <f t="shared" ref="E15:J15" si="2">E14/20</f>
         <v>0</v>
       </c>
       <c r="F15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K15" s="13"/>
@@ -11260,28 +11949,28 @@
         <v>0</v>
       </c>
       <c r="D16" s="37">
-        <f t="shared" ref="D16:J16" si="2">D15+D14</f>
+        <f t="shared" ref="D16:J16" si="3">D15+D14</f>
         <v>0</v>
       </c>
       <c r="E16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G16" s="37"/>
       <c r="H16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K16" s="37"/>
@@ -11296,28 +11985,28 @@
         <v>0</v>
       </c>
       <c r="D17" s="37">
-        <f t="shared" ref="D17:J17" si="3">D14/40</f>
+        <f t="shared" ref="D17:J17" si="4">D14/40</f>
         <v>0</v>
       </c>
       <c r="E17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G17" s="37"/>
       <c r="H17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K17" s="37"/>
@@ -11489,6 +12178,9 @@
       <c r="K7" s="12" t="s">
         <v>8</v>
       </c>
+      <c r="L7" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="27"/>
@@ -11506,6 +12198,10 @@
       <c r="J8" s="12"/>
       <c r="K8" s="28">
         <f>SUM(H8:J8)/20</f>
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <f>SUM(C8:F8,H8,I8,J8)/40</f>
         <v>0</v>
       </c>
     </row>
@@ -11521,6 +12217,10 @@
       <c r="I9" s="12"/>
       <c r="J9" s="12"/>
       <c r="K9" s="28"/>
+      <c r="L9">
+        <f t="shared" ref="L9:L12" si="0">SUM(C9:F9,H9,I9,J9)/40</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
@@ -11534,6 +12234,10 @@
       <c r="I10" s="12"/>
       <c r="J10" s="12"/>
       <c r="K10" s="28"/>
+      <c r="L10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
@@ -11547,6 +12251,10 @@
       <c r="I11" s="12"/>
       <c r="J11" s="12"/>
       <c r="K11" s="12"/>
+      <c r="L11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
@@ -11560,6 +12268,10 @@
       <c r="I12" s="12"/>
       <c r="J12" s="12"/>
       <c r="K12" s="12"/>
+      <c r="L12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
@@ -11578,39 +12290,39 @@
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:K14" si="0">SUM(C8:C13)</f>
+        <f t="shared" ref="C14:K14" si="1">SUM(C8:C13)</f>
         <v>0</v>
       </c>
       <c r="D14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="E14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L14" s="36">
@@ -11629,24 +12341,24 @@
         <v>0</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:J15" si="1">E14/20</f>
+        <f t="shared" ref="E15:J15" si="2">E14/20</f>
         <v>0</v>
       </c>
       <c r="F15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K15" s="13"/>
@@ -11661,28 +12373,28 @@
         <v>0</v>
       </c>
       <c r="D16" s="37">
-        <f t="shared" ref="D16:J16" si="2">D15+D14</f>
+        <f t="shared" ref="D16:J16" si="3">D15+D14</f>
         <v>0</v>
       </c>
       <c r="E16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G16" s="37"/>
       <c r="H16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K16" s="37"/>
@@ -11697,28 +12409,28 @@
         <v>0</v>
       </c>
       <c r="D17" s="37">
-        <f t="shared" ref="D17:J17" si="3">D14/40</f>
+        <f t="shared" ref="D17:J17" si="4">D14/40</f>
         <v>0</v>
       </c>
       <c r="E17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G17" s="37"/>
       <c r="H17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K17" s="37"/>
@@ -11891,6 +12603,9 @@
       <c r="K7" s="12" t="s">
         <v>8</v>
       </c>
+      <c r="L7" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="27"/>
@@ -11908,6 +12623,10 @@
       <c r="J8" s="12"/>
       <c r="K8" s="28">
         <f>SUM(H8:J8)/20</f>
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <f>SUM(C8:F8,H8,I8,J8)/40</f>
         <v>0</v>
       </c>
     </row>
@@ -11923,6 +12642,10 @@
       <c r="I9" s="12"/>
       <c r="J9" s="12"/>
       <c r="K9" s="28"/>
+      <c r="L9">
+        <f t="shared" ref="L9:L12" si="0">SUM(C9:F9,H9,I9,J9)/40</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
@@ -11936,6 +12659,10 @@
       <c r="I10" s="12"/>
       <c r="J10" s="12"/>
       <c r="K10" s="28"/>
+      <c r="L10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
@@ -11949,6 +12676,10 @@
       <c r="I11" s="12"/>
       <c r="J11" s="12"/>
       <c r="K11" s="12"/>
+      <c r="L11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
@@ -11962,6 +12693,10 @@
       <c r="I12" s="12"/>
       <c r="J12" s="12"/>
       <c r="K12" s="12"/>
+      <c r="L12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
@@ -11980,39 +12715,39 @@
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:K14" si="0">SUM(C8:C13)</f>
+        <f t="shared" ref="C14:K14" si="1">SUM(C8:C13)</f>
         <v>0</v>
       </c>
       <c r="D14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="E14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L14" s="36">
@@ -12031,24 +12766,24 @@
         <v>0</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:J15" si="1">E14/20</f>
+        <f t="shared" ref="E15:J15" si="2">E14/20</f>
         <v>0</v>
       </c>
       <c r="F15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K15" s="13"/>
@@ -12063,28 +12798,28 @@
         <v>0</v>
       </c>
       <c r="D16" s="37">
-        <f t="shared" ref="D16:J16" si="2">D15+D14</f>
+        <f t="shared" ref="D16:J16" si="3">D15+D14</f>
         <v>0</v>
       </c>
       <c r="E16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G16" s="37"/>
       <c r="H16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K16" s="37"/>
@@ -12099,28 +12834,28 @@
         <v>0</v>
       </c>
       <c r="D17" s="37">
-        <f t="shared" ref="D17:J17" si="3">D14/40</f>
+        <f t="shared" ref="D17:J17" si="4">D14/40</f>
         <v>0</v>
       </c>
       <c r="E17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G17" s="37"/>
       <c r="H17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K17" s="37"/>
@@ -12292,6 +13027,9 @@
       <c r="K7" s="12" t="s">
         <v>8</v>
       </c>
+      <c r="L7" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="27">
@@ -12329,6 +13067,10 @@
         <f>SUM(H8:J8)/20</f>
         <v>9.9499999999999993</v>
       </c>
+      <c r="L8">
+        <f>SUM(C8:F8,H8,I8,J8)/40</f>
+        <v>7.4749999999999996</v>
+      </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" s="27">
@@ -12366,6 +13108,10 @@
         <f t="shared" ref="K9:K12" si="1">SUM(H9:J9)/20</f>
         <v>10.199999999999999</v>
       </c>
+      <c r="L9">
+        <f t="shared" ref="L9:L12" si="2">SUM(C9:F9,H9,I9,J9)/40</f>
+        <v>7.85</v>
+      </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" s="27">
@@ -12403,6 +13149,10 @@
         <f t="shared" si="1"/>
         <v>9.25</v>
       </c>
+      <c r="L10">
+        <f t="shared" si="2"/>
+        <v>6.875</v>
+      </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" s="27">
@@ -12440,6 +13190,10 @@
         <f t="shared" si="1"/>
         <v>10.35</v>
       </c>
+      <c r="L11">
+        <f t="shared" si="2"/>
+        <v>6.625</v>
+      </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" s="27">
@@ -12476,6 +13230,10 @@
       <c r="K12" s="28">
         <f t="shared" si="1"/>
         <v>9.35</v>
+      </c>
+      <c r="L12">
+        <f t="shared" si="2"/>
+        <v>6.8</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
@@ -12495,39 +13253,39 @@
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:K14" si="2">SUM(C8:C13)</f>
+        <f t="shared" ref="C14:K14" si="3">SUM(C8:C13)</f>
         <v>200</v>
       </c>
       <c r="D14" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>48</v>
       </c>
       <c r="E14" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>111</v>
       </c>
       <c r="F14" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>84</v>
       </c>
       <c r="G14" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>12.15</v>
       </c>
       <c r="H14" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>324</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>288</v>
       </c>
       <c r="J14" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>370</v>
       </c>
       <c r="K14" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>49.1</v>
       </c>
       <c r="L14" s="36">
@@ -12546,24 +13304,24 @@
         <v>2.4</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:J15" si="3">E14/20</f>
+        <f t="shared" ref="E15:J15" si="4">E14/20</f>
         <v>5.55</v>
       </c>
       <c r="F15" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4.2</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>16.2</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>14.4</v>
       </c>
       <c r="J15" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>18.5</v>
       </c>
       <c r="K15" s="13"/>
@@ -12578,28 +13336,28 @@
         <v>200</v>
       </c>
       <c r="D16" s="37">
-        <f t="shared" ref="D16:J16" si="4">D15+D14</f>
+        <f t="shared" ref="D16:J16" si="5">D15+D14</f>
         <v>50.4</v>
       </c>
       <c r="E16" s="37">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>116.55</v>
       </c>
       <c r="F16" s="37">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>88.2</v>
       </c>
       <c r="G16" s="37"/>
       <c r="H16" s="37">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>340.2</v>
       </c>
       <c r="I16" s="37">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>302.39999999999998</v>
       </c>
       <c r="J16" s="37">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>388.5</v>
       </c>
       <c r="K16" s="37"/>
@@ -12614,28 +13372,28 @@
         <v>5</v>
       </c>
       <c r="D17" s="37">
-        <f t="shared" ref="D17:J17" si="5">D14/40</f>
+        <f t="shared" ref="D17:J17" si="6">D14/40</f>
         <v>1.2</v>
       </c>
       <c r="E17" s="37">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2.7749999999999999</v>
       </c>
       <c r="F17" s="37">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2.1</v>
       </c>
       <c r="G17" s="37"/>
       <c r="H17" s="37">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>8.1</v>
       </c>
       <c r="I17" s="37">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>7.2</v>
       </c>
       <c r="J17" s="37">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>9.25</v>
       </c>
       <c r="K17" s="37"/>
@@ -12808,6 +13566,9 @@
       <c r="K7" s="12" t="s">
         <v>8</v>
       </c>
+      <c r="L7" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="27">
@@ -12845,6 +13606,10 @@
         <f>SUM(H8:J8)/20</f>
         <v>17.649999999999999</v>
       </c>
+      <c r="L8">
+        <f>SUM(C8:F8,H8,I8,J8)/40</f>
+        <v>18.5</v>
+      </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" s="27">
@@ -12882,6 +13647,10 @@
         <f t="shared" ref="K9:K13" si="1">SUM(H9:J9)/20</f>
         <v>14.8</v>
       </c>
+      <c r="L9">
+        <f t="shared" ref="L9:L12" si="2">SUM(C9:F9,H9,I9,J9)/40</f>
+        <v>17.2</v>
+      </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" s="27">
@@ -12918,6 +13687,10 @@
       <c r="K10" s="28">
         <f t="shared" si="1"/>
         <v>13.65</v>
+      </c>
+      <c r="L10">
+        <f t="shared" si="2"/>
+        <v>16.625</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
@@ -12938,6 +13711,10 @@
       <c r="J11" s="12"/>
       <c r="K11" s="28">
         <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -12959,6 +13736,10 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
+      <c r="L12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
@@ -12983,39 +13764,39 @@
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:K14" si="2">SUM(C8:C13)</f>
+        <f t="shared" ref="C14:K14" si="3">SUM(C8:C13)</f>
         <v>399</v>
       </c>
       <c r="D14" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>298</v>
       </c>
       <c r="E14" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>210</v>
       </c>
       <c r="F14" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>264</v>
       </c>
       <c r="G14" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>38.6</v>
       </c>
       <c r="H14" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>236</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>330</v>
       </c>
       <c r="J14" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>356</v>
       </c>
       <c r="K14" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>46.1</v>
       </c>
       <c r="L14" s="36">
@@ -13034,24 +13815,24 @@
         <v>14.9</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:J15" si="3">E14/20</f>
+        <f t="shared" ref="E15:J15" si="4">E14/20</f>
         <v>10.5</v>
       </c>
       <c r="F15" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>13.2</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>11.8</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>16.5</v>
       </c>
       <c r="J15" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>17.8</v>
       </c>
       <c r="K15" s="13"/>
@@ -13066,28 +13847,28 @@
         <v>399</v>
       </c>
       <c r="D16" s="37">
-        <f t="shared" ref="D16:J16" si="4">D15+D14</f>
+        <f t="shared" ref="D16:J16" si="5">D15+D14</f>
         <v>312.89999999999998</v>
       </c>
       <c r="E16" s="37">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>220.5</v>
       </c>
       <c r="F16" s="37">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>277.2</v>
       </c>
       <c r="G16" s="37"/>
       <c r="H16" s="37">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>247.8</v>
       </c>
       <c r="I16" s="37">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>346.5</v>
       </c>
       <c r="J16" s="37">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>373.8</v>
       </c>
       <c r="K16" s="37"/>
@@ -13102,28 +13883,28 @@
         <v>9.9749999999999996</v>
       </c>
       <c r="D17" s="37">
-        <f t="shared" ref="D17:J17" si="5">D14/40</f>
+        <f t="shared" ref="D17:J17" si="6">D14/40</f>
         <v>7.45</v>
       </c>
       <c r="E17" s="37">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>5.25</v>
       </c>
       <c r="F17" s="37">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>6.6</v>
       </c>
       <c r="G17" s="37"/>
       <c r="H17" s="37">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>5.9</v>
       </c>
       <c r="I17" s="37">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>8.25</v>
       </c>
       <c r="J17" s="37">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>8.9</v>
       </c>
       <c r="K17" s="37"/>
@@ -13296,6 +14077,9 @@
       <c r="K7" s="12" t="s">
         <v>8</v>
       </c>
+      <c r="L7" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="27">
@@ -13331,6 +14115,10 @@
       <c r="K8" s="28">
         <v>7</v>
       </c>
+      <c r="L8">
+        <f>SUM(C8:F8,H8,I8,J8)/40</f>
+        <v>15.35</v>
+      </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" s="27">
@@ -13366,6 +14154,10 @@
       <c r="K9" s="28">
         <v>14</v>
       </c>
+      <c r="L9">
+        <f t="shared" ref="L9:L12" si="0">SUM(C9:F9,H9,I9,J9)/40</f>
+        <v>10</v>
+      </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" s="27">
@@ -13400,6 +14192,10 @@
       </c>
       <c r="K10" s="28">
         <v>2</v>
+      </c>
+      <c r="L10">
+        <f t="shared" si="0"/>
+        <v>3.45</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
@@ -13414,6 +14210,10 @@
       <c r="I11" s="12"/>
       <c r="J11" s="12"/>
       <c r="K11" s="12"/>
+      <c r="L11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" s="13"/>
@@ -13430,6 +14230,10 @@
       <c r="I12" s="12"/>
       <c r="J12" s="12"/>
       <c r="K12" s="12"/>
+      <c r="L12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" s="13"/>
@@ -13467,7 +14271,7 @@
         <v>40</v>
       </c>
       <c r="C15" s="14">
-        <f t="shared" ref="C15" si="0">SUM(C8:C14)</f>
+        <f t="shared" ref="C15" si="1">SUM(C8:C14)</f>
         <v>178</v>
       </c>
       <c r="D15" s="14">
@@ -13475,24 +14279,24 @@
         <v>0</v>
       </c>
       <c r="E15" s="14">
-        <f t="shared" ref="E15:J15" si="1">E14/20</f>
+        <f t="shared" ref="E15:J15" si="2">E14/20</f>
         <v>0</v>
       </c>
       <c r="F15" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G15" s="14"/>
       <c r="H15" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I15" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J15" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K15" s="14"/>
@@ -13507,28 +14311,28 @@
         <v>178</v>
       </c>
       <c r="D16" s="13">
-        <f t="shared" ref="D16:J16" si="2">D15+D14</f>
+        <f t="shared" ref="D16:J16" si="3">D15+D14</f>
         <v>0</v>
       </c>
       <c r="E16" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F16" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G16" s="13"/>
       <c r="H16" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I16" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J16" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K16" s="13"/>
@@ -13557,35 +14361,35 @@
       <c r="B18" s="1"/>
       <c r="C18" s="42"/>
       <c r="D18" s="26">
-        <f t="shared" ref="D18:K18" si="3">D15/40</f>
+        <f t="shared" ref="D18:K18" si="4">D15/40</f>
         <v>0</v>
       </c>
       <c r="E18" s="26">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F18" s="26">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G18" s="26">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H18" s="26">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I18" s="26">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J18" s="26">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K18" s="26">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -13749,6 +14553,9 @@
       <c r="K7" s="12" t="s">
         <v>8</v>
       </c>
+      <c r="L7" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="27">
@@ -13784,6 +14591,10 @@
       <c r="K8" s="28">
         <v>33</v>
       </c>
+      <c r="L8">
+        <f>SUM(C8:F8,H8,I8,J8)/40</f>
+        <v>26.75</v>
+      </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" s="27">
@@ -13818,6 +14629,10 @@
       </c>
       <c r="K9" s="28">
         <v>6</v>
+      </c>
+      <c r="L9">
+        <f t="shared" ref="L9:L12" si="0">SUM(C9:F9,H9,I9,J9)/40</f>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.35">
@@ -13832,6 +14647,10 @@
       <c r="I10" s="12"/>
       <c r="J10" s="12"/>
       <c r="K10" s="12"/>
+      <c r="L10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" s="10"/>
@@ -13845,6 +14664,10 @@
       <c r="I11" s="12"/>
       <c r="J11" s="12"/>
       <c r="K11" s="12"/>
+      <c r="L11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" s="10"/>
@@ -13858,44 +14681,48 @@
       <c r="I12" s="12"/>
       <c r="J12" s="12"/>
       <c r="K12" s="12"/>
+      <c r="L12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" s="13"/>
       <c r="B13" s="10"/>
       <c r="C13" s="14">
-        <f t="shared" ref="C13:K13" si="0">SUM(C8:C12)</f>
+        <f t="shared" ref="C13:K13" si="1">SUM(C8:C12)</f>
         <v>290</v>
       </c>
       <c r="D13" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>110</v>
       </c>
       <c r="E13" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>110</v>
       </c>
       <c r="F13" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="G13" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
       <c r="H13" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>270</v>
       </c>
       <c r="I13" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>225</v>
       </c>
       <c r="J13" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>285</v>
       </c>
       <c r="K13" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>39</v>
       </c>
     </row>
@@ -13927,24 +14754,24 @@
         <v>0</v>
       </c>
       <c r="E15" s="37">
-        <f t="shared" ref="E15:J15" si="1">E14/20</f>
+        <f t="shared" ref="E15:J15" si="2">E14/20</f>
         <v>0</v>
       </c>
       <c r="F15" s="37">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G15" s="37"/>
       <c r="H15" s="37">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I15" s="37">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J15" s="37">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K15" s="37"/>
@@ -13959,28 +14786,28 @@
         <v>0</v>
       </c>
       <c r="D16" s="37">
-        <f t="shared" ref="D16:J16" si="2">D15+D14</f>
+        <f t="shared" ref="D16:J16" si="3">D15+D14</f>
         <v>0</v>
       </c>
       <c r="E16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G16" s="37"/>
       <c r="H16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K16" s="37"/>
@@ -14154,6 +14981,9 @@
       <c r="K7" s="12" t="s">
         <v>8</v>
       </c>
+      <c r="L7" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="27"/>
@@ -14167,6 +14997,10 @@
       <c r="I8" s="29"/>
       <c r="J8" s="29"/>
       <c r="K8" s="29"/>
+      <c r="L8">
+        <f>SUM(C8:F8,H8,I8,J8)/40</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" s="27"/>
@@ -14180,6 +15014,10 @@
       <c r="I9" s="29"/>
       <c r="J9" s="29"/>
       <c r="K9" s="29"/>
+      <c r="L9">
+        <f t="shared" ref="L9:L12" si="0">SUM(C9:F9,H9,I9,J9)/40</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
@@ -14193,6 +15031,10 @@
       <c r="I10" s="29"/>
       <c r="J10" s="29"/>
       <c r="K10" s="29"/>
+      <c r="L10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
@@ -14206,6 +15048,10 @@
       <c r="I11" s="29"/>
       <c r="J11" s="29"/>
       <c r="K11" s="29"/>
+      <c r="L11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
@@ -14219,6 +15065,10 @@
       <c r="I12" s="29"/>
       <c r="J12" s="29"/>
       <c r="K12" s="29"/>
+      <c r="L12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
@@ -14237,39 +15087,39 @@
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:K14" si="0">SUM(C8:C13)</f>
+        <f t="shared" ref="C14:K14" si="1">SUM(C8:C13)</f>
         <v>0</v>
       </c>
       <c r="D14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="E14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L14" s="36">
@@ -14288,24 +15138,24 @@
         <v>0</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:J15" si="1">E14/20</f>
+        <f t="shared" ref="E15:J15" si="2">E14/20</f>
         <v>0</v>
       </c>
       <c r="F15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K15" s="13"/>
@@ -14320,28 +15170,28 @@
         <v>0</v>
       </c>
       <c r="D16" s="37">
-        <f t="shared" ref="D16:J16" si="2">D15+D14</f>
+        <f t="shared" ref="D16:J16" si="3">D15+D14</f>
         <v>0</v>
       </c>
       <c r="E16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G16" s="37"/>
       <c r="H16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K16" s="37"/>
@@ -14356,28 +15206,28 @@
         <v>0</v>
       </c>
       <c r="D17" s="37">
-        <f t="shared" ref="D17:J17" si="3">D14/40</f>
+        <f t="shared" ref="D17:J17" si="4">D14/40</f>
         <v>0</v>
       </c>
       <c r="E17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G17" s="37"/>
       <c r="H17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K17" s="37"/>
@@ -14549,6 +15399,9 @@
       <c r="K7" s="12" t="s">
         <v>8</v>
       </c>
+      <c r="L7" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="27">
@@ -14582,6 +15435,10 @@
       <c r="K8" s="28">
         <v>9</v>
       </c>
+      <c r="L8">
+        <f>SUM(C8:F8,H8,I8,J8)/40</f>
+        <v>10.050000000000001</v>
+      </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" s="27">
@@ -14617,6 +15474,10 @@
       <c r="K9" s="28">
         <v>13</v>
       </c>
+      <c r="L9">
+        <f t="shared" ref="L9:L12" si="0">SUM(C9:F9,H9,I9,J9)/40</f>
+        <v>15.8</v>
+      </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" s="27">
@@ -14651,6 +15512,10 @@
       </c>
       <c r="K10" s="28">
         <v>24</v>
+      </c>
+      <c r="L10">
+        <f t="shared" si="0"/>
+        <v>25.5</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
@@ -14665,6 +15530,10 @@
       <c r="I11" s="12"/>
       <c r="J11" s="12"/>
       <c r="K11" s="12"/>
+      <c r="L11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
@@ -14678,6 +15547,10 @@
       <c r="I12" s="12"/>
       <c r="J12" s="12"/>
       <c r="K12" s="12"/>
+      <c r="L12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
@@ -14696,39 +15569,39 @@
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:K14" si="0">SUM(C8:C13)</f>
+        <f t="shared" ref="C14:K14" si="1">SUM(C8:C13)</f>
         <v>172</v>
       </c>
       <c r="D14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>411</v>
       </c>
       <c r="E14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>280</v>
       </c>
       <c r="F14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>259</v>
       </c>
       <c r="G14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>47</v>
       </c>
       <c r="H14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>308</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>230</v>
       </c>
       <c r="J14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>394</v>
       </c>
       <c r="K14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>46</v>
       </c>
       <c r="L14" s="36">
@@ -14747,24 +15620,24 @@
         <v>20.55</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:J15" si="1">E14/20</f>
+        <f t="shared" ref="E15:J15" si="2">E14/20</f>
         <v>14</v>
       </c>
       <c r="F15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>12.95</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>15.4</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>11.5</v>
       </c>
       <c r="J15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>19.7</v>
       </c>
       <c r="K15" s="13"/>
@@ -14779,28 +15652,28 @@
         <v>172</v>
       </c>
       <c r="D16" s="37">
-        <f t="shared" ref="D16:J16" si="2">D15+D14</f>
+        <f t="shared" ref="D16:J16" si="3">D15+D14</f>
         <v>431.55</v>
       </c>
       <c r="E16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>294</v>
       </c>
       <c r="F16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>271.95</v>
       </c>
       <c r="G16" s="37"/>
       <c r="H16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>323.39999999999998</v>
       </c>
       <c r="I16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>241.5</v>
       </c>
       <c r="J16" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>413.7</v>
       </c>
       <c r="K16" s="37"/>
@@ -14815,28 +15688,28 @@
         <v>4.3</v>
       </c>
       <c r="D17" s="37">
-        <f t="shared" ref="D17:J17" si="3">D14/40</f>
+        <f t="shared" ref="D17:J17" si="4">D14/40</f>
         <v>10.275</v>
       </c>
       <c r="E17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>7</v>
       </c>
       <c r="F17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>6.4749999999999996</v>
       </c>
       <c r="G17" s="37"/>
       <c r="H17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>7.7</v>
       </c>
       <c r="I17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5.75</v>
       </c>
       <c r="J17" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>9.85</v>
       </c>
       <c r="K17" s="37"/>

--- a/Final Execution SKU wise.xlsx
+++ b/Final Execution SKU wise.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81233A15-C6E9-49CF-85DC-B233163C042E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEAD9106-5A21-4481-8159-46552178BC53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" activeTab="14" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" activeTab="17" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
   </bookViews>
   <sheets>
     <sheet name="last month" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="62">
   <si>
     <t>Gate Pass</t>
   </si>
@@ -240,6 +240,9 @@
   <si>
     <t xml:space="preserve">Furqan </t>
   </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
 </sst>
 </file>
 
@@ -300,7 +303,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -337,8 +340,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="28">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -671,11 +680,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
@@ -781,6 +799,16 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -817,10 +845,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1166,57 +1193,57 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="49"/>
+      <c r="B2" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="53"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="52"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="55"/>
+      <c r="K3" s="56"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="50"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="52"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="55"/>
+      <c r="K4" s="56"/>
     </row>
     <row r="5" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="53"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="55"/>
+      <c r="B5" s="57"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="58"/>
+      <c r="H5" s="58"/>
+      <c r="I5" s="58"/>
+      <c r="J5" s="58"/>
+      <c r="K5" s="59"/>
     </row>
     <row r="6" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="1"/>
@@ -1224,18 +1251,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="56" t="s">
+      <c r="D6" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="57" t="s">
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="57"/>
-      <c r="J6" s="57"/>
-      <c r="K6" s="58"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="62"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
@@ -1536,57 +1563,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="49"/>
+      <c r="B2" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="53"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="52"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="55"/>
+      <c r="K3" s="56"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="50"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="52"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="55"/>
+      <c r="K4" s="56"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="53"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="55"/>
+      <c r="B5" s="57"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="58"/>
+      <c r="H5" s="58"/>
+      <c r="I5" s="58"/>
+      <c r="J5" s="58"/>
+      <c r="K5" s="59"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -1594,18 +1621,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="56" t="s">
+      <c r="D6" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="57" t="s">
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="57"/>
-      <c r="J6" s="57"/>
-      <c r="K6" s="58"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="62"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -2066,57 +2093,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="49"/>
+      <c r="B2" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="53"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="52"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="55"/>
+      <c r="K3" s="56"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="50"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="52"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="55"/>
+      <c r="K4" s="56"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="53"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="55"/>
+      <c r="B5" s="57"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="58"/>
+      <c r="H5" s="58"/>
+      <c r="I5" s="58"/>
+      <c r="J5" s="58"/>
+      <c r="K5" s="59"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -2124,18 +2151,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="56" t="s">
+      <c r="D6" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="57" t="s">
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="57"/>
-      <c r="J6" s="57"/>
-      <c r="K6" s="58"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="62"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -2520,57 +2547,57 @@
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="49"/>
+      <c r="B2" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="53"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="52"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="55"/>
+      <c r="K3" s="56"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="50"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="52"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="55"/>
+      <c r="K4" s="56"/>
     </row>
     <row r="5" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="53"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="55"/>
+      <c r="B5" s="57"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="58"/>
+      <c r="H5" s="58"/>
+      <c r="I5" s="58"/>
+      <c r="J5" s="58"/>
+      <c r="K5" s="59"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -2578,18 +2605,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="56" t="s">
+      <c r="D6" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="57" t="s">
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="57"/>
-      <c r="J6" s="57"/>
-      <c r="K6" s="58"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="62"/>
       <c r="Q6" s="33" t="s">
         <v>35</v>
       </c>
@@ -3038,57 +3065,57 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="49"/>
+      <c r="B2" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="53"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="52"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="55"/>
+      <c r="K3" s="56"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="50"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="52"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="55"/>
+      <c r="K4" s="56"/>
     </row>
     <row r="5" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="53"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="55"/>
+      <c r="B5" s="57"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="58"/>
+      <c r="H5" s="58"/>
+      <c r="I5" s="58"/>
+      <c r="J5" s="58"/>
+      <c r="K5" s="59"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -3096,18 +3123,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="56" t="s">
+      <c r="D6" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="57" t="s">
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="57"/>
-      <c r="J6" s="57"/>
-      <c r="K6" s="58"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="62"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -3528,57 +3555,57 @@
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="49"/>
+      <c r="B2" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="53"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="52"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="55"/>
+      <c r="K3" s="56"/>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="50"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="52"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="55"/>
+      <c r="K4" s="56"/>
     </row>
     <row r="5" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="53"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="55"/>
+      <c r="B5" s="57"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="58"/>
+      <c r="H5" s="58"/>
+      <c r="I5" s="58"/>
+      <c r="J5" s="58"/>
+      <c r="K5" s="59"/>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -3586,18 +3613,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="56" t="s">
+      <c r="D6" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="57" t="s">
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="57"/>
-      <c r="J6" s="57"/>
-      <c r="K6" s="58"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="62"/>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -4195,57 +4222,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="49"/>
+      <c r="B2" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="53"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="52"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="55"/>
+      <c r="K3" s="56"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="50"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="52"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="55"/>
+      <c r="K4" s="56"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="53"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="55"/>
+      <c r="B5" s="57"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="58"/>
+      <c r="H5" s="58"/>
+      <c r="I5" s="58"/>
+      <c r="J5" s="58"/>
+      <c r="K5" s="59"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -4253,18 +4280,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="56" t="s">
+      <c r="D6" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="57" t="s">
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="57"/>
-      <c r="J6" s="57"/>
-      <c r="K6" s="58"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="62"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -4306,7 +4333,7 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="27"/>
-      <c r="B8" s="60"/>
+      <c r="B8" s="48"/>
       <c r="C8" s="29"/>
       <c r="D8" s="29"/>
       <c r="E8" s="29"/>
@@ -4329,7 +4356,7 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" s="27"/>
-      <c r="B9" s="60"/>
+      <c r="B9" s="48"/>
       <c r="C9" s="29"/>
       <c r="D9" s="29"/>
       <c r="E9" s="29"/>
@@ -4346,7 +4373,7 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
-      <c r="B10" s="60"/>
+      <c r="B10" s="48"/>
       <c r="C10" s="29"/>
       <c r="D10" s="29"/>
       <c r="E10" s="29"/>
@@ -4619,57 +4646,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="49"/>
+      <c r="B2" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="53"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="52"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="55"/>
+      <c r="K3" s="56"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="50"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="52"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="55"/>
+      <c r="K4" s="56"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="53"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="55"/>
+      <c r="B5" s="57"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="58"/>
+      <c r="H5" s="58"/>
+      <c r="I5" s="58"/>
+      <c r="J5" s="58"/>
+      <c r="K5" s="59"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -4677,18 +4704,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="56" t="s">
+      <c r="D6" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="57" t="s">
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="57"/>
-      <c r="J6" s="57"/>
-      <c r="K6" s="58"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="62"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -4724,7 +4751,7 @@
       <c r="K7" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="L7" s="59" t="s">
+      <c r="L7" s="47" t="s">
         <v>59</v>
       </c>
     </row>
@@ -5085,57 +5112,57 @@
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="49"/>
+      <c r="B2" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="53"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="52"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="55"/>
+      <c r="K3" s="56"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="50"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="52"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="55"/>
+      <c r="K4" s="56"/>
     </row>
     <row r="5" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="53"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="55"/>
+      <c r="B5" s="57"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="58"/>
+      <c r="H5" s="58"/>
+      <c r="I5" s="58"/>
+      <c r="J5" s="58"/>
+      <c r="K5" s="59"/>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -5143,18 +5170,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="56" t="s">
+      <c r="D6" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="57" t="s">
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="57"/>
-      <c r="J6" s="57"/>
-      <c r="K6" s="58"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="62"/>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -5192,6 +5219,9 @@
       </c>
       <c r="L7" t="s">
         <v>59</v>
+      </c>
+      <c r="M7" t="s">
+        <v>58</v>
       </c>
       <c r="O7" s="41"/>
       <c r="P7" s="41" t="s">
@@ -5239,6 +5269,9 @@
         <f>SUM(C8:F8,H8,I8,J8)/40</f>
         <v>13.6</v>
       </c>
+      <c r="M8" s="49">
+        <v>5</v>
+      </c>
       <c r="O8" s="41" t="s">
         <v>9</v>
       </c>
@@ -5287,6 +5320,9 @@
         <f t="shared" ref="L9:L12" si="2">SUM(C9:F9,H9,I9,J9)/40</f>
         <v>8.9</v>
       </c>
+      <c r="M9" s="49">
+        <v>9</v>
+      </c>
       <c r="O9" s="41" t="s">
         <v>11</v>
       </c>
@@ -5334,6 +5370,9 @@
       <c r="L10">
         <f t="shared" si="2"/>
         <v>7.55</v>
+      </c>
+      <c r="M10" s="49">
+        <v>6</v>
       </c>
       <c r="O10" s="41" t="s">
         <v>60</v>
@@ -5573,7 +5612,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{257F4DF8-C865-4EAB-87FC-B54CA70AD20E}">
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.90625" bestFit="1" customWidth="1"/>
@@ -5588,7 +5627,7 @@
     <col min="11" max="11" width="5.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5601,80 +5640,80 @@
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="49"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B2" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="53"/>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="52"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B3" s="54"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="55"/>
+      <c r="K3" s="56"/>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="50"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="52"/>
-    </row>
-    <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B4" s="54"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="55"/>
+      <c r="K4" s="56"/>
+    </row>
+    <row r="5" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="53"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="55"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B5" s="57"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="58"/>
+      <c r="H5" s="58"/>
+      <c r="I5" s="58"/>
+      <c r="J5" s="58"/>
+      <c r="K5" s="59"/>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
       <c r="B6" s="2"/>
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="56" t="s">
+      <c r="D6" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="57" t="s">
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="57"/>
-      <c r="J6" s="57"/>
-      <c r="K6" s="58"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="I6" s="61"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="62"/>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
         <v>4</v>
       </c>
@@ -5708,68 +5747,143 @@
       <c r="K7" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="L7" t="s">
+      <c r="L7" s="50" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M7" s="50" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8" s="27"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
+      <c r="B8" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="12">
+        <v>24</v>
+      </c>
+      <c r="D8" s="12">
+        <v>54</v>
+      </c>
+      <c r="E8" s="12">
+        <v>25</v>
+      </c>
+      <c r="F8" s="12">
+        <v>25</v>
+      </c>
       <c r="G8" s="28">
         <f>SUM(D8:F8)/20</f>
-        <v>0</v>
-      </c>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="12"/>
+        <v>5.2</v>
+      </c>
+      <c r="H8" s="12">
+        <v>111</v>
+      </c>
+      <c r="I8" s="12">
+        <v>76</v>
+      </c>
+      <c r="J8" s="12">
+        <v>111</v>
+      </c>
       <c r="K8" s="28">
         <f>SUM(H8:J8)/20</f>
-        <v>0</v>
-      </c>
-      <c r="L8">
+        <v>14.9</v>
+      </c>
+      <c r="L8" s="63">
         <f>SUM(C8:F8,H8,I8,J8)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+        <v>10.65</v>
+      </c>
+      <c r="M8" s="63">
+        <v>7</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9" s="27"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12"/>
-      <c r="K9" s="28"/>
-      <c r="L9">
-        <f t="shared" ref="L9:L12" si="0">SUM(C9:F9,H9,I9,J9)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B9" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="12">
+        <v>124</v>
+      </c>
+      <c r="D9" s="12">
+        <v>40</v>
+      </c>
+      <c r="E9" s="12">
+        <v>55</v>
+      </c>
+      <c r="F9" s="12">
+        <v>55</v>
+      </c>
+      <c r="G9" s="28">
+        <f t="shared" ref="G9:G10" si="0">SUM(D9:F9)/20</f>
+        <v>7.5</v>
+      </c>
+      <c r="H9" s="12">
+        <v>30</v>
+      </c>
+      <c r="I9" s="12">
+        <v>20</v>
+      </c>
+      <c r="J9" s="12">
+        <v>10</v>
+      </c>
+      <c r="K9" s="28">
+        <f t="shared" ref="K9:K10" si="1">SUM(H9:J9)/20</f>
+        <v>3</v>
+      </c>
+      <c r="L9" s="63">
+        <f t="shared" ref="L9:L12" si="2">SUM(C9:F9,H9,I9,J9)/40</f>
+        <v>8.35</v>
+      </c>
+      <c r="M9" s="63">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="28"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="28"/>
-      <c r="L10">
+      <c r="B10" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="12">
+        <v>210</v>
+      </c>
+      <c r="D10" s="12">
+        <v>340</v>
+      </c>
+      <c r="E10" s="12">
+        <v>320</v>
+      </c>
+      <c r="F10" s="12">
+        <v>160</v>
+      </c>
+      <c r="G10" s="28">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+        <v>41</v>
+      </c>
+      <c r="H10" s="12">
+        <v>335</v>
+      </c>
+      <c r="I10" s="12">
+        <v>290</v>
+      </c>
+      <c r="J10" s="12">
+        <v>495</v>
+      </c>
+      <c r="K10" s="28">
+        <f t="shared" si="1"/>
+        <v>56</v>
+      </c>
+      <c r="L10" s="63">
+        <f t="shared" si="2"/>
+        <v>53.75</v>
+      </c>
+      <c r="M10" s="63">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11"/>
       <c r="C11" s="12"/>
@@ -5781,12 +5895,13 @@
       <c r="I11" s="12"/>
       <c r="J11" s="12"/>
       <c r="K11" s="12"/>
-      <c r="L11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="L11" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M11" s="41"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
       <c r="B12" s="11"/>
       <c r="C12" s="12"/>
@@ -5798,12 +5913,13 @@
       <c r="I12" s="12"/>
       <c r="J12" s="12"/>
       <c r="K12" s="12"/>
-      <c r="L12">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="L12" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M12" s="41"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
       <c r="B13" s="11"/>
       <c r="C13" s="12"/>
@@ -5815,52 +5931,54 @@
       <c r="I13" s="12"/>
       <c r="J13" s="12"/>
       <c r="K13" s="12"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="L13" s="41"/>
+      <c r="M13" s="41"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:K14" si="1">SUM(C8:C13)</f>
-        <v>0</v>
+        <f t="shared" ref="C14:K14" si="3">SUM(C8:C13)</f>
+        <v>358</v>
       </c>
       <c r="D14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>434</v>
       </c>
       <c r="E14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>400</v>
       </c>
       <c r="F14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>240</v>
       </c>
       <c r="G14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>53.7</v>
       </c>
       <c r="H14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>476</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>386</v>
       </c>
       <c r="J14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>616</v>
       </c>
       <c r="K14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>73.900000000000006</v>
       </c>
       <c r="L14" s="36">
         <f>C14+D14+E14+F14+H14+I14+J14</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+        <v>2910</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15" s="13"/>
       <c r="B15" s="10" t="s">
         <v>40</v>
@@ -5868,64 +5986,64 @@
       <c r="C15" s="13"/>
       <c r="D15" s="13">
         <f>D14/20</f>
-        <v>0</v>
+        <v>21.7</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:J15" si="2">E14/20</f>
-        <v>0</v>
+        <f t="shared" ref="E15:J15" si="4">E14/20</f>
+        <v>20</v>
       </c>
       <c r="F15" s="13">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>12</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>23.8</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>19.3</v>
       </c>
       <c r="J15" s="13">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>30.8</v>
       </c>
       <c r="K15" s="13"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16" s="13"/>
       <c r="B16" s="10" t="s">
         <v>39</v>
       </c>
       <c r="C16" s="37">
         <f>C15+C14</f>
-        <v>0</v>
+        <v>358</v>
       </c>
       <c r="D16" s="37">
-        <f t="shared" ref="D16:J16" si="3">D15+D14</f>
-        <v>0</v>
+        <f t="shared" ref="D16:J16" si="5">D15+D14</f>
+        <v>455.7</v>
       </c>
       <c r="E16" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>420</v>
       </c>
       <c r="F16" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>252</v>
       </c>
       <c r="G16" s="37"/>
       <c r="H16" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>499.8</v>
       </c>
       <c r="I16" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>405.3</v>
       </c>
       <c r="J16" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>646.79999999999995</v>
       </c>
       <c r="K16" s="37"/>
     </row>
@@ -5936,37 +6054,37 @@
       </c>
       <c r="C17" s="37">
         <f>C14/40</f>
-        <v>0</v>
+        <v>8.9499999999999993</v>
       </c>
       <c r="D17" s="37">
-        <f t="shared" ref="D17:J17" si="4">D14/40</f>
-        <v>0</v>
+        <f t="shared" ref="D17:J17" si="6">D14/40</f>
+        <v>10.85</v>
       </c>
       <c r="E17" s="37">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>10</v>
       </c>
       <c r="F17" s="37">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>6</v>
       </c>
       <c r="G17" s="37"/>
       <c r="H17" s="37">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>11.9</v>
       </c>
       <c r="I17" s="37">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>9.65</v>
       </c>
       <c r="J17" s="37">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>15.4</v>
       </c>
       <c r="K17" s="37"/>
       <c r="L17" s="36">
         <f>SUM(C17:J17)</f>
-        <v>0</v>
+        <v>72.75</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">
@@ -6027,57 +6145,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="49"/>
+      <c r="B2" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="53"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="52"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="55"/>
+      <c r="K3" s="56"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="50"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="52"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="55"/>
+      <c r="K4" s="56"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="53"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="55"/>
+      <c r="B5" s="57"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="58"/>
+      <c r="H5" s="58"/>
+      <c r="I5" s="58"/>
+      <c r="J5" s="58"/>
+      <c r="K5" s="59"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -6085,18 +6203,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="56" t="s">
+      <c r="D6" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="57" t="s">
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="57"/>
-      <c r="J6" s="57"/>
-      <c r="K6" s="58"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="62"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -6451,57 +6569,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="49"/>
+      <c r="B2" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="53"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="52"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="55"/>
+      <c r="K3" s="56"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="50"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="52"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="55"/>
+      <c r="K4" s="56"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="53"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="55"/>
+      <c r="B5" s="57"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="58"/>
+      <c r="H5" s="58"/>
+      <c r="I5" s="58"/>
+      <c r="J5" s="58"/>
+      <c r="K5" s="59"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -6509,18 +6627,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="56" t="s">
+      <c r="D6" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="57" t="s">
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="57"/>
-      <c r="J6" s="57"/>
-      <c r="K6" s="58"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="62"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -6923,57 +7041,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="49"/>
+      <c r="B2" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="53"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="52"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="55"/>
+      <c r="K3" s="56"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="50"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="52"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="55"/>
+      <c r="K4" s="56"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="53"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="55"/>
+      <c r="B5" s="57"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="58"/>
+      <c r="H5" s="58"/>
+      <c r="I5" s="58"/>
+      <c r="J5" s="58"/>
+      <c r="K5" s="59"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -6981,18 +7099,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="56" t="s">
+      <c r="D6" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="57" t="s">
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="57"/>
-      <c r="J6" s="57"/>
-      <c r="K6" s="58"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="62"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -7347,57 +7465,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="49"/>
+      <c r="B2" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="53"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="52"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="55"/>
+      <c r="K3" s="56"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="50"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="52"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="55"/>
+      <c r="K4" s="56"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="53"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="55"/>
+      <c r="B5" s="57"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="58"/>
+      <c r="H5" s="58"/>
+      <c r="I5" s="58"/>
+      <c r="J5" s="58"/>
+      <c r="K5" s="59"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -7405,18 +7523,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="56" t="s">
+      <c r="D6" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="57" t="s">
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="57"/>
-      <c r="J6" s="57"/>
-      <c r="K6" s="58"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="62"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -7771,57 +7889,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="49"/>
+      <c r="B2" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="53"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="52"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="55"/>
+      <c r="K3" s="56"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="50"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="52"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="55"/>
+      <c r="K4" s="56"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="53"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="55"/>
+      <c r="B5" s="57"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="58"/>
+      <c r="H5" s="58"/>
+      <c r="I5" s="58"/>
+      <c r="J5" s="58"/>
+      <c r="K5" s="59"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -7829,18 +7947,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="56" t="s">
+      <c r="D6" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="57" t="s">
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="57"/>
-      <c r="J6" s="57"/>
-      <c r="K6" s="58"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="62"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -8195,57 +8313,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="49"/>
+      <c r="B2" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="53"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="52"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="55"/>
+      <c r="K3" s="56"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="50"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="52"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="55"/>
+      <c r="K4" s="56"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="53"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="55"/>
+      <c r="B5" s="57"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="58"/>
+      <c r="H5" s="58"/>
+      <c r="I5" s="58"/>
+      <c r="J5" s="58"/>
+      <c r="K5" s="59"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -8253,18 +8371,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="56" t="s">
+      <c r="D6" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="57" t="s">
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="57"/>
-      <c r="J6" s="57"/>
-      <c r="K6" s="58"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="62"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -8619,57 +8737,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="49"/>
+      <c r="B2" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="53"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="52"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="55"/>
+      <c r="K3" s="56"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="50"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="52"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="55"/>
+      <c r="K4" s="56"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="53"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="55"/>
+      <c r="B5" s="57"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="58"/>
+      <c r="H5" s="58"/>
+      <c r="I5" s="58"/>
+      <c r="J5" s="58"/>
+      <c r="K5" s="59"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -8677,18 +8795,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="56" t="s">
+      <c r="D6" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="57" t="s">
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="57"/>
-      <c r="J6" s="57"/>
-      <c r="K6" s="58"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="62"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -9043,57 +9161,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="49"/>
+      <c r="B2" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="53"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="52"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="55"/>
+      <c r="K3" s="56"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="50"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="52"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="55"/>
+      <c r="K4" s="56"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="53"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="55"/>
+      <c r="B5" s="57"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="58"/>
+      <c r="H5" s="58"/>
+      <c r="I5" s="58"/>
+      <c r="J5" s="58"/>
+      <c r="K5" s="59"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -9101,18 +9219,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="56" t="s">
+      <c r="D6" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="57" t="s">
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="57"/>
-      <c r="J6" s="57"/>
-      <c r="K6" s="58"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="62"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -9467,57 +9585,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="49"/>
+      <c r="B2" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="53"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="52"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="55"/>
+      <c r="K3" s="56"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="50"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="52"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="55"/>
+      <c r="K4" s="56"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="53"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="55"/>
+      <c r="B5" s="57"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="58"/>
+      <c r="H5" s="58"/>
+      <c r="I5" s="58"/>
+      <c r="J5" s="58"/>
+      <c r="K5" s="59"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -9525,18 +9643,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="56" t="s">
+      <c r="D6" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="57" t="s">
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="57"/>
-      <c r="J6" s="57"/>
-      <c r="K6" s="58"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="62"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -9891,57 +10009,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="49"/>
+      <c r="B2" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="53"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="52"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="55"/>
+      <c r="K3" s="56"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="50"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="52"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="55"/>
+      <c r="K4" s="56"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="53"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="55"/>
+      <c r="B5" s="57"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="58"/>
+      <c r="H5" s="58"/>
+      <c r="I5" s="58"/>
+      <c r="J5" s="58"/>
+      <c r="K5" s="59"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -9949,18 +10067,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="56" t="s">
+      <c r="D6" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="57" t="s">
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="57"/>
-      <c r="J6" s="57"/>
-      <c r="K6" s="58"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="62"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -10315,57 +10433,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="49"/>
+      <c r="B2" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="53"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="52"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="55"/>
+      <c r="K3" s="56"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="50"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="52"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="55"/>
+      <c r="K4" s="56"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="53"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="55"/>
+      <c r="B5" s="57"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="58"/>
+      <c r="H5" s="58"/>
+      <c r="I5" s="58"/>
+      <c r="J5" s="58"/>
+      <c r="K5" s="59"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -10373,18 +10491,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="56" t="s">
+      <c r="D6" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="57" t="s">
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="57"/>
-      <c r="J6" s="57"/>
-      <c r="K6" s="58"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="62"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -10739,57 +10857,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="49"/>
+      <c r="B2" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="53"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="52"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="55"/>
+      <c r="K3" s="56"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="50"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="52"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="55"/>
+      <c r="K4" s="56"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="53"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="55"/>
+      <c r="B5" s="57"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="58"/>
+      <c r="H5" s="58"/>
+      <c r="I5" s="58"/>
+      <c r="J5" s="58"/>
+      <c r="K5" s="59"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -10797,18 +10915,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="56" t="s">
+      <c r="D6" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="57" t="s">
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="57"/>
-      <c r="J6" s="57"/>
-      <c r="K6" s="58"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="62"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -11163,57 +11281,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="49"/>
+      <c r="B2" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="53"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="52"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="55"/>
+      <c r="K3" s="56"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="50"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="52"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="55"/>
+      <c r="K4" s="56"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="53"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="55"/>
+      <c r="B5" s="57"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="58"/>
+      <c r="H5" s="58"/>
+      <c r="I5" s="58"/>
+      <c r="J5" s="58"/>
+      <c r="K5" s="59"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -11221,18 +11339,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="56" t="s">
+      <c r="D6" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="57" t="s">
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="57"/>
-      <c r="J6" s="57"/>
-      <c r="K6" s="58"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="62"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -11649,57 +11767,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="49"/>
+      <c r="B2" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="53"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="52"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="55"/>
+      <c r="K3" s="56"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="50"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="52"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="55"/>
+      <c r="K4" s="56"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="53"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="55"/>
+      <c r="B5" s="57"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="58"/>
+      <c r="H5" s="58"/>
+      <c r="I5" s="58"/>
+      <c r="J5" s="58"/>
+      <c r="K5" s="59"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -11707,18 +11825,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="56" t="s">
+      <c r="D6" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="57" t="s">
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="57"/>
-      <c r="J6" s="57"/>
-      <c r="K6" s="58"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="62"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -12073,57 +12191,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="49"/>
+      <c r="B2" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="53"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="52"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="55"/>
+      <c r="K3" s="56"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="50"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="52"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="55"/>
+      <c r="K4" s="56"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="53"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="55"/>
+      <c r="B5" s="57"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="58"/>
+      <c r="H5" s="58"/>
+      <c r="I5" s="58"/>
+      <c r="J5" s="58"/>
+      <c r="K5" s="59"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -12131,18 +12249,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="56" t="s">
+      <c r="D6" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="57" t="s">
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="57"/>
-      <c r="J6" s="57"/>
-      <c r="K6" s="58"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="62"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -12498,57 +12616,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="49"/>
+      <c r="B2" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="53"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="52"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="55"/>
+      <c r="K3" s="56"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="50"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="52"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="55"/>
+      <c r="K4" s="56"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="53"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="55"/>
+      <c r="B5" s="57"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="58"/>
+      <c r="H5" s="58"/>
+      <c r="I5" s="58"/>
+      <c r="J5" s="58"/>
+      <c r="K5" s="59"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -12556,18 +12674,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="56" t="s">
+      <c r="D6" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="57" t="s">
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="57"/>
-      <c r="J6" s="57"/>
-      <c r="K6" s="58"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="62"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -12922,57 +13040,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="49"/>
+      <c r="B2" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="53"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="52"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="55"/>
+      <c r="K3" s="56"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="50"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="52"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="55"/>
+      <c r="K4" s="56"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="53"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="55"/>
+      <c r="B5" s="57"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="58"/>
+      <c r="H5" s="58"/>
+      <c r="I5" s="58"/>
+      <c r="J5" s="58"/>
+      <c r="K5" s="59"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -12980,18 +13098,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="56" t="s">
+      <c r="D6" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="57" t="s">
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="57"/>
-      <c r="J6" s="57"/>
-      <c r="K6" s="58"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="62"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -13461,57 +13579,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="49"/>
+      <c r="B2" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="53"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="52"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="55"/>
+      <c r="K3" s="56"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="50"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="52"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="55"/>
+      <c r="K4" s="56"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="53"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="55"/>
+      <c r="B5" s="57"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="58"/>
+      <c r="H5" s="58"/>
+      <c r="I5" s="58"/>
+      <c r="J5" s="58"/>
+      <c r="K5" s="59"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -13519,18 +13637,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="56" t="s">
+      <c r="D6" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="57" t="s">
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="57"/>
-      <c r="J6" s="57"/>
-      <c r="K6" s="58"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="62"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -13972,57 +14090,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="49"/>
+      <c r="B2" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="53"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="52"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="55"/>
+      <c r="K3" s="56"/>
     </row>
     <row r="4" spans="1:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="50"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="52"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="55"/>
+      <c r="K4" s="56"/>
     </row>
     <row r="5" spans="1:12" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="53"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="55"/>
+      <c r="B5" s="57"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="58"/>
+      <c r="H5" s="58"/>
+      <c r="I5" s="58"/>
+      <c r="J5" s="58"/>
+      <c r="K5" s="59"/>
     </row>
     <row r="6" spans="1:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -14030,18 +14148,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="56" t="s">
+      <c r="D6" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="57" t="s">
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="57"/>
-      <c r="J6" s="57"/>
-      <c r="K6" s="58"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="62"/>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -14448,57 +14566,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="49"/>
+      <c r="B2" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="53"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="52"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="55"/>
+      <c r="K3" s="56"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="50"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="52"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="55"/>
+      <c r="K4" s="56"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="53"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="55"/>
+      <c r="B5" s="57"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="58"/>
+      <c r="H5" s="58"/>
+      <c r="I5" s="58"/>
+      <c r="J5" s="58"/>
+      <c r="K5" s="59"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -14506,18 +14624,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="56" t="s">
+      <c r="D6" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="57" t="s">
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="57"/>
-      <c r="J6" s="57"/>
-      <c r="K6" s="58"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="62"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -14876,57 +14994,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="49"/>
+      <c r="B2" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="53"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="52"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="55"/>
+      <c r="K3" s="56"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="50"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="52"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="55"/>
+      <c r="K4" s="56"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="53"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="55"/>
+      <c r="B5" s="57"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="58"/>
+      <c r="H5" s="58"/>
+      <c r="I5" s="58"/>
+      <c r="J5" s="58"/>
+      <c r="K5" s="59"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -14934,18 +15052,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="56" t="s">
+      <c r="D6" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="57" t="s">
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="57"/>
-      <c r="J6" s="57"/>
-      <c r="K6" s="58"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="62"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -15294,57 +15412,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="49"/>
+      <c r="B2" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="53"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="52"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="55"/>
+      <c r="K3" s="56"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="50"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="52"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="55"/>
+      <c r="K4" s="56"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="53"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="55"/>
+      <c r="B5" s="57"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="58"/>
+      <c r="H5" s="58"/>
+      <c r="I5" s="58"/>
+      <c r="J5" s="58"/>
+      <c r="K5" s="59"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -15352,18 +15470,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="56" t="s">
+      <c r="D6" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="57" t="s">
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="57"/>
-      <c r="J6" s="57"/>
-      <c r="K6" s="58"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="62"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">

--- a/Final Execution SKU wise.xlsx
+++ b/Final Execution SKU wise.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEAD9106-5A21-4481-8159-46552178BC53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ACB7BE5-A93A-47ED-A448-5DC1E0E4920A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" activeTab="17" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
   </bookViews>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="65">
   <si>
     <t>Gate Pass</t>
   </si>
@@ -242,6 +242,15 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>ok</t>
+  </si>
+  <si>
+    <t>opening</t>
+  </si>
+  <si>
+    <t>meat 70</t>
   </si>
 </sst>
 </file>
@@ -809,6 +818,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -844,9 +856,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1193,57 +1202,57 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="51" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="53"/>
+      <c r="B2" s="52" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="54"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="55"/>
-      <c r="K3" s="56"/>
+      <c r="B3" s="55"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="57"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55"/>
-      <c r="K4" s="56"/>
+      <c r="B4" s="55"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="57"/>
     </row>
     <row r="5" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="57"/>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="58"/>
-      <c r="I5" s="58"/>
-      <c r="J5" s="58"/>
-      <c r="K5" s="59"/>
+      <c r="B5" s="58"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="59"/>
+      <c r="K5" s="60"/>
     </row>
     <row r="6" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="1"/>
@@ -1251,18 +1260,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="60" t="s">
+      <c r="D6" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="61"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="61" t="s">
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="61"/>
-      <c r="J6" s="61"/>
-      <c r="K6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="62"/>
+      <c r="K6" s="63"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
@@ -1563,57 +1572,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="51" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="53"/>
+      <c r="B2" s="52" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="54"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="55"/>
-      <c r="K3" s="56"/>
+      <c r="B3" s="55"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="57"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55"/>
-      <c r="K4" s="56"/>
+      <c r="B4" s="55"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="57"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="57"/>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="58"/>
-      <c r="I5" s="58"/>
-      <c r="J5" s="58"/>
-      <c r="K5" s="59"/>
+      <c r="B5" s="58"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="59"/>
+      <c r="K5" s="60"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -1621,18 +1630,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="60" t="s">
+      <c r="D6" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="61"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="61" t="s">
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="61"/>
-      <c r="J6" s="61"/>
-      <c r="K6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="62"/>
+      <c r="K6" s="63"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -2093,57 +2102,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="51" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="53"/>
+      <c r="B2" s="52" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="54"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="55"/>
-      <c r="K3" s="56"/>
+      <c r="B3" s="55"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="57"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55"/>
-      <c r="K4" s="56"/>
+      <c r="B4" s="55"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="57"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="57"/>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="58"/>
-      <c r="I5" s="58"/>
-      <c r="J5" s="58"/>
-      <c r="K5" s="59"/>
+      <c r="B5" s="58"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="59"/>
+      <c r="K5" s="60"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -2151,18 +2160,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="60" t="s">
+      <c r="D6" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="61"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="61" t="s">
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="61"/>
-      <c r="J6" s="61"/>
-      <c r="K6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="62"/>
+      <c r="K6" s="63"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -2547,57 +2556,57 @@
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="51" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="53"/>
+      <c r="B2" s="52" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="54"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="55"/>
-      <c r="K3" s="56"/>
+      <c r="B3" s="55"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="57"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55"/>
-      <c r="K4" s="56"/>
+      <c r="B4" s="55"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="57"/>
     </row>
     <row r="5" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="57"/>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="58"/>
-      <c r="I5" s="58"/>
-      <c r="J5" s="58"/>
-      <c r="K5" s="59"/>
+      <c r="B5" s="58"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="59"/>
+      <c r="K5" s="60"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -2605,18 +2614,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="60" t="s">
+      <c r="D6" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="61"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="61" t="s">
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="61"/>
-      <c r="J6" s="61"/>
-      <c r="K6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="62"/>
+      <c r="K6" s="63"/>
       <c r="Q6" s="33" t="s">
         <v>35</v>
       </c>
@@ -3065,57 +3074,57 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="51" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="53"/>
+      <c r="B2" s="52" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="54"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="55"/>
-      <c r="K3" s="56"/>
+      <c r="B3" s="55"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="57"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55"/>
-      <c r="K4" s="56"/>
+      <c r="B4" s="55"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="57"/>
     </row>
     <row r="5" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="57"/>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="58"/>
-      <c r="I5" s="58"/>
-      <c r="J5" s="58"/>
-      <c r="K5" s="59"/>
+      <c r="B5" s="58"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="59"/>
+      <c r="K5" s="60"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -3123,18 +3132,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="60" t="s">
+      <c r="D6" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="61"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="61" t="s">
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="61"/>
-      <c r="J6" s="61"/>
-      <c r="K6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="62"/>
+      <c r="K6" s="63"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -3555,57 +3564,57 @@
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="51" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="53"/>
+      <c r="B2" s="52" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="54"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="55"/>
-      <c r="K3" s="56"/>
+      <c r="B3" s="55"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="57"/>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55"/>
-      <c r="K4" s="56"/>
+      <c r="B4" s="55"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="57"/>
     </row>
     <row r="5" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="57"/>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="58"/>
-      <c r="I5" s="58"/>
-      <c r="J5" s="58"/>
-      <c r="K5" s="59"/>
+      <c r="B5" s="58"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="59"/>
+      <c r="K5" s="60"/>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -3613,18 +3622,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="60" t="s">
+      <c r="D6" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="61"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="61" t="s">
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="61"/>
-      <c r="J6" s="61"/>
-      <c r="K6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="62"/>
+      <c r="K6" s="63"/>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -4222,57 +4231,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="51" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="53"/>
+      <c r="B2" s="52" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="54"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="55"/>
-      <c r="K3" s="56"/>
+      <c r="B3" s="55"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="57"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55"/>
-      <c r="K4" s="56"/>
+      <c r="B4" s="55"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="57"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="57"/>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="58"/>
-      <c r="I5" s="58"/>
-      <c r="J5" s="58"/>
-      <c r="K5" s="59"/>
+      <c r="B5" s="58"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="59"/>
+      <c r="K5" s="60"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -4280,18 +4289,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="60" t="s">
+      <c r="D6" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="61"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="61" t="s">
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="61"/>
-      <c r="J6" s="61"/>
-      <c r="K6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="62"/>
+      <c r="K6" s="63"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -4646,57 +4655,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="51" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="53"/>
+      <c r="B2" s="52" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="54"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="55"/>
-      <c r="K3" s="56"/>
+      <c r="B3" s="55"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="57"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55"/>
-      <c r="K4" s="56"/>
+      <c r="B4" s="55"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="57"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="57"/>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="58"/>
-      <c r="I5" s="58"/>
-      <c r="J5" s="58"/>
-      <c r="K5" s="59"/>
+      <c r="B5" s="58"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="59"/>
+      <c r="K5" s="60"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -4704,18 +4713,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="60" t="s">
+      <c r="D6" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="61"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="61" t="s">
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="61"/>
-      <c r="J6" s="61"/>
-      <c r="K6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="62"/>
+      <c r="K6" s="63"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -5082,7 +5091,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7A2FBED-8856-42CC-977B-5977D4F16323}">
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:R19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.90625" bestFit="1" customWidth="1"/>
@@ -5097,7 +5106,7 @@
     <col min="11" max="11" width="5.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5110,80 +5119,80 @@
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="51" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="53"/>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="B2" s="52" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="54"/>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="55"/>
-      <c r="K3" s="56"/>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="B3" s="55"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="57"/>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55"/>
-      <c r="K4" s="56"/>
-    </row>
-    <row r="5" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B4" s="55"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="57"/>
+    </row>
+    <row r="5" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="57"/>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="58"/>
-      <c r="I5" s="58"/>
-      <c r="J5" s="58"/>
-      <c r="K5" s="59"/>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="B5" s="58"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="59"/>
+      <c r="K5" s="60"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
       <c r="B6" s="2"/>
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="60" t="s">
+      <c r="D6" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="61"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="61" t="s">
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="61"/>
-      <c r="J6" s="61"/>
-      <c r="K6" s="62"/>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="I6" s="62"/>
+      <c r="J6" s="62"/>
+      <c r="K6" s="63"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
         <v>4</v>
       </c>
@@ -5231,7 +5240,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A8" s="27"/>
       <c r="B8" s="10" t="s">
         <v>9</v>
@@ -5281,44 +5290,45 @@
       <c r="Q8" s="41">
         <v>13.6</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="R8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A9" s="27"/>
       <c r="B9" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="12">
-        <v>24</v>
-      </c>
+      <c r="C9" s="12"/>
       <c r="D9" s="12">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="E9" s="12">
-        <v>62</v>
+        <v>12</v>
       </c>
       <c r="F9" s="12">
-        <v>62</v>
+        <v>12</v>
       </c>
       <c r="G9" s="28">
         <f t="shared" ref="G9:G10" si="0">SUM(D9:F9)/20</f>
-        <v>8.8000000000000007</v>
+        <v>1.8</v>
       </c>
       <c r="H9" s="12">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="I9" s="12">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="J9" s="12">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="K9" s="28">
         <f t="shared" ref="K9:K10" si="1">SUM(H9:J9)/20</f>
-        <v>7.8</v>
+        <v>5.75</v>
       </c>
       <c r="L9">
         <f t="shared" ref="L9:L12" si="2">SUM(C9:F9,H9,I9,J9)/40</f>
-        <v>8.9</v>
+        <v>3.7749999999999999</v>
       </c>
       <c r="M9" s="49">
         <v>9</v>
@@ -5327,19 +5337,22 @@
         <v>11</v>
       </c>
       <c r="P9" s="41">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Q9" s="41">
         <v>8.9</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="R9" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
         <v>60</v>
       </c>
       <c r="C10" s="12">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D10" s="12">
         <v>66</v>
@@ -5355,21 +5368,21 @@
         <v>8.6</v>
       </c>
       <c r="H10" s="12">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="I10" s="12">
         <v>5</v>
       </c>
       <c r="J10" s="12">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="K10" s="28">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L10">
         <f t="shared" si="2"/>
-        <v>7.55</v>
+        <v>5.4</v>
       </c>
       <c r="M10" s="49">
         <v>6</v>
@@ -5378,13 +5391,16 @@
         <v>60</v>
       </c>
       <c r="P10" s="41">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q10" s="41">
         <v>7.5</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="R10" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11"/>
       <c r="C11" s="12"/>
@@ -5401,7 +5417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
       <c r="B12" s="11"/>
       <c r="C12" s="12"/>
@@ -5418,7 +5434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
       <c r="B13" s="11"/>
       <c r="C13" s="12"/>
@@ -5431,51 +5447,51 @@
       <c r="J13" s="12"/>
       <c r="K13" s="12"/>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
         <f t="shared" ref="C14:K14" si="3">SUM(C8:C13)</f>
-        <v>198</v>
+        <v>168</v>
       </c>
       <c r="D14" s="14">
         <f t="shared" si="3"/>
-        <v>188</v>
+        <v>148</v>
       </c>
       <c r="E14" s="14">
         <f t="shared" si="3"/>
-        <v>198</v>
+        <v>148</v>
       </c>
       <c r="F14" s="14">
         <f t="shared" si="3"/>
-        <v>122</v>
+        <v>72</v>
       </c>
       <c r="G14" s="14">
         <f t="shared" si="3"/>
-        <v>25.4</v>
+        <v>18.399999999999999</v>
       </c>
       <c r="H14" s="14">
         <f t="shared" si="3"/>
-        <v>165</v>
+        <v>117</v>
       </c>
       <c r="I14" s="14">
         <f t="shared" si="3"/>
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="J14" s="14">
         <f t="shared" si="3"/>
-        <v>213</v>
+        <v>156</v>
       </c>
       <c r="K14" s="14">
         <f t="shared" si="3"/>
-        <v>24.8</v>
+        <v>18.75</v>
       </c>
       <c r="L14" s="36">
         <f>C14+D14+E14+F14+H14+I14+J14</f>
-        <v>1202</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A15" s="13"/>
       <c r="B15" s="10" t="s">
         <v>40</v>
@@ -5483,64 +5499,64 @@
       <c r="C15" s="13"/>
       <c r="D15" s="13">
         <f>D14/20</f>
-        <v>9.4</v>
+        <v>7.4</v>
       </c>
       <c r="E15" s="13">
         <f t="shared" ref="E15:J15" si="4">E14/20</f>
-        <v>9.9</v>
+        <v>7.4</v>
       </c>
       <c r="F15" s="13">
         <f t="shared" si="4"/>
-        <v>6.1</v>
+        <v>3.6</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13">
         <f t="shared" si="4"/>
-        <v>8.25</v>
+        <v>5.85</v>
       </c>
       <c r="I15" s="13">
         <f t="shared" si="4"/>
-        <v>5.9</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="J15" s="13">
         <f t="shared" si="4"/>
-        <v>10.65</v>
+        <v>7.8</v>
       </c>
       <c r="K15" s="13"/>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A16" s="13"/>
       <c r="B16" s="10" t="s">
         <v>39</v>
       </c>
       <c r="C16" s="37">
         <f>C15+C14</f>
-        <v>198</v>
+        <v>168</v>
       </c>
       <c r="D16" s="37">
         <f t="shared" ref="D16:J16" si="5">D15+D14</f>
-        <v>197.4</v>
+        <v>155.4</v>
       </c>
       <c r="E16" s="37">
         <f t="shared" si="5"/>
-        <v>207.9</v>
+        <v>155.4</v>
       </c>
       <c r="F16" s="37">
         <f t="shared" si="5"/>
-        <v>128.1</v>
+        <v>75.599999999999994</v>
       </c>
       <c r="G16" s="37"/>
       <c r="H16" s="37">
         <f t="shared" si="5"/>
-        <v>173.25</v>
+        <v>122.85</v>
       </c>
       <c r="I16" s="37">
         <f t="shared" si="5"/>
-        <v>123.9</v>
+        <v>107.1</v>
       </c>
       <c r="J16" s="37">
         <f t="shared" si="5"/>
-        <v>223.65</v>
+        <v>163.80000000000001</v>
       </c>
       <c r="K16" s="37"/>
     </row>
@@ -5551,37 +5567,37 @@
       </c>
       <c r="C17" s="37">
         <f>C14/40</f>
-        <v>4.95</v>
+        <v>4.2</v>
       </c>
       <c r="D17" s="37">
         <f t="shared" ref="D17:J17" si="6">D14/40</f>
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="E17" s="37">
         <f t="shared" si="6"/>
-        <v>4.95</v>
+        <v>3.7</v>
       </c>
       <c r="F17" s="37">
         <f t="shared" si="6"/>
-        <v>3.05</v>
+        <v>1.8</v>
       </c>
       <c r="G17" s="37"/>
       <c r="H17" s="37">
         <f t="shared" si="6"/>
-        <v>4.125</v>
+        <v>2.9249999999999998</v>
       </c>
       <c r="I17" s="37">
         <f t="shared" si="6"/>
-        <v>2.95</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="J17" s="37">
         <f t="shared" si="6"/>
-        <v>5.3250000000000002</v>
+        <v>3.9</v>
       </c>
       <c r="K17" s="37"/>
       <c r="L17" s="36">
         <f>SUM(C17:J17)</f>
-        <v>30.05</v>
+        <v>22.775000000000002</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">
@@ -5612,7 +5628,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{257F4DF8-C865-4EAB-87FC-B54CA70AD20E}">
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:S19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.90625" bestFit="1" customWidth="1"/>
@@ -5627,7 +5643,7 @@
     <col min="11" max="11" width="5.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5640,80 +5656,86 @@
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="51" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="53"/>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="B2" s="52" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="54"/>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="55"/>
-      <c r="K3" s="56"/>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="B3" s="55"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="57"/>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55"/>
-      <c r="K4" s="56"/>
-    </row>
-    <row r="5" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B4" s="55"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="57"/>
+    </row>
+    <row r="5" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="57"/>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="58"/>
-      <c r="I5" s="58"/>
-      <c r="J5" s="58"/>
-      <c r="K5" s="59"/>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="B5" s="58"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="59"/>
+      <c r="K5" s="60"/>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
       <c r="B6" s="2"/>
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="60" t="s">
+      <c r="D6" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="61"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="61" t="s">
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="61"/>
-      <c r="J6" s="61"/>
-      <c r="K6" s="62"/>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="I6" s="62"/>
+      <c r="J6" s="62"/>
+      <c r="K6" s="63"/>
+      <c r="R6" t="s">
+        <v>63</v>
+      </c>
+      <c r="S6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
         <v>4</v>
       </c>
@@ -5754,7 +5776,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A8" s="27"/>
       <c r="B8" s="10" t="s">
         <v>32</v>
@@ -5776,114 +5798,123 @@
         <v>5.2</v>
       </c>
       <c r="H8" s="12">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="I8" s="12">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="J8" s="12">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="K8" s="28">
         <f>SUM(H8:J8)/20</f>
-        <v>14.9</v>
-      </c>
-      <c r="L8" s="63">
+        <v>12.9</v>
+      </c>
+      <c r="L8" s="51">
         <f>SUM(C8:F8,H8,I8,J8)/40</f>
-        <v>10.65</v>
-      </c>
-      <c r="M8" s="63">
+        <v>9.65</v>
+      </c>
+      <c r="M8" s="51">
         <v>7</v>
+      </c>
+      <c r="N8" t="s">
+        <v>62</v>
       </c>
       <c r="Q8" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A9" s="27"/>
       <c r="B9" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="12">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="D9" s="12">
         <v>40</v>
       </c>
       <c r="E9" s="12">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="F9" s="12">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="G9" s="28">
         <f t="shared" ref="G9:G10" si="0">SUM(D9:F9)/20</f>
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="H9" s="12">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I9" s="12">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J9" s="12">
         <v>10</v>
       </c>
       <c r="K9" s="28">
         <f t="shared" ref="K9:K10" si="1">SUM(H9:J9)/20</f>
-        <v>3</v>
-      </c>
-      <c r="L9" s="63">
+        <v>2</v>
+      </c>
+      <c r="L9" s="51">
         <f t="shared" ref="L9:L12" si="2">SUM(C9:F9,H9,I9,J9)/40</f>
-        <v>8.35</v>
-      </c>
-      <c r="M9" s="63">
+        <v>7.1</v>
+      </c>
+      <c r="M9" s="51">
         <v>9</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="N9" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
         <v>16</v>
       </c>
       <c r="C10" s="12">
-        <v>210</v>
+        <v>120</v>
       </c>
       <c r="D10" s="12">
-        <v>340</v>
+        <v>220</v>
       </c>
       <c r="E10" s="12">
-        <v>320</v>
+        <v>240</v>
       </c>
       <c r="F10" s="12">
         <v>160</v>
       </c>
       <c r="G10" s="28">
         <f t="shared" si="0"/>
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="H10" s="12">
-        <v>335</v>
+        <v>295</v>
       </c>
       <c r="I10" s="12">
-        <v>290</v>
+        <v>250</v>
       </c>
       <c r="J10" s="12">
-        <v>495</v>
+        <v>415</v>
       </c>
       <c r="K10" s="28">
         <f t="shared" si="1"/>
-        <v>56</v>
-      </c>
-      <c r="L10" s="63">
+        <v>48</v>
+      </c>
+      <c r="L10" s="51">
         <f t="shared" si="2"/>
-        <v>53.75</v>
-      </c>
-      <c r="M10" s="63">
+        <v>42.5</v>
+      </c>
+      <c r="M10" s="51">
         <v>17</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="N10" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11"/>
       <c r="C11" s="12"/>
@@ -5901,7 +5932,7 @@
       </c>
       <c r="M11" s="41"/>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
       <c r="B12" s="11"/>
       <c r="C12" s="12"/>
@@ -5919,7 +5950,7 @@
       </c>
       <c r="M12" s="41"/>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
       <c r="B13" s="11"/>
       <c r="C13" s="12"/>
@@ -5934,51 +5965,51 @@
       <c r="L13" s="41"/>
       <c r="M13" s="41"/>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
         <f t="shared" ref="C14:K14" si="3">SUM(C8:C13)</f>
-        <v>358</v>
+        <v>258</v>
       </c>
       <c r="D14" s="14">
         <f t="shared" si="3"/>
-        <v>434</v>
+        <v>314</v>
       </c>
       <c r="E14" s="14">
         <f t="shared" si="3"/>
-        <v>400</v>
+        <v>310</v>
       </c>
       <c r="F14" s="14">
         <f t="shared" si="3"/>
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="G14" s="14">
         <f t="shared" si="3"/>
-        <v>53.7</v>
+        <v>42.7</v>
       </c>
       <c r="H14" s="14">
         <f t="shared" si="3"/>
-        <v>476</v>
+        <v>411</v>
       </c>
       <c r="I14" s="14">
         <f t="shared" si="3"/>
-        <v>386</v>
+        <v>321</v>
       </c>
       <c r="J14" s="14">
         <f t="shared" si="3"/>
-        <v>616</v>
+        <v>526</v>
       </c>
       <c r="K14" s="14">
         <f t="shared" si="3"/>
-        <v>73.900000000000006</v>
+        <v>62.9</v>
       </c>
       <c r="L14" s="36">
         <f>C14+D14+E14+F14+H14+I14+J14</f>
-        <v>2910</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A15" s="13"/>
       <c r="B15" s="10" t="s">
         <v>40</v>
@@ -5986,64 +6017,64 @@
       <c r="C15" s="13"/>
       <c r="D15" s="13">
         <f>D14/20</f>
-        <v>21.7</v>
+        <v>15.7</v>
       </c>
       <c r="E15" s="13">
         <f t="shared" ref="E15:J15" si="4">E14/20</f>
-        <v>20</v>
+        <v>15.5</v>
       </c>
       <c r="F15" s="13">
         <f t="shared" si="4"/>
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13">
         <f t="shared" si="4"/>
-        <v>23.8</v>
+        <v>20.55</v>
       </c>
       <c r="I15" s="13">
         <f t="shared" si="4"/>
-        <v>19.3</v>
+        <v>16.05</v>
       </c>
       <c r="J15" s="13">
         <f t="shared" si="4"/>
-        <v>30.8</v>
+        <v>26.3</v>
       </c>
       <c r="K15" s="13"/>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A16" s="13"/>
       <c r="B16" s="10" t="s">
         <v>39</v>
       </c>
       <c r="C16" s="37">
         <f>C15+C14</f>
-        <v>358</v>
+        <v>258</v>
       </c>
       <c r="D16" s="37">
         <f t="shared" ref="D16:J16" si="5">D15+D14</f>
-        <v>455.7</v>
+        <v>329.7</v>
       </c>
       <c r="E16" s="37">
         <f t="shared" si="5"/>
-        <v>420</v>
+        <v>325.5</v>
       </c>
       <c r="F16" s="37">
         <f t="shared" si="5"/>
-        <v>252</v>
+        <v>241.5</v>
       </c>
       <c r="G16" s="37"/>
       <c r="H16" s="37">
         <f t="shared" si="5"/>
-        <v>499.8</v>
+        <v>431.55</v>
       </c>
       <c r="I16" s="37">
         <f t="shared" si="5"/>
-        <v>405.3</v>
+        <v>337.05</v>
       </c>
       <c r="J16" s="37">
         <f t="shared" si="5"/>
-        <v>646.79999999999995</v>
+        <v>552.29999999999995</v>
       </c>
       <c r="K16" s="37"/>
     </row>
@@ -6054,37 +6085,37 @@
       </c>
       <c r="C17" s="37">
         <f>C14/40</f>
-        <v>8.9499999999999993</v>
+        <v>6.45</v>
       </c>
       <c r="D17" s="37">
         <f t="shared" ref="D17:J17" si="6">D14/40</f>
-        <v>10.85</v>
+        <v>7.85</v>
       </c>
       <c r="E17" s="37">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>7.75</v>
       </c>
       <c r="F17" s="37">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="G17" s="37"/>
       <c r="H17" s="37">
         <f t="shared" si="6"/>
-        <v>11.9</v>
+        <v>10.275</v>
       </c>
       <c r="I17" s="37">
         <f t="shared" si="6"/>
-        <v>9.65</v>
+        <v>8.0250000000000004</v>
       </c>
       <c r="J17" s="37">
         <f t="shared" si="6"/>
-        <v>15.4</v>
+        <v>13.15</v>
       </c>
       <c r="K17" s="37"/>
       <c r="L17" s="36">
         <f>SUM(C17:J17)</f>
-        <v>72.75</v>
+        <v>59.25</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">
@@ -6145,57 +6176,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="51" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="53"/>
+      <c r="B2" s="52" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="54"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="55"/>
-      <c r="K3" s="56"/>
+      <c r="B3" s="55"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="57"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55"/>
-      <c r="K4" s="56"/>
+      <c r="B4" s="55"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="57"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="57"/>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="58"/>
-      <c r="I5" s="58"/>
-      <c r="J5" s="58"/>
-      <c r="K5" s="59"/>
+      <c r="B5" s="58"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="59"/>
+      <c r="K5" s="60"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -6203,18 +6234,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="60" t="s">
+      <c r="D6" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="61"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="61" t="s">
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="61"/>
-      <c r="J6" s="61"/>
-      <c r="K6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="62"/>
+      <c r="K6" s="63"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -6569,57 +6600,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="51" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="53"/>
+      <c r="B2" s="52" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="54"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="55"/>
-      <c r="K3" s="56"/>
+      <c r="B3" s="55"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="57"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55"/>
-      <c r="K4" s="56"/>
+      <c r="B4" s="55"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="57"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="57"/>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="58"/>
-      <c r="I5" s="58"/>
-      <c r="J5" s="58"/>
-      <c r="K5" s="59"/>
+      <c r="B5" s="58"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="59"/>
+      <c r="K5" s="60"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -6627,18 +6658,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="60" t="s">
+      <c r="D6" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="61"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="61" t="s">
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="61"/>
-      <c r="J6" s="61"/>
-      <c r="K6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="62"/>
+      <c r="K6" s="63"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -7041,57 +7072,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="51" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="53"/>
+      <c r="B2" s="52" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="54"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="55"/>
-      <c r="K3" s="56"/>
+      <c r="B3" s="55"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="57"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55"/>
-      <c r="K4" s="56"/>
+      <c r="B4" s="55"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="57"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="57"/>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="58"/>
-      <c r="I5" s="58"/>
-      <c r="J5" s="58"/>
-      <c r="K5" s="59"/>
+      <c r="B5" s="58"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="59"/>
+      <c r="K5" s="60"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -7099,18 +7130,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="60" t="s">
+      <c r="D6" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="61"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="61" t="s">
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="61"/>
-      <c r="J6" s="61"/>
-      <c r="K6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="62"/>
+      <c r="K6" s="63"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -7465,57 +7496,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="51" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="53"/>
+      <c r="B2" s="52" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="54"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="55"/>
-      <c r="K3" s="56"/>
+      <c r="B3" s="55"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="57"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55"/>
-      <c r="K4" s="56"/>
+      <c r="B4" s="55"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="57"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="57"/>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="58"/>
-      <c r="I5" s="58"/>
-      <c r="J5" s="58"/>
-      <c r="K5" s="59"/>
+      <c r="B5" s="58"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="59"/>
+      <c r="K5" s="60"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -7523,18 +7554,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="60" t="s">
+      <c r="D6" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="61"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="61" t="s">
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="61"/>
-      <c r="J6" s="61"/>
-      <c r="K6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="62"/>
+      <c r="K6" s="63"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -7889,57 +7920,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="51" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="53"/>
+      <c r="B2" s="52" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="54"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="55"/>
-      <c r="K3" s="56"/>
+      <c r="B3" s="55"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="57"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55"/>
-      <c r="K4" s="56"/>
+      <c r="B4" s="55"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="57"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="57"/>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="58"/>
-      <c r="I5" s="58"/>
-      <c r="J5" s="58"/>
-      <c r="K5" s="59"/>
+      <c r="B5" s="58"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="59"/>
+      <c r="K5" s="60"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -7947,18 +7978,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="60" t="s">
+      <c r="D6" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="61"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="61" t="s">
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="61"/>
-      <c r="J6" s="61"/>
-      <c r="K6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="62"/>
+      <c r="K6" s="63"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -8313,57 +8344,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="51" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="53"/>
+      <c r="B2" s="52" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="54"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="55"/>
-      <c r="K3" s="56"/>
+      <c r="B3" s="55"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="57"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55"/>
-      <c r="K4" s="56"/>
+      <c r="B4" s="55"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="57"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="57"/>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="58"/>
-      <c r="I5" s="58"/>
-      <c r="J5" s="58"/>
-      <c r="K5" s="59"/>
+      <c r="B5" s="58"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="59"/>
+      <c r="K5" s="60"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -8371,18 +8402,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="60" t="s">
+      <c r="D6" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="61"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="61" t="s">
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="61"/>
-      <c r="J6" s="61"/>
-      <c r="K6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="62"/>
+      <c r="K6" s="63"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -8737,57 +8768,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="51" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="53"/>
+      <c r="B2" s="52" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="54"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="55"/>
-      <c r="K3" s="56"/>
+      <c r="B3" s="55"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="57"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55"/>
-      <c r="K4" s="56"/>
+      <c r="B4" s="55"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="57"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="57"/>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="58"/>
-      <c r="I5" s="58"/>
-      <c r="J5" s="58"/>
-      <c r="K5" s="59"/>
+      <c r="B5" s="58"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="59"/>
+      <c r="K5" s="60"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -8795,18 +8826,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="60" t="s">
+      <c r="D6" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="61"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="61" t="s">
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="61"/>
-      <c r="J6" s="61"/>
-      <c r="K6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="62"/>
+      <c r="K6" s="63"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -9161,57 +9192,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="51" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="53"/>
+      <c r="B2" s="52" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="54"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="55"/>
-      <c r="K3" s="56"/>
+      <c r="B3" s="55"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="57"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55"/>
-      <c r="K4" s="56"/>
+      <c r="B4" s="55"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="57"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="57"/>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="58"/>
-      <c r="I5" s="58"/>
-      <c r="J5" s="58"/>
-      <c r="K5" s="59"/>
+      <c r="B5" s="58"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="59"/>
+      <c r="K5" s="60"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -9219,18 +9250,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="60" t="s">
+      <c r="D6" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="61"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="61" t="s">
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="61"/>
-      <c r="J6" s="61"/>
-      <c r="K6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="62"/>
+      <c r="K6" s="63"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -9585,57 +9616,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="51" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="53"/>
+      <c r="B2" s="52" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="54"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="55"/>
-      <c r="K3" s="56"/>
+      <c r="B3" s="55"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="57"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55"/>
-      <c r="K4" s="56"/>
+      <c r="B4" s="55"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="57"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="57"/>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="58"/>
-      <c r="I5" s="58"/>
-      <c r="J5" s="58"/>
-      <c r="K5" s="59"/>
+      <c r="B5" s="58"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="59"/>
+      <c r="K5" s="60"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -9643,18 +9674,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="60" t="s">
+      <c r="D6" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="61"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="61" t="s">
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="61"/>
-      <c r="J6" s="61"/>
-      <c r="K6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="62"/>
+      <c r="K6" s="63"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -10009,57 +10040,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="51" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="53"/>
+      <c r="B2" s="52" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="54"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="55"/>
-      <c r="K3" s="56"/>
+      <c r="B3" s="55"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="57"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55"/>
-      <c r="K4" s="56"/>
+      <c r="B4" s="55"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="57"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="57"/>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="58"/>
-      <c r="I5" s="58"/>
-      <c r="J5" s="58"/>
-      <c r="K5" s="59"/>
+      <c r="B5" s="58"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="59"/>
+      <c r="K5" s="60"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -10067,18 +10098,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="60" t="s">
+      <c r="D6" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="61"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="61" t="s">
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="61"/>
-      <c r="J6" s="61"/>
-      <c r="K6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="62"/>
+      <c r="K6" s="63"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -10433,57 +10464,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="51" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="53"/>
+      <c r="B2" s="52" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="54"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="55"/>
-      <c r="K3" s="56"/>
+      <c r="B3" s="55"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="57"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55"/>
-      <c r="K4" s="56"/>
+      <c r="B4" s="55"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="57"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="57"/>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="58"/>
-      <c r="I5" s="58"/>
-      <c r="J5" s="58"/>
-      <c r="K5" s="59"/>
+      <c r="B5" s="58"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="59"/>
+      <c r="K5" s="60"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -10491,18 +10522,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="60" t="s">
+      <c r="D6" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="61"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="61" t="s">
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="61"/>
-      <c r="J6" s="61"/>
-      <c r="K6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="62"/>
+      <c r="K6" s="63"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -10857,57 +10888,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="51" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="53"/>
+      <c r="B2" s="52" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="54"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="55"/>
-      <c r="K3" s="56"/>
+      <c r="B3" s="55"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="57"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55"/>
-      <c r="K4" s="56"/>
+      <c r="B4" s="55"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="57"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="57"/>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="58"/>
-      <c r="I5" s="58"/>
-      <c r="J5" s="58"/>
-      <c r="K5" s="59"/>
+      <c r="B5" s="58"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="59"/>
+      <c r="K5" s="60"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -10915,18 +10946,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="60" t="s">
+      <c r="D6" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="61"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="61" t="s">
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="61"/>
-      <c r="J6" s="61"/>
-      <c r="K6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="62"/>
+      <c r="K6" s="63"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -11281,57 +11312,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="51" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="53"/>
+      <c r="B2" s="52" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="54"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="55"/>
-      <c r="K3" s="56"/>
+      <c r="B3" s="55"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="57"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55"/>
-      <c r="K4" s="56"/>
+      <c r="B4" s="55"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="57"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="57"/>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="58"/>
-      <c r="I5" s="58"/>
-      <c r="J5" s="58"/>
-      <c r="K5" s="59"/>
+      <c r="B5" s="58"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="59"/>
+      <c r="K5" s="60"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -11339,18 +11370,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="60" t="s">
+      <c r="D6" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="61"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="61" t="s">
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="61"/>
-      <c r="J6" s="61"/>
-      <c r="K6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="62"/>
+      <c r="K6" s="63"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -11767,57 +11798,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="51" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="53"/>
+      <c r="B2" s="52" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="54"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="55"/>
-      <c r="K3" s="56"/>
+      <c r="B3" s="55"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="57"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55"/>
-      <c r="K4" s="56"/>
+      <c r="B4" s="55"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="57"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="57"/>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="58"/>
-      <c r="I5" s="58"/>
-      <c r="J5" s="58"/>
-      <c r="K5" s="59"/>
+      <c r="B5" s="58"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="59"/>
+      <c r="K5" s="60"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -11825,18 +11856,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="60" t="s">
+      <c r="D6" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="61"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="61" t="s">
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="61"/>
-      <c r="J6" s="61"/>
-      <c r="K6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="62"/>
+      <c r="K6" s="63"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -12191,57 +12222,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="51" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="53"/>
+      <c r="B2" s="52" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="54"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="55"/>
-      <c r="K3" s="56"/>
+      <c r="B3" s="55"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="57"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55"/>
-      <c r="K4" s="56"/>
+      <c r="B4" s="55"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="57"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="57"/>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="58"/>
-      <c r="I5" s="58"/>
-      <c r="J5" s="58"/>
-      <c r="K5" s="59"/>
+      <c r="B5" s="58"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="59"/>
+      <c r="K5" s="60"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -12249,18 +12280,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="60" t="s">
+      <c r="D6" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="61"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="61" t="s">
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="61"/>
-      <c r="J6" s="61"/>
-      <c r="K6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="62"/>
+      <c r="K6" s="63"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -12616,57 +12647,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="51" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="53"/>
+      <c r="B2" s="52" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="54"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="55"/>
-      <c r="K3" s="56"/>
+      <c r="B3" s="55"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="57"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55"/>
-      <c r="K4" s="56"/>
+      <c r="B4" s="55"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="57"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="57"/>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="58"/>
-      <c r="I5" s="58"/>
-      <c r="J5" s="58"/>
-      <c r="K5" s="59"/>
+      <c r="B5" s="58"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="59"/>
+      <c r="K5" s="60"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -12674,18 +12705,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="60" t="s">
+      <c r="D6" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="61"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="61" t="s">
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="61"/>
-      <c r="J6" s="61"/>
-      <c r="K6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="62"/>
+      <c r="K6" s="63"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -13040,57 +13071,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="51" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="53"/>
+      <c r="B2" s="52" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="54"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="55"/>
-      <c r="K3" s="56"/>
+      <c r="B3" s="55"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="57"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55"/>
-      <c r="K4" s="56"/>
+      <c r="B4" s="55"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="57"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="57"/>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="58"/>
-      <c r="I5" s="58"/>
-      <c r="J5" s="58"/>
-      <c r="K5" s="59"/>
+      <c r="B5" s="58"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="59"/>
+      <c r="K5" s="60"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -13098,18 +13129,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="60" t="s">
+      <c r="D6" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="61"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="61" t="s">
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="61"/>
-      <c r="J6" s="61"/>
-      <c r="K6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="62"/>
+      <c r="K6" s="63"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -13579,57 +13610,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="51" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="53"/>
+      <c r="B2" s="52" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="54"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="55"/>
-      <c r="K3" s="56"/>
+      <c r="B3" s="55"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="57"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55"/>
-      <c r="K4" s="56"/>
+      <c r="B4" s="55"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="57"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="57"/>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="58"/>
-      <c r="I5" s="58"/>
-      <c r="J5" s="58"/>
-      <c r="K5" s="59"/>
+      <c r="B5" s="58"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="59"/>
+      <c r="K5" s="60"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -13637,18 +13668,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="60" t="s">
+      <c r="D6" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="61"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="61" t="s">
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="61"/>
-      <c r="J6" s="61"/>
-      <c r="K6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="62"/>
+      <c r="K6" s="63"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -14090,57 +14121,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="51" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="53"/>
+      <c r="B2" s="52" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="54"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="55"/>
-      <c r="K3" s="56"/>
+      <c r="B3" s="55"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="57"/>
     </row>
     <row r="4" spans="1:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55"/>
-      <c r="K4" s="56"/>
+      <c r="B4" s="55"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="57"/>
     </row>
     <row r="5" spans="1:12" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="57"/>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="58"/>
-      <c r="I5" s="58"/>
-      <c r="J5" s="58"/>
-      <c r="K5" s="59"/>
+      <c r="B5" s="58"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="59"/>
+      <c r="K5" s="60"/>
     </row>
     <row r="6" spans="1:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -14148,18 +14179,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="60" t="s">
+      <c r="D6" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="61"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="61" t="s">
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="61"/>
-      <c r="J6" s="61"/>
-      <c r="K6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="62"/>
+      <c r="K6" s="63"/>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -14566,57 +14597,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="51" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="53"/>
+      <c r="B2" s="52" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="54"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="55"/>
-      <c r="K3" s="56"/>
+      <c r="B3" s="55"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="57"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55"/>
-      <c r="K4" s="56"/>
+      <c r="B4" s="55"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="57"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="57"/>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="58"/>
-      <c r="I5" s="58"/>
-      <c r="J5" s="58"/>
-      <c r="K5" s="59"/>
+      <c r="B5" s="58"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="59"/>
+      <c r="K5" s="60"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -14624,18 +14655,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="60" t="s">
+      <c r="D6" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="61"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="61" t="s">
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="61"/>
-      <c r="J6" s="61"/>
-      <c r="K6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="62"/>
+      <c r="K6" s="63"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -14994,57 +15025,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="51" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="53"/>
+      <c r="B2" s="52" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="54"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="55"/>
-      <c r="K3" s="56"/>
+      <c r="B3" s="55"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="57"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55"/>
-      <c r="K4" s="56"/>
+      <c r="B4" s="55"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="57"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="57"/>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="58"/>
-      <c r="I5" s="58"/>
-      <c r="J5" s="58"/>
-      <c r="K5" s="59"/>
+      <c r="B5" s="58"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="59"/>
+      <c r="K5" s="60"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -15052,18 +15083,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="60" t="s">
+      <c r="D6" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="61"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="61" t="s">
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="61"/>
-      <c r="J6" s="61"/>
-      <c r="K6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="62"/>
+      <c r="K6" s="63"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -15412,57 +15443,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="51" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="53"/>
+      <c r="B2" s="52" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="54"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="55"/>
-      <c r="K3" s="56"/>
+      <c r="B3" s="55"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="57"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55"/>
-      <c r="K4" s="56"/>
+      <c r="B4" s="55"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="57"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="57"/>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="58"/>
-      <c r="I5" s="58"/>
-      <c r="J5" s="58"/>
-      <c r="K5" s="59"/>
+      <c r="B5" s="58"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="59"/>
+      <c r="K5" s="60"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -15470,18 +15501,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="60" t="s">
+      <c r="D6" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="61"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="61" t="s">
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="61"/>
-      <c r="J6" s="61"/>
-      <c r="K6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="62"/>
+      <c r="K6" s="63"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">

--- a/Final Execution SKU wise.xlsx
+++ b/Final Execution SKU wise.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ACB7BE5-A93A-47ED-A448-5DC1E0E4920A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12A60956-A832-4C05-AF6F-B5E66C593E8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" activeTab="17" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" activeTab="19" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
   </bookViews>
   <sheets>
     <sheet name="last month" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="715" uniqueCount="71">
   <si>
     <t>Gate Pass</t>
   </si>
@@ -251,6 +251,24 @@
   </si>
   <si>
     <t>meat 70</t>
+  </si>
+  <si>
+    <t>Rambo Jameel</t>
+  </si>
+  <si>
+    <t>Rambo me</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Executed </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Umair </t>
+  </si>
+  <si>
+    <t>Executed</t>
+  </si>
+  <si>
+    <t>Zeshan</t>
   </si>
 </sst>
 </file>
@@ -6146,11 +6164,11 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48CE528A-B31C-4333-9BC5-136993154ACA}">
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.90625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.54296875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.08984375" customWidth="1"/>
     <col min="5" max="5" width="4.26953125" bestFit="1" customWidth="1"/>
@@ -6161,7 +6179,7 @@
     <col min="11" max="11" width="5.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -6174,7 +6192,7 @@
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="52" t="s">
         <v>0</v>
@@ -6189,7 +6207,7 @@
       <c r="J2" s="53"/>
       <c r="K2" s="54"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="55"/>
       <c r="C3" s="56"/>
@@ -6202,7 +6220,7 @@
       <c r="J3" s="56"/>
       <c r="K3" s="57"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" s="55"/>
       <c r="C4" s="56"/>
@@ -6215,7 +6233,7 @@
       <c r="J4" s="56"/>
       <c r="K4" s="57"/>
     </row>
-    <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
       <c r="B5" s="58"/>
       <c r="C5" s="59"/>
@@ -6228,7 +6246,7 @@
       <c r="J5" s="59"/>
       <c r="K5" s="60"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
       <c r="B6" s="2"/>
       <c r="C6" s="3" t="s">
@@ -6247,7 +6265,7 @@
       <c r="J6" s="62"/>
       <c r="K6" s="63"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
         <v>4</v>
       </c>
@@ -6285,98 +6303,213 @@
         <v>59</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" s="27"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
+      <c r="B8" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="12">
+        <v>64</v>
+      </c>
+      <c r="D8" s="12">
+        <v>0</v>
+      </c>
+      <c r="E8" s="12">
+        <v>0</v>
+      </c>
+      <c r="F8" s="12">
+        <v>0</v>
+      </c>
       <c r="G8" s="28">
         <f>SUM(D8:F8)/20</f>
         <v>0</v>
       </c>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="12"/>
+      <c r="H8" s="12">
+        <v>60</v>
+      </c>
+      <c r="I8" s="12">
+        <v>40</v>
+      </c>
+      <c r="J8" s="12">
+        <v>60</v>
+      </c>
       <c r="K8" s="28">
         <f>SUM(H8:J8)/20</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L8">
         <f>SUM(C8:F8,H8,I8,J8)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+        <v>5.6</v>
+      </c>
+      <c r="M8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" s="27"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12"/>
-      <c r="K9" s="28"/>
+      <c r="B9" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="12">
+        <v>100</v>
+      </c>
+      <c r="D9" s="12">
+        <v>67</v>
+      </c>
+      <c r="E9" s="12">
+        <v>57</v>
+      </c>
+      <c r="F9" s="12">
+        <v>54</v>
+      </c>
+      <c r="G9" s="28">
+        <f t="shared" ref="G9:G12" si="0">SUM(D9:F9)/20</f>
+        <v>8.9</v>
+      </c>
+      <c r="H9" s="12">
+        <v>132</v>
+      </c>
+      <c r="I9" s="12">
+        <v>112</v>
+      </c>
+      <c r="J9" s="12">
+        <v>126</v>
+      </c>
+      <c r="K9" s="28">
+        <f t="shared" ref="K9:K12" si="1">SUM(H9:J9)/20</f>
+        <v>18.5</v>
+      </c>
       <c r="L9">
-        <f t="shared" ref="L9:L12" si="0">SUM(C9:F9,H9,I9,J9)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+        <f t="shared" ref="L9:L12" si="2">SUM(C9:F9,H9,I9,J9)/40</f>
+        <v>16.2</v>
+      </c>
+      <c r="M9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="28"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="28"/>
+      <c r="B10" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="12">
+        <v>90</v>
+      </c>
+      <c r="D10" s="12">
+        <v>196</v>
+      </c>
+      <c r="E10" s="12">
+        <v>193</v>
+      </c>
+      <c r="F10" s="12">
+        <v>154</v>
+      </c>
+      <c r="G10" s="28">
+        <f t="shared" si="0"/>
+        <v>27.15</v>
+      </c>
+      <c r="H10" s="12">
+        <v>170</v>
+      </c>
+      <c r="I10" s="12">
+        <v>145</v>
+      </c>
+      <c r="J10" s="12">
+        <v>145</v>
+      </c>
+      <c r="K10" s="28">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
       <c r="L10">
+        <f t="shared" si="2"/>
+        <v>27.324999999999999</v>
+      </c>
+      <c r="M10" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A11" s="11"/>
+      <c r="B11" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12">
+        <v>240</v>
+      </c>
+      <c r="E11" s="12">
+        <v>520</v>
+      </c>
+      <c r="F11" s="12">
+        <v>480</v>
+      </c>
+      <c r="G11" s="28">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A11" s="11"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="12"/>
-      <c r="K11" s="12"/>
+        <v>62</v>
+      </c>
+      <c r="H11" s="12">
+        <v>440</v>
+      </c>
+      <c r="I11" s="12">
+        <v>680</v>
+      </c>
+      <c r="J11" s="12">
+        <v>680</v>
+      </c>
+      <c r="K11" s="28">
+        <f t="shared" si="1"/>
+        <v>90</v>
+      </c>
       <c r="L11">
+        <f t="shared" si="2"/>
+        <v>76</v>
+      </c>
+      <c r="M11" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A12" s="11"/>
+      <c r="B12" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12">
+        <v>40</v>
+      </c>
+      <c r="E12" s="12">
+        <v>80</v>
+      </c>
+      <c r="F12" s="12">
+        <v>120</v>
+      </c>
+      <c r="G12" s="28">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A12" s="11"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="12"/>
-      <c r="K12" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="H12" s="12">
+        <v>80</v>
+      </c>
+      <c r="I12" s="12">
+        <v>80</v>
+      </c>
+      <c r="J12" s="12">
+        <v>80</v>
+      </c>
+      <c r="K12" s="28">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
       <c r="L12">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="M12" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
       <c r="B13" s="11"/>
       <c r="C13" s="12"/>
@@ -6389,51 +6522,51 @@
       <c r="J13" s="12"/>
       <c r="K13" s="12"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:K14" si="1">SUM(C8:C13)</f>
-        <v>0</v>
+        <f t="shared" ref="C14:K14" si="3">SUM(C8:C13)</f>
+        <v>254</v>
       </c>
       <c r="D14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>543</v>
       </c>
       <c r="E14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>850</v>
       </c>
       <c r="F14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>808</v>
       </c>
       <c r="G14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>110.05</v>
       </c>
       <c r="H14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>882</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1057</v>
       </c>
       <c r="J14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1091</v>
       </c>
       <c r="K14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>151.5</v>
       </c>
       <c r="L14" s="36">
         <f>C14+D14+E14+F14+H14+I14+J14</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+        <v>5485</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" s="13"/>
       <c r="B15" s="10" t="s">
         <v>40</v>
@@ -6441,64 +6574,67 @@
       <c r="C15" s="13"/>
       <c r="D15" s="13">
         <f>D14/20</f>
-        <v>0</v>
+        <v>27.15</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:J15" si="2">E14/20</f>
-        <v>0</v>
+        <f t="shared" ref="E15:J15" si="4">E14/20</f>
+        <v>42.5</v>
       </c>
       <c r="F15" s="13">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>40.4</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>44.1</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>52.85</v>
       </c>
       <c r="J15" s="13">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>54.55</v>
       </c>
       <c r="K15" s="13"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" s="13"/>
       <c r="B16" s="10" t="s">
         <v>39</v>
       </c>
       <c r="C16" s="37">
         <f>C15+C14</f>
-        <v>0</v>
+        <v>254</v>
       </c>
       <c r="D16" s="37">
-        <f t="shared" ref="D16:J16" si="3">D15+D14</f>
-        <v>0</v>
+        <f t="shared" ref="D16:J16" si="5">D15+D14</f>
+        <v>570.15</v>
       </c>
       <c r="E16" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>892.5</v>
       </c>
       <c r="F16" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>848.4</v>
       </c>
       <c r="G16" s="37"/>
       <c r="H16" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>926.1</v>
       </c>
       <c r="I16" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>1109.8499999999999</v>
       </c>
       <c r="J16" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>1145.55</v>
       </c>
       <c r="K16" s="37"/>
     </row>
@@ -6509,37 +6645,37 @@
       </c>
       <c r="C17" s="37">
         <f>C14/40</f>
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="D17" s="37">
-        <f t="shared" ref="D17:J17" si="4">D14/40</f>
-        <v>0</v>
+        <f t="shared" ref="D17:J17" si="6">D14/40</f>
+        <v>13.574999999999999</v>
       </c>
       <c r="E17" s="37">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>21.25</v>
       </c>
       <c r="F17" s="37">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>20.2</v>
       </c>
       <c r="G17" s="37"/>
       <c r="H17" s="37">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>22.05</v>
       </c>
       <c r="I17" s="37">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>26.425000000000001</v>
       </c>
       <c r="J17" s="37">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>27.274999999999999</v>
       </c>
       <c r="K17" s="37"/>
       <c r="L17" s="36">
         <f>SUM(C17:J17)</f>
-        <v>0</v>
+        <v>137.125</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">
@@ -7042,7 +7178,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90006E98-333A-4EDC-84AE-78E28F8069BD}">
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.90625" bestFit="1" customWidth="1"/>
@@ -7057,7 +7193,7 @@
     <col min="11" max="11" width="5.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -7070,7 +7206,7 @@
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="52" t="s">
         <v>0</v>
@@ -7085,7 +7221,7 @@
       <c r="J2" s="53"/>
       <c r="K2" s="54"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="55"/>
       <c r="C3" s="56"/>
@@ -7098,7 +7234,7 @@
       <c r="J3" s="56"/>
       <c r="K3" s="57"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" s="55"/>
       <c r="C4" s="56"/>
@@ -7111,7 +7247,7 @@
       <c r="J4" s="56"/>
       <c r="K4" s="57"/>
     </row>
-    <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
       <c r="B5" s="58"/>
       <c r="C5" s="59"/>
@@ -7124,7 +7260,7 @@
       <c r="J5" s="59"/>
       <c r="K5" s="60"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
       <c r="B6" s="2"/>
       <c r="C6" s="3" t="s">
@@ -7143,7 +7279,7 @@
       <c r="J6" s="62"/>
       <c r="K6" s="63"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
         <v>4</v>
       </c>
@@ -7180,17 +7316,26 @@
       <c r="L7" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M7" s="49"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" s="27"/>
-      <c r="B8" s="10"/>
+      <c r="B8" s="10" t="s">
+        <v>32</v>
+      </c>
       <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
+      <c r="D8" s="12">
+        <v>25</v>
+      </c>
+      <c r="E8" s="12">
+        <v>10</v>
+      </c>
+      <c r="F8" s="12">
+        <v>25</v>
+      </c>
       <c r="G8" s="28">
         <f>SUM(D8:F8)/20</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H8" s="12"/>
       <c r="I8" s="12"/>
@@ -7201,44 +7346,89 @@
       </c>
       <c r="L8">
         <f>SUM(C8:F8,H8,I8,J8)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+        <v>1.5</v>
+      </c>
+      <c r="M8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" s="27"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12"/>
-      <c r="K9" s="28"/>
+      <c r="B9" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="12">
+        <v>12</v>
+      </c>
+      <c r="D9" s="12">
+        <v>46</v>
+      </c>
+      <c r="E9" s="12">
+        <v>86</v>
+      </c>
+      <c r="F9" s="12">
+        <v>46</v>
+      </c>
+      <c r="G9" s="28">
+        <f t="shared" ref="G9:G10" si="0">SUM(D9:F9)/20</f>
+        <v>8.9</v>
+      </c>
+      <c r="H9" s="12">
+        <v>116</v>
+      </c>
+      <c r="I9" s="12">
+        <v>66</v>
+      </c>
+      <c r="J9" s="12">
+        <v>76</v>
+      </c>
+      <c r="K9" s="28">
+        <f t="shared" ref="K9:K10" si="1">SUM(H9:J9)/20</f>
+        <v>12.9</v>
+      </c>
       <c r="L9">
-        <f t="shared" ref="L9:L12" si="0">SUM(C9:F9,H9,I9,J9)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+        <f t="shared" ref="L9:L12" si="2">SUM(C9:F9,H9,I9,J9)/40</f>
+        <v>11.2</v>
+      </c>
+      <c r="M9" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
-      <c r="B10" s="10"/>
+      <c r="B10" s="10" t="s">
+        <v>70</v>
+      </c>
       <c r="C10" s="12"/>
       <c r="D10" s="12"/>
       <c r="E10" s="12"/>
       <c r="F10" s="12"/>
-      <c r="G10" s="28"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="28"/>
+      <c r="G10" s="28">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H10" s="12">
+        <v>800</v>
+      </c>
+      <c r="I10" s="12">
+        <v>400</v>
+      </c>
+      <c r="J10" s="12">
+        <v>800</v>
+      </c>
+      <c r="K10" s="28">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
       <c r="L10">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v>50</v>
+      </c>
+      <c r="M10" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11"/>
       <c r="C11" s="12"/>
@@ -7251,11 +7441,11 @@
       <c r="J11" s="12"/>
       <c r="K11" s="12"/>
       <c r="L11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
       <c r="B12" s="11"/>
       <c r="C12" s="12"/>
@@ -7268,11 +7458,11 @@
       <c r="J12" s="12"/>
       <c r="K12" s="12"/>
       <c r="L12">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
       <c r="B13" s="11"/>
       <c r="C13" s="12"/>
@@ -7285,51 +7475,51 @@
       <c r="J13" s="12"/>
       <c r="K13" s="12"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:K14" si="1">SUM(C8:C13)</f>
-        <v>0</v>
+        <f t="shared" ref="C14:K14" si="3">SUM(C8:C13)</f>
+        <v>12</v>
       </c>
       <c r="D14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>71</v>
       </c>
       <c r="E14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>96</v>
       </c>
       <c r="F14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>71</v>
       </c>
       <c r="G14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>11.9</v>
       </c>
       <c r="H14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>916</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>466</v>
       </c>
       <c r="J14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>876</v>
       </c>
       <c r="K14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>112.9</v>
       </c>
       <c r="L14" s="36">
         <f>C14+D14+E14+F14+H14+I14+J14</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+        <v>2508</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" s="13"/>
       <c r="B15" s="10" t="s">
         <v>40</v>
@@ -7337,64 +7527,64 @@
       <c r="C15" s="13"/>
       <c r="D15" s="13">
         <f>D14/20</f>
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:J15" si="2">E14/20</f>
-        <v>0</v>
+        <f t="shared" ref="E15:J15" si="4">E14/20</f>
+        <v>4.8</v>
       </c>
       <c r="F15" s="13">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>3.55</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>45.8</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>23.3</v>
       </c>
       <c r="J15" s="13">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>43.8</v>
       </c>
       <c r="K15" s="13"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" s="13"/>
       <c r="B16" s="10" t="s">
         <v>39</v>
       </c>
       <c r="C16" s="37">
         <f>C15+C14</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D16" s="37">
-        <f t="shared" ref="D16:J16" si="3">D15+D14</f>
-        <v>0</v>
+        <f t="shared" ref="D16:J16" si="5">D15+D14</f>
+        <v>74.55</v>
       </c>
       <c r="E16" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>100.8</v>
       </c>
       <c r="F16" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>74.55</v>
       </c>
       <c r="G16" s="37"/>
       <c r="H16" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>961.8</v>
       </c>
       <c r="I16" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>489.3</v>
       </c>
       <c r="J16" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>919.8</v>
       </c>
       <c r="K16" s="37"/>
     </row>
@@ -7405,37 +7595,37 @@
       </c>
       <c r="C17" s="37">
         <f>C14/40</f>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="D17" s="37">
-        <f t="shared" ref="D17:J17" si="4">D14/40</f>
-        <v>0</v>
+        <f t="shared" ref="D17:J17" si="6">D14/40</f>
+        <v>1.7749999999999999</v>
       </c>
       <c r="E17" s="37">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>2.4</v>
       </c>
       <c r="F17" s="37">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>1.7749999999999999</v>
       </c>
       <c r="G17" s="37"/>
       <c r="H17" s="37">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>22.9</v>
       </c>
       <c r="I17" s="37">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>11.65</v>
       </c>
       <c r="J17" s="37">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>21.9</v>
       </c>
       <c r="K17" s="37"/>
       <c r="L17" s="36">
         <f>SUM(C17:J17)</f>
-        <v>0</v>
+        <v>62.699999999999996</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">
@@ -7466,7 +7656,7 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77C45487-B908-4B5C-9BA4-6B5B2A14CAC7}">
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.90625" bestFit="1" customWidth="1"/>
@@ -7481,7 +7671,7 @@
     <col min="11" max="11" width="5.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -7494,7 +7684,7 @@
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="52" t="s">
         <v>0</v>
@@ -7509,7 +7699,7 @@
       <c r="J2" s="53"/>
       <c r="K2" s="54"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="55"/>
       <c r="C3" s="56"/>
@@ -7522,7 +7712,7 @@
       <c r="J3" s="56"/>
       <c r="K3" s="57"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" s="55"/>
       <c r="C4" s="56"/>
@@ -7535,7 +7725,7 @@
       <c r="J4" s="56"/>
       <c r="K4" s="57"/>
     </row>
-    <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
       <c r="B5" s="58"/>
       <c r="C5" s="59"/>
@@ -7548,7 +7738,7 @@
       <c r="J5" s="59"/>
       <c r="K5" s="60"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
       <c r="B6" s="2"/>
       <c r="C6" s="3" t="s">
@@ -7567,7 +7757,7 @@
       <c r="J6" s="62"/>
       <c r="K6" s="63"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
         <v>4</v>
       </c>
@@ -7604,99 +7794,219 @@
       <c r="L7" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M7" s="49" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" s="27"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
+      <c r="B8" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="12">
+        <v>200</v>
+      </c>
+      <c r="D8" s="12">
+        <v>60</v>
+      </c>
+      <c r="E8" s="12">
+        <v>60</v>
+      </c>
+      <c r="F8" s="12">
+        <v>0</v>
+      </c>
       <c r="G8" s="28">
         <f>SUM(D8:F8)/20</f>
-        <v>0</v>
-      </c>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="12"/>
+        <v>6</v>
+      </c>
+      <c r="H8" s="12">
+        <v>80</v>
+      </c>
+      <c r="I8" s="12">
+        <v>80</v>
+      </c>
+      <c r="J8" s="12">
+        <v>150</v>
+      </c>
       <c r="K8" s="28">
         <f>SUM(H8:J8)/20</f>
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="L8">
         <f>SUM(C8:F8,H8,I8,J8)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+        <v>15.75</v>
+      </c>
+      <c r="M8" s="49">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" s="27"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12"/>
-      <c r="K9" s="28"/>
+      <c r="B9" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" s="12">
+        <v>222</v>
+      </c>
+      <c r="D9" s="12">
+        <v>42</v>
+      </c>
+      <c r="E9" s="12">
+        <v>32</v>
+      </c>
+      <c r="F9" s="12">
+        <v>22</v>
+      </c>
+      <c r="G9" s="28">
+        <f t="shared" ref="G9:G12" si="0">SUM(D9:F9)/20</f>
+        <v>4.8</v>
+      </c>
+      <c r="H9" s="12">
+        <v>66</v>
+      </c>
+      <c r="I9" s="12">
+        <v>66</v>
+      </c>
+      <c r="J9" s="12">
+        <v>64</v>
+      </c>
+      <c r="K9" s="28">
+        <f t="shared" ref="K9:K12" si="1">SUM(H9:J9)/20</f>
+        <v>9.8000000000000007</v>
+      </c>
       <c r="L9">
-        <f t="shared" ref="L9:L12" si="0">SUM(C9:F9,H9,I9,J9)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+        <f t="shared" ref="L9:L12" si="2">SUM(C9:F9,H9,I9,J9)/40</f>
+        <v>12.85</v>
+      </c>
+      <c r="M9" s="49">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="28"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="28"/>
+      <c r="B10" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="12">
+        <v>92</v>
+      </c>
+      <c r="D10" s="12">
+        <v>15</v>
+      </c>
+      <c r="E10" s="12">
+        <v>10</v>
+      </c>
+      <c r="F10" s="12">
+        <v>15</v>
+      </c>
+      <c r="G10" s="28">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="H10" s="12">
+        <v>100</v>
+      </c>
+      <c r="I10" s="12">
+        <v>100</v>
+      </c>
+      <c r="J10" s="12">
+        <v>120</v>
+      </c>
+      <c r="K10" s="28">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
       <c r="L10">
+        <f t="shared" si="2"/>
+        <v>11.3</v>
+      </c>
+      <c r="M10" s="49">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A11" s="11"/>
+      <c r="B11" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="12">
+        <v>22</v>
+      </c>
+      <c r="D11" s="12">
+        <v>31</v>
+      </c>
+      <c r="E11" s="12">
+        <v>31</v>
+      </c>
+      <c r="F11" s="12">
+        <v>31</v>
+      </c>
+      <c r="G11" s="28">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A11" s="11"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="12"/>
-      <c r="K11" s="12"/>
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="H11" s="12">
+        <v>150</v>
+      </c>
+      <c r="I11" s="12">
+        <v>75</v>
+      </c>
+      <c r="J11" s="12">
+        <v>140</v>
+      </c>
+      <c r="K11" s="28">
+        <f t="shared" si="1"/>
+        <v>18.25</v>
+      </c>
       <c r="L11">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="M11" s="42">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A12" s="11"/>
+      <c r="B12" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12">
+        <v>105</v>
+      </c>
+      <c r="E12" s="12">
+        <v>93</v>
+      </c>
+      <c r="F12" s="12">
+        <v>134</v>
+      </c>
+      <c r="G12" s="28">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A12" s="11"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="12"/>
-      <c r="K12" s="12"/>
+        <v>16.600000000000001</v>
+      </c>
+      <c r="H12" s="12">
+        <v>29</v>
+      </c>
+      <c r="I12" s="12">
+        <v>68</v>
+      </c>
+      <c r="J12" s="12">
+        <v>40</v>
+      </c>
+      <c r="K12" s="28">
+        <f t="shared" si="1"/>
+        <v>6.85</v>
+      </c>
       <c r="L12">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v>11.725</v>
+      </c>
+      <c r="M12" s="42">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
       <c r="B13" s="11"/>
       <c r="C13" s="12"/>
@@ -7709,51 +8019,51 @@
       <c r="J13" s="12"/>
       <c r="K13" s="12"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:K14" si="1">SUM(C8:C13)</f>
-        <v>0</v>
+        <f t="shared" ref="C14:K14" si="3">SUM(C8:C13)</f>
+        <v>536</v>
       </c>
       <c r="D14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>253</v>
       </c>
       <c r="E14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>226</v>
       </c>
       <c r="F14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>202</v>
       </c>
       <c r="G14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>34.050000000000004</v>
       </c>
       <c r="H14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>425</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>389</v>
       </c>
       <c r="J14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>514</v>
       </c>
       <c r="K14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>66.399999999999991</v>
       </c>
       <c r="L14" s="36">
         <f>C14+D14+E14+F14+H14+I14+J14</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+        <v>2545</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" s="13"/>
       <c r="B15" s="10" t="s">
         <v>40</v>
@@ -7761,64 +8071,64 @@
       <c r="C15" s="13"/>
       <c r="D15" s="13">
         <f>D14/20</f>
-        <v>0</v>
+        <v>12.65</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:J15" si="2">E14/20</f>
-        <v>0</v>
+        <f t="shared" ref="E15:J15" si="4">E14/20</f>
+        <v>11.3</v>
       </c>
       <c r="F15" s="13">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>10.1</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>21.25</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>19.45</v>
       </c>
       <c r="J15" s="13">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>25.7</v>
       </c>
       <c r="K15" s="13"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" s="13"/>
       <c r="B16" s="10" t="s">
         <v>39</v>
       </c>
       <c r="C16" s="37">
         <f>C15+C14</f>
-        <v>0</v>
+        <v>536</v>
       </c>
       <c r="D16" s="37">
-        <f t="shared" ref="D16:J16" si="3">D15+D14</f>
-        <v>0</v>
+        <f t="shared" ref="D16:J16" si="5">D15+D14</f>
+        <v>265.64999999999998</v>
       </c>
       <c r="E16" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>237.3</v>
       </c>
       <c r="F16" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>212.1</v>
       </c>
       <c r="G16" s="37"/>
       <c r="H16" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>446.25</v>
       </c>
       <c r="I16" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>408.45</v>
       </c>
       <c r="J16" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>539.70000000000005</v>
       </c>
       <c r="K16" s="37"/>
     </row>
@@ -7829,37 +8139,37 @@
       </c>
       <c r="C17" s="37">
         <f>C14/40</f>
-        <v>0</v>
+        <v>13.4</v>
       </c>
       <c r="D17" s="37">
-        <f t="shared" ref="D17:J17" si="4">D14/40</f>
-        <v>0</v>
+        <f t="shared" ref="D17:J17" si="6">D14/40</f>
+        <v>6.3250000000000002</v>
       </c>
       <c r="E17" s="37">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>5.65</v>
       </c>
       <c r="F17" s="37">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>5.05</v>
       </c>
       <c r="G17" s="37"/>
       <c r="H17" s="37">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>10.625</v>
       </c>
       <c r="I17" s="37">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>9.7249999999999996</v>
       </c>
       <c r="J17" s="37">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>12.85</v>
       </c>
       <c r="K17" s="37"/>
       <c r="L17" s="36">
         <f>SUM(C17:J17)</f>
-        <v>0</v>
+        <v>63.625</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">

--- a/Final Execution SKU wise.xlsx
+++ b/Final Execution SKU wise.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12A60956-A832-4C05-AF6F-B5E66C593E8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{651D6863-66D4-4DE2-B153-D4B02F619761}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" activeTab="19" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" activeTab="20" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
   </bookViews>
   <sheets>
     <sheet name="last month" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="715" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="74">
   <si>
     <t>Gate Pass</t>
   </si>
@@ -269,6 +269,15 @@
   </si>
   <si>
     <t>Zeshan</t>
+  </si>
+  <si>
+    <t>Umair</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shakoor </t>
+  </si>
+  <si>
+    <t>Bilal</t>
   </si>
 </sst>
 </file>
@@ -720,7 +729,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
@@ -838,6 +847,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1189,7 +1201,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{642BA86E-F402-4488-8063-E587A4C46F24}">
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4.6328125" bestFit="1" customWidth="1"/>
@@ -1220,57 +1232,57 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="52" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="54"/>
+      <c r="B2" s="53" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="55"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="55"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="57"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="58"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="55"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="57"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="58"/>
     </row>
     <row r="5" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="58"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
-      <c r="E5" s="59"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="59"/>
-      <c r="I5" s="59"/>
-      <c r="J5" s="59"/>
-      <c r="K5" s="60"/>
+      <c r="B5" s="59"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
+      <c r="H5" s="60"/>
+      <c r="I5" s="60"/>
+      <c r="J5" s="60"/>
+      <c r="K5" s="61"/>
     </row>
     <row r="6" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="1"/>
@@ -1278,18 +1290,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="61" t="s">
+      <c r="D6" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="63"/>
-      <c r="H6" s="62" t="s">
+      <c r="E6" s="63"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="62"/>
-      <c r="J6" s="62"/>
-      <c r="K6" s="63"/>
+      <c r="I6" s="63"/>
+      <c r="J6" s="63"/>
+      <c r="K6" s="64"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
@@ -1547,6 +1559,41 @@
       <c r="I19" s="26"/>
       <c r="J19" s="26"/>
       <c r="K19" s="26"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B22" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B23" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B24" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B25" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B26" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B27" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B28" t="s">
+        <v>73</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1590,57 +1637,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="52" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="54"/>
+      <c r="B2" s="53" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="55"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="55"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="57"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="58"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="55"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="57"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="58"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="58"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
-      <c r="E5" s="59"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="59"/>
-      <c r="I5" s="59"/>
-      <c r="J5" s="59"/>
-      <c r="K5" s="60"/>
+      <c r="B5" s="59"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
+      <c r="H5" s="60"/>
+      <c r="I5" s="60"/>
+      <c r="J5" s="60"/>
+      <c r="K5" s="61"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -1648,18 +1695,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="61" t="s">
+      <c r="D6" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="63"/>
-      <c r="H6" s="62" t="s">
+      <c r="E6" s="63"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="62"/>
-      <c r="J6" s="62"/>
-      <c r="K6" s="63"/>
+      <c r="I6" s="63"/>
+      <c r="J6" s="63"/>
+      <c r="K6" s="64"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -2120,57 +2167,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="52" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="54"/>
+      <c r="B2" s="53" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="55"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="55"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="57"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="58"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="55"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="57"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="58"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="58"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
-      <c r="E5" s="59"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="59"/>
-      <c r="I5" s="59"/>
-      <c r="J5" s="59"/>
-      <c r="K5" s="60"/>
+      <c r="B5" s="59"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
+      <c r="H5" s="60"/>
+      <c r="I5" s="60"/>
+      <c r="J5" s="60"/>
+      <c r="K5" s="61"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -2178,18 +2225,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="61" t="s">
+      <c r="D6" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="63"/>
-      <c r="H6" s="62" t="s">
+      <c r="E6" s="63"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="62"/>
-      <c r="J6" s="62"/>
-      <c r="K6" s="63"/>
+      <c r="I6" s="63"/>
+      <c r="J6" s="63"/>
+      <c r="K6" s="64"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -2574,57 +2621,57 @@
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="52" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="54"/>
+      <c r="B2" s="53" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="55"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="55"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="57"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="58"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="55"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="57"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="58"/>
     </row>
     <row r="5" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="58"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
-      <c r="E5" s="59"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="59"/>
-      <c r="I5" s="59"/>
-      <c r="J5" s="59"/>
-      <c r="K5" s="60"/>
+      <c r="B5" s="59"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
+      <c r="H5" s="60"/>
+      <c r="I5" s="60"/>
+      <c r="J5" s="60"/>
+      <c r="K5" s="61"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -2632,18 +2679,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="61" t="s">
+      <c r="D6" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="63"/>
-      <c r="H6" s="62" t="s">
+      <c r="E6" s="63"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="62"/>
-      <c r="J6" s="62"/>
-      <c r="K6" s="63"/>
+      <c r="I6" s="63"/>
+      <c r="J6" s="63"/>
+      <c r="K6" s="64"/>
       <c r="Q6" s="33" t="s">
         <v>35</v>
       </c>
@@ -3092,57 +3139,57 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="52" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="54"/>
+      <c r="B2" s="53" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="55"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="55"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="57"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="58"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="55"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="57"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="58"/>
     </row>
     <row r="5" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="58"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
-      <c r="E5" s="59"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="59"/>
-      <c r="I5" s="59"/>
-      <c r="J5" s="59"/>
-      <c r="K5" s="60"/>
+      <c r="B5" s="59"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
+      <c r="H5" s="60"/>
+      <c r="I5" s="60"/>
+      <c r="J5" s="60"/>
+      <c r="K5" s="61"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -3150,18 +3197,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="61" t="s">
+      <c r="D6" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="63"/>
-      <c r="H6" s="62" t="s">
+      <c r="E6" s="63"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="62"/>
-      <c r="J6" s="62"/>
-      <c r="K6" s="63"/>
+      <c r="I6" s="63"/>
+      <c r="J6" s="63"/>
+      <c r="K6" s="64"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -3582,57 +3629,57 @@
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="52" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="54"/>
+      <c r="B2" s="53" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="55"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="55"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="57"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="58"/>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="55"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="57"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="58"/>
     </row>
     <row r="5" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="58"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
-      <c r="E5" s="59"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="59"/>
-      <c r="I5" s="59"/>
-      <c r="J5" s="59"/>
-      <c r="K5" s="60"/>
+      <c r="B5" s="59"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
+      <c r="H5" s="60"/>
+      <c r="I5" s="60"/>
+      <c r="J5" s="60"/>
+      <c r="K5" s="61"/>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -3640,18 +3687,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="61" t="s">
+      <c r="D6" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="63"/>
-      <c r="H6" s="62" t="s">
+      <c r="E6" s="63"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="62"/>
-      <c r="J6" s="62"/>
-      <c r="K6" s="63"/>
+      <c r="I6" s="63"/>
+      <c r="J6" s="63"/>
+      <c r="K6" s="64"/>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -4249,57 +4296,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="52" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="54"/>
+      <c r="B2" s="53" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="55"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="55"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="57"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="58"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="55"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="57"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="58"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="58"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
-      <c r="E5" s="59"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="59"/>
-      <c r="I5" s="59"/>
-      <c r="J5" s="59"/>
-      <c r="K5" s="60"/>
+      <c r="B5" s="59"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
+      <c r="H5" s="60"/>
+      <c r="I5" s="60"/>
+      <c r="J5" s="60"/>
+      <c r="K5" s="61"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -4307,18 +4354,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="61" t="s">
+      <c r="D6" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="63"/>
-      <c r="H6" s="62" t="s">
+      <c r="E6" s="63"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="62"/>
-      <c r="J6" s="62"/>
-      <c r="K6" s="63"/>
+      <c r="I6" s="63"/>
+      <c r="J6" s="63"/>
+      <c r="K6" s="64"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -4673,57 +4720,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="52" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="54"/>
+      <c r="B2" s="53" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="55"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="55"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="57"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="58"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="55"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="57"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="58"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="58"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
-      <c r="E5" s="59"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="59"/>
-      <c r="I5" s="59"/>
-      <c r="J5" s="59"/>
-      <c r="K5" s="60"/>
+      <c r="B5" s="59"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
+      <c r="H5" s="60"/>
+      <c r="I5" s="60"/>
+      <c r="J5" s="60"/>
+      <c r="K5" s="61"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -4731,18 +4778,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="61" t="s">
+      <c r="D6" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="63"/>
-      <c r="H6" s="62" t="s">
+      <c r="E6" s="63"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="62"/>
-      <c r="J6" s="62"/>
-      <c r="K6" s="63"/>
+      <c r="I6" s="63"/>
+      <c r="J6" s="63"/>
+      <c r="K6" s="64"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -5139,57 +5186,57 @@
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="52" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="54"/>
+      <c r="B2" s="53" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="55"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="55"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="57"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="58"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="55"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="57"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="58"/>
     </row>
     <row r="5" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="58"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
-      <c r="E5" s="59"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="59"/>
-      <c r="I5" s="59"/>
-      <c r="J5" s="59"/>
-      <c r="K5" s="60"/>
+      <c r="B5" s="59"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
+      <c r="H5" s="60"/>
+      <c r="I5" s="60"/>
+      <c r="J5" s="60"/>
+      <c r="K5" s="61"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -5197,18 +5244,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="61" t="s">
+      <c r="D6" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="63"/>
-      <c r="H6" s="62" t="s">
+      <c r="E6" s="63"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="62"/>
-      <c r="J6" s="62"/>
-      <c r="K6" s="63"/>
+      <c r="I6" s="63"/>
+      <c r="J6" s="63"/>
+      <c r="K6" s="64"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -5676,57 +5723,57 @@
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="52" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="54"/>
+      <c r="B2" s="53" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="55"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="55"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="57"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="58"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="55"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="57"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="58"/>
     </row>
     <row r="5" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="58"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
-      <c r="E5" s="59"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="59"/>
-      <c r="I5" s="59"/>
-      <c r="J5" s="59"/>
-      <c r="K5" s="60"/>
+      <c r="B5" s="59"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
+      <c r="H5" s="60"/>
+      <c r="I5" s="60"/>
+      <c r="J5" s="60"/>
+      <c r="K5" s="61"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -5734,18 +5781,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="61" t="s">
+      <c r="D6" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="63"/>
-      <c r="H6" s="62" t="s">
+      <c r="E6" s="63"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="62"/>
-      <c r="J6" s="62"/>
-      <c r="K6" s="63"/>
+      <c r="I6" s="63"/>
+      <c r="J6" s="63"/>
+      <c r="K6" s="64"/>
       <c r="R6" t="s">
         <v>63</v>
       </c>
@@ -6194,57 +6241,57 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="52" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="54"/>
+      <c r="B2" s="53" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="55"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="55"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="57"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="58"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="55"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="57"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="58"/>
     </row>
     <row r="5" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="58"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
-      <c r="E5" s="59"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="59"/>
-      <c r="I5" s="59"/>
-      <c r="J5" s="59"/>
-      <c r="K5" s="60"/>
+      <c r="B5" s="59"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
+      <c r="H5" s="60"/>
+      <c r="I5" s="60"/>
+      <c r="J5" s="60"/>
+      <c r="K5" s="61"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -6252,18 +6299,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="61" t="s">
+      <c r="D6" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="63"/>
-      <c r="H6" s="62" t="s">
+      <c r="E6" s="63"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="62"/>
-      <c r="J6" s="62"/>
-      <c r="K6" s="63"/>
+      <c r="I6" s="63"/>
+      <c r="J6" s="63"/>
+      <c r="K6" s="64"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -6736,57 +6783,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="52" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="54"/>
+      <c r="B2" s="53" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="55"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="55"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="57"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="58"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="55"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="57"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="58"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="58"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
-      <c r="E5" s="59"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="59"/>
-      <c r="I5" s="59"/>
-      <c r="J5" s="59"/>
-      <c r="K5" s="60"/>
+      <c r="B5" s="59"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
+      <c r="H5" s="60"/>
+      <c r="I5" s="60"/>
+      <c r="J5" s="60"/>
+      <c r="K5" s="61"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -6794,18 +6841,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="61" t="s">
+      <c r="D6" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="63"/>
-      <c r="H6" s="62" t="s">
+      <c r="E6" s="63"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="62"/>
-      <c r="J6" s="62"/>
-      <c r="K6" s="63"/>
+      <c r="I6" s="63"/>
+      <c r="J6" s="63"/>
+      <c r="K6" s="64"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -7208,57 +7255,57 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="52" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="54"/>
+      <c r="B2" s="53" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="55"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="55"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="57"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="58"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="55"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="57"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="58"/>
     </row>
     <row r="5" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="58"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
-      <c r="E5" s="59"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="59"/>
-      <c r="I5" s="59"/>
-      <c r="J5" s="59"/>
-      <c r="K5" s="60"/>
+      <c r="B5" s="59"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
+      <c r="H5" s="60"/>
+      <c r="I5" s="60"/>
+      <c r="J5" s="60"/>
+      <c r="K5" s="61"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -7266,18 +7313,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="61" t="s">
+      <c r="D6" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="63"/>
-      <c r="H6" s="62" t="s">
+      <c r="E6" s="63"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="62"/>
-      <c r="J6" s="62"/>
-      <c r="K6" s="63"/>
+      <c r="I6" s="63"/>
+      <c r="J6" s="63"/>
+      <c r="K6" s="64"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -7686,57 +7733,57 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="52" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="54"/>
+      <c r="B2" s="53" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="55"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="55"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="57"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="58"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="55"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="57"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="58"/>
     </row>
     <row r="5" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="58"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
-      <c r="E5" s="59"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="59"/>
-      <c r="I5" s="59"/>
-      <c r="J5" s="59"/>
-      <c r="K5" s="60"/>
+      <c r="B5" s="59"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
+      <c r="H5" s="60"/>
+      <c r="I5" s="60"/>
+      <c r="J5" s="60"/>
+      <c r="K5" s="61"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -7744,18 +7791,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="61" t="s">
+      <c r="D6" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="63"/>
-      <c r="H6" s="62" t="s">
+      <c r="E6" s="63"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="62"/>
-      <c r="J6" s="62"/>
-      <c r="K6" s="63"/>
+      <c r="I6" s="63"/>
+      <c r="J6" s="63"/>
+      <c r="K6" s="64"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -7812,9 +7859,7 @@
       <c r="E8" s="12">
         <v>60</v>
       </c>
-      <c r="F8" s="12">
-        <v>0</v>
-      </c>
+      <c r="F8" s="12"/>
       <c r="G8" s="28">
         <f>SUM(D8:F8)/20</f>
         <v>6</v>
@@ -7836,8 +7881,8 @@
         <f>SUM(C8:F8,H8,I8,J8)/40</f>
         <v>15.75</v>
       </c>
-      <c r="M8" s="49">
-        <v>11</v>
+      <c r="M8" s="49" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.35">
@@ -7845,42 +7890,26 @@
       <c r="B9" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="C9" s="12">
-        <v>222</v>
-      </c>
-      <c r="D9" s="12">
-        <v>42</v>
-      </c>
-      <c r="E9" s="12">
-        <v>32</v>
-      </c>
-      <c r="F9" s="12">
-        <v>22</v>
-      </c>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
       <c r="G9" s="28">
         <f t="shared" ref="G9:G12" si="0">SUM(D9:F9)/20</f>
-        <v>4.8</v>
-      </c>
-      <c r="H9" s="12">
-        <v>66</v>
-      </c>
-      <c r="I9" s="12">
-        <v>66</v>
-      </c>
-      <c r="J9" s="12">
-        <v>64</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H9" s="12"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="12"/>
       <c r="K9" s="28">
         <f t="shared" ref="K9:K12" si="1">SUM(H9:J9)/20</f>
-        <v>9.8000000000000007</v>
+        <v>0</v>
       </c>
       <c r="L9">
         <f t="shared" ref="L9:L12" si="2">SUM(C9:F9,H9,I9,J9)/40</f>
-        <v>12.85</v>
-      </c>
-      <c r="M9" s="49">
-        <v>8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M9" s="49"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
@@ -7888,7 +7917,7 @@
         <v>34</v>
       </c>
       <c r="C10" s="12">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="D10" s="12">
         <v>15</v>
@@ -7904,24 +7933,24 @@
         <v>2</v>
       </c>
       <c r="H10" s="12">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="I10" s="12">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="J10" s="12">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="K10" s="28">
         <f t="shared" si="1"/>
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="L10">
         <f t="shared" si="2"/>
-        <v>11.3</v>
-      </c>
-      <c r="M10" s="49">
-        <v>5</v>
+        <v>9</v>
+      </c>
+      <c r="M10" s="49" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.35">
@@ -7930,40 +7959,40 @@
         <v>32</v>
       </c>
       <c r="C11" s="12">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="D11" s="12">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="E11" s="12">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="F11" s="12">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="G11" s="28">
         <f t="shared" si="0"/>
-        <v>4.6500000000000004</v>
+        <v>0.9</v>
       </c>
       <c r="H11" s="12">
-        <v>150</v>
+        <v>115</v>
       </c>
       <c r="I11" s="12">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="J11" s="12">
-        <v>140</v>
+        <v>115</v>
       </c>
       <c r="K11" s="28">
         <f t="shared" si="1"/>
-        <v>18.25</v>
+        <v>14</v>
       </c>
       <c r="L11">
         <f t="shared" si="2"/>
-        <v>12</v>
-      </c>
-      <c r="M11" s="42">
-        <v>7</v>
+        <v>7.75</v>
+      </c>
+      <c r="M11" s="42" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.35">
@@ -7972,39 +8001,25 @@
         <v>9</v>
       </c>
       <c r="C12" s="12"/>
-      <c r="D12" s="12">
-        <v>105</v>
-      </c>
-      <c r="E12" s="12">
-        <v>93</v>
-      </c>
-      <c r="F12" s="12">
-        <v>134</v>
-      </c>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
       <c r="G12" s="28">
         <f t="shared" si="0"/>
-        <v>16.600000000000001</v>
-      </c>
-      <c r="H12" s="12">
-        <v>29</v>
-      </c>
-      <c r="I12" s="12">
-        <v>68</v>
-      </c>
-      <c r="J12" s="12">
-        <v>40</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="12"/>
       <c r="K12" s="28">
         <f t="shared" si="1"/>
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="L12">
         <f t="shared" si="2"/>
-        <v>11.725</v>
-      </c>
-      <c r="M12" s="42">
-        <v>8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M12" s="42"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
@@ -8024,43 +8039,43 @@
       <c r="B14" s="10"/>
       <c r="C14" s="14">
         <f t="shared" ref="C14:K14" si="3">SUM(C8:C13)</f>
-        <v>536</v>
+        <v>292</v>
       </c>
       <c r="D14" s="14">
         <f t="shared" si="3"/>
-        <v>253</v>
+        <v>81</v>
       </c>
       <c r="E14" s="14">
         <f t="shared" si="3"/>
-        <v>226</v>
+        <v>76</v>
       </c>
       <c r="F14" s="14">
         <f t="shared" si="3"/>
-        <v>202</v>
+        <v>21</v>
       </c>
       <c r="G14" s="14">
         <f t="shared" si="3"/>
-        <v>34.050000000000004</v>
+        <v>8.9</v>
       </c>
       <c r="H14" s="14">
         <f t="shared" si="3"/>
-        <v>425</v>
+        <v>275</v>
       </c>
       <c r="I14" s="14">
         <f t="shared" si="3"/>
-        <v>389</v>
+        <v>210</v>
       </c>
       <c r="J14" s="14">
         <f t="shared" si="3"/>
-        <v>514</v>
+        <v>345</v>
       </c>
       <c r="K14" s="14">
         <f t="shared" si="3"/>
-        <v>66.399999999999991</v>
+        <v>41.5</v>
       </c>
       <c r="L14" s="36">
         <f>C14+D14+E14+F14+H14+I14+J14</f>
-        <v>2545</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">
@@ -8071,28 +8086,28 @@
       <c r="C15" s="13"/>
       <c r="D15" s="13">
         <f>D14/20</f>
-        <v>12.65</v>
+        <v>4.05</v>
       </c>
       <c r="E15" s="13">
         <f t="shared" ref="E15:J15" si="4">E14/20</f>
-        <v>11.3</v>
+        <v>3.8</v>
       </c>
       <c r="F15" s="13">
         <f t="shared" si="4"/>
-        <v>10.1</v>
+        <v>1.05</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13">
         <f t="shared" si="4"/>
-        <v>21.25</v>
+        <v>13.75</v>
       </c>
       <c r="I15" s="13">
         <f t="shared" si="4"/>
-        <v>19.45</v>
+        <v>10.5</v>
       </c>
       <c r="J15" s="13">
         <f t="shared" si="4"/>
-        <v>25.7</v>
+        <v>17.25</v>
       </c>
       <c r="K15" s="13"/>
     </row>
@@ -8103,32 +8118,32 @@
       </c>
       <c r="C16" s="37">
         <f>C15+C14</f>
-        <v>536</v>
+        <v>292</v>
       </c>
       <c r="D16" s="37">
         <f t="shared" ref="D16:J16" si="5">D15+D14</f>
-        <v>265.64999999999998</v>
+        <v>85.05</v>
       </c>
       <c r="E16" s="37">
         <f t="shared" si="5"/>
-        <v>237.3</v>
+        <v>79.8</v>
       </c>
       <c r="F16" s="37">
         <f t="shared" si="5"/>
-        <v>212.1</v>
+        <v>22.05</v>
       </c>
       <c r="G16" s="37"/>
       <c r="H16" s="37">
         <f t="shared" si="5"/>
-        <v>446.25</v>
+        <v>288.75</v>
       </c>
       <c r="I16" s="37">
         <f t="shared" si="5"/>
-        <v>408.45</v>
+        <v>220.5</v>
       </c>
       <c r="J16" s="37">
         <f t="shared" si="5"/>
-        <v>539.70000000000005</v>
+        <v>362.25</v>
       </c>
       <c r="K16" s="37"/>
     </row>
@@ -8139,37 +8154,37 @@
       </c>
       <c r="C17" s="37">
         <f>C14/40</f>
-        <v>13.4</v>
+        <v>7.3</v>
       </c>
       <c r="D17" s="37">
         <f t="shared" ref="D17:J17" si="6">D14/40</f>
-        <v>6.3250000000000002</v>
+        <v>2.0249999999999999</v>
       </c>
       <c r="E17" s="37">
         <f t="shared" si="6"/>
-        <v>5.65</v>
+        <v>1.9</v>
       </c>
       <c r="F17" s="37">
         <f t="shared" si="6"/>
-        <v>5.05</v>
+        <v>0.52500000000000002</v>
       </c>
       <c r="G17" s="37"/>
       <c r="H17" s="37">
         <f t="shared" si="6"/>
-        <v>10.625</v>
+        <v>6.875</v>
       </c>
       <c r="I17" s="37">
         <f t="shared" si="6"/>
-        <v>9.7249999999999996</v>
+        <v>5.25</v>
       </c>
       <c r="J17" s="37">
         <f t="shared" si="6"/>
-        <v>12.85</v>
+        <v>8.625</v>
       </c>
       <c r="K17" s="37"/>
       <c r="L17" s="36">
         <f>SUM(C17:J17)</f>
-        <v>63.625</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">
@@ -8230,57 +8245,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="52" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="54"/>
+      <c r="B2" s="53" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="55"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="55"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="57"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="58"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="55"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="57"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="58"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="58"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
-      <c r="E5" s="59"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="59"/>
-      <c r="I5" s="59"/>
-      <c r="J5" s="59"/>
-      <c r="K5" s="60"/>
+      <c r="B5" s="59"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
+      <c r="H5" s="60"/>
+      <c r="I5" s="60"/>
+      <c r="J5" s="60"/>
+      <c r="K5" s="61"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -8288,18 +8303,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="61" t="s">
+      <c r="D6" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="63"/>
-      <c r="H6" s="62" t="s">
+      <c r="E6" s="63"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="62"/>
-      <c r="J6" s="62"/>
-      <c r="K6" s="63"/>
+      <c r="I6" s="63"/>
+      <c r="J6" s="63"/>
+      <c r="K6" s="64"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -8341,18 +8356,18 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="27"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
+      <c r="B8" s="48"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
       <c r="G8" s="28">
         <f>SUM(D8:F8)/20</f>
         <v>0</v>
       </c>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="12"/>
+      <c r="H8" s="29"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="29"/>
       <c r="K8" s="28">
         <f>SUM(H8:J8)/20</f>
         <v>0</v>
@@ -8364,15 +8379,15 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" s="27"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
+      <c r="B9" s="48"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="29"/>
       <c r="G9" s="28"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12"/>
+      <c r="H9" s="29"/>
+      <c r="I9" s="29"/>
+      <c r="J9" s="29"/>
       <c r="K9" s="28"/>
       <c r="L9">
         <f t="shared" ref="L9:L12" si="0">SUM(C9:F9,H9,I9,J9)/40</f>
@@ -8381,15 +8396,15 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
+      <c r="B10" s="48"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="29"/>
       <c r="G10" s="28"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="12"/>
+      <c r="H10" s="29"/>
+      <c r="I10" s="29"/>
+      <c r="J10" s="29"/>
       <c r="K10" s="28"/>
       <c r="L10">
         <f t="shared" si="0"/>
@@ -8624,7 +8639,7 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F16114E-0AD8-4652-8B31-88E6EC8B6522}">
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.90625" bestFit="1" customWidth="1"/>
@@ -8639,7 +8654,7 @@
     <col min="11" max="11" width="5.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -8652,80 +8667,80 @@
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="52" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="54"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B2" s="53" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="55"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="55"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="57"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B3" s="56"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="58"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="55"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="57"/>
-    </row>
-    <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B4" s="56"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="58"/>
+    </row>
+    <row r="5" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="58"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
-      <c r="E5" s="59"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="59"/>
-      <c r="I5" s="59"/>
-      <c r="J5" s="59"/>
-      <c r="K5" s="60"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B5" s="59"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
+      <c r="H5" s="60"/>
+      <c r="I5" s="60"/>
+      <c r="J5" s="60"/>
+      <c r="K5" s="61"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
       <c r="B6" s="2"/>
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="61" t="s">
+      <c r="D6" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="63"/>
-      <c r="H6" s="62" t="s">
+      <c r="E6" s="63"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="62"/>
-      <c r="J6" s="62"/>
-      <c r="K6" s="63"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="I6" s="63"/>
+      <c r="J6" s="63"/>
+      <c r="K6" s="64"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
         <v>4</v>
       </c>
@@ -8759,102 +8774,220 @@
       <c r="K7" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="L7" t="s">
+      <c r="L7" s="52" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M7" s="52" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" s="27"/>
-      <c r="B8" s="10"/>
+      <c r="B8" s="10" t="s">
+        <v>71</v>
+      </c>
       <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
+      <c r="D8" s="12">
+        <v>118</v>
+      </c>
+      <c r="E8" s="12">
+        <v>124</v>
+      </c>
+      <c r="F8" s="12">
+        <v>104</v>
+      </c>
       <c r="G8" s="28">
         <f>SUM(D8:F8)/20</f>
-        <v>0</v>
-      </c>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="12"/>
+        <v>17.3</v>
+      </c>
+      <c r="H8" s="12">
+        <v>115</v>
+      </c>
+      <c r="I8" s="12">
+        <v>120</v>
+      </c>
+      <c r="J8" s="12">
+        <v>110</v>
+      </c>
       <c r="K8" s="28">
         <f>SUM(H8:J8)/20</f>
-        <v>0</v>
+        <v>17.25</v>
       </c>
       <c r="L8">
         <f>SUM(C8:F8,H8,I8,J8)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+        <v>17.274999999999999</v>
+      </c>
+      <c r="M8" s="52">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" s="27"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12"/>
-      <c r="K9" s="28"/>
+      <c r="B9" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="12">
+        <v>40</v>
+      </c>
+      <c r="D9" s="12">
+        <v>50</v>
+      </c>
+      <c r="E9" s="12">
+        <v>40</v>
+      </c>
+      <c r="F9" s="12">
+        <v>50</v>
+      </c>
+      <c r="G9" s="28">
+        <f t="shared" ref="G9:G12" si="0">SUM(D9:F9)/20</f>
+        <v>7</v>
+      </c>
+      <c r="H9" s="12">
+        <v>110</v>
+      </c>
+      <c r="I9" s="12">
+        <v>100</v>
+      </c>
+      <c r="J9" s="12">
+        <v>90</v>
+      </c>
+      <c r="K9" s="28">
+        <f t="shared" ref="K9:K12" si="1">SUM(H9:J9)/20</f>
+        <v>15</v>
+      </c>
       <c r="L9">
-        <f t="shared" ref="L9:L12" si="0">SUM(C9:F9,H9,I9,J9)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+        <f t="shared" ref="L9:L12" si="2">SUM(C9:F9,H9,I9,J9)/40</f>
+        <v>12</v>
+      </c>
+      <c r="M9" s="52">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
-      <c r="B10" s="10"/>
+      <c r="B10" s="10" t="s">
+        <v>32</v>
+      </c>
       <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="28"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="28"/>
+      <c r="D10" s="12">
+        <v>135</v>
+      </c>
+      <c r="E10" s="12">
+        <v>130</v>
+      </c>
+      <c r="F10" s="12">
+        <v>147</v>
+      </c>
+      <c r="G10" s="28">
+        <f t="shared" si="0"/>
+        <v>20.6</v>
+      </c>
+      <c r="H10" s="12">
+        <v>130</v>
+      </c>
+      <c r="I10" s="12">
+        <v>84</v>
+      </c>
+      <c r="J10" s="12">
+        <v>90</v>
+      </c>
+      <c r="K10" s="28">
+        <f t="shared" si="1"/>
+        <v>15.2</v>
+      </c>
       <c r="L10">
+        <f t="shared" si="2"/>
+        <v>17.899999999999999</v>
+      </c>
+      <c r="M10" s="52">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A11" s="11"/>
+      <c r="B11" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11" s="12">
+        <v>130</v>
+      </c>
+      <c r="D11" s="12">
+        <v>55</v>
+      </c>
+      <c r="E11" s="12">
+        <v>56</v>
+      </c>
+      <c r="F11" s="12">
+        <v>95</v>
+      </c>
+      <c r="G11" s="28">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A11" s="11"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="12"/>
-      <c r="K11" s="12"/>
+        <v>10.3</v>
+      </c>
+      <c r="H11" s="12">
+        <v>85</v>
+      </c>
+      <c r="I11" s="12">
+        <v>70</v>
+      </c>
+      <c r="J11" s="12">
+        <v>85</v>
+      </c>
+      <c r="K11" s="28">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
       <c r="L11">
+        <f t="shared" si="2"/>
+        <v>14.4</v>
+      </c>
+      <c r="M11" s="52">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A12" s="11"/>
+      <c r="B12" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="12">
+        <v>60</v>
+      </c>
+      <c r="D12" s="12">
+        <v>38</v>
+      </c>
+      <c r="E12" s="12">
+        <v>38</v>
+      </c>
+      <c r="F12" s="12">
+        <v>38</v>
+      </c>
+      <c r="G12" s="28">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A12" s="11"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="12"/>
-      <c r="K12" s="12"/>
+        <v>5.7</v>
+      </c>
+      <c r="H12" s="12">
+        <v>28</v>
+      </c>
+      <c r="I12" s="12">
+        <v>28</v>
+      </c>
+      <c r="J12" s="12">
+        <v>29</v>
+      </c>
+      <c r="K12" s="28">
+        <f t="shared" si="1"/>
+        <v>4.25</v>
+      </c>
       <c r="L12">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v>6.4749999999999996</v>
+      </c>
+      <c r="M12" s="52">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
       <c r="B13" s="11"/>
       <c r="C13" s="12"/>
@@ -8867,51 +9000,51 @@
       <c r="J13" s="12"/>
       <c r="K13" s="12"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:K14" si="1">SUM(C8:C13)</f>
-        <v>0</v>
+        <f t="shared" ref="C14:K14" si="3">SUM(C8:C13)</f>
+        <v>230</v>
       </c>
       <c r="D14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>396</v>
       </c>
       <c r="E14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>388</v>
       </c>
       <c r="F14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>434</v>
       </c>
       <c r="G14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>60.900000000000006</v>
       </c>
       <c r="H14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>468</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>402</v>
       </c>
       <c r="J14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>404</v>
       </c>
       <c r="K14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>63.7</v>
       </c>
       <c r="L14" s="36">
         <f>C14+D14+E14+F14+H14+I14+J14</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+        <v>2722</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" s="13"/>
       <c r="B15" s="10" t="s">
         <v>40</v>
@@ -8919,64 +9052,64 @@
       <c r="C15" s="13"/>
       <c r="D15" s="13">
         <f>D14/20</f>
-        <v>0</v>
+        <v>19.8</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:J15" si="2">E14/20</f>
-        <v>0</v>
+        <f t="shared" ref="E15:J15" si="4">E14/20</f>
+        <v>19.399999999999999</v>
       </c>
       <c r="F15" s="13">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>21.7</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>23.4</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>20.100000000000001</v>
       </c>
       <c r="J15" s="13">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>20.2</v>
       </c>
       <c r="K15" s="13"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" s="13"/>
       <c r="B16" s="10" t="s">
         <v>39</v>
       </c>
       <c r="C16" s="37">
         <f>C15+C14</f>
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="D16" s="37">
-        <f t="shared" ref="D16:J16" si="3">D15+D14</f>
-        <v>0</v>
+        <f t="shared" ref="D16:J16" si="5">D15+D14</f>
+        <v>415.8</v>
       </c>
       <c r="E16" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>407.4</v>
       </c>
       <c r="F16" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>455.7</v>
       </c>
       <c r="G16" s="37"/>
       <c r="H16" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>491.4</v>
       </c>
       <c r="I16" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>422.1</v>
       </c>
       <c r="J16" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>424.2</v>
       </c>
       <c r="K16" s="37"/>
     </row>
@@ -8987,37 +9120,37 @@
       </c>
       <c r="C17" s="37">
         <f>C14/40</f>
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="D17" s="37">
-        <f t="shared" ref="D17:J17" si="4">D14/40</f>
-        <v>0</v>
+        <f t="shared" ref="D17:J17" si="6">D14/40</f>
+        <v>9.9</v>
       </c>
       <c r="E17" s="37">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>9.6999999999999993</v>
       </c>
       <c r="F17" s="37">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>10.85</v>
       </c>
       <c r="G17" s="37"/>
       <c r="H17" s="37">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>11.7</v>
       </c>
       <c r="I17" s="37">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>10.050000000000001</v>
       </c>
       <c r="J17" s="37">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>10.1</v>
       </c>
       <c r="K17" s="37"/>
       <c r="L17" s="36">
         <f>SUM(C17:J17)</f>
-        <v>0</v>
+        <v>68.05</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">
@@ -9043,6 +9176,18 @@
     <mergeCell ref="H6:K6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{7C4076FE-357D-47D3-8F62-0DB2CEAFAFF4}">
+          <x14:formula1>
+            <xm:f>'last month'!$B$22:$B$28</xm:f>
+          </x14:formula1>
+          <xm:sqref>B8:B12</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
@@ -9078,57 +9223,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="52" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="54"/>
+      <c r="B2" s="53" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="55"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="55"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="57"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="58"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="55"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="57"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="58"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="58"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
-      <c r="E5" s="59"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="59"/>
-      <c r="I5" s="59"/>
-      <c r="J5" s="59"/>
-      <c r="K5" s="60"/>
+      <c r="B5" s="59"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
+      <c r="H5" s="60"/>
+      <c r="I5" s="60"/>
+      <c r="J5" s="60"/>
+      <c r="K5" s="61"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -9136,18 +9281,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="61" t="s">
+      <c r="D6" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="63"/>
-      <c r="H6" s="62" t="s">
+      <c r="E6" s="63"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="62"/>
-      <c r="J6" s="62"/>
-      <c r="K6" s="63"/>
+      <c r="I6" s="63"/>
+      <c r="J6" s="63"/>
+      <c r="K6" s="64"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -9502,57 +9647,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="52" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="54"/>
+      <c r="B2" s="53" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="55"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="55"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="57"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="58"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="55"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="57"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="58"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="58"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
-      <c r="E5" s="59"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="59"/>
-      <c r="I5" s="59"/>
-      <c r="J5" s="59"/>
-      <c r="K5" s="60"/>
+      <c r="B5" s="59"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
+      <c r="H5" s="60"/>
+      <c r="I5" s="60"/>
+      <c r="J5" s="60"/>
+      <c r="K5" s="61"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -9560,18 +9705,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="61" t="s">
+      <c r="D6" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="63"/>
-      <c r="H6" s="62" t="s">
+      <c r="E6" s="63"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="62"/>
-      <c r="J6" s="62"/>
-      <c r="K6" s="63"/>
+      <c r="I6" s="63"/>
+      <c r="J6" s="63"/>
+      <c r="K6" s="64"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -9926,57 +10071,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="52" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="54"/>
+      <c r="B2" s="53" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="55"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="55"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="57"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="58"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="55"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="57"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="58"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="58"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
-      <c r="E5" s="59"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="59"/>
-      <c r="I5" s="59"/>
-      <c r="J5" s="59"/>
-      <c r="K5" s="60"/>
+      <c r="B5" s="59"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
+      <c r="H5" s="60"/>
+      <c r="I5" s="60"/>
+      <c r="J5" s="60"/>
+      <c r="K5" s="61"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -9984,18 +10129,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="61" t="s">
+      <c r="D6" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="63"/>
-      <c r="H6" s="62" t="s">
+      <c r="E6" s="63"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="62"/>
-      <c r="J6" s="62"/>
-      <c r="K6" s="63"/>
+      <c r="I6" s="63"/>
+      <c r="J6" s="63"/>
+      <c r="K6" s="64"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -10350,57 +10495,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="52" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="54"/>
+      <c r="B2" s="53" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="55"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="55"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="57"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="58"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="55"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="57"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="58"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="58"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
-      <c r="E5" s="59"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="59"/>
-      <c r="I5" s="59"/>
-      <c r="J5" s="59"/>
-      <c r="K5" s="60"/>
+      <c r="B5" s="59"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
+      <c r="H5" s="60"/>
+      <c r="I5" s="60"/>
+      <c r="J5" s="60"/>
+      <c r="K5" s="61"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -10408,18 +10553,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="61" t="s">
+      <c r="D6" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="63"/>
-      <c r="H6" s="62" t="s">
+      <c r="E6" s="63"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="62"/>
-      <c r="J6" s="62"/>
-      <c r="K6" s="63"/>
+      <c r="I6" s="63"/>
+      <c r="J6" s="63"/>
+      <c r="K6" s="64"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -10774,57 +10919,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="52" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="54"/>
+      <c r="B2" s="53" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="55"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="55"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="57"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="58"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="55"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="57"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="58"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="58"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
-      <c r="E5" s="59"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="59"/>
-      <c r="I5" s="59"/>
-      <c r="J5" s="59"/>
-      <c r="K5" s="60"/>
+      <c r="B5" s="59"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
+      <c r="H5" s="60"/>
+      <c r="I5" s="60"/>
+      <c r="J5" s="60"/>
+      <c r="K5" s="61"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -10832,18 +10977,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="61" t="s">
+      <c r="D6" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="63"/>
-      <c r="H6" s="62" t="s">
+      <c r="E6" s="63"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="62"/>
-      <c r="J6" s="62"/>
-      <c r="K6" s="63"/>
+      <c r="I6" s="63"/>
+      <c r="J6" s="63"/>
+      <c r="K6" s="64"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -11198,57 +11343,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="52" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="54"/>
+      <c r="B2" s="53" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="55"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="55"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="57"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="58"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="55"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="57"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="58"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="58"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
-      <c r="E5" s="59"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="59"/>
-      <c r="I5" s="59"/>
-      <c r="J5" s="59"/>
-      <c r="K5" s="60"/>
+      <c r="B5" s="59"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
+      <c r="H5" s="60"/>
+      <c r="I5" s="60"/>
+      <c r="J5" s="60"/>
+      <c r="K5" s="61"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -11256,18 +11401,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="61" t="s">
+      <c r="D6" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="63"/>
-      <c r="H6" s="62" t="s">
+      <c r="E6" s="63"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="62"/>
-      <c r="J6" s="62"/>
-      <c r="K6" s="63"/>
+      <c r="I6" s="63"/>
+      <c r="J6" s="63"/>
+      <c r="K6" s="64"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -11622,57 +11767,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="52" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="54"/>
+      <c r="B2" s="53" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="55"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="55"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="57"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="58"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="55"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="57"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="58"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="58"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
-      <c r="E5" s="59"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="59"/>
-      <c r="I5" s="59"/>
-      <c r="J5" s="59"/>
-      <c r="K5" s="60"/>
+      <c r="B5" s="59"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
+      <c r="H5" s="60"/>
+      <c r="I5" s="60"/>
+      <c r="J5" s="60"/>
+      <c r="K5" s="61"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -11680,18 +11825,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="61" t="s">
+      <c r="D6" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="63"/>
-      <c r="H6" s="62" t="s">
+      <c r="E6" s="63"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="62"/>
-      <c r="J6" s="62"/>
-      <c r="K6" s="63"/>
+      <c r="I6" s="63"/>
+      <c r="J6" s="63"/>
+      <c r="K6" s="64"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -12108,57 +12253,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="52" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="54"/>
+      <c r="B2" s="53" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="55"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="55"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="57"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="58"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="55"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="57"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="58"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="58"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
-      <c r="E5" s="59"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="59"/>
-      <c r="I5" s="59"/>
-      <c r="J5" s="59"/>
-      <c r="K5" s="60"/>
+      <c r="B5" s="59"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
+      <c r="H5" s="60"/>
+      <c r="I5" s="60"/>
+      <c r="J5" s="60"/>
+      <c r="K5" s="61"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -12166,18 +12311,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="61" t="s">
+      <c r="D6" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="63"/>
-      <c r="H6" s="62" t="s">
+      <c r="E6" s="63"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="62"/>
-      <c r="J6" s="62"/>
-      <c r="K6" s="63"/>
+      <c r="I6" s="63"/>
+      <c r="J6" s="63"/>
+      <c r="K6" s="64"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -12532,57 +12677,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="52" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="54"/>
+      <c r="B2" s="53" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="55"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="55"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="57"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="58"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="55"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="57"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="58"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="58"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
-      <c r="E5" s="59"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="59"/>
-      <c r="I5" s="59"/>
-      <c r="J5" s="59"/>
-      <c r="K5" s="60"/>
+      <c r="B5" s="59"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
+      <c r="H5" s="60"/>
+      <c r="I5" s="60"/>
+      <c r="J5" s="60"/>
+      <c r="K5" s="61"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -12590,18 +12735,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="61" t="s">
+      <c r="D6" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="63"/>
-      <c r="H6" s="62" t="s">
+      <c r="E6" s="63"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="62"/>
-      <c r="J6" s="62"/>
-      <c r="K6" s="63"/>
+      <c r="I6" s="63"/>
+      <c r="J6" s="63"/>
+      <c r="K6" s="64"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -12957,57 +13102,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="52" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="54"/>
+      <c r="B2" s="53" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="55"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="55"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="57"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="58"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="55"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="57"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="58"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="58"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
-      <c r="E5" s="59"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="59"/>
-      <c r="I5" s="59"/>
-      <c r="J5" s="59"/>
-      <c r="K5" s="60"/>
+      <c r="B5" s="59"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
+      <c r="H5" s="60"/>
+      <c r="I5" s="60"/>
+      <c r="J5" s="60"/>
+      <c r="K5" s="61"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -13015,18 +13160,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="61" t="s">
+      <c r="D6" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="63"/>
-      <c r="H6" s="62" t="s">
+      <c r="E6" s="63"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="62"/>
-      <c r="J6" s="62"/>
-      <c r="K6" s="63"/>
+      <c r="I6" s="63"/>
+      <c r="J6" s="63"/>
+      <c r="K6" s="64"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -13381,57 +13526,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="52" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="54"/>
+      <c r="B2" s="53" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="55"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="55"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="57"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="58"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="55"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="57"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="58"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="58"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
-      <c r="E5" s="59"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="59"/>
-      <c r="I5" s="59"/>
-      <c r="J5" s="59"/>
-      <c r="K5" s="60"/>
+      <c r="B5" s="59"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
+      <c r="H5" s="60"/>
+      <c r="I5" s="60"/>
+      <c r="J5" s="60"/>
+      <c r="K5" s="61"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -13439,18 +13584,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="61" t="s">
+      <c r="D6" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="63"/>
-      <c r="H6" s="62" t="s">
+      <c r="E6" s="63"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="62"/>
-      <c r="J6" s="62"/>
-      <c r="K6" s="63"/>
+      <c r="I6" s="63"/>
+      <c r="J6" s="63"/>
+      <c r="K6" s="64"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -13920,57 +14065,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="52" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="54"/>
+      <c r="B2" s="53" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="55"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="55"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="57"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="58"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="55"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="57"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="58"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="58"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
-      <c r="E5" s="59"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="59"/>
-      <c r="I5" s="59"/>
-      <c r="J5" s="59"/>
-      <c r="K5" s="60"/>
+      <c r="B5" s="59"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
+      <c r="H5" s="60"/>
+      <c r="I5" s="60"/>
+      <c r="J5" s="60"/>
+      <c r="K5" s="61"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -13978,18 +14123,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="61" t="s">
+      <c r="D6" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="63"/>
-      <c r="H6" s="62" t="s">
+      <c r="E6" s="63"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="62"/>
-      <c r="J6" s="62"/>
-      <c r="K6" s="63"/>
+      <c r="I6" s="63"/>
+      <c r="J6" s="63"/>
+      <c r="K6" s="64"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -14431,57 +14576,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="52" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="54"/>
+      <c r="B2" s="53" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="55"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="55"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="57"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="58"/>
     </row>
     <row r="4" spans="1:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="55"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="57"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="58"/>
     </row>
     <row r="5" spans="1:12" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="58"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
-      <c r="E5" s="59"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="59"/>
-      <c r="I5" s="59"/>
-      <c r="J5" s="59"/>
-      <c r="K5" s="60"/>
+      <c r="B5" s="59"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
+      <c r="H5" s="60"/>
+      <c r="I5" s="60"/>
+      <c r="J5" s="60"/>
+      <c r="K5" s="61"/>
     </row>
     <row r="6" spans="1:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -14489,18 +14634,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="61" t="s">
+      <c r="D6" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="63"/>
-      <c r="H6" s="62" t="s">
+      <c r="E6" s="63"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="62"/>
-      <c r="J6" s="62"/>
-      <c r="K6" s="63"/>
+      <c r="I6" s="63"/>
+      <c r="J6" s="63"/>
+      <c r="K6" s="64"/>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -14907,57 +15052,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="52" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="54"/>
+      <c r="B2" s="53" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="55"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="55"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="57"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="58"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="55"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="57"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="58"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="58"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
-      <c r="E5" s="59"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="59"/>
-      <c r="I5" s="59"/>
-      <c r="J5" s="59"/>
-      <c r="K5" s="60"/>
+      <c r="B5" s="59"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
+      <c r="H5" s="60"/>
+      <c r="I5" s="60"/>
+      <c r="J5" s="60"/>
+      <c r="K5" s="61"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -14965,18 +15110,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="61" t="s">
+      <c r="D6" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="63"/>
-      <c r="H6" s="62" t="s">
+      <c r="E6" s="63"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="62"/>
-      <c r="J6" s="62"/>
-      <c r="K6" s="63"/>
+      <c r="I6" s="63"/>
+      <c r="J6" s="63"/>
+      <c r="K6" s="64"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -15335,57 +15480,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="52" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="54"/>
+      <c r="B2" s="53" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="55"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="55"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="57"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="58"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="55"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="57"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="58"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="58"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
-      <c r="E5" s="59"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="59"/>
-      <c r="I5" s="59"/>
-      <c r="J5" s="59"/>
-      <c r="K5" s="60"/>
+      <c r="B5" s="59"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
+      <c r="H5" s="60"/>
+      <c r="I5" s="60"/>
+      <c r="J5" s="60"/>
+      <c r="K5" s="61"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -15393,18 +15538,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="61" t="s">
+      <c r="D6" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="63"/>
-      <c r="H6" s="62" t="s">
+      <c r="E6" s="63"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="62"/>
-      <c r="J6" s="62"/>
-      <c r="K6" s="63"/>
+      <c r="I6" s="63"/>
+      <c r="J6" s="63"/>
+      <c r="K6" s="64"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -15753,57 +15898,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="52" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="54"/>
+      <c r="B2" s="53" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="55"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="55"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="57"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="58"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="55"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="57"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="58"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="58"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
-      <c r="E5" s="59"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="59"/>
-      <c r="I5" s="59"/>
-      <c r="J5" s="59"/>
-      <c r="K5" s="60"/>
+      <c r="B5" s="59"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
+      <c r="H5" s="60"/>
+      <c r="I5" s="60"/>
+      <c r="J5" s="60"/>
+      <c r="K5" s="61"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -15811,18 +15956,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="61" t="s">
+      <c r="D6" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="63"/>
-      <c r="H6" s="62" t="s">
+      <c r="E6" s="63"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="62"/>
-      <c r="J6" s="62"/>
-      <c r="K6" s="63"/>
+      <c r="I6" s="63"/>
+      <c r="J6" s="63"/>
+      <c r="K6" s="64"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">

--- a/Final Execution SKU wise.xlsx
+++ b/Final Execution SKU wise.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{651D6863-66D4-4DE2-B153-D4B02F619761}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{645F0B82-F0DC-4C39-AFD4-4452506F5AA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" activeTab="20" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
   </bookViews>

--- a/Final Execution SKU wise.xlsx
+++ b/Final Execution SKU wise.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{645F0B82-F0DC-4C39-AFD4-4452506F5AA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8007181-B4D0-40C3-B261-F538C8F2C3FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" activeTab="20" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" activeTab="23" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
   </bookViews>
   <sheets>
     <sheet name="last month" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="75">
   <si>
     <t>Gate Pass</t>
   </si>
@@ -278,6 +278,9 @@
   </si>
   <si>
     <t>Bilal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aslam </t>
   </si>
 </sst>
 </file>
@@ -729,7 +732,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
@@ -851,6 +854,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1232,57 +1236,57 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="53" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="55"/>
+      <c r="B2" s="54" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="56"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="56"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="58"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="59"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="56"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="58"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="59"/>
     </row>
     <row r="5" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="59"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
-      <c r="H5" s="60"/>
-      <c r="I5" s="60"/>
-      <c r="J5" s="60"/>
-      <c r="K5" s="61"/>
+      <c r="B5" s="60"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="61"/>
+      <c r="K5" s="62"/>
     </row>
     <row r="6" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="1"/>
@@ -1290,18 +1294,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="62" t="s">
+      <c r="D6" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="63"/>
-      <c r="F6" s="63"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="63" t="s">
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="63"/>
-      <c r="J6" s="63"/>
-      <c r="K6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
+      <c r="K6" s="65"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
@@ -1637,57 +1641,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="53" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="55"/>
+      <c r="B2" s="54" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="56"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="56"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="58"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="59"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="56"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="58"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="59"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="59"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
-      <c r="H5" s="60"/>
-      <c r="I5" s="60"/>
-      <c r="J5" s="60"/>
-      <c r="K5" s="61"/>
+      <c r="B5" s="60"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="61"/>
+      <c r="K5" s="62"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -1695,18 +1699,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="62" t="s">
+      <c r="D6" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="63"/>
-      <c r="F6" s="63"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="63" t="s">
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="63"/>
-      <c r="J6" s="63"/>
-      <c r="K6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
+      <c r="K6" s="65"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -2167,57 +2171,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="53" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="55"/>
+      <c r="B2" s="54" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="56"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="56"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="58"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="59"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="56"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="58"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="59"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="59"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
-      <c r="H5" s="60"/>
-      <c r="I5" s="60"/>
-      <c r="J5" s="60"/>
-      <c r="K5" s="61"/>
+      <c r="B5" s="60"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="61"/>
+      <c r="K5" s="62"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -2225,18 +2229,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="62" t="s">
+      <c r="D6" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="63"/>
-      <c r="F6" s="63"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="63" t="s">
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="63"/>
-      <c r="J6" s="63"/>
-      <c r="K6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
+      <c r="K6" s="65"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -2621,57 +2625,57 @@
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="53" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="55"/>
+      <c r="B2" s="54" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="56"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="56"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="58"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="59"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="56"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="58"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="59"/>
     </row>
     <row r="5" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="59"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
-      <c r="H5" s="60"/>
-      <c r="I5" s="60"/>
-      <c r="J5" s="60"/>
-      <c r="K5" s="61"/>
+      <c r="B5" s="60"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="61"/>
+      <c r="K5" s="62"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -2679,18 +2683,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="62" t="s">
+      <c r="D6" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="63"/>
-      <c r="F6" s="63"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="63" t="s">
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="63"/>
-      <c r="J6" s="63"/>
-      <c r="K6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
+      <c r="K6" s="65"/>
       <c r="Q6" s="33" t="s">
         <v>35</v>
       </c>
@@ -3139,57 +3143,57 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="53" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="55"/>
+      <c r="B2" s="54" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="56"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="56"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="58"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="59"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="56"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="58"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="59"/>
     </row>
     <row r="5" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="59"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
-      <c r="H5" s="60"/>
-      <c r="I5" s="60"/>
-      <c r="J5" s="60"/>
-      <c r="K5" s="61"/>
+      <c r="B5" s="60"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="61"/>
+      <c r="K5" s="62"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -3197,18 +3201,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="62" t="s">
+      <c r="D6" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="63"/>
-      <c r="F6" s="63"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="63" t="s">
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="63"/>
-      <c r="J6" s="63"/>
-      <c r="K6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
+      <c r="K6" s="65"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -3629,57 +3633,57 @@
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="53" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="55"/>
+      <c r="B2" s="54" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="56"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="56"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="58"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="59"/>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="56"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="58"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="59"/>
     </row>
     <row r="5" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="59"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
-      <c r="H5" s="60"/>
-      <c r="I5" s="60"/>
-      <c r="J5" s="60"/>
-      <c r="K5" s="61"/>
+      <c r="B5" s="60"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="61"/>
+      <c r="K5" s="62"/>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -3687,18 +3691,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="62" t="s">
+      <c r="D6" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="63"/>
-      <c r="F6" s="63"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="63" t="s">
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="63"/>
-      <c r="J6" s="63"/>
-      <c r="K6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
+      <c r="K6" s="65"/>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -4296,57 +4300,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="53" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="55"/>
+      <c r="B2" s="54" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="56"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="56"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="58"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="59"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="56"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="58"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="59"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="59"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
-      <c r="H5" s="60"/>
-      <c r="I5" s="60"/>
-      <c r="J5" s="60"/>
-      <c r="K5" s="61"/>
+      <c r="B5" s="60"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="61"/>
+      <c r="K5" s="62"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -4354,18 +4358,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="62" t="s">
+      <c r="D6" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="63"/>
-      <c r="F6" s="63"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="63" t="s">
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="63"/>
-      <c r="J6" s="63"/>
-      <c r="K6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
+      <c r="K6" s="65"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -4720,57 +4724,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="53" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="55"/>
+      <c r="B2" s="54" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="56"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="56"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="58"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="59"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="56"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="58"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="59"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="59"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
-      <c r="H5" s="60"/>
-      <c r="I5" s="60"/>
-      <c r="J5" s="60"/>
-      <c r="K5" s="61"/>
+      <c r="B5" s="60"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="61"/>
+      <c r="K5" s="62"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -4778,18 +4782,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="62" t="s">
+      <c r="D6" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="63"/>
-      <c r="F6" s="63"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="63" t="s">
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="63"/>
-      <c r="J6" s="63"/>
-      <c r="K6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
+      <c r="K6" s="65"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -5186,57 +5190,57 @@
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="53" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="55"/>
+      <c r="B2" s="54" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="56"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="56"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="58"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="59"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="56"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="58"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="59"/>
     </row>
     <row r="5" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="59"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
-      <c r="H5" s="60"/>
-      <c r="I5" s="60"/>
-      <c r="J5" s="60"/>
-      <c r="K5" s="61"/>
+      <c r="B5" s="60"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="61"/>
+      <c r="K5" s="62"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -5244,18 +5248,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="62" t="s">
+      <c r="D6" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="63"/>
-      <c r="F6" s="63"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="63" t="s">
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="63"/>
-      <c r="J6" s="63"/>
-      <c r="K6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
+      <c r="K6" s="65"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -5723,57 +5727,57 @@
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="53" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="55"/>
+      <c r="B2" s="54" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="56"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="56"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="58"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="59"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="56"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="58"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="59"/>
     </row>
     <row r="5" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="59"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
-      <c r="H5" s="60"/>
-      <c r="I5" s="60"/>
-      <c r="J5" s="60"/>
-      <c r="K5" s="61"/>
+      <c r="B5" s="60"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="61"/>
+      <c r="K5" s="62"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -5781,18 +5785,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="62" t="s">
+      <c r="D6" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="63"/>
-      <c r="F6" s="63"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="63" t="s">
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="63"/>
-      <c r="J6" s="63"/>
-      <c r="K6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
+      <c r="K6" s="65"/>
       <c r="R6" t="s">
         <v>63</v>
       </c>
@@ -6241,57 +6245,57 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="53" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="55"/>
+      <c r="B2" s="54" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="56"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="56"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="58"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="59"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="56"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="58"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="59"/>
     </row>
     <row r="5" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="59"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
-      <c r="H5" s="60"/>
-      <c r="I5" s="60"/>
-      <c r="J5" s="60"/>
-      <c r="K5" s="61"/>
+      <c r="B5" s="60"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="61"/>
+      <c r="K5" s="62"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -6299,18 +6303,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="62" t="s">
+      <c r="D6" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="63"/>
-      <c r="F6" s="63"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="63" t="s">
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="63"/>
-      <c r="J6" s="63"/>
-      <c r="K6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
+      <c r="K6" s="65"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -6783,57 +6787,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="53" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="55"/>
+      <c r="B2" s="54" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="56"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="56"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="58"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="59"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="56"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="58"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="59"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="59"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
-      <c r="H5" s="60"/>
-      <c r="I5" s="60"/>
-      <c r="J5" s="60"/>
-      <c r="K5" s="61"/>
+      <c r="B5" s="60"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="61"/>
+      <c r="K5" s="62"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -6841,18 +6845,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="62" t="s">
+      <c r="D6" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="63"/>
-      <c r="F6" s="63"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="63" t="s">
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="63"/>
-      <c r="J6" s="63"/>
-      <c r="K6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
+      <c r="K6" s="65"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -7255,57 +7259,57 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="53" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="55"/>
+      <c r="B2" s="54" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="56"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="56"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="58"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="59"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="56"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="58"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="59"/>
     </row>
     <row r="5" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="59"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
-      <c r="H5" s="60"/>
-      <c r="I5" s="60"/>
-      <c r="J5" s="60"/>
-      <c r="K5" s="61"/>
+      <c r="B5" s="60"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="61"/>
+      <c r="K5" s="62"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -7313,18 +7317,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="62" t="s">
+      <c r="D6" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="63"/>
-      <c r="F6" s="63"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="63" t="s">
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="63"/>
-      <c r="J6" s="63"/>
-      <c r="K6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
+      <c r="K6" s="65"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -7733,57 +7737,57 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="53" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="55"/>
+      <c r="B2" s="54" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="56"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="56"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="58"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="59"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="56"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="58"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="59"/>
     </row>
     <row r="5" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="59"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
-      <c r="H5" s="60"/>
-      <c r="I5" s="60"/>
-      <c r="J5" s="60"/>
-      <c r="K5" s="61"/>
+      <c r="B5" s="60"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="61"/>
+      <c r="K5" s="62"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -7791,18 +7795,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="62" t="s">
+      <c r="D6" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="63"/>
-      <c r="F6" s="63"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="63" t="s">
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="63"/>
-      <c r="J6" s="63"/>
-      <c r="K6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
+      <c r="K6" s="65"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -7890,26 +7894,42 @@
       <c r="B9" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
+      <c r="C9" s="12">
+        <v>212</v>
+      </c>
+      <c r="D9" s="12">
+        <v>32</v>
+      </c>
+      <c r="E9" s="12">
+        <v>32</v>
+      </c>
+      <c r="F9" s="12">
+        <v>12</v>
+      </c>
       <c r="G9" s="28">
-        <f t="shared" ref="G9:G12" si="0">SUM(D9:F9)/20</f>
-        <v>0</v>
-      </c>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12"/>
+        <f t="shared" ref="G9:G13" si="0">SUM(D9:F9)/20</f>
+        <v>3.8</v>
+      </c>
+      <c r="H9" s="12">
+        <v>66</v>
+      </c>
+      <c r="I9" s="12">
+        <v>36</v>
+      </c>
+      <c r="J9" s="12">
+        <v>37</v>
+      </c>
       <c r="K9" s="28">
-        <f t="shared" ref="K9:K12" si="1">SUM(H9:J9)/20</f>
-        <v>0</v>
+        <f t="shared" ref="K9:K13" si="1">SUM(H9:J9)/20</f>
+        <v>6.95</v>
       </c>
       <c r="L9">
-        <f t="shared" ref="L9:L12" si="2">SUM(C9:F9,H9,I9,J9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="M9" s="49"/>
+        <f t="shared" ref="L9:L13" si="2">SUM(C9:F9,H9,I9,J9)/40</f>
+        <v>10.675000000000001</v>
+      </c>
+      <c r="M9" s="49" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
@@ -8001,81 +8021,122 @@
         <v>9</v>
       </c>
       <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
+      <c r="D12" s="12">
+        <v>54</v>
+      </c>
+      <c r="E12" s="12">
+        <v>57</v>
+      </c>
+      <c r="F12" s="12">
+        <v>75</v>
+      </c>
       <c r="G12" s="28">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="12"/>
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="H12" s="12">
+        <v>27</v>
+      </c>
+      <c r="I12" s="12">
+        <v>23</v>
+      </c>
+      <c r="J12" s="12">
+        <v>28</v>
+      </c>
       <c r="K12" s="28">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="L12">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M12" s="42"/>
+        <v>6.6</v>
+      </c>
+      <c r="M12" s="42" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
-      <c r="B13" s="11"/>
+      <c r="B13" s="11" t="s">
+        <v>74</v>
+      </c>
       <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="12"/>
-      <c r="K13" s="12"/>
+      <c r="D13" s="12">
+        <v>314</v>
+      </c>
+      <c r="E13" s="12">
+        <v>353</v>
+      </c>
+      <c r="F13" s="12">
+        <v>388</v>
+      </c>
+      <c r="G13" s="12">
+        <f t="shared" si="0"/>
+        <v>52.75</v>
+      </c>
+      <c r="H13" s="12">
+        <v>350</v>
+      </c>
+      <c r="I13" s="12">
+        <v>311</v>
+      </c>
+      <c r="J13" s="12">
+        <v>396</v>
+      </c>
+      <c r="K13" s="12">
+        <f t="shared" si="1"/>
+        <v>52.85</v>
+      </c>
+      <c r="L13">
+        <f t="shared" si="2"/>
+        <v>52.8</v>
+      </c>
+      <c r="M13" s="42" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
         <f t="shared" ref="C14:K14" si="3">SUM(C8:C13)</f>
-        <v>292</v>
+        <v>504</v>
       </c>
       <c r="D14" s="14">
         <f t="shared" si="3"/>
-        <v>81</v>
+        <v>481</v>
       </c>
       <c r="E14" s="14">
         <f t="shared" si="3"/>
-        <v>76</v>
+        <v>518</v>
       </c>
       <c r="F14" s="14">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>496</v>
       </c>
       <c r="G14" s="14">
         <f t="shared" si="3"/>
-        <v>8.9</v>
+        <v>74.75</v>
       </c>
       <c r="H14" s="14">
         <f t="shared" si="3"/>
-        <v>275</v>
+        <v>718</v>
       </c>
       <c r="I14" s="14">
         <f t="shared" si="3"/>
-        <v>210</v>
+        <v>580</v>
       </c>
       <c r="J14" s="14">
         <f t="shared" si="3"/>
-        <v>345</v>
+        <v>806</v>
       </c>
       <c r="K14" s="14">
         <f t="shared" si="3"/>
-        <v>41.5</v>
+        <v>105.2</v>
       </c>
       <c r="L14" s="36">
         <f>C14+D14+E14+F14+H14+I14+J14</f>
-        <v>1300</v>
+        <v>4103</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">
@@ -8086,28 +8147,28 @@
       <c r="C15" s="13"/>
       <c r="D15" s="13">
         <f>D14/20</f>
-        <v>4.05</v>
+        <v>24.05</v>
       </c>
       <c r="E15" s="13">
         <f t="shared" ref="E15:J15" si="4">E14/20</f>
-        <v>3.8</v>
+        <v>25.9</v>
       </c>
       <c r="F15" s="13">
         <f t="shared" si="4"/>
-        <v>1.05</v>
+        <v>24.8</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13">
         <f t="shared" si="4"/>
-        <v>13.75</v>
+        <v>35.9</v>
       </c>
       <c r="I15" s="13">
         <f t="shared" si="4"/>
-        <v>10.5</v>
+        <v>29</v>
       </c>
       <c r="J15" s="13">
         <f t="shared" si="4"/>
-        <v>17.25</v>
+        <v>40.299999999999997</v>
       </c>
       <c r="K15" s="13"/>
     </row>
@@ -8118,32 +8179,32 @@
       </c>
       <c r="C16" s="37">
         <f>C15+C14</f>
-        <v>292</v>
+        <v>504</v>
       </c>
       <c r="D16" s="37">
         <f t="shared" ref="D16:J16" si="5">D15+D14</f>
-        <v>85.05</v>
+        <v>505.05</v>
       </c>
       <c r="E16" s="37">
         <f t="shared" si="5"/>
-        <v>79.8</v>
+        <v>543.9</v>
       </c>
       <c r="F16" s="37">
         <f t="shared" si="5"/>
-        <v>22.05</v>
+        <v>520.79999999999995</v>
       </c>
       <c r="G16" s="37"/>
       <c r="H16" s="37">
         <f t="shared" si="5"/>
-        <v>288.75</v>
+        <v>753.9</v>
       </c>
       <c r="I16" s="37">
         <f t="shared" si="5"/>
-        <v>220.5</v>
+        <v>609</v>
       </c>
       <c r="J16" s="37">
         <f t="shared" si="5"/>
-        <v>362.25</v>
+        <v>846.3</v>
       </c>
       <c r="K16" s="37"/>
     </row>
@@ -8154,37 +8215,37 @@
       </c>
       <c r="C17" s="37">
         <f>C14/40</f>
-        <v>7.3</v>
+        <v>12.6</v>
       </c>
       <c r="D17" s="37">
         <f t="shared" ref="D17:J17" si="6">D14/40</f>
-        <v>2.0249999999999999</v>
+        <v>12.025</v>
       </c>
       <c r="E17" s="37">
         <f t="shared" si="6"/>
-        <v>1.9</v>
+        <v>12.95</v>
       </c>
       <c r="F17" s="37">
         <f t="shared" si="6"/>
-        <v>0.52500000000000002</v>
+        <v>12.4</v>
       </c>
       <c r="G17" s="37"/>
       <c r="H17" s="37">
         <f t="shared" si="6"/>
-        <v>6.875</v>
+        <v>17.95</v>
       </c>
       <c r="I17" s="37">
         <f t="shared" si="6"/>
-        <v>5.25</v>
+        <v>14.5</v>
       </c>
       <c r="J17" s="37">
         <f t="shared" si="6"/>
-        <v>8.625</v>
+        <v>20.149999999999999</v>
       </c>
       <c r="K17" s="37"/>
       <c r="L17" s="36">
         <f>SUM(C17:J17)</f>
-        <v>32.5</v>
+        <v>102.57499999999999</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">
@@ -8245,57 +8306,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="53" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="55"/>
+      <c r="B2" s="54" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="56"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="56"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="58"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="59"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="56"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="58"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="59"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="59"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
-      <c r="H5" s="60"/>
-      <c r="I5" s="60"/>
-      <c r="J5" s="60"/>
-      <c r="K5" s="61"/>
+      <c r="B5" s="60"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="61"/>
+      <c r="K5" s="62"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -8303,18 +8364,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="62" t="s">
+      <c r="D6" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="63"/>
-      <c r="F6" s="63"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="63" t="s">
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="63"/>
-      <c r="J6" s="63"/>
-      <c r="K6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
+      <c r="K6" s="65"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -8669,57 +8730,57 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="53" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="55"/>
+      <c r="B2" s="54" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="56"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="56"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="58"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="59"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="56"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="58"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="59"/>
     </row>
     <row r="5" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="59"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
-      <c r="H5" s="60"/>
-      <c r="I5" s="60"/>
-      <c r="J5" s="60"/>
-      <c r="K5" s="61"/>
+      <c r="B5" s="60"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="61"/>
+      <c r="K5" s="62"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -8727,18 +8788,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="62" t="s">
+      <c r="D6" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="63"/>
-      <c r="F6" s="63"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="63" t="s">
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="63"/>
-      <c r="J6" s="63"/>
-      <c r="K6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
+      <c r="K6" s="65"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -8883,24 +8944,24 @@
         <v>20.6</v>
       </c>
       <c r="H10" s="12">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="I10" s="12">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="J10" s="12">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="K10" s="28">
         <f t="shared" si="1"/>
-        <v>15.2</v>
+        <v>14.6</v>
       </c>
       <c r="L10">
         <f t="shared" si="2"/>
-        <v>17.899999999999999</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="M10" s="52">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.35">
@@ -8912,37 +8973,37 @@
         <v>130</v>
       </c>
       <c r="D11" s="12">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="E11" s="12">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="F11" s="12">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="G11" s="28">
         <f t="shared" si="0"/>
-        <v>10.3</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="H11" s="12">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="I11" s="12">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="J11" s="12">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="K11" s="28">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L11">
         <f t="shared" si="2"/>
-        <v>14.4</v>
+        <v>11.4</v>
       </c>
       <c r="M11" s="52">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.35">
@@ -8954,37 +9015,37 @@
         <v>60</v>
       </c>
       <c r="D12" s="12">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="E12" s="12">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F12" s="12">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="G12" s="28">
         <f t="shared" si="0"/>
-        <v>5.7</v>
+        <v>3</v>
       </c>
       <c r="H12" s="12">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="I12" s="12">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="J12" s="12">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="K12" s="28">
         <f t="shared" si="1"/>
-        <v>4.25</v>
+        <v>2</v>
       </c>
       <c r="L12">
         <f t="shared" si="2"/>
-        <v>6.4749999999999996</v>
+        <v>4</v>
       </c>
       <c r="M12" s="52">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.35">
@@ -9009,39 +9070,39 @@
       </c>
       <c r="D14" s="14">
         <f t="shared" si="3"/>
-        <v>396</v>
+        <v>363</v>
       </c>
       <c r="E14" s="14">
         <f t="shared" si="3"/>
-        <v>388</v>
+        <v>360</v>
       </c>
       <c r="F14" s="14">
         <f t="shared" si="3"/>
-        <v>434</v>
+        <v>401</v>
       </c>
       <c r="G14" s="14">
         <f t="shared" si="3"/>
-        <v>60.900000000000006</v>
+        <v>56.2</v>
       </c>
       <c r="H14" s="14">
         <f t="shared" si="3"/>
-        <v>468</v>
+        <v>419</v>
       </c>
       <c r="I14" s="14">
         <f t="shared" si="3"/>
-        <v>402</v>
+        <v>363</v>
       </c>
       <c r="J14" s="14">
         <f t="shared" si="3"/>
-        <v>404</v>
+        <v>355</v>
       </c>
       <c r="K14" s="14">
         <f t="shared" si="3"/>
-        <v>63.7</v>
+        <v>56.85</v>
       </c>
       <c r="L14" s="36">
         <f>C14+D14+E14+F14+H14+I14+J14</f>
-        <v>2722</v>
+        <v>2491</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">
@@ -9052,28 +9113,28 @@
       <c r="C15" s="13"/>
       <c r="D15" s="13">
         <f>D14/20</f>
-        <v>19.8</v>
+        <v>18.149999999999999</v>
       </c>
       <c r="E15" s="13">
         <f t="shared" ref="E15:J15" si="4">E14/20</f>
-        <v>19.399999999999999</v>
+        <v>18</v>
       </c>
       <c r="F15" s="13">
         <f t="shared" si="4"/>
-        <v>21.7</v>
+        <v>20.05</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13">
         <f t="shared" si="4"/>
-        <v>23.4</v>
+        <v>20.95</v>
       </c>
       <c r="I15" s="13">
         <f t="shared" si="4"/>
-        <v>20.100000000000001</v>
+        <v>18.149999999999999</v>
       </c>
       <c r="J15" s="13">
         <f t="shared" si="4"/>
-        <v>20.2</v>
+        <v>17.75</v>
       </c>
       <c r="K15" s="13"/>
     </row>
@@ -9088,28 +9149,28 @@
       </c>
       <c r="D16" s="37">
         <f t="shared" ref="D16:J16" si="5">D15+D14</f>
-        <v>415.8</v>
+        <v>381.15</v>
       </c>
       <c r="E16" s="37">
         <f t="shared" si="5"/>
-        <v>407.4</v>
+        <v>378</v>
       </c>
       <c r="F16" s="37">
         <f t="shared" si="5"/>
-        <v>455.7</v>
+        <v>421.05</v>
       </c>
       <c r="G16" s="37"/>
       <c r="H16" s="37">
         <f t="shared" si="5"/>
-        <v>491.4</v>
+        <v>439.95</v>
       </c>
       <c r="I16" s="37">
         <f t="shared" si="5"/>
-        <v>422.1</v>
+        <v>381.15</v>
       </c>
       <c r="J16" s="37">
         <f t="shared" si="5"/>
-        <v>424.2</v>
+        <v>372.75</v>
       </c>
       <c r="K16" s="37"/>
     </row>
@@ -9124,33 +9185,33 @@
       </c>
       <c r="D17" s="37">
         <f t="shared" ref="D17:J17" si="6">D14/40</f>
-        <v>9.9</v>
+        <v>9.0749999999999993</v>
       </c>
       <c r="E17" s="37">
         <f t="shared" si="6"/>
-        <v>9.6999999999999993</v>
+        <v>9</v>
       </c>
       <c r="F17" s="37">
         <f t="shared" si="6"/>
-        <v>10.85</v>
+        <v>10.025</v>
       </c>
       <c r="G17" s="37"/>
       <c r="H17" s="37">
         <f t="shared" si="6"/>
-        <v>11.7</v>
+        <v>10.475</v>
       </c>
       <c r="I17" s="37">
         <f t="shared" si="6"/>
-        <v>10.050000000000001</v>
+        <v>9.0749999999999993</v>
       </c>
       <c r="J17" s="37">
         <f t="shared" si="6"/>
-        <v>10.1</v>
+        <v>8.875</v>
       </c>
       <c r="K17" s="37"/>
       <c r="L17" s="36">
         <f>SUM(C17:J17)</f>
-        <v>68.05</v>
+        <v>62.275000000000006</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">
@@ -9178,7 +9239,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{7C4076FE-357D-47D3-8F62-0DB2CEAFAFF4}">
           <x14:formula1>
             <xm:f>'last month'!$B$22:$B$28</xm:f>
@@ -9193,7 +9254,7 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48CA099E-5370-4419-9FCD-0778E6459525}">
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.90625" bestFit="1" customWidth="1"/>
@@ -9208,7 +9269,7 @@
     <col min="11" max="11" width="5.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -9221,80 +9282,80 @@
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="53" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="55"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B2" s="54" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="56"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="56"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="58"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B3" s="57"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="59"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="56"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="58"/>
-    </row>
-    <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B4" s="57"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="59"/>
+    </row>
+    <row r="5" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="59"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
-      <c r="H5" s="60"/>
-      <c r="I5" s="60"/>
-      <c r="J5" s="60"/>
-      <c r="K5" s="61"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B5" s="60"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="61"/>
+      <c r="K5" s="62"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
       <c r="B6" s="2"/>
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="62" t="s">
+      <c r="D6" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="63"/>
-      <c r="F6" s="63"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="63" t="s">
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="63"/>
-      <c r="J6" s="63"/>
-      <c r="K6" s="64"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
+      <c r="K6" s="65"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
         <v>4</v>
       </c>
@@ -9328,102 +9389,222 @@
       <c r="K7" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="L7" t="s">
+      <c r="L7" s="43" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M7" s="49" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" s="27"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
+      <c r="B8" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" s="12">
+        <v>60</v>
+      </c>
+      <c r="D8" s="12">
+        <v>21</v>
+      </c>
+      <c r="E8" s="12">
+        <v>21</v>
+      </c>
+      <c r="F8" s="12">
+        <v>19</v>
+      </c>
       <c r="G8" s="28">
         <f>SUM(D8:F8)/20</f>
-        <v>0</v>
-      </c>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="12"/>
+        <v>3.05</v>
+      </c>
+      <c r="H8" s="12">
+        <v>82</v>
+      </c>
+      <c r="I8" s="12">
+        <v>82</v>
+      </c>
+      <c r="J8" s="12">
+        <v>76</v>
+      </c>
       <c r="K8" s="28">
         <f>SUM(H8:J8)/20</f>
-        <v>0</v>
-      </c>
-      <c r="L8">
+        <v>12</v>
+      </c>
+      <c r="L8" s="53">
         <f>SUM(C8:F8,H8,I8,J8)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+        <v>9.0250000000000004</v>
+      </c>
+      <c r="M8" s="49">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" s="27"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12"/>
-      <c r="K9" s="28"/>
-      <c r="L9">
-        <f t="shared" ref="L9:L12" si="0">SUM(C9:F9,H9,I9,J9)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B9" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="12">
+        <v>60</v>
+      </c>
+      <c r="D9" s="12">
+        <v>100</v>
+      </c>
+      <c r="E9" s="12">
+        <v>60</v>
+      </c>
+      <c r="F9" s="12">
+        <v>100</v>
+      </c>
+      <c r="G9" s="28">
+        <f t="shared" ref="G9:G12" si="0">SUM(D9:F9)/20</f>
+        <v>13</v>
+      </c>
+      <c r="H9" s="12">
+        <v>40</v>
+      </c>
+      <c r="I9" s="12">
+        <v>40</v>
+      </c>
+      <c r="J9" s="12">
+        <v>80</v>
+      </c>
+      <c r="K9" s="28">
+        <f t="shared" ref="K9:K12" si="1">SUM(H9:J9)/20</f>
+        <v>8</v>
+      </c>
+      <c r="L9" s="53">
+        <f t="shared" ref="L9:L12" si="2">SUM(C9:F9,H9,I9,J9)/40</f>
+        <v>12</v>
+      </c>
+      <c r="M9" s="49">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="28"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="28"/>
-      <c r="L10">
+      <c r="B10" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="12">
+        <v>120</v>
+      </c>
+      <c r="D10" s="12">
+        <v>105</v>
+      </c>
+      <c r="E10" s="12">
+        <v>65</v>
+      </c>
+      <c r="F10" s="12">
+        <v>10</v>
+      </c>
+      <c r="G10" s="28">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+      <c r="H10" s="12">
+        <v>70</v>
+      </c>
+      <c r="I10" s="12">
+        <v>50</v>
+      </c>
+      <c r="J10" s="12">
+        <v>80</v>
+      </c>
+      <c r="K10" s="28">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="L10" s="53">
+        <f t="shared" si="2"/>
+        <v>12.5</v>
+      </c>
+      <c r="M10" s="49">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
-      <c r="B11" s="11"/>
+      <c r="B11" s="11" t="s">
+        <v>9</v>
+      </c>
       <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="12"/>
-      <c r="K11" s="12"/>
-      <c r="L11">
+      <c r="D11" s="12">
+        <v>120</v>
+      </c>
+      <c r="E11" s="12">
+        <v>120</v>
+      </c>
+      <c r="F11" s="12">
+        <v>80</v>
+      </c>
+      <c r="G11" s="28">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+        <v>16</v>
+      </c>
+      <c r="H11" s="12">
+        <v>133</v>
+      </c>
+      <c r="I11" s="12">
+        <v>143</v>
+      </c>
+      <c r="J11" s="12">
+        <v>124</v>
+      </c>
+      <c r="K11" s="28">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="L11" s="53">
+        <f t="shared" si="2"/>
+        <v>18</v>
+      </c>
+      <c r="M11" s="42">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="12"/>
-      <c r="K12" s="12"/>
-      <c r="L12">
+      <c r="B12" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="12">
+        <v>0</v>
+      </c>
+      <c r="D12" s="12">
+        <v>0</v>
+      </c>
+      <c r="E12" s="12">
+        <v>10</v>
+      </c>
+      <c r="F12" s="12">
+        <v>10</v>
+      </c>
+      <c r="G12" s="28">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+      <c r="H12" s="12">
+        <v>0</v>
+      </c>
+      <c r="I12" s="12">
+        <v>34</v>
+      </c>
+      <c r="J12" s="12">
+        <v>74</v>
+      </c>
+      <c r="K12" s="28">
+        <f t="shared" si="1"/>
+        <v>5.4</v>
+      </c>
+      <c r="L12" s="53">
+        <f t="shared" si="2"/>
+        <v>3.2</v>
+      </c>
+      <c r="M12" s="42">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
       <c r="B13" s="11"/>
       <c r="C13" s="12"/>
@@ -9436,51 +9617,51 @@
       <c r="J13" s="12"/>
       <c r="K13" s="12"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:K14" si="1">SUM(C8:C13)</f>
-        <v>0</v>
+        <f t="shared" ref="C14:K14" si="3">SUM(C8:C13)</f>
+        <v>240</v>
       </c>
       <c r="D14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>346</v>
       </c>
       <c r="E14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>276</v>
       </c>
       <c r="F14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>219</v>
       </c>
       <c r="G14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>42.05</v>
       </c>
       <c r="H14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>325</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>349</v>
       </c>
       <c r="J14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>434</v>
       </c>
       <c r="K14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>55.4</v>
       </c>
       <c r="L14" s="36">
         <f>C14+D14+E14+F14+H14+I14+J14</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" s="13"/>
       <c r="B15" s="10" t="s">
         <v>40</v>
@@ -9488,64 +9669,64 @@
       <c r="C15" s="13"/>
       <c r="D15" s="13">
         <f>D14/20</f>
-        <v>0</v>
+        <v>17.3</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:J15" si="2">E14/20</f>
-        <v>0</v>
+        <f t="shared" ref="E15:J15" si="4">E14/20</f>
+        <v>13.8</v>
       </c>
       <c r="F15" s="13">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>10.95</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>16.25</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>17.45</v>
       </c>
       <c r="J15" s="13">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>21.7</v>
       </c>
       <c r="K15" s="13"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" s="13"/>
       <c r="B16" s="10" t="s">
         <v>39</v>
       </c>
       <c r="C16" s="37">
         <f>C15+C14</f>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="D16" s="37">
-        <f t="shared" ref="D16:J16" si="3">D15+D14</f>
-        <v>0</v>
+        <f t="shared" ref="D16:J16" si="5">D15+D14</f>
+        <v>363.3</v>
       </c>
       <c r="E16" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>289.8</v>
       </c>
       <c r="F16" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>229.95</v>
       </c>
       <c r="G16" s="37"/>
       <c r="H16" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>341.25</v>
       </c>
       <c r="I16" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>366.45</v>
       </c>
       <c r="J16" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>455.7</v>
       </c>
       <c r="K16" s="37"/>
     </row>
@@ -9556,37 +9737,37 @@
       </c>
       <c r="C17" s="37">
         <f>C14/40</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D17" s="37">
-        <f t="shared" ref="D17:J17" si="4">D14/40</f>
-        <v>0</v>
+        <f t="shared" ref="D17:J17" si="6">D14/40</f>
+        <v>8.65</v>
       </c>
       <c r="E17" s="37">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>6.9</v>
       </c>
       <c r="F17" s="37">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>5.4749999999999996</v>
       </c>
       <c r="G17" s="37"/>
       <c r="H17" s="37">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>8.125</v>
       </c>
       <c r="I17" s="37">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>8.7249999999999996</v>
       </c>
       <c r="J17" s="37">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>10.85</v>
       </c>
       <c r="K17" s="37"/>
       <c r="L17" s="36">
         <f>SUM(C17:J17)</f>
-        <v>0</v>
+        <v>54.725000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">
@@ -9647,57 +9828,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="53" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="55"/>
+      <c r="B2" s="54" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="56"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="56"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="58"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="59"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="56"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="58"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="59"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="59"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
-      <c r="H5" s="60"/>
-      <c r="I5" s="60"/>
-      <c r="J5" s="60"/>
-      <c r="K5" s="61"/>
+      <c r="B5" s="60"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="61"/>
+      <c r="K5" s="62"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -9705,18 +9886,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="62" t="s">
+      <c r="D6" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="63"/>
-      <c r="F6" s="63"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="63" t="s">
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="63"/>
-      <c r="J6" s="63"/>
-      <c r="K6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
+      <c r="K6" s="65"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -10071,57 +10252,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="53" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="55"/>
+      <c r="B2" s="54" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="56"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="56"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="58"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="59"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="56"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="58"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="59"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="59"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
-      <c r="H5" s="60"/>
-      <c r="I5" s="60"/>
-      <c r="J5" s="60"/>
-      <c r="K5" s="61"/>
+      <c r="B5" s="60"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="61"/>
+      <c r="K5" s="62"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -10129,18 +10310,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="62" t="s">
+      <c r="D6" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="63"/>
-      <c r="F6" s="63"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="63" t="s">
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="63"/>
-      <c r="J6" s="63"/>
-      <c r="K6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
+      <c r="K6" s="65"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -10495,57 +10676,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="53" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="55"/>
+      <c r="B2" s="54" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="56"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="56"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="58"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="59"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="56"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="58"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="59"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="59"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
-      <c r="H5" s="60"/>
-      <c r="I5" s="60"/>
-      <c r="J5" s="60"/>
-      <c r="K5" s="61"/>
+      <c r="B5" s="60"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="61"/>
+      <c r="K5" s="62"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -10553,18 +10734,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="62" t="s">
+      <c r="D6" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="63"/>
-      <c r="F6" s="63"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="63" t="s">
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="63"/>
-      <c r="J6" s="63"/>
-      <c r="K6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
+      <c r="K6" s="65"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -10919,57 +11100,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="53" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="55"/>
+      <c r="B2" s="54" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="56"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="56"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="58"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="59"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="56"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="58"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="59"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="59"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
-      <c r="H5" s="60"/>
-      <c r="I5" s="60"/>
-      <c r="J5" s="60"/>
-      <c r="K5" s="61"/>
+      <c r="B5" s="60"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="61"/>
+      <c r="K5" s="62"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -10977,18 +11158,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="62" t="s">
+      <c r="D6" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="63"/>
-      <c r="F6" s="63"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="63" t="s">
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="63"/>
-      <c r="J6" s="63"/>
-      <c r="K6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
+      <c r="K6" s="65"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -11343,57 +11524,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="53" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="55"/>
+      <c r="B2" s="54" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="56"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="56"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="58"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="59"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="56"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="58"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="59"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="59"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
-      <c r="H5" s="60"/>
-      <c r="I5" s="60"/>
-      <c r="J5" s="60"/>
-      <c r="K5" s="61"/>
+      <c r="B5" s="60"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="61"/>
+      <c r="K5" s="62"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -11401,18 +11582,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="62" t="s">
+      <c r="D6" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="63"/>
-      <c r="F6" s="63"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="63" t="s">
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="63"/>
-      <c r="J6" s="63"/>
-      <c r="K6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
+      <c r="K6" s="65"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -11767,57 +11948,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="53" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="55"/>
+      <c r="B2" s="54" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="56"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="56"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="58"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="59"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="56"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="58"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="59"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="59"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
-      <c r="H5" s="60"/>
-      <c r="I5" s="60"/>
-      <c r="J5" s="60"/>
-      <c r="K5" s="61"/>
+      <c r="B5" s="60"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="61"/>
+      <c r="K5" s="62"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -11825,18 +12006,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="62" t="s">
+      <c r="D6" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="63"/>
-      <c r="F6" s="63"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="63" t="s">
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="63"/>
-      <c r="J6" s="63"/>
-      <c r="K6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
+      <c r="K6" s="65"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -12253,57 +12434,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="53" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="55"/>
+      <c r="B2" s="54" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="56"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="56"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="58"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="59"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="56"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="58"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="59"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="59"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
-      <c r="H5" s="60"/>
-      <c r="I5" s="60"/>
-      <c r="J5" s="60"/>
-      <c r="K5" s="61"/>
+      <c r="B5" s="60"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="61"/>
+      <c r="K5" s="62"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -12311,18 +12492,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="62" t="s">
+      <c r="D6" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="63"/>
-      <c r="F6" s="63"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="63" t="s">
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="63"/>
-      <c r="J6" s="63"/>
-      <c r="K6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
+      <c r="K6" s="65"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -12677,57 +12858,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="53" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="55"/>
+      <c r="B2" s="54" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="56"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="56"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="58"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="59"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="56"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="58"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="59"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="59"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
-      <c r="H5" s="60"/>
-      <c r="I5" s="60"/>
-      <c r="J5" s="60"/>
-      <c r="K5" s="61"/>
+      <c r="B5" s="60"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="61"/>
+      <c r="K5" s="62"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -12735,18 +12916,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="62" t="s">
+      <c r="D6" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="63"/>
-      <c r="F6" s="63"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="63" t="s">
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="63"/>
-      <c r="J6" s="63"/>
-      <c r="K6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
+      <c r="K6" s="65"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -13102,57 +13283,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="53" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="55"/>
+      <c r="B2" s="54" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="56"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="56"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="58"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="59"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="56"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="58"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="59"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="59"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
-      <c r="H5" s="60"/>
-      <c r="I5" s="60"/>
-      <c r="J5" s="60"/>
-      <c r="K5" s="61"/>
+      <c r="B5" s="60"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="61"/>
+      <c r="K5" s="62"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -13160,18 +13341,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="62" t="s">
+      <c r="D6" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="63"/>
-      <c r="F6" s="63"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="63" t="s">
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="63"/>
-      <c r="J6" s="63"/>
-      <c r="K6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
+      <c r="K6" s="65"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -13526,57 +13707,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="53" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="55"/>
+      <c r="B2" s="54" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="56"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="56"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="58"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="59"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="56"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="58"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="59"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="59"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
-      <c r="H5" s="60"/>
-      <c r="I5" s="60"/>
-      <c r="J5" s="60"/>
-      <c r="K5" s="61"/>
+      <c r="B5" s="60"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="61"/>
+      <c r="K5" s="62"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -13584,18 +13765,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="62" t="s">
+      <c r="D6" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="63"/>
-      <c r="F6" s="63"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="63" t="s">
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="63"/>
-      <c r="J6" s="63"/>
-      <c r="K6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
+      <c r="K6" s="65"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -14065,57 +14246,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="53" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="55"/>
+      <c r="B2" s="54" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="56"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="56"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="58"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="59"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="56"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="58"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="59"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="59"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
-      <c r="H5" s="60"/>
-      <c r="I5" s="60"/>
-      <c r="J5" s="60"/>
-      <c r="K5" s="61"/>
+      <c r="B5" s="60"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="61"/>
+      <c r="K5" s="62"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -14123,18 +14304,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="62" t="s">
+      <c r="D6" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="63"/>
-      <c r="F6" s="63"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="63" t="s">
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="63"/>
-      <c r="J6" s="63"/>
-      <c r="K6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
+      <c r="K6" s="65"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -14576,57 +14757,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="53" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="55"/>
+      <c r="B2" s="54" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="56"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="56"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="58"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="59"/>
     </row>
     <row r="4" spans="1:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="56"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="58"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="59"/>
     </row>
     <row r="5" spans="1:12" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="59"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
-      <c r="H5" s="60"/>
-      <c r="I5" s="60"/>
-      <c r="J5" s="60"/>
-      <c r="K5" s="61"/>
+      <c r="B5" s="60"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="61"/>
+      <c r="K5" s="62"/>
     </row>
     <row r="6" spans="1:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -14634,18 +14815,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="62" t="s">
+      <c r="D6" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="63"/>
-      <c r="F6" s="63"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="63" t="s">
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="63"/>
-      <c r="J6" s="63"/>
-      <c r="K6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
+      <c r="K6" s="65"/>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -15052,57 +15233,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="53" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="55"/>
+      <c r="B2" s="54" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="56"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="56"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="58"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="59"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="56"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="58"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="59"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="59"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
-      <c r="H5" s="60"/>
-      <c r="I5" s="60"/>
-      <c r="J5" s="60"/>
-      <c r="K5" s="61"/>
+      <c r="B5" s="60"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="61"/>
+      <c r="K5" s="62"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -15110,18 +15291,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="62" t="s">
+      <c r="D6" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="63"/>
-      <c r="F6" s="63"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="63" t="s">
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="63"/>
-      <c r="J6" s="63"/>
-      <c r="K6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
+      <c r="K6" s="65"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -15480,57 +15661,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="53" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="55"/>
+      <c r="B2" s="54" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="56"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="56"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="58"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="59"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="56"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="58"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="59"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="59"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
-      <c r="H5" s="60"/>
-      <c r="I5" s="60"/>
-      <c r="J5" s="60"/>
-      <c r="K5" s="61"/>
+      <c r="B5" s="60"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="61"/>
+      <c r="K5" s="62"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -15538,18 +15719,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="62" t="s">
+      <c r="D6" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="63"/>
-      <c r="F6" s="63"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="63" t="s">
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="63"/>
-      <c r="J6" s="63"/>
-      <c r="K6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
+      <c r="K6" s="65"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -15898,57 +16079,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="53" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="55"/>
+      <c r="B2" s="54" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="56"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="56"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="58"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="59"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="56"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="58"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="59"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="59"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
-      <c r="H5" s="60"/>
-      <c r="I5" s="60"/>
-      <c r="J5" s="60"/>
-      <c r="K5" s="61"/>
+      <c r="B5" s="60"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="61"/>
+      <c r="K5" s="62"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -15956,18 +16137,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="62" t="s">
+      <c r="D6" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="63"/>
-      <c r="F6" s="63"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="63" t="s">
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="63"/>
-      <c r="J6" s="63"/>
-      <c r="K6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
+      <c r="K6" s="65"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">

--- a/Final Execution SKU wise.xlsx
+++ b/Final Execution SKU wise.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8007181-B4D0-40C3-B261-F538C8F2C3FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E34BECC-42EE-4931-92F5-0C13503E7507}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" activeTab="23" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
   </bookViews>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="78">
   <si>
     <t>Gate Pass</t>
   </si>
@@ -281,6 +281,15 @@
   </si>
   <si>
     <t xml:space="preserve">Aslam </t>
+  </si>
+  <si>
+    <t>Booking</t>
+  </si>
+  <si>
+    <t>Umer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sum </t>
   </si>
 </sst>
 </file>
@@ -9254,6 +9263,757 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48CA099E-5370-4419-9FCD-0778E6459525}">
+  <dimension ref="A1:X19"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="3.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.08984375" customWidth="1"/>
+    <col min="5" max="5" width="4.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="3.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="4.26953125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="3.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A2" s="1"/>
+      <c r="B2" s="54" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="56"/>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A3" s="1"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="59"/>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A4" s="1"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="59"/>
+      <c r="S4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="1"/>
+      <c r="B5" s="60"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="61"/>
+      <c r="K5" s="62"/>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A6" s="1"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="63" t="s">
+        <v>2</v>
+      </c>
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="64" t="s">
+        <v>3</v>
+      </c>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
+      <c r="K6" s="65"/>
+      <c r="P6" s="45">
+        <v>60</v>
+      </c>
+      <c r="Q6" s="45">
+        <v>70</v>
+      </c>
+      <c r="R6" s="45">
+        <v>70</v>
+      </c>
+      <c r="S6" s="45">
+        <v>70</v>
+      </c>
+      <c r="T6" s="45">
+        <v>120</v>
+      </c>
+      <c r="U6" s="45">
+        <v>120</v>
+      </c>
+      <c r="V6" s="45">
+        <v>120</v>
+      </c>
+      <c r="W6" t="s">
+        <v>77</v>
+      </c>
+      <c r="X6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A7" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="38" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="I7" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="J7" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="K7" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="L7" s="43" t="s">
+        <v>59</v>
+      </c>
+      <c r="M7" s="49" t="s">
+        <v>58</v>
+      </c>
+      <c r="P7" s="41" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q7" s="41" t="s">
+        <v>14</v>
+      </c>
+      <c r="R7" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="S7" s="41" t="s">
+        <v>13</v>
+      </c>
+      <c r="T7" s="41" t="s">
+        <v>14</v>
+      </c>
+      <c r="U7" s="41" t="s">
+        <v>7</v>
+      </c>
+      <c r="V7" s="41" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A8" s="27"/>
+      <c r="B8" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" s="12">
+        <v>40</v>
+      </c>
+      <c r="D8" s="12">
+        <v>0</v>
+      </c>
+      <c r="E8" s="12">
+        <v>0</v>
+      </c>
+      <c r="F8" s="12">
+        <v>0</v>
+      </c>
+      <c r="G8" s="28">
+        <f>SUM(D8:F8)/20</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="12">
+        <v>82</v>
+      </c>
+      <c r="I8" s="12">
+        <v>82</v>
+      </c>
+      <c r="J8" s="12">
+        <v>76</v>
+      </c>
+      <c r="K8" s="28">
+        <f>SUM(H8:J8)/20</f>
+        <v>12</v>
+      </c>
+      <c r="L8" s="53">
+        <f>SUM(C8:F8,H8,I8,J8)/40</f>
+        <v>7</v>
+      </c>
+      <c r="M8" s="49">
+        <v>4</v>
+      </c>
+      <c r="O8" t="s">
+        <v>71</v>
+      </c>
+      <c r="P8" s="41">
+        <v>60</v>
+      </c>
+      <c r="Q8" s="41">
+        <v>21</v>
+      </c>
+      <c r="R8" s="41">
+        <v>21</v>
+      </c>
+      <c r="S8" s="41">
+        <v>19</v>
+      </c>
+      <c r="T8" s="41">
+        <v>82</v>
+      </c>
+      <c r="U8" s="41">
+        <v>82</v>
+      </c>
+      <c r="V8" s="41">
+        <v>76</v>
+      </c>
+      <c r="W8">
+        <f>SUM(P8:V8)</f>
+        <v>361</v>
+      </c>
+      <c r="X8">
+        <f>W8/40</f>
+        <v>9.0250000000000004</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A9" s="27"/>
+      <c r="B9" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="12">
+        <v>20</v>
+      </c>
+      <c r="D9" s="12">
+        <v>100</v>
+      </c>
+      <c r="E9" s="12">
+        <v>60</v>
+      </c>
+      <c r="F9" s="12">
+        <v>100</v>
+      </c>
+      <c r="G9" s="28">
+        <f t="shared" ref="G9:G12" si="0">SUM(D9:F9)/20</f>
+        <v>13</v>
+      </c>
+      <c r="H9" s="12">
+        <v>40</v>
+      </c>
+      <c r="I9" s="12">
+        <v>40</v>
+      </c>
+      <c r="J9" s="12">
+        <v>80</v>
+      </c>
+      <c r="K9" s="28">
+        <f t="shared" ref="K9:K12" si="1">SUM(H9:J9)/20</f>
+        <v>8</v>
+      </c>
+      <c r="L9" s="53">
+        <f t="shared" ref="L9:L12" si="2">SUM(C9:F9,H9,I9,J9)/40</f>
+        <v>11</v>
+      </c>
+      <c r="M9" s="49">
+        <v>3</v>
+      </c>
+      <c r="O9" t="s">
+        <v>32</v>
+      </c>
+      <c r="P9" s="41">
+        <v>60</v>
+      </c>
+      <c r="Q9" s="41">
+        <v>100</v>
+      </c>
+      <c r="R9" s="41">
+        <v>60</v>
+      </c>
+      <c r="S9" s="41">
+        <v>100</v>
+      </c>
+      <c r="T9" s="41">
+        <v>40</v>
+      </c>
+      <c r="U9" s="41">
+        <v>40</v>
+      </c>
+      <c r="V9" s="41">
+        <v>80</v>
+      </c>
+      <c r="W9">
+        <f t="shared" ref="W9:W12" si="3">SUM(P9:V9)</f>
+        <v>480</v>
+      </c>
+      <c r="X9">
+        <f t="shared" ref="X9:X12" si="4">W9/40</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A10" s="27"/>
+      <c r="B10" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="12">
+        <v>120</v>
+      </c>
+      <c r="D10" s="12">
+        <v>105</v>
+      </c>
+      <c r="E10" s="12">
+        <v>65</v>
+      </c>
+      <c r="F10" s="12">
+        <v>10</v>
+      </c>
+      <c r="G10" s="28">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="H10" s="12">
+        <v>70</v>
+      </c>
+      <c r="I10" s="12">
+        <v>50</v>
+      </c>
+      <c r="J10" s="12">
+        <v>80</v>
+      </c>
+      <c r="K10" s="28">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="L10" s="53">
+        <f t="shared" si="2"/>
+        <v>12.5</v>
+      </c>
+      <c r="M10" s="49">
+        <v>8</v>
+      </c>
+      <c r="O10" t="s">
+        <v>16</v>
+      </c>
+      <c r="P10" s="41">
+        <v>120</v>
+      </c>
+      <c r="Q10" s="41">
+        <v>105</v>
+      </c>
+      <c r="R10" s="41">
+        <v>65</v>
+      </c>
+      <c r="S10" s="41">
+        <v>10</v>
+      </c>
+      <c r="T10" s="41">
+        <v>70</v>
+      </c>
+      <c r="U10" s="41">
+        <v>50</v>
+      </c>
+      <c r="V10" s="41">
+        <v>80</v>
+      </c>
+      <c r="W10">
+        <f t="shared" si="3"/>
+        <v>500</v>
+      </c>
+      <c r="X10">
+        <f t="shared" si="4"/>
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A11" s="11"/>
+      <c r="B11" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12">
+        <v>120</v>
+      </c>
+      <c r="E11" s="12">
+        <v>120</v>
+      </c>
+      <c r="F11" s="12">
+        <v>80</v>
+      </c>
+      <c r="G11" s="28">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="H11" s="12">
+        <v>133</v>
+      </c>
+      <c r="I11" s="12">
+        <v>133</v>
+      </c>
+      <c r="J11" s="12">
+        <v>94</v>
+      </c>
+      <c r="K11" s="28">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="L11" s="53">
+        <f t="shared" si="2"/>
+        <v>17</v>
+      </c>
+      <c r="M11" s="42">
+        <v>2</v>
+      </c>
+      <c r="O11" t="s">
+        <v>9</v>
+      </c>
+      <c r="P11" s="41"/>
+      <c r="Q11" s="41">
+        <v>120</v>
+      </c>
+      <c r="R11" s="41">
+        <v>120</v>
+      </c>
+      <c r="S11" s="41">
+        <v>80</v>
+      </c>
+      <c r="T11" s="41">
+        <v>133</v>
+      </c>
+      <c r="U11" s="41">
+        <v>143</v>
+      </c>
+      <c r="V11" s="41">
+        <v>124</v>
+      </c>
+      <c r="W11">
+        <f t="shared" si="3"/>
+        <v>720</v>
+      </c>
+      <c r="X11">
+        <f t="shared" si="4"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A12" s="11"/>
+      <c r="B12" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12">
+        <v>0</v>
+      </c>
+      <c r="E12" s="12">
+        <v>0</v>
+      </c>
+      <c r="F12" s="12">
+        <v>0</v>
+      </c>
+      <c r="G12" s="28">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H12" s="12">
+        <v>0</v>
+      </c>
+      <c r="I12" s="12">
+        <v>24</v>
+      </c>
+      <c r="J12" s="12">
+        <v>40</v>
+      </c>
+      <c r="K12" s="28">
+        <f t="shared" si="1"/>
+        <v>3.2</v>
+      </c>
+      <c r="L12" s="53">
+        <f t="shared" si="2"/>
+        <v>1.6</v>
+      </c>
+      <c r="M12" s="42">
+        <v>2</v>
+      </c>
+      <c r="O12" t="s">
+        <v>34</v>
+      </c>
+      <c r="P12" s="41">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="41">
+        <v>0</v>
+      </c>
+      <c r="R12" s="41">
+        <v>10</v>
+      </c>
+      <c r="S12" s="41">
+        <v>10</v>
+      </c>
+      <c r="T12" s="41">
+        <v>0</v>
+      </c>
+      <c r="U12" s="41">
+        <v>34</v>
+      </c>
+      <c r="V12" s="41">
+        <v>74</v>
+      </c>
+      <c r="W12">
+        <f t="shared" si="3"/>
+        <v>128</v>
+      </c>
+      <c r="X12">
+        <f t="shared" si="4"/>
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="12"/>
+      <c r="K13" s="12"/>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A14" s="13"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="14">
+        <f t="shared" ref="C14:K14" si="5">SUM(C8:C13)</f>
+        <v>180</v>
+      </c>
+      <c r="D14" s="14">
+        <f t="shared" si="5"/>
+        <v>325</v>
+      </c>
+      <c r="E14" s="14">
+        <f t="shared" si="5"/>
+        <v>245</v>
+      </c>
+      <c r="F14" s="14">
+        <f t="shared" si="5"/>
+        <v>190</v>
+      </c>
+      <c r="G14" s="14">
+        <f t="shared" si="5"/>
+        <v>38</v>
+      </c>
+      <c r="H14" s="14">
+        <f t="shared" si="5"/>
+        <v>325</v>
+      </c>
+      <c r="I14" s="14">
+        <f t="shared" si="5"/>
+        <v>329</v>
+      </c>
+      <c r="J14" s="14">
+        <f t="shared" si="5"/>
+        <v>370</v>
+      </c>
+      <c r="K14" s="14">
+        <f t="shared" si="5"/>
+        <v>51.2</v>
+      </c>
+      <c r="L14" s="36">
+        <f>C14+D14+E14+F14+H14+I14+J14</f>
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A15" s="13"/>
+      <c r="B15" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13">
+        <f>D14/20</f>
+        <v>16.25</v>
+      </c>
+      <c r="E15" s="13">
+        <f t="shared" ref="E15:J15" si="6">E14/20</f>
+        <v>12.25</v>
+      </c>
+      <c r="F15" s="13">
+        <f t="shared" si="6"/>
+        <v>9.5</v>
+      </c>
+      <c r="G15" s="13"/>
+      <c r="H15" s="13">
+        <f t="shared" si="6"/>
+        <v>16.25</v>
+      </c>
+      <c r="I15" s="13">
+        <f t="shared" si="6"/>
+        <v>16.45</v>
+      </c>
+      <c r="J15" s="13">
+        <f t="shared" si="6"/>
+        <v>18.5</v>
+      </c>
+      <c r="K15" s="13"/>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A16" s="13"/>
+      <c r="B16" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" s="37">
+        <f>C15+C14</f>
+        <v>180</v>
+      </c>
+      <c r="D16" s="37">
+        <f t="shared" ref="D16:J16" si="7">D15+D14</f>
+        <v>341.25</v>
+      </c>
+      <c r="E16" s="37">
+        <f t="shared" si="7"/>
+        <v>257.25</v>
+      </c>
+      <c r="F16" s="37">
+        <f t="shared" si="7"/>
+        <v>199.5</v>
+      </c>
+      <c r="G16" s="37"/>
+      <c r="H16" s="37">
+        <f t="shared" si="7"/>
+        <v>341.25</v>
+      </c>
+      <c r="I16" s="37">
+        <f t="shared" si="7"/>
+        <v>345.45</v>
+      </c>
+      <c r="J16" s="37">
+        <f t="shared" si="7"/>
+        <v>388.5</v>
+      </c>
+      <c r="K16" s="37"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A17" s="13"/>
+      <c r="B17" s="40" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" s="37">
+        <f>C14/40</f>
+        <v>4.5</v>
+      </c>
+      <c r="D17" s="37">
+        <f t="shared" ref="D17:J17" si="8">D14/40</f>
+        <v>8.125</v>
+      </c>
+      <c r="E17" s="37">
+        <f t="shared" si="8"/>
+        <v>6.125</v>
+      </c>
+      <c r="F17" s="37">
+        <f t="shared" si="8"/>
+        <v>4.75</v>
+      </c>
+      <c r="G17" s="37"/>
+      <c r="H17" s="37">
+        <f t="shared" si="8"/>
+        <v>8.125</v>
+      </c>
+      <c r="I17" s="37">
+        <f t="shared" si="8"/>
+        <v>8.2249999999999996</v>
+      </c>
+      <c r="J17" s="37">
+        <f t="shared" si="8"/>
+        <v>9.25</v>
+      </c>
+      <c r="K17" s="37"/>
+      <c r="L17" s="36">
+        <f>SUM(C17:J17)</f>
+        <v>49.1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="C18" s="32"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="26"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="26"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="26"/>
+      <c r="I19" s="26"/>
+      <c r="J19" s="26"/>
+      <c r="K19" s="26"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B2:K5"/>
+    <mergeCell ref="D6:G6"/>
+    <mergeCell ref="H6:K6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01DA99B6-9D4E-4476-9E64-5E442631703E}">
   <dimension ref="A1:M19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -9389,7 +10149,7 @@
       <c r="K7" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="L7" s="43" t="s">
+      <c r="L7" t="s">
         <v>59</v>
       </c>
       <c r="M7" s="49" t="s">
@@ -9399,40 +10159,34 @@
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" s="27"/>
       <c r="B8" s="10" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C8" s="12">
-        <v>60</v>
-      </c>
-      <c r="D8" s="12">
-        <v>21</v>
-      </c>
-      <c r="E8" s="12">
-        <v>21</v>
-      </c>
-      <c r="F8" s="12">
-        <v>19</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
       <c r="G8" s="28">
         <f>SUM(D8:F8)/20</f>
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="H8" s="12">
-        <v>82</v>
+        <v>30</v>
       </c>
       <c r="I8" s="12">
-        <v>82</v>
+        <v>10</v>
       </c>
       <c r="J8" s="12">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="K8" s="28">
         <f>SUM(H8:J8)/20</f>
-        <v>12</v>
-      </c>
-      <c r="L8" s="53">
+        <v>4.2</v>
+      </c>
+      <c r="L8">
         <f>SUM(C8:F8,H8,I8,J8)/40</f>
-        <v>9.0250000000000004</v>
+        <v>5.05</v>
       </c>
       <c r="M8" s="49">
         <v>6</v>
@@ -9441,167 +10195,167 @@
     <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" s="27"/>
       <c r="B9" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" s="12">
-        <v>60</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="C9" s="12"/>
       <c r="D9" s="12">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="E9" s="12">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="F9" s="12">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G9" s="28">
         <f t="shared" ref="G9:G12" si="0">SUM(D9:F9)/20</f>
-        <v>13</v>
+        <v>2.5</v>
       </c>
       <c r="H9" s="12">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="I9" s="12">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="J9" s="12">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="K9" s="28">
         <f t="shared" ref="K9:K12" si="1">SUM(H9:J9)/20</f>
-        <v>8</v>
-      </c>
-      <c r="L9" s="53">
+        <v>12.2</v>
+      </c>
+      <c r="L9">
         <f t="shared" ref="L9:L12" si="2">SUM(C9:F9,H9,I9,J9)/40</f>
-        <v>12</v>
+        <v>7.35</v>
       </c>
       <c r="M9" s="49">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C10" s="12">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="D10" s="12">
-        <v>105</v>
+        <v>55</v>
       </c>
       <c r="E10" s="12">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="F10" s="12">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G10" s="28">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H10" s="12">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="I10" s="12">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="J10" s="12">
-        <v>80</v>
+        <v>53</v>
       </c>
       <c r="K10" s="28">
         <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="L10" s="53">
+        <v>5.5</v>
+      </c>
+      <c r="L10">
         <f t="shared" si="2"/>
-        <v>12.5</v>
+        <v>7.5</v>
       </c>
       <c r="M10" s="49">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="12"/>
+        <v>71</v>
+      </c>
+      <c r="C11" s="12">
+        <v>120</v>
+      </c>
       <c r="D11" s="12">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="E11" s="12">
         <v>120</v>
       </c>
       <c r="F11" s="12">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="G11" s="28">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="H11" s="12">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="I11" s="12">
-        <v>143</v>
+        <v>112</v>
       </c>
       <c r="J11" s="12">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="K11" s="28">
         <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="L11" s="53">
+        <v>17.3</v>
+      </c>
+      <c r="L11">
         <f t="shared" si="2"/>
-        <v>18</v>
+        <v>16.149999999999999</v>
       </c>
       <c r="M11" s="42">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
       <c r="B12" s="11" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C12" s="12">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="D12" s="12">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E12" s="12">
         <v>10</v>
       </c>
       <c r="F12" s="12">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G12" s="28">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H12" s="12">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="I12" s="12">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="J12" s="12">
-        <v>74</v>
+        <v>150</v>
       </c>
       <c r="K12" s="28">
         <f t="shared" si="1"/>
-        <v>5.4</v>
-      </c>
-      <c r="L12" s="53">
+        <v>15</v>
+      </c>
+      <c r="L12">
         <f t="shared" si="2"/>
-        <v>3.2</v>
+        <v>9.75</v>
       </c>
       <c r="M12" s="42">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.35">
@@ -9622,43 +10376,43 @@
       <c r="B14" s="10"/>
       <c r="C14" s="14">
         <f t="shared" ref="C14:K14" si="3">SUM(C8:C13)</f>
-        <v>240</v>
+        <v>398</v>
       </c>
       <c r="D14" s="14">
         <f t="shared" si="3"/>
-        <v>346</v>
+        <v>155</v>
       </c>
       <c r="E14" s="14">
         <f t="shared" si="3"/>
-        <v>276</v>
+        <v>195</v>
       </c>
       <c r="F14" s="14">
         <f t="shared" si="3"/>
-        <v>219</v>
+        <v>0</v>
       </c>
       <c r="G14" s="14">
         <f t="shared" si="3"/>
-        <v>42.05</v>
+        <v>17.5</v>
       </c>
       <c r="H14" s="14">
         <f t="shared" si="3"/>
-        <v>325</v>
+        <v>344</v>
       </c>
       <c r="I14" s="14">
         <f t="shared" si="3"/>
-        <v>349</v>
+        <v>286</v>
       </c>
       <c r="J14" s="14">
         <f t="shared" si="3"/>
-        <v>434</v>
+        <v>454</v>
       </c>
       <c r="K14" s="14">
         <f t="shared" si="3"/>
-        <v>55.4</v>
+        <v>54.2</v>
       </c>
       <c r="L14" s="36">
         <f>C14+D14+E14+F14+H14+I14+J14</f>
-        <v>2189</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">
@@ -9669,28 +10423,28 @@
       <c r="C15" s="13"/>
       <c r="D15" s="13">
         <f>D14/20</f>
-        <v>17.3</v>
+        <v>7.75</v>
       </c>
       <c r="E15" s="13">
         <f t="shared" ref="E15:J15" si="4">E14/20</f>
-        <v>13.8</v>
+        <v>9.75</v>
       </c>
       <c r="F15" s="13">
         <f t="shared" si="4"/>
-        <v>10.95</v>
+        <v>0</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13">
         <f t="shared" si="4"/>
-        <v>16.25</v>
+        <v>17.2</v>
       </c>
       <c r="I15" s="13">
         <f t="shared" si="4"/>
-        <v>17.45</v>
+        <v>14.3</v>
       </c>
       <c r="J15" s="13">
         <f t="shared" si="4"/>
-        <v>21.7</v>
+        <v>22.7</v>
       </c>
       <c r="K15" s="13"/>
     </row>
@@ -9701,32 +10455,32 @@
       </c>
       <c r="C16" s="37">
         <f>C15+C14</f>
-        <v>240</v>
+        <v>398</v>
       </c>
       <c r="D16" s="37">
         <f t="shared" ref="D16:J16" si="5">D15+D14</f>
-        <v>363.3</v>
+        <v>162.75</v>
       </c>
       <c r="E16" s="37">
         <f t="shared" si="5"/>
-        <v>289.8</v>
+        <v>204.75</v>
       </c>
       <c r="F16" s="37">
         <f t="shared" si="5"/>
-        <v>229.95</v>
+        <v>0</v>
       </c>
       <c r="G16" s="37"/>
       <c r="H16" s="37">
         <f t="shared" si="5"/>
-        <v>341.25</v>
+        <v>361.2</v>
       </c>
       <c r="I16" s="37">
         <f t="shared" si="5"/>
-        <v>366.45</v>
+        <v>300.3</v>
       </c>
       <c r="J16" s="37">
         <f t="shared" si="5"/>
-        <v>455.7</v>
+        <v>476.7</v>
       </c>
       <c r="K16" s="37"/>
     </row>
@@ -9737,461 +10491,37 @@
       </c>
       <c r="C17" s="37">
         <f>C14/40</f>
-        <v>6</v>
+        <v>9.9499999999999993</v>
       </c>
       <c r="D17" s="37">
         <f t="shared" ref="D17:J17" si="6">D14/40</f>
-        <v>8.65</v>
+        <v>3.875</v>
       </c>
       <c r="E17" s="37">
         <f t="shared" si="6"/>
-        <v>6.9</v>
+        <v>4.875</v>
       </c>
       <c r="F17" s="37">
         <f t="shared" si="6"/>
-        <v>5.4749999999999996</v>
+        <v>0</v>
       </c>
       <c r="G17" s="37"/>
       <c r="H17" s="37">
         <f t="shared" si="6"/>
-        <v>8.125</v>
+        <v>8.6</v>
       </c>
       <c r="I17" s="37">
         <f t="shared" si="6"/>
-        <v>8.7249999999999996</v>
+        <v>7.15</v>
       </c>
       <c r="J17" s="37">
         <f t="shared" si="6"/>
-        <v>10.85</v>
+        <v>11.35</v>
       </c>
       <c r="K17" s="37"/>
       <c r="L17" s="36">
         <f>SUM(C17:J17)</f>
-        <v>54.725000000000001</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="C18" s="32"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="26"/>
-      <c r="D19" s="26"/>
-      <c r="E19" s="26"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="26"/>
-      <c r="H19" s="26"/>
-      <c r="I19" s="26"/>
-      <c r="J19" s="26"/>
-      <c r="K19" s="26"/>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="B2:K5"/>
-    <mergeCell ref="D6:G6"/>
-    <mergeCell ref="H6:K6"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01DA99B6-9D4E-4476-9E64-5E442631703E}">
-  <dimension ref="A1:L19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="3.90625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.08984375" customWidth="1"/>
-    <col min="5" max="5" width="4.26953125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="3.08984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="4.26953125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="3.54296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.81640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2" s="1"/>
-      <c r="B2" s="54" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="56"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A3" s="1"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="59"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A4" s="1"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="59"/>
-    </row>
-    <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="1"/>
-      <c r="B5" s="60"/>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61"/>
-      <c r="J5" s="61"/>
-      <c r="K5" s="62"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A6" s="1"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="63" t="s">
-        <v>2</v>
-      </c>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="64" t="s">
-        <v>3</v>
-      </c>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
-      <c r="K6" s="65"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A7" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="38" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="H7" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="I7" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="J7" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="K7" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="L7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A8" s="27"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="28">
-        <f>SUM(D8:F8)/20</f>
-        <v>0</v>
-      </c>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="12"/>
-      <c r="K8" s="28">
-        <f>SUM(H8:J8)/20</f>
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <f>SUM(C8:F8,H8,I8,J8)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A9" s="27"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12"/>
-      <c r="K9" s="28"/>
-      <c r="L9">
-        <f t="shared" ref="L9:L12" si="0">SUM(C9:F9,H9,I9,J9)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A10" s="27"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="28"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="28"/>
-      <c r="L10">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A11" s="11"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="12"/>
-      <c r="K11" s="12"/>
-      <c r="L11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A12" s="11"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="12"/>
-      <c r="K12" s="12"/>
-      <c r="L12">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A13" s="11"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="12"/>
-      <c r="K13" s="12"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A14" s="13"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="14">
-        <f t="shared" ref="C14:K14" si="1">SUM(C8:C13)</f>
-        <v>0</v>
-      </c>
-      <c r="D14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L14" s="36">
-        <f>C14+D14+E14+F14+H14+I14+J14</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A15" s="13"/>
-      <c r="B15" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13">
-        <f>D14/20</f>
-        <v>0</v>
-      </c>
-      <c r="E15" s="13">
-        <f t="shared" ref="E15:J15" si="2">E14/20</f>
-        <v>0</v>
-      </c>
-      <c r="F15" s="13">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I15" s="13">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J15" s="13">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K15" s="13"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A16" s="13"/>
-      <c r="B16" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="C16" s="37">
-        <f>C15+C14</f>
-        <v>0</v>
-      </c>
-      <c r="D16" s="37">
-        <f t="shared" ref="D16:J16" si="3">D15+D14</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F16" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G16" s="37"/>
-      <c r="H16" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I16" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J16" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K16" s="37"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A17" s="13"/>
-      <c r="B17" s="40" t="s">
-        <v>41</v>
-      </c>
-      <c r="C17" s="37">
-        <f>C14/40</f>
-        <v>0</v>
-      </c>
-      <c r="D17" s="37">
-        <f t="shared" ref="D17:J17" si="4">D14/40</f>
-        <v>0</v>
-      </c>
-      <c r="E17" s="37">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F17" s="37">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G17" s="37"/>
-      <c r="H17" s="37">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I17" s="37">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J17" s="37">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K17" s="37"/>
-      <c r="L17" s="36">
-        <f>SUM(C17:J17)</f>
-        <v>0</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">

--- a/Final Execution SKU wise.xlsx
+++ b/Final Execution SKU wise.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E34BECC-42EE-4931-92F5-0C13503E7507}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77F83C70-287F-4FD6-BD2F-8015A48077F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" activeTab="23" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
   </bookViews>

--- a/Final Execution SKU wise.xlsx
+++ b/Final Execution SKU wise.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77F83C70-287F-4FD6-BD2F-8015A48077F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04F2D00D-B863-47E8-B123-6AD2147D71A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" activeTab="23" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" activeTab="24" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
   </bookViews>
   <sheets>
     <sheet name="last month" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="801" uniqueCount="79">
   <si>
     <t>Gate Pass</t>
   </si>
@@ -290,6 +290,9 @@
   </si>
   <si>
     <t xml:space="preserve">Sum </t>
+  </si>
+  <si>
+    <t>Supply</t>
   </si>
 </sst>
 </file>
@@ -741,7 +744,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
@@ -864,6 +867,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1245,57 +1249,57 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="54" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="56"/>
+      <c r="B2" s="55" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="57"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="59"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="60"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="59"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="60"/>
     </row>
     <row r="5" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="60"/>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61"/>
-      <c r="J5" s="61"/>
-      <c r="K5" s="62"/>
+      <c r="B5" s="61"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="62"/>
+      <c r="J5" s="62"/>
+      <c r="K5" s="63"/>
     </row>
     <row r="6" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="1"/>
@@ -1303,18 +1307,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="63" t="s">
+      <c r="D6" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="64" t="s">
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
-      <c r="K6" s="65"/>
+      <c r="I6" s="65"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="66"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
@@ -1650,57 +1654,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="54" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="56"/>
+      <c r="B2" s="55" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="57"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="59"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="60"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="59"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="60"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="60"/>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61"/>
-      <c r="J5" s="61"/>
-      <c r="K5" s="62"/>
+      <c r="B5" s="61"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="62"/>
+      <c r="J5" s="62"/>
+      <c r="K5" s="63"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -1708,18 +1712,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="63" t="s">
+      <c r="D6" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="64" t="s">
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
-      <c r="K6" s="65"/>
+      <c r="I6" s="65"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="66"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -2180,57 +2184,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="54" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="56"/>
+      <c r="B2" s="55" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="57"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="59"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="60"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="59"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="60"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="60"/>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61"/>
-      <c r="J5" s="61"/>
-      <c r="K5" s="62"/>
+      <c r="B5" s="61"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="62"/>
+      <c r="J5" s="62"/>
+      <c r="K5" s="63"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -2238,18 +2242,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="63" t="s">
+      <c r="D6" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="64" t="s">
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
-      <c r="K6" s="65"/>
+      <c r="I6" s="65"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="66"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -2634,57 +2638,57 @@
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="54" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="56"/>
+      <c r="B2" s="55" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="57"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="59"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="60"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="59"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="60"/>
     </row>
     <row r="5" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="60"/>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61"/>
-      <c r="J5" s="61"/>
-      <c r="K5" s="62"/>
+      <c r="B5" s="61"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="62"/>
+      <c r="J5" s="62"/>
+      <c r="K5" s="63"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -2692,18 +2696,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="63" t="s">
+      <c r="D6" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="64" t="s">
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
-      <c r="K6" s="65"/>
+      <c r="I6" s="65"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="66"/>
       <c r="Q6" s="33" t="s">
         <v>35</v>
       </c>
@@ -3152,57 +3156,57 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="54" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="56"/>
+      <c r="B2" s="55" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="57"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="59"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="60"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="59"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="60"/>
     </row>
     <row r="5" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="60"/>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61"/>
-      <c r="J5" s="61"/>
-      <c r="K5" s="62"/>
+      <c r="B5" s="61"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="62"/>
+      <c r="J5" s="62"/>
+      <c r="K5" s="63"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -3210,18 +3214,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="63" t="s">
+      <c r="D6" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="64" t="s">
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
-      <c r="K6" s="65"/>
+      <c r="I6" s="65"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="66"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -3642,57 +3646,57 @@
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="54" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="56"/>
+      <c r="B2" s="55" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="57"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="59"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="60"/>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="59"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="60"/>
     </row>
     <row r="5" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="60"/>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61"/>
-      <c r="J5" s="61"/>
-      <c r="K5" s="62"/>
+      <c r="B5" s="61"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="62"/>
+      <c r="J5" s="62"/>
+      <c r="K5" s="63"/>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -3700,18 +3704,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="63" t="s">
+      <c r="D6" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="64" t="s">
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
-      <c r="K6" s="65"/>
+      <c r="I6" s="65"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="66"/>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -4309,57 +4313,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="54" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="56"/>
+      <c r="B2" s="55" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="57"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="59"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="60"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="59"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="60"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="60"/>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61"/>
-      <c r="J5" s="61"/>
-      <c r="K5" s="62"/>
+      <c r="B5" s="61"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="62"/>
+      <c r="J5" s="62"/>
+      <c r="K5" s="63"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -4367,18 +4371,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="63" t="s">
+      <c r="D6" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="64" t="s">
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
-      <c r="K6" s="65"/>
+      <c r="I6" s="65"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="66"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -4733,57 +4737,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="54" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="56"/>
+      <c r="B2" s="55" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="57"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="59"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="60"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="59"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="60"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="60"/>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61"/>
-      <c r="J5" s="61"/>
-      <c r="K5" s="62"/>
+      <c r="B5" s="61"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="62"/>
+      <c r="J5" s="62"/>
+      <c r="K5" s="63"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -4791,18 +4795,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="63" t="s">
+      <c r="D6" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="64" t="s">
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
-      <c r="K6" s="65"/>
+      <c r="I6" s="65"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="66"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -5199,57 +5203,57 @@
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="54" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="56"/>
+      <c r="B2" s="55" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="57"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="59"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="60"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="59"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="60"/>
     </row>
     <row r="5" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="60"/>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61"/>
-      <c r="J5" s="61"/>
-      <c r="K5" s="62"/>
+      <c r="B5" s="61"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="62"/>
+      <c r="J5" s="62"/>
+      <c r="K5" s="63"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -5257,18 +5261,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="63" t="s">
+      <c r="D6" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="64" t="s">
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
-      <c r="K6" s="65"/>
+      <c r="I6" s="65"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="66"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -5736,57 +5740,57 @@
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="54" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="56"/>
+      <c r="B2" s="55" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="57"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="59"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="60"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="59"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="60"/>
     </row>
     <row r="5" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="60"/>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61"/>
-      <c r="J5" s="61"/>
-      <c r="K5" s="62"/>
+      <c r="B5" s="61"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="62"/>
+      <c r="J5" s="62"/>
+      <c r="K5" s="63"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -5794,18 +5798,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="63" t="s">
+      <c r="D6" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="64" t="s">
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
-      <c r="K6" s="65"/>
+      <c r="I6" s="65"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="66"/>
       <c r="R6" t="s">
         <v>63</v>
       </c>
@@ -6254,57 +6258,57 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="54" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="56"/>
+      <c r="B2" s="55" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="57"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="59"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="60"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="59"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="60"/>
     </row>
     <row r="5" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="60"/>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61"/>
-      <c r="J5" s="61"/>
-      <c r="K5" s="62"/>
+      <c r="B5" s="61"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="62"/>
+      <c r="J5" s="62"/>
+      <c r="K5" s="63"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -6312,18 +6316,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="63" t="s">
+      <c r="D6" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="64" t="s">
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
-      <c r="K6" s="65"/>
+      <c r="I6" s="65"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="66"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -6796,57 +6800,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="54" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="56"/>
+      <c r="B2" s="55" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="57"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="59"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="60"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="59"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="60"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="60"/>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61"/>
-      <c r="J5" s="61"/>
-      <c r="K5" s="62"/>
+      <c r="B5" s="61"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="62"/>
+      <c r="J5" s="62"/>
+      <c r="K5" s="63"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -6854,18 +6858,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="63" t="s">
+      <c r="D6" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="64" t="s">
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
-      <c r="K6" s="65"/>
+      <c r="I6" s="65"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="66"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -7268,57 +7272,57 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="54" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="56"/>
+      <c r="B2" s="55" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="57"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="59"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="60"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="59"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="60"/>
     </row>
     <row r="5" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="60"/>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61"/>
-      <c r="J5" s="61"/>
-      <c r="K5" s="62"/>
+      <c r="B5" s="61"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="62"/>
+      <c r="J5" s="62"/>
+      <c r="K5" s="63"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -7326,18 +7330,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="63" t="s">
+      <c r="D6" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="64" t="s">
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
-      <c r="K6" s="65"/>
+      <c r="I6" s="65"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="66"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -7746,57 +7750,57 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="54" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="56"/>
+      <c r="B2" s="55" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="57"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="59"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="60"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="59"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="60"/>
     </row>
     <row r="5" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="60"/>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61"/>
-      <c r="J5" s="61"/>
-      <c r="K5" s="62"/>
+      <c r="B5" s="61"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="62"/>
+      <c r="J5" s="62"/>
+      <c r="K5" s="63"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -7804,18 +7808,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="63" t="s">
+      <c r="D6" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="64" t="s">
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
-      <c r="K6" s="65"/>
+      <c r="I6" s="65"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="66"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -8315,57 +8319,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="54" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="56"/>
+      <c r="B2" s="55" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="57"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="59"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="60"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="59"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="60"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="60"/>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61"/>
-      <c r="J5" s="61"/>
-      <c r="K5" s="62"/>
+      <c r="B5" s="61"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="62"/>
+      <c r="J5" s="62"/>
+      <c r="K5" s="63"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -8373,18 +8377,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="63" t="s">
+      <c r="D6" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="64" t="s">
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
-      <c r="K6" s="65"/>
+      <c r="I6" s="65"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="66"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -8739,57 +8743,57 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="54" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="56"/>
+      <c r="B2" s="55" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="57"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="59"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="60"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="59"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="60"/>
     </row>
     <row r="5" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="60"/>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61"/>
-      <c r="J5" s="61"/>
-      <c r="K5" s="62"/>
+      <c r="B5" s="61"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="62"/>
+      <c r="J5" s="62"/>
+      <c r="K5" s="63"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -8797,18 +8801,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="63" t="s">
+      <c r="D6" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="64" t="s">
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
-      <c r="K6" s="65"/>
+      <c r="I6" s="65"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="66"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -9293,60 +9297,60 @@
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="54" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="56"/>
+      <c r="B2" s="55" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="57"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="59"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="60"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="59"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="60"/>
       <c r="S4" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="60"/>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61"/>
-      <c r="J5" s="61"/>
-      <c r="K5" s="62"/>
+      <c r="B5" s="61"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="62"/>
+      <c r="J5" s="62"/>
+      <c r="K5" s="63"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -9354,18 +9358,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="63" t="s">
+      <c r="D6" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="64" t="s">
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
-      <c r="K6" s="65"/>
+      <c r="I6" s="65"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="66"/>
       <c r="P6" s="45">
         <v>60</v>
       </c>
@@ -10014,7 +10018,7 @@
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01DA99B6-9D4E-4476-9E64-5E442631703E}">
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:AA19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.90625" bestFit="1" customWidth="1"/>
@@ -10027,95 +10031,128 @@
     <col min="8" max="9" width="4.26953125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="3.54296875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="3.54296875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="4" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="3.90625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.26953125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="3.08984375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="3.90625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="3.6328125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="3.08984375" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="5.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
+      <c r="E1" s="1" t="s">
+        <v>75</v>
+      </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="U1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="54" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="56"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="B2" s="55" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="57"/>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="59"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="B3" s="58"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="60"/>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="59"/>
-    </row>
-    <row r="5" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B4" s="58"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="60"/>
+    </row>
+    <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="60"/>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61"/>
-      <c r="J5" s="61"/>
-      <c r="K5" s="62"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="B5" s="61"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="62"/>
+      <c r="J5" s="62"/>
+      <c r="K5" s="63"/>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
       <c r="B6" s="2"/>
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="63" t="s">
+      <c r="D6" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="64" t="s">
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
-      <c r="K6" s="65"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="I6" s="65"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="66"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="R6" s="64" t="s">
+        <v>2</v>
+      </c>
+      <c r="S6" s="65"/>
+      <c r="T6" s="65"/>
+      <c r="U6" s="66"/>
+      <c r="V6" s="65" t="s">
+        <v>3</v>
+      </c>
+      <c r="W6" s="65"/>
+      <c r="X6" s="65"/>
+      <c r="Y6" s="66"/>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
         <v>4</v>
       </c>
@@ -10149,14 +10186,53 @@
       <c r="K7" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="L7" t="s">
+      <c r="L7" s="41" t="s">
         <v>59</v>
       </c>
-      <c r="M7" s="49" t="s">
+      <c r="M7" s="12" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="O7" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="P7" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q7" s="38" t="s">
+        <v>6</v>
+      </c>
+      <c r="R7" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S7" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="T7" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="U7" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="V7" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="W7" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="X7" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y7" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>59</v>
+      </c>
+      <c r="AA7" s="49" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A8" s="27"/>
       <c r="B8" s="10" t="s">
         <v>76</v>
@@ -10184,15 +10260,49 @@
         <f>SUM(H8:J8)/20</f>
         <v>4.2</v>
       </c>
-      <c r="L8">
+      <c r="L8" s="54">
         <f>SUM(C8:F8,H8,I8,J8)/40</f>
         <v>5.05</v>
       </c>
-      <c r="M8" s="49">
+      <c r="M8" s="51">
         <v>6</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="O8" s="27"/>
+      <c r="P8" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q8" s="12">
+        <v>72</v>
+      </c>
+      <c r="R8" s="12"/>
+      <c r="S8" s="12"/>
+      <c r="T8" s="12"/>
+      <c r="U8" s="28">
+        <f>SUM(R8:T8)/20</f>
+        <v>0</v>
+      </c>
+      <c r="V8" s="12">
+        <v>30</v>
+      </c>
+      <c r="W8" s="12">
+        <v>10</v>
+      </c>
+      <c r="X8" s="12">
+        <v>26</v>
+      </c>
+      <c r="Y8" s="28">
+        <f>SUM(V8:X8)/20</f>
+        <v>3.3</v>
+      </c>
+      <c r="Z8">
+        <f>SUM(Q8:T8,V8,W8,X8)/40</f>
+        <v>3.45</v>
+      </c>
+      <c r="AA8" s="49">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A9" s="27"/>
       <c r="B9" s="10" t="s">
         <v>34</v>
@@ -10224,15 +10334,55 @@
         <f t="shared" ref="K9:K12" si="1">SUM(H9:J9)/20</f>
         <v>12.2</v>
       </c>
-      <c r="L9">
+      <c r="L9" s="54">
         <f t="shared" ref="L9:L12" si="2">SUM(C9:F9,H9,I9,J9)/40</f>
         <v>7.35</v>
       </c>
-      <c r="M9" s="49">
+      <c r="M9" s="51">
         <v>6</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="O9" s="27"/>
+      <c r="P9" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q9" s="12">
+        <v>0</v>
+      </c>
+      <c r="R9" s="12">
+        <v>0</v>
+      </c>
+      <c r="S9" s="12">
+        <v>0</v>
+      </c>
+      <c r="T9" s="12">
+        <v>0</v>
+      </c>
+      <c r="U9" s="28">
+        <f t="shared" ref="U9:U12" si="3">SUM(R9:T9)/20</f>
+        <v>0</v>
+      </c>
+      <c r="V9" s="12">
+        <v>0</v>
+      </c>
+      <c r="W9" s="12">
+        <v>0</v>
+      </c>
+      <c r="X9" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="28">
+        <f t="shared" ref="Y9:Y12" si="4">SUM(V9:X9)/20</f>
+        <v>0</v>
+      </c>
+      <c r="Z9">
+        <f t="shared" ref="Z9:Z12" si="5">SUM(Q9:T9,V9,W9,X9)/40</f>
+        <v>0</v>
+      </c>
+      <c r="AA9" s="49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
         <v>9</v>
@@ -10266,15 +10416,55 @@
         <f t="shared" si="1"/>
         <v>5.5</v>
       </c>
-      <c r="L10">
+      <c r="L10" s="54">
         <f t="shared" si="2"/>
         <v>7.5</v>
       </c>
-      <c r="M10" s="49">
+      <c r="M10" s="51">
         <v>7</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="O10" s="27"/>
+      <c r="P10" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q10" s="12">
+        <v>90</v>
+      </c>
+      <c r="R10" s="12">
+        <v>40</v>
+      </c>
+      <c r="S10" s="12">
+        <v>40</v>
+      </c>
+      <c r="T10" s="12">
+        <v>0</v>
+      </c>
+      <c r="U10" s="28">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="V10" s="12">
+        <v>34</v>
+      </c>
+      <c r="W10" s="12">
+        <v>13</v>
+      </c>
+      <c r="X10" s="12">
+        <v>43</v>
+      </c>
+      <c r="Y10" s="28">
+        <f t="shared" si="4"/>
+        <v>4.5</v>
+      </c>
+      <c r="Z10">
+        <f t="shared" si="5"/>
+        <v>6.5</v>
+      </c>
+      <c r="AA10" s="49">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
         <v>71</v>
@@ -10308,15 +10498,55 @@
         <f t="shared" si="1"/>
         <v>17.3</v>
       </c>
-      <c r="L11">
+      <c r="L11" s="54">
         <f t="shared" si="2"/>
         <v>16.149999999999999</v>
       </c>
-      <c r="M11" s="42">
+      <c r="M11" s="51">
         <v>6</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="O11" s="11"/>
+      <c r="P11" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q11" s="12">
+        <v>40</v>
+      </c>
+      <c r="R11" s="12">
+        <v>20</v>
+      </c>
+      <c r="S11" s="12">
+        <v>40</v>
+      </c>
+      <c r="T11" s="12">
+        <v>0</v>
+      </c>
+      <c r="U11" s="28">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="V11" s="12">
+        <v>80</v>
+      </c>
+      <c r="W11" s="12">
+        <v>70</v>
+      </c>
+      <c r="X11" s="12">
+        <v>70</v>
+      </c>
+      <c r="Y11" s="28">
+        <f t="shared" si="4"/>
+        <v>11</v>
+      </c>
+      <c r="Z11">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
+      <c r="AA11" s="42">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
       <c r="B12" s="11" t="s">
         <v>70</v>
@@ -10350,15 +10580,55 @@
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="L12">
+      <c r="L12" s="54">
         <f t="shared" si="2"/>
         <v>9.75</v>
       </c>
-      <c r="M12" s="42">
+      <c r="M12" s="51">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="O12" s="11"/>
+      <c r="P12" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q12" s="12">
+        <v>60</v>
+      </c>
+      <c r="R12" s="12">
+        <v>10</v>
+      </c>
+      <c r="S12" s="12">
+        <v>10</v>
+      </c>
+      <c r="T12" s="12">
+        <v>0</v>
+      </c>
+      <c r="U12" s="28">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="V12" s="12">
+        <v>70</v>
+      </c>
+      <c r="W12" s="12">
+        <v>40</v>
+      </c>
+      <c r="X12" s="12">
+        <v>110</v>
+      </c>
+      <c r="Y12" s="28">
+        <f t="shared" si="4"/>
+        <v>11</v>
+      </c>
+      <c r="Z12">
+        <f t="shared" si="5"/>
+        <v>7.5</v>
+      </c>
+      <c r="AA12" s="42">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
       <c r="B13" s="11"/>
       <c r="C13" s="12"/>
@@ -10371,43 +10641,43 @@
       <c r="J13" s="12"/>
       <c r="K13" s="12"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:K14" si="3">SUM(C8:C13)</f>
+        <f t="shared" ref="C14:K14" si="6">SUM(C8:C13)</f>
         <v>398</v>
       </c>
       <c r="D14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>155</v>
       </c>
       <c r="E14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>195</v>
       </c>
       <c r="F14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="G14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>17.5</v>
       </c>
       <c r="H14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>344</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>286</v>
       </c>
       <c r="J14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>454</v>
       </c>
       <c r="K14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>54.2</v>
       </c>
       <c r="L14" s="36">
@@ -10415,7 +10685,7 @@
         <v>1832</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="13"/>
       <c r="B15" s="10" t="s">
         <v>40</v>
@@ -10426,29 +10696,29 @@
         <v>7.75</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:J15" si="4">E14/20</f>
+        <f t="shared" ref="E15:J15" si="7">E14/20</f>
         <v>9.75</v>
       </c>
       <c r="F15" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>17.2</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>14.3</v>
       </c>
       <c r="J15" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>22.7</v>
       </c>
       <c r="K15" s="13"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="13"/>
       <c r="B16" s="10" t="s">
         <v>39</v>
@@ -10458,28 +10728,28 @@
         <v>398</v>
       </c>
       <c r="D16" s="37">
-        <f t="shared" ref="D16:J16" si="5">D15+D14</f>
+        <f t="shared" ref="D16:J16" si="8">D15+D14</f>
         <v>162.75</v>
       </c>
       <c r="E16" s="37">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>204.75</v>
       </c>
       <c r="F16" s="37">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="G16" s="37"/>
       <c r="H16" s="37">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>361.2</v>
       </c>
       <c r="I16" s="37">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>300.3</v>
       </c>
       <c r="J16" s="37">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>476.7</v>
       </c>
       <c r="K16" s="37"/>
@@ -10494,28 +10764,28 @@
         <v>9.9499999999999993</v>
       </c>
       <c r="D17" s="37">
-        <f t="shared" ref="D17:J17" si="6">D14/40</f>
+        <f t="shared" ref="D17:J17" si="9">D14/40</f>
         <v>3.875</v>
       </c>
       <c r="E17" s="37">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>4.875</v>
       </c>
       <c r="F17" s="37">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="G17" s="37"/>
       <c r="H17" s="37">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>8.6</v>
       </c>
       <c r="I17" s="37">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>7.15</v>
       </c>
       <c r="J17" s="37">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>11.35</v>
       </c>
       <c r="K17" s="37"/>
@@ -10541,10 +10811,12 @@
       <c r="K19" s="26"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="5">
     <mergeCell ref="B2:K5"/>
     <mergeCell ref="D6:G6"/>
     <mergeCell ref="H6:K6"/>
+    <mergeCell ref="R6:U6"/>
+    <mergeCell ref="V6:Y6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10582,57 +10854,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="54" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="56"/>
+      <c r="B2" s="55" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="57"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="59"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="60"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="59"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="60"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="60"/>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61"/>
-      <c r="J5" s="61"/>
-      <c r="K5" s="62"/>
+      <c r="B5" s="61"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="62"/>
+      <c r="J5" s="62"/>
+      <c r="K5" s="63"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -10640,18 +10912,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="63" t="s">
+      <c r="D6" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="64" t="s">
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
-      <c r="K6" s="65"/>
+      <c r="I6" s="65"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="66"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -11006,57 +11278,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="54" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="56"/>
+      <c r="B2" s="55" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="57"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="59"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="60"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="59"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="60"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="60"/>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61"/>
-      <c r="J5" s="61"/>
-      <c r="K5" s="62"/>
+      <c r="B5" s="61"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="62"/>
+      <c r="J5" s="62"/>
+      <c r="K5" s="63"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -11064,18 +11336,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="63" t="s">
+      <c r="D6" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="64" t="s">
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
-      <c r="K6" s="65"/>
+      <c r="I6" s="65"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="66"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -11400,7 +11672,7 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C349645-DD2F-49D3-B3AF-0E6F627D58A3}">
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:V19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.90625" bestFit="1" customWidth="1"/>
@@ -11413,9 +11685,17 @@
     <col min="8" max="9" width="4.26953125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="3.54296875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="4.26953125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="3.90625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="3.26953125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.08984375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="3.90625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="3.6328125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="3.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -11428,80 +11708,80 @@
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="54" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="56"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B2" s="55" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="57"/>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="59"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B3" s="58"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="60"/>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="59"/>
-    </row>
-    <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B4" s="58"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="60"/>
+    </row>
+    <row r="5" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="60"/>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61"/>
-      <c r="J5" s="61"/>
-      <c r="K5" s="62"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B5" s="61"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="62"/>
+      <c r="J5" s="62"/>
+      <c r="K5" s="63"/>
+    </row>
+    <row r="6" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="1"/>
       <c r="B6" s="2"/>
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="63" t="s">
+      <c r="D6" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="64" t="s">
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
-      <c r="K6" s="65"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="I6" s="65"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="66"/>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
         <v>4</v>
       </c>
@@ -11538,99 +11818,266 @@
       <c r="L7" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M7" s="49" t="s">
+        <v>58</v>
+      </c>
+      <c r="O7" s="2"/>
+      <c r="P7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="64" t="s">
+        <v>2</v>
+      </c>
+      <c r="R7" s="65"/>
+      <c r="S7" s="65"/>
+      <c r="T7" s="65" t="s">
+        <v>3</v>
+      </c>
+      <c r="U7" s="65"/>
+      <c r="V7" s="65"/>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A8" s="27"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
+      <c r="B8" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="12">
+        <v>190</v>
+      </c>
+      <c r="D8" s="12">
+        <v>80</v>
+      </c>
+      <c r="E8" s="12">
+        <v>40</v>
+      </c>
+      <c r="F8" s="12">
+        <v>0</v>
+      </c>
       <c r="G8" s="28">
         <f>SUM(D8:F8)/20</f>
-        <v>0</v>
-      </c>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="12"/>
+        <v>6</v>
+      </c>
+      <c r="H8" s="12">
+        <v>106</v>
+      </c>
+      <c r="I8" s="12">
+        <v>16</v>
+      </c>
+      <c r="J8" s="12">
+        <v>138</v>
+      </c>
       <c r="K8" s="28">
         <f>SUM(H8:J8)/20</f>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L8">
         <f>SUM(C8:F8,H8,I8,J8)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+        <v>14.25</v>
+      </c>
+      <c r="M8" s="49">
+        <v>7</v>
+      </c>
+      <c r="O8" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="P8" s="38" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q8" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R8" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="S8" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="T8" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="U8" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="V8" s="12" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A9" s="27"/>
-      <c r="B9" s="10"/>
+      <c r="B9" s="10" t="s">
+        <v>68</v>
+      </c>
       <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
+      <c r="D9" s="12">
+        <v>60</v>
+      </c>
+      <c r="E9" s="12">
+        <v>100</v>
+      </c>
       <c r="F9" s="12"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12"/>
-      <c r="K9" s="28"/>
+      <c r="G9" s="28">
+        <f t="shared" ref="G9:G12" si="0">SUM(D9:F9)/20</f>
+        <v>8</v>
+      </c>
+      <c r="H9" s="12">
+        <v>247</v>
+      </c>
+      <c r="I9" s="12">
+        <v>247</v>
+      </c>
+      <c r="J9" s="12">
+        <v>258</v>
+      </c>
+      <c r="K9" s="28">
+        <f t="shared" ref="K9:K12" si="1">SUM(H9:J9)/20</f>
+        <v>37.6</v>
+      </c>
       <c r="L9">
-        <f t="shared" ref="L9:L12" si="0">SUM(C9:F9,H9,I9,J9)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+        <f t="shared" ref="L9:L12" si="2">SUM(C9:F9,H9,I9,J9)/40</f>
+        <v>22.8</v>
+      </c>
+      <c r="M9" s="49">
+        <v>8</v>
+      </c>
+      <c r="O9" s="10"/>
+      <c r="P9" s="12"/>
+      <c r="Q9" s="12"/>
+      <c r="R9" s="12"/>
+      <c r="S9" s="12"/>
+      <c r="T9" s="12"/>
+      <c r="U9" s="12"/>
+      <c r="V9" s="12"/>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
-      <c r="B10" s="10"/>
+      <c r="B10" s="10" t="s">
+        <v>11</v>
+      </c>
       <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="28"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="28"/>
+      <c r="D10" s="12">
+        <v>20</v>
+      </c>
+      <c r="E10" s="12">
+        <v>40</v>
+      </c>
+      <c r="F10" s="12">
+        <v>0</v>
+      </c>
+      <c r="G10" s="28">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="H10" s="12">
+        <v>70</v>
+      </c>
+      <c r="I10" s="12">
+        <v>55</v>
+      </c>
+      <c r="J10" s="12">
+        <v>75</v>
+      </c>
+      <c r="K10" s="28">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
       <c r="L10">
+        <f t="shared" si="2"/>
+        <v>6.5</v>
+      </c>
+      <c r="M10" s="49">
+        <v>4</v>
+      </c>
+      <c r="O10" s="10"/>
+      <c r="P10" s="12"/>
+      <c r="Q10" s="12"/>
+      <c r="R10" s="12"/>
+      <c r="S10" s="12"/>
+      <c r="T10" s="12"/>
+      <c r="U10" s="12"/>
+      <c r="V10" s="12"/>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A11" s="11"/>
+      <c r="B11" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="12">
+        <v>60</v>
+      </c>
+      <c r="D11" s="12">
+        <v>20</v>
+      </c>
+      <c r="E11" s="12">
+        <v>20</v>
+      </c>
+      <c r="F11" s="12">
+        <v>0</v>
+      </c>
+      <c r="G11" s="28">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A11" s="11"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="12"/>
-      <c r="K11" s="12"/>
+        <v>2</v>
+      </c>
+      <c r="H11" s="12">
+        <v>16</v>
+      </c>
+      <c r="I11" s="12">
+        <v>40</v>
+      </c>
+      <c r="J11" s="12">
+        <v>72</v>
+      </c>
+      <c r="K11" s="28">
+        <f t="shared" si="1"/>
+        <v>6.4</v>
+      </c>
       <c r="L11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v>5.7</v>
+      </c>
+      <c r="M11" s="42">
+        <v>5</v>
+      </c>
+      <c r="O11" s="10"/>
+      <c r="P11" s="12"/>
+      <c r="Q11" s="12"/>
+      <c r="R11" s="12"/>
+      <c r="S11" s="12"/>
+      <c r="T11" s="12"/>
+      <c r="U11" s="12"/>
+      <c r="V11" s="12"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
       <c r="B12" s="11"/>
       <c r="C12" s="12"/>
       <c r="D12" s="12"/>
       <c r="E12" s="12"/>
       <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
+      <c r="G12" s="28">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="H12" s="12"/>
       <c r="I12" s="12"/>
       <c r="J12" s="12"/>
-      <c r="K12" s="12"/>
+      <c r="K12" s="28">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="L12">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O12" s="11"/>
+      <c r="P12" s="12"/>
+      <c r="Q12" s="12"/>
+      <c r="R12" s="12"/>
+      <c r="S12" s="12"/>
+      <c r="T12" s="12"/>
+      <c r="U12" s="12"/>
+      <c r="V12" s="12"/>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
       <c r="B13" s="11"/>
       <c r="C13" s="12"/>
@@ -11642,52 +12089,68 @@
       <c r="I13" s="12"/>
       <c r="J13" s="12"/>
       <c r="K13" s="12"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="O13" s="11"/>
+      <c r="P13" s="12"/>
+      <c r="Q13" s="12"/>
+      <c r="R13" s="12"/>
+      <c r="S13" s="12"/>
+      <c r="T13" s="12"/>
+      <c r="U13" s="12"/>
+      <c r="V13" s="12"/>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:K14" si="1">SUM(C8:C13)</f>
-        <v>0</v>
+        <f t="shared" ref="C14:K14" si="3">SUM(C8:C13)</f>
+        <v>250</v>
       </c>
       <c r="D14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>180</v>
       </c>
       <c r="E14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>200</v>
       </c>
       <c r="F14" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>19</v>
       </c>
       <c r="H14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>439</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>358</v>
       </c>
       <c r="J14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>543</v>
       </c>
       <c r="K14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>67</v>
       </c>
       <c r="L14" s="36">
         <f>C14+D14+E14+F14+H14+I14+J14</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+        <v>1970</v>
+      </c>
+      <c r="O14" s="11"/>
+      <c r="P14" s="12"/>
+      <c r="Q14" s="12"/>
+      <c r="R14" s="12"/>
+      <c r="S14" s="12"/>
+      <c r="T14" s="12"/>
+      <c r="U14" s="12"/>
+      <c r="V14" s="12"/>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A15" s="13"/>
       <c r="B15" s="10" t="s">
         <v>40</v>
@@ -11695,64 +12158,64 @@
       <c r="C15" s="13"/>
       <c r="D15" s="13">
         <f>D14/20</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:J15" si="2">E14/20</f>
-        <v>0</v>
+        <f t="shared" ref="E15:J15" si="4">E14/20</f>
+        <v>10</v>
       </c>
       <c r="F15" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>21.95</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>17.899999999999999</v>
       </c>
       <c r="J15" s="13">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>27.15</v>
       </c>
       <c r="K15" s="13"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A16" s="13"/>
       <c r="B16" s="10" t="s">
         <v>39</v>
       </c>
       <c r="C16" s="37">
         <f>C15+C14</f>
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="D16" s="37">
-        <f t="shared" ref="D16:J16" si="3">D15+D14</f>
-        <v>0</v>
+        <f t="shared" ref="D16:J16" si="5">D15+D14</f>
+        <v>189</v>
       </c>
       <c r="E16" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>210</v>
       </c>
       <c r="F16" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G16" s="37"/>
       <c r="H16" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>460.95</v>
       </c>
       <c r="I16" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>375.9</v>
       </c>
       <c r="J16" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>570.15</v>
       </c>
       <c r="K16" s="37"/>
     </row>
@@ -11763,37 +12226,37 @@
       </c>
       <c r="C17" s="37">
         <f>C14/40</f>
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="D17" s="37">
-        <f t="shared" ref="D17:J17" si="4">D14/40</f>
-        <v>0</v>
+        <f t="shared" ref="D17:J17" si="6">D14/40</f>
+        <v>4.5</v>
       </c>
       <c r="E17" s="37">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>5</v>
       </c>
       <c r="F17" s="37">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="G17" s="37"/>
       <c r="H17" s="37">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>10.975</v>
       </c>
       <c r="I17" s="37">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>8.9499999999999993</v>
       </c>
       <c r="J17" s="37">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>13.574999999999999</v>
       </c>
       <c r="K17" s="37"/>
       <c r="L17" s="36">
         <f>SUM(C17:J17)</f>
-        <v>0</v>
+        <v>49.25</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">
@@ -11813,10 +12276,12 @@
       <c r="K19" s="26"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="5">
     <mergeCell ref="B2:K5"/>
     <mergeCell ref="D6:G6"/>
     <mergeCell ref="H6:K6"/>
+    <mergeCell ref="Q7:S7"/>
+    <mergeCell ref="T7:V7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11854,57 +12319,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="54" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="56"/>
+      <c r="B2" s="55" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="57"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="59"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="60"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="59"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="60"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="60"/>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61"/>
-      <c r="J5" s="61"/>
-      <c r="K5" s="62"/>
+      <c r="B5" s="61"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="62"/>
+      <c r="J5" s="62"/>
+      <c r="K5" s="63"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -11912,18 +12377,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="63" t="s">
+      <c r="D6" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="64" t="s">
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
-      <c r="K6" s="65"/>
+      <c r="I6" s="65"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="66"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -12278,57 +12743,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="54" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="56"/>
+      <c r="B2" s="55" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="57"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="59"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="60"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="59"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="60"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="60"/>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61"/>
-      <c r="J5" s="61"/>
-      <c r="K5" s="62"/>
+      <c r="B5" s="61"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="62"/>
+      <c r="J5" s="62"/>
+      <c r="K5" s="63"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -12336,18 +12801,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="63" t="s">
+      <c r="D6" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="64" t="s">
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
-      <c r="K6" s="65"/>
+      <c r="I6" s="65"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="66"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -12764,57 +13229,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="54" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="56"/>
+      <c r="B2" s="55" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="57"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="59"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="60"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="59"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="60"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="60"/>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61"/>
-      <c r="J5" s="61"/>
-      <c r="K5" s="62"/>
+      <c r="B5" s="61"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="62"/>
+      <c r="J5" s="62"/>
+      <c r="K5" s="63"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -12822,18 +13287,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="63" t="s">
+      <c r="D6" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="64" t="s">
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
-      <c r="K6" s="65"/>
+      <c r="I6" s="65"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="66"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -13188,57 +13653,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="54" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="56"/>
+      <c r="B2" s="55" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="57"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="59"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="60"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="59"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="60"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="60"/>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61"/>
-      <c r="J5" s="61"/>
-      <c r="K5" s="62"/>
+      <c r="B5" s="61"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="62"/>
+      <c r="J5" s="62"/>
+      <c r="K5" s="63"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -13246,18 +13711,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="63" t="s">
+      <c r="D6" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="64" t="s">
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
-      <c r="K6" s="65"/>
+      <c r="I6" s="65"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="66"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -13613,57 +14078,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="54" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="56"/>
+      <c r="B2" s="55" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="57"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="59"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="60"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="59"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="60"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="60"/>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61"/>
-      <c r="J5" s="61"/>
-      <c r="K5" s="62"/>
+      <c r="B5" s="61"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="62"/>
+      <c r="J5" s="62"/>
+      <c r="K5" s="63"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -13671,18 +14136,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="63" t="s">
+      <c r="D6" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="64" t="s">
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
-      <c r="K6" s="65"/>
+      <c r="I6" s="65"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="66"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -14037,57 +14502,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="54" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="56"/>
+      <c r="B2" s="55" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="57"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="59"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="60"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="59"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="60"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="60"/>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61"/>
-      <c r="J5" s="61"/>
-      <c r="K5" s="62"/>
+      <c r="B5" s="61"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="62"/>
+      <c r="J5" s="62"/>
+      <c r="K5" s="63"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -14095,18 +14560,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="63" t="s">
+      <c r="D6" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="64" t="s">
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
-      <c r="K6" s="65"/>
+      <c r="I6" s="65"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="66"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -14576,57 +15041,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="54" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="56"/>
+      <c r="B2" s="55" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="57"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="59"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="60"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="59"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="60"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="60"/>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61"/>
-      <c r="J5" s="61"/>
-      <c r="K5" s="62"/>
+      <c r="B5" s="61"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="62"/>
+      <c r="J5" s="62"/>
+      <c r="K5" s="63"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -14634,18 +15099,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="63" t="s">
+      <c r="D6" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="64" t="s">
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
-      <c r="K6" s="65"/>
+      <c r="I6" s="65"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="66"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -15087,57 +15552,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="54" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="56"/>
+      <c r="B2" s="55" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="57"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="59"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="60"/>
     </row>
     <row r="4" spans="1:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="59"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="60"/>
     </row>
     <row r="5" spans="1:12" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="60"/>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61"/>
-      <c r="J5" s="61"/>
-      <c r="K5" s="62"/>
+      <c r="B5" s="61"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="62"/>
+      <c r="J5" s="62"/>
+      <c r="K5" s="63"/>
     </row>
     <row r="6" spans="1:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -15145,18 +15610,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="63" t="s">
+      <c r="D6" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="64" t="s">
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
-      <c r="K6" s="65"/>
+      <c r="I6" s="65"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="66"/>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -15563,57 +16028,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="54" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="56"/>
+      <c r="B2" s="55" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="57"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="59"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="60"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="59"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="60"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="60"/>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61"/>
-      <c r="J5" s="61"/>
-      <c r="K5" s="62"/>
+      <c r="B5" s="61"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="62"/>
+      <c r="J5" s="62"/>
+      <c r="K5" s="63"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -15621,18 +16086,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="63" t="s">
+      <c r="D6" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="64" t="s">
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
-      <c r="K6" s="65"/>
+      <c r="I6" s="65"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="66"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -15991,57 +16456,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="54" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="56"/>
+      <c r="B2" s="55" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="57"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="59"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="60"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="59"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="60"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="60"/>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61"/>
-      <c r="J5" s="61"/>
-      <c r="K5" s="62"/>
+      <c r="B5" s="61"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="62"/>
+      <c r="J5" s="62"/>
+      <c r="K5" s="63"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -16049,18 +16514,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="63" t="s">
+      <c r="D6" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="64" t="s">
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
-      <c r="K6" s="65"/>
+      <c r="I6" s="65"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="66"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -16409,57 +16874,57 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="54" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="56"/>
+      <c r="B2" s="55" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="57"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="59"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="60"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="59"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="60"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="60"/>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61"/>
-      <c r="J5" s="61"/>
-      <c r="K5" s="62"/>
+      <c r="B5" s="61"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="62"/>
+      <c r="J5" s="62"/>
+      <c r="K5" s="63"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -16467,18 +16932,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="63" t="s">
+      <c r="D6" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="64" t="s">
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
-      <c r="K6" s="65"/>
+      <c r="I6" s="65"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="66"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">

--- a/Final Execution SKU wise.xlsx
+++ b/Final Execution SKU wise.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04F2D00D-B863-47E8-B123-6AD2147D71A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D2FE5B8-6033-4894-8CA3-215C53556F8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" activeTab="24" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" firstSheet="1" activeTab="28" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
   </bookViews>
   <sheets>
     <sheet name="last month" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="801" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="820" uniqueCount="81">
   <si>
     <t>Gate Pass</t>
   </si>
@@ -293,6 +293,12 @@
   </si>
   <si>
     <t>Supply</t>
+  </si>
+  <si>
+    <t>Execution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shops </t>
   </si>
 </sst>
 </file>
@@ -744,7 +750,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
@@ -903,6 +909,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -11672,7 +11684,7 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C349645-DD2F-49D3-B3AF-0E6F627D58A3}">
-  <dimension ref="A1:V19"/>
+  <dimension ref="A1:AA19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.90625" bestFit="1" customWidth="1"/>
@@ -11686,32 +11698,34 @@
     <col min="10" max="10" width="3.54296875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="5.81640625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="4.26953125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="4" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6.453125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="3.90625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="3.26953125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.6328125" customWidth="1"/>
     <col min="19" max="19" width="3.08984375" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="3.90625" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="3.6328125" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="3.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+      <c r="F1" s="52"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="Q1" s="67"/>
+      <c r="R1" s="67"/>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="55" t="s">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="C2" s="56"/>
       <c r="D2" s="56"/>
@@ -11722,8 +11736,21 @@
       <c r="I2" s="56"/>
       <c r="J2" s="56"/>
       <c r="K2" s="57"/>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="O2" s="1"/>
+      <c r="P2" s="55" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q2" s="56"/>
+      <c r="R2" s="56"/>
+      <c r="S2" s="56"/>
+      <c r="T2" s="56"/>
+      <c r="U2" s="56"/>
+      <c r="V2" s="56"/>
+      <c r="W2" s="56"/>
+      <c r="X2" s="56"/>
+      <c r="Y2" s="57"/>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="58"/>
       <c r="C3" s="59"/>
@@ -11735,8 +11762,19 @@
       <c r="I3" s="59"/>
       <c r="J3" s="59"/>
       <c r="K3" s="60"/>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="O3" s="1"/>
+      <c r="P3" s="58"/>
+      <c r="Q3" s="59"/>
+      <c r="R3" s="59"/>
+      <c r="S3" s="59"/>
+      <c r="T3" s="59"/>
+      <c r="U3" s="59"/>
+      <c r="V3" s="59"/>
+      <c r="W3" s="59"/>
+      <c r="X3" s="59"/>
+      <c r="Y3" s="60"/>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" s="58"/>
       <c r="C4" s="59"/>
@@ -11748,8 +11786,19 @@
       <c r="I4" s="59"/>
       <c r="J4" s="59"/>
       <c r="K4" s="60"/>
-    </row>
-    <row r="5" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O4" s="1"/>
+      <c r="P4" s="58"/>
+      <c r="Q4" s="59"/>
+      <c r="R4" s="59"/>
+      <c r="S4" s="59"/>
+      <c r="T4" s="59"/>
+      <c r="U4" s="59"/>
+      <c r="V4" s="59"/>
+      <c r="W4" s="59"/>
+      <c r="X4" s="59"/>
+      <c r="Y4" s="60"/>
+    </row>
+    <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
       <c r="B5" s="61"/>
       <c r="C5" s="62"/>
@@ -11761,8 +11810,19 @@
       <c r="I5" s="62"/>
       <c r="J5" s="62"/>
       <c r="K5" s="63"/>
-    </row>
-    <row r="6" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O5" s="1"/>
+      <c r="P5" s="61"/>
+      <c r="Q5" s="62"/>
+      <c r="R5" s="62"/>
+      <c r="S5" s="62"/>
+      <c r="T5" s="62"/>
+      <c r="U5" s="62"/>
+      <c r="V5" s="62"/>
+      <c r="W5" s="62"/>
+      <c r="X5" s="62"/>
+      <c r="Y5" s="63"/>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
       <c r="B6" s="2"/>
       <c r="C6" s="3" t="s">
@@ -11780,8 +11840,25 @@
       <c r="I6" s="65"/>
       <c r="J6" s="65"/>
       <c r="K6" s="66"/>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="O6" s="1"/>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="R6" s="64" t="s">
+        <v>2</v>
+      </c>
+      <c r="S6" s="65"/>
+      <c r="T6" s="65"/>
+      <c r="U6" s="66"/>
+      <c r="V6" s="65" t="s">
+        <v>3</v>
+      </c>
+      <c r="W6" s="65"/>
+      <c r="X6" s="65"/>
+      <c r="Y6" s="66"/>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
         <v>4</v>
       </c>
@@ -11821,22 +11898,47 @@
       <c r="M7" s="49" t="s">
         <v>58</v>
       </c>
-      <c r="O7" s="2"/>
-      <c r="P7" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="64" t="s">
-        <v>2</v>
-      </c>
-      <c r="R7" s="65"/>
-      <c r="S7" s="65"/>
-      <c r="T7" s="65" t="s">
-        <v>3</v>
-      </c>
-      <c r="U7" s="65"/>
-      <c r="V7" s="65"/>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="O7" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="P7" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q7" s="38" t="s">
+        <v>6</v>
+      </c>
+      <c r="R7" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S7" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="T7" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="U7" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="V7" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="W7" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="X7" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y7" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>59</v>
+      </c>
+      <c r="AA7" s="49" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A8" s="27"/>
       <c r="B8" s="10" t="s">
         <v>16</v>
@@ -11877,32 +11979,48 @@
       <c r="M8" s="49">
         <v>7</v>
       </c>
-      <c r="O8" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="P8" s="38" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q8" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R8" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="S8" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="T8" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="U8" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="V8" s="12" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="O8" s="27"/>
+      <c r="P8" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q8" s="12">
+        <v>40</v>
+      </c>
+      <c r="R8" s="12">
+        <v>0</v>
+      </c>
+      <c r="S8" s="12">
+        <v>40</v>
+      </c>
+      <c r="T8" s="12">
+        <v>0</v>
+      </c>
+      <c r="U8" s="28">
+        <f>SUM(R8:T8)/20</f>
+        <v>2</v>
+      </c>
+      <c r="V8" s="12">
+        <v>60</v>
+      </c>
+      <c r="W8" s="12">
+        <v>10</v>
+      </c>
+      <c r="X8" s="12">
+        <v>10</v>
+      </c>
+      <c r="Y8" s="28">
+        <f>SUM(V8:X8)/20</f>
+        <v>4</v>
+      </c>
+      <c r="Z8">
+        <f>SUM(Q8:T8,V8,W8,X8)/40</f>
+        <v>4</v>
+      </c>
+      <c r="AA8" s="49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A9" s="27"/>
       <c r="B9" s="10" t="s">
         <v>68</v>
@@ -11939,16 +12057,46 @@
       <c r="M9" s="49">
         <v>8</v>
       </c>
-      <c r="O9" s="10"/>
-      <c r="P9" s="12"/>
+      <c r="O9" s="27"/>
+      <c r="P9" s="10" t="s">
+        <v>68</v>
+      </c>
       <c r="Q9" s="12"/>
-      <c r="R9" s="12"/>
-      <c r="S9" s="12"/>
-      <c r="T9" s="12"/>
-      <c r="U9" s="12"/>
-      <c r="V9" s="12"/>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="R9" s="12">
+        <v>60</v>
+      </c>
+      <c r="S9" s="12">
+        <v>60</v>
+      </c>
+      <c r="T9" s="12">
+        <v>0</v>
+      </c>
+      <c r="U9" s="28">
+        <f t="shared" ref="U9:U12" si="3">SUM(R9:T9)/20</f>
+        <v>6</v>
+      </c>
+      <c r="V9" s="12">
+        <v>247</v>
+      </c>
+      <c r="W9" s="12">
+        <v>247</v>
+      </c>
+      <c r="X9" s="12">
+        <v>258</v>
+      </c>
+      <c r="Y9" s="28">
+        <f t="shared" ref="Y9:Y12" si="4">SUM(V9:X9)/20</f>
+        <v>37.6</v>
+      </c>
+      <c r="Z9">
+        <f t="shared" ref="Z9:Z12" si="5">SUM(Q9:T9,V9,W9,X9)/40</f>
+        <v>21.8</v>
+      </c>
+      <c r="AA9" s="49">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
         <v>11</v>
@@ -11987,16 +12135,32 @@
       <c r="M10" s="49">
         <v>4</v>
       </c>
-      <c r="O10" s="10"/>
-      <c r="P10" s="12"/>
+      <c r="O10" s="27"/>
+      <c r="P10" s="10" t="s">
+        <v>11</v>
+      </c>
       <c r="Q10" s="12"/>
       <c r="R10" s="12"/>
       <c r="S10" s="12"/>
       <c r="T10" s="12"/>
-      <c r="U10" s="12"/>
+      <c r="U10" s="28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="V10" s="12"/>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W10" s="12"/>
+      <c r="X10" s="12"/>
+      <c r="Y10" s="28">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Z10">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA10" s="49"/>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
         <v>15</v>
@@ -12037,16 +12201,48 @@
       <c r="M11" s="42">
         <v>5</v>
       </c>
-      <c r="O11" s="10"/>
-      <c r="P11" s="12"/>
-      <c r="Q11" s="12"/>
-      <c r="R11" s="12"/>
-      <c r="S11" s="12"/>
-      <c r="T11" s="12"/>
-      <c r="U11" s="12"/>
-      <c r="V11" s="12"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="O11" s="11"/>
+      <c r="P11" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q11" s="12">
+        <v>60</v>
+      </c>
+      <c r="R11" s="12">
+        <v>0</v>
+      </c>
+      <c r="S11" s="12">
+        <v>0</v>
+      </c>
+      <c r="T11" s="12">
+        <v>0</v>
+      </c>
+      <c r="U11" s="28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V11" s="12">
+        <v>16</v>
+      </c>
+      <c r="W11" s="12">
+        <v>40</v>
+      </c>
+      <c r="X11" s="12">
+        <v>72</v>
+      </c>
+      <c r="Y11" s="28">
+        <f t="shared" si="4"/>
+        <v>6.4</v>
+      </c>
+      <c r="Z11">
+        <f t="shared" si="5"/>
+        <v>4.7</v>
+      </c>
+      <c r="AA11" s="42">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
       <c r="B12" s="11"/>
       <c r="C12" s="12"/>
@@ -12069,15 +12265,28 @@
         <v>0</v>
       </c>
       <c r="O12" s="11"/>
-      <c r="P12" s="12"/>
+      <c r="P12" s="11"/>
       <c r="Q12" s="12"/>
       <c r="R12" s="12"/>
       <c r="S12" s="12"/>
       <c r="T12" s="12"/>
-      <c r="U12" s="12"/>
+      <c r="U12" s="28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="V12" s="12"/>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W12" s="12"/>
+      <c r="X12" s="12"/>
+      <c r="Y12" s="28">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Z12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
       <c r="B13" s="11"/>
       <c r="C13" s="12"/>
@@ -12090,67 +12299,104 @@
       <c r="J13" s="12"/>
       <c r="K13" s="12"/>
       <c r="O13" s="11"/>
-      <c r="P13" s="12"/>
+      <c r="P13" s="11"/>
       <c r="Q13" s="12"/>
       <c r="R13" s="12"/>
       <c r="S13" s="12"/>
       <c r="T13" s="12"/>
       <c r="U13" s="12"/>
       <c r="V13" s="12"/>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W13" s="12"/>
+      <c r="X13" s="12"/>
+      <c r="Y13" s="12"/>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:K14" si="3">SUM(C8:C13)</f>
+        <f t="shared" ref="C14:K14" si="6">SUM(C8:C13)</f>
         <v>250</v>
       </c>
       <c r="D14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>180</v>
       </c>
       <c r="E14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>200</v>
       </c>
       <c r="F14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="G14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>19</v>
       </c>
       <c r="H14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>439</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>358</v>
       </c>
       <c r="J14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>543</v>
       </c>
       <c r="K14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>67</v>
       </c>
       <c r="L14" s="36">
         <f>C14+D14+E14+F14+H14+I14+J14</f>
         <v>1970</v>
       </c>
-      <c r="O14" s="11"/>
-      <c r="P14" s="12"/>
-      <c r="Q14" s="12"/>
-      <c r="R14" s="12"/>
-      <c r="S14" s="12"/>
-      <c r="T14" s="12"/>
-      <c r="U14" s="12"/>
-      <c r="V14" s="12"/>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="O14" s="13"/>
+      <c r="P14" s="10"/>
+      <c r="Q14" s="14">
+        <f t="shared" ref="Q14:Y14" si="7">SUM(Q8:Q13)</f>
+        <v>100</v>
+      </c>
+      <c r="R14" s="14">
+        <f t="shared" si="7"/>
+        <v>60</v>
+      </c>
+      <c r="S14" s="14">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+      <c r="T14" s="14">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="14">
+        <f t="shared" si="7"/>
+        <v>8</v>
+      </c>
+      <c r="V14" s="14">
+        <f t="shared" si="7"/>
+        <v>323</v>
+      </c>
+      <c r="W14" s="14">
+        <f t="shared" si="7"/>
+        <v>297</v>
+      </c>
+      <c r="X14" s="14">
+        <f t="shared" si="7"/>
+        <v>340</v>
+      </c>
+      <c r="Y14" s="14">
+        <f t="shared" si="7"/>
+        <v>48</v>
+      </c>
+      <c r="Z14" s="36">
+        <f>Q14+R14+S14+T14+V14+W14+X14</f>
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="13"/>
       <c r="B15" s="10" t="s">
         <v>40</v>
@@ -12161,29 +12407,60 @@
         <v>9</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:J15" si="4">E14/20</f>
+        <f t="shared" ref="E15:J15" si="8">E14/20</f>
         <v>10</v>
       </c>
       <c r="F15" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>21.95</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>17.899999999999999</v>
       </c>
       <c r="J15" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>27.15</v>
       </c>
       <c r="K15" s="13"/>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="O15" s="13"/>
+      <c r="P15" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q15" s="13"/>
+      <c r="R15" s="13">
+        <f>R14/20</f>
+        <v>3</v>
+      </c>
+      <c r="S15" s="13">
+        <f t="shared" ref="S15:T15" si="9">S14/20</f>
+        <v>5</v>
+      </c>
+      <c r="T15" s="13">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="13"/>
+      <c r="V15" s="13">
+        <f t="shared" ref="V15:X15" si="10">V14/20</f>
+        <v>16.149999999999999</v>
+      </c>
+      <c r="W15" s="13">
+        <f t="shared" si="10"/>
+        <v>14.85</v>
+      </c>
+      <c r="X15" s="13">
+        <f t="shared" si="10"/>
+        <v>17</v>
+      </c>
+      <c r="Y15" s="13"/>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="13"/>
       <c r="B16" s="10" t="s">
         <v>39</v>
@@ -12193,33 +12470,67 @@
         <v>250</v>
       </c>
       <c r="D16" s="37">
-        <f t="shared" ref="D16:J16" si="5">D15+D14</f>
+        <f t="shared" ref="D16:J16" si="11">D15+D14</f>
         <v>189</v>
       </c>
       <c r="E16" s="37">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>210</v>
       </c>
       <c r="F16" s="37">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="G16" s="37"/>
       <c r="H16" s="37">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>460.95</v>
       </c>
       <c r="I16" s="37">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>375.9</v>
       </c>
       <c r="J16" s="37">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>570.15</v>
       </c>
       <c r="K16" s="37"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="O16" s="13"/>
+      <c r="P16" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q16" s="37">
+        <f>Q15+Q14</f>
+        <v>100</v>
+      </c>
+      <c r="R16" s="37">
+        <f t="shared" ref="R16:T16" si="12">R15+R14</f>
+        <v>63</v>
+      </c>
+      <c r="S16" s="37">
+        <f t="shared" si="12"/>
+        <v>105</v>
+      </c>
+      <c r="T16" s="37">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="37"/>
+      <c r="V16" s="37">
+        <f t="shared" ref="V16:X16" si="13">V15+V14</f>
+        <v>339.15</v>
+      </c>
+      <c r="W16" s="37">
+        <f t="shared" si="13"/>
+        <v>311.85000000000002</v>
+      </c>
+      <c r="X16" s="37">
+        <f t="shared" si="13"/>
+        <v>357</v>
+      </c>
+      <c r="Y16" s="37"/>
+    </row>
+    <row r="17" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A17" s="13"/>
       <c r="B17" s="40" t="s">
         <v>41</v>
@@ -12229,28 +12540,28 @@
         <v>6.25</v>
       </c>
       <c r="D17" s="37">
-        <f t="shared" ref="D17:J17" si="6">D14/40</f>
+        <f t="shared" ref="D17:J17" si="14">D14/40</f>
         <v>4.5</v>
       </c>
       <c r="E17" s="37">
-        <f t="shared" si="6"/>
+        <f t="shared" si="14"/>
         <v>5</v>
       </c>
       <c r="F17" s="37">
-        <f t="shared" si="6"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="G17" s="37"/>
       <c r="H17" s="37">
-        <f t="shared" si="6"/>
+        <f t="shared" si="14"/>
         <v>10.975</v>
       </c>
       <c r="I17" s="37">
-        <f t="shared" si="6"/>
+        <f t="shared" si="14"/>
         <v>8.9499999999999993</v>
       </c>
       <c r="J17" s="37">
-        <f t="shared" si="6"/>
+        <f t="shared" si="14"/>
         <v>13.574999999999999</v>
       </c>
       <c r="K17" s="37"/>
@@ -12258,11 +12569,49 @@
         <f>SUM(C17:J17)</f>
         <v>49.25</v>
       </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="O17" s="13"/>
+      <c r="P17" s="40" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q17" s="37">
+        <f>Q14/40</f>
+        <v>2.5</v>
+      </c>
+      <c r="R17" s="37">
+        <f t="shared" ref="R17:T17" si="15">R14/40</f>
+        <v>1.5</v>
+      </c>
+      <c r="S17" s="37">
+        <f t="shared" si="15"/>
+        <v>2.5</v>
+      </c>
+      <c r="T17" s="37">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="U17" s="37"/>
+      <c r="V17" s="37">
+        <f t="shared" ref="V17:X17" si="16">V14/40</f>
+        <v>8.0749999999999993</v>
+      </c>
+      <c r="W17" s="37">
+        <f t="shared" si="16"/>
+        <v>7.4249999999999998</v>
+      </c>
+      <c r="X17" s="37">
+        <f t="shared" si="16"/>
+        <v>8.5</v>
+      </c>
+      <c r="Y17" s="37"/>
+      <c r="Z17" s="36">
+        <f>SUM(Q17:X17)</f>
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26" x14ac:dyDescent="0.35">
       <c r="C18" s="32"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="26"/>
@@ -12276,12 +12625,14 @@
       <c r="K19" s="26"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="7">
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="P2:Y5"/>
+    <mergeCell ref="R6:U6"/>
+    <mergeCell ref="V6:Y6"/>
     <mergeCell ref="B2:K5"/>
     <mergeCell ref="D6:G6"/>
     <mergeCell ref="H6:K6"/>
-    <mergeCell ref="Q7:S7"/>
-    <mergeCell ref="T7:V7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -12289,7 +12640,7 @@
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2852D254-6817-4C2C-AE7A-E9C5892E76B5}">
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.90625" bestFit="1" customWidth="1"/>
@@ -12304,7 +12655,7 @@
     <col min="11" max="11" width="5.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -12317,10 +12668,10 @@
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="55" t="s">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="C2" s="56"/>
       <c r="D2" s="56"/>
@@ -12332,7 +12683,7 @@
       <c r="J2" s="56"/>
       <c r="K2" s="57"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="58"/>
       <c r="C3" s="59"/>
@@ -12345,7 +12696,7 @@
       <c r="J3" s="59"/>
       <c r="K3" s="60"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" s="58"/>
       <c r="C4" s="59"/>
@@ -12358,7 +12709,7 @@
       <c r="J4" s="59"/>
       <c r="K4" s="60"/>
     </row>
-    <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
       <c r="B5" s="61"/>
       <c r="C5" s="62"/>
@@ -12371,7 +12722,7 @@
       <c r="J5" s="62"/>
       <c r="K5" s="63"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
       <c r="B6" s="2"/>
       <c r="C6" s="3" t="s">
@@ -12390,7 +12741,7 @@
       <c r="J6" s="65"/>
       <c r="K6" s="66"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
         <v>4</v>
       </c>
@@ -12424,14 +12775,21 @@
       <c r="K7" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="L7" t="s">
+      <c r="L7" s="53" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M7" s="68" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" s="27"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="12"/>
+      <c r="B8" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="C8" s="12">
+        <v>48</v>
+      </c>
       <c r="D8" s="12"/>
       <c r="E8" s="12"/>
       <c r="F8" s="12"/>
@@ -12439,92 +12797,203 @@
         <f>SUM(D8:F8)/20</f>
         <v>0</v>
       </c>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="12"/>
+      <c r="H8" s="12">
+        <v>19</v>
+      </c>
+      <c r="I8" s="12">
+        <v>7</v>
+      </c>
+      <c r="J8" s="12">
+        <v>31</v>
+      </c>
       <c r="K8" s="28">
         <f>SUM(H8:J8)/20</f>
-        <v>0</v>
-      </c>
-      <c r="L8">
+        <v>2.85</v>
+      </c>
+      <c r="L8" s="53">
         <f>SUM(C8:F8,H8,I8,J8)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+        <v>2.625</v>
+      </c>
+      <c r="M8" s="53">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" s="27"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12"/>
-      <c r="K9" s="28"/>
-      <c r="L9">
-        <f t="shared" ref="L9:L12" si="0">SUM(C9:F9,H9,I9,J9)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B9" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="12">
+        <v>36</v>
+      </c>
+      <c r="D9" s="12">
+        <v>26</v>
+      </c>
+      <c r="E9" s="12">
+        <v>26</v>
+      </c>
+      <c r="F9" s="12">
+        <v>0</v>
+      </c>
+      <c r="G9" s="28">
+        <f t="shared" ref="G9:G12" si="0">SUM(D9:F9)/20</f>
+        <v>2.6</v>
+      </c>
+      <c r="H9" s="12">
+        <v>169</v>
+      </c>
+      <c r="I9" s="12">
+        <v>64</v>
+      </c>
+      <c r="J9" s="12">
+        <v>129</v>
+      </c>
+      <c r="K9" s="28">
+        <f t="shared" ref="K9:K12" si="1">SUM(H9:J9)/20</f>
+        <v>18.100000000000001</v>
+      </c>
+      <c r="L9" s="53">
+        <f t="shared" ref="L9:L12" si="2">SUM(C9:F9,H9,I9,J9)/40</f>
+        <v>11.25</v>
+      </c>
+      <c r="M9" s="53">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="28"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="28"/>
-      <c r="L10">
+      <c r="B10" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="C10" s="12">
+        <v>352</v>
+      </c>
+      <c r="D10" s="12">
+        <v>35</v>
+      </c>
+      <c r="E10" s="12">
+        <v>35</v>
+      </c>
+      <c r="F10" s="12">
+        <v>0</v>
+      </c>
+      <c r="G10" s="28">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+        <v>3.5</v>
+      </c>
+      <c r="H10" s="12">
+        <v>20</v>
+      </c>
+      <c r="I10" s="12">
+        <v>20</v>
+      </c>
+      <c r="J10" s="12">
+        <v>20</v>
+      </c>
+      <c r="K10" s="28">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="L10" s="53">
+        <f t="shared" si="2"/>
+        <v>12.05</v>
+      </c>
+      <c r="M10" s="53">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="12"/>
-      <c r="K11" s="12"/>
-      <c r="L11">
+      <c r="B11" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="12">
+        <v>340</v>
+      </c>
+      <c r="D11" s="12">
+        <v>106</v>
+      </c>
+      <c r="E11" s="12">
+        <v>106</v>
+      </c>
+      <c r="F11" s="12">
+        <v>0</v>
+      </c>
+      <c r="G11" s="28">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+        <v>10.6</v>
+      </c>
+      <c r="H11" s="12">
+        <v>111</v>
+      </c>
+      <c r="I11" s="12">
+        <v>96</v>
+      </c>
+      <c r="J11" s="12">
+        <v>133</v>
+      </c>
+      <c r="K11" s="28">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="L11" s="53">
+        <f t="shared" si="2"/>
+        <v>22.3</v>
+      </c>
+      <c r="M11" s="53">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="12"/>
-      <c r="K12" s="12"/>
-      <c r="L12">
+      <c r="B12" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="12">
+        <v>22</v>
+      </c>
+      <c r="D12" s="12">
+        <v>50</v>
+      </c>
+      <c r="E12" s="12">
+        <v>30</v>
+      </c>
+      <c r="F12" s="12">
+        <v>0</v>
+      </c>
+      <c r="G12" s="28">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+      <c r="H12" s="12">
+        <v>10</v>
+      </c>
+      <c r="I12" s="12">
+        <v>10</v>
+      </c>
+      <c r="J12" s="12">
+        <v>30</v>
+      </c>
+      <c r="K12" s="28">
+        <f t="shared" si="1"/>
+        <v>2.5</v>
+      </c>
+      <c r="L12" s="53">
+        <f t="shared" si="2"/>
+        <v>3.8</v>
+      </c>
+      <c r="M12" s="53">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
       <c r="B13" s="11"/>
       <c r="C13" s="12"/>
       <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
+      <c r="E13" s="12">
+        <v>0</v>
+      </c>
       <c r="F13" s="12"/>
       <c r="G13" s="12"/>
       <c r="H13" s="12"/>
@@ -12532,51 +13001,51 @@
       <c r="J13" s="12"/>
       <c r="K13" s="12"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:K14" si="1">SUM(C8:C13)</f>
-        <v>0</v>
+        <f t="shared" ref="C14:K14" si="3">SUM(C8:C13)</f>
+        <v>798</v>
       </c>
       <c r="D14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>217</v>
       </c>
       <c r="E14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>197</v>
       </c>
       <c r="F14" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>20.7</v>
       </c>
       <c r="H14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>329</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>197</v>
       </c>
       <c r="J14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>343</v>
       </c>
       <c r="K14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>43.45</v>
       </c>
       <c r="L14" s="36">
         <f>C14+D14+E14+F14+H14+I14+J14</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+        <v>2081</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" s="13"/>
       <c r="B15" s="10" t="s">
         <v>40</v>
@@ -12584,64 +13053,64 @@
       <c r="C15" s="13"/>
       <c r="D15" s="13">
         <f>D14/20</f>
-        <v>0</v>
+        <v>10.85</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:J15" si="2">E14/20</f>
-        <v>0</v>
+        <f t="shared" ref="E15:J15" si="4">E14/20</f>
+        <v>9.85</v>
       </c>
       <c r="F15" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>16.45</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>9.85</v>
       </c>
       <c r="J15" s="13">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>17.149999999999999</v>
       </c>
       <c r="K15" s="13"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" s="13"/>
       <c r="B16" s="10" t="s">
         <v>39</v>
       </c>
       <c r="C16" s="37">
         <f>C15+C14</f>
-        <v>0</v>
+        <v>798</v>
       </c>
       <c r="D16" s="37">
-        <f t="shared" ref="D16:J16" si="3">D15+D14</f>
-        <v>0</v>
+        <f t="shared" ref="D16:J16" si="5">D15+D14</f>
+        <v>227.85</v>
       </c>
       <c r="E16" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>206.85</v>
       </c>
       <c r="F16" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G16" s="37"/>
       <c r="H16" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>345.45</v>
       </c>
       <c r="I16" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>206.85</v>
       </c>
       <c r="J16" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>360.15</v>
       </c>
       <c r="K16" s="37"/>
     </row>
@@ -12652,37 +13121,37 @@
       </c>
       <c r="C17" s="37">
         <f>C14/40</f>
-        <v>0</v>
+        <v>19.95</v>
       </c>
       <c r="D17" s="37">
-        <f t="shared" ref="D17:J17" si="4">D14/40</f>
-        <v>0</v>
+        <f t="shared" ref="D17:J17" si="6">D14/40</f>
+        <v>5.4249999999999998</v>
       </c>
       <c r="E17" s="37">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>4.9249999999999998</v>
       </c>
       <c r="F17" s="37">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="G17" s="37"/>
       <c r="H17" s="37">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>8.2249999999999996</v>
       </c>
       <c r="I17" s="37">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>4.9249999999999998</v>
       </c>
       <c r="J17" s="37">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>8.5749999999999993</v>
       </c>
       <c r="K17" s="37"/>
       <c r="L17" s="36">
         <f>SUM(C17:J17)</f>
-        <v>0</v>
+        <v>52.024999999999991</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">

--- a/Final Execution SKU wise.xlsx
+++ b/Final Execution SKU wise.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D2FE5B8-6033-4894-8CA3-215C53556F8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCAE4F30-E0EA-4D71-915B-FA2B1D3EEED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" firstSheet="1" activeTab="28" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" firstSheet="1" activeTab="27" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
   </bookViews>
   <sheets>
     <sheet name="last month" sheetId="1" r:id="rId1"/>
@@ -750,7 +750,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
@@ -912,9 +912,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -12778,7 +12775,7 @@
       <c r="L7" s="53" t="s">
         <v>59</v>
       </c>
-      <c r="M7" s="68" t="s">
+      <c r="M7" s="49" t="s">
         <v>80</v>
       </c>
     </row>

--- a/Final Execution SKU wise.xlsx
+++ b/Final Execution SKU wise.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCAE4F30-E0EA-4D71-915B-FA2B1D3EEED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31C01FE5-6F68-4064-8029-3047330D929C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" firstSheet="1" activeTab="27" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" firstSheet="1" activeTab="28" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
   </bookViews>
   <sheets>
     <sheet name="last month" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="820" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="844" uniqueCount="81">
   <si>
     <t>Gate Pass</t>
   </si>
@@ -404,7 +404,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="29">
+  <borders count="32">
     <border>
       <left/>
       <right/>
@@ -746,11 +746,48 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
@@ -911,6 +948,18 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -12637,7 +12686,7 @@
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2852D254-6817-4C2C-AE7A-E9C5892E76B5}">
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:AA19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.90625" bestFit="1" customWidth="1"/>
@@ -12650,9 +12699,17 @@
     <col min="8" max="9" width="4.26953125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="3.54296875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="4" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="3.90625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.26953125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="3.08984375" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="5" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="3.08984375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="5.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -12665,7 +12722,7 @@
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="1"/>
       <c r="B2" s="55" t="s">
         <v>75</v>
@@ -12679,8 +12736,10 @@
       <c r="I2" s="56"/>
       <c r="J2" s="56"/>
       <c r="K2" s="57"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="Q2" s="71"/>
+      <c r="R2" s="71"/>
+    </row>
+    <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="58"/>
       <c r="C3" s="59"/>
@@ -12692,8 +12751,21 @@
       <c r="I3" s="59"/>
       <c r="J3" s="59"/>
       <c r="K3" s="60"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="O3" s="1"/>
+      <c r="P3" s="55" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q3" s="56"/>
+      <c r="R3" s="56"/>
+      <c r="S3" s="56"/>
+      <c r="T3" s="56"/>
+      <c r="U3" s="56"/>
+      <c r="V3" s="56"/>
+      <c r="W3" s="56"/>
+      <c r="X3" s="56"/>
+      <c r="Y3" s="57"/>
+    </row>
+    <row r="4" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" s="58"/>
       <c r="C4" s="59"/>
@@ -12705,8 +12777,19 @@
       <c r="I4" s="59"/>
       <c r="J4" s="59"/>
       <c r="K4" s="60"/>
-    </row>
-    <row r="5" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O4" s="1"/>
+      <c r="P4" s="58"/>
+      <c r="Q4" s="59"/>
+      <c r="R4" s="59"/>
+      <c r="S4" s="59"/>
+      <c r="T4" s="59"/>
+      <c r="U4" s="59"/>
+      <c r="V4" s="59"/>
+      <c r="W4" s="59"/>
+      <c r="X4" s="59"/>
+      <c r="Y4" s="60"/>
+    </row>
+    <row r="5" spans="1:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
       <c r="B5" s="61"/>
       <c r="C5" s="62"/>
@@ -12718,8 +12801,19 @@
       <c r="I5" s="62"/>
       <c r="J5" s="62"/>
       <c r="K5" s="63"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="O5" s="1"/>
+      <c r="P5" s="58"/>
+      <c r="Q5" s="59"/>
+      <c r="R5" s="59"/>
+      <c r="S5" s="59"/>
+      <c r="T5" s="59"/>
+      <c r="U5" s="59"/>
+      <c r="V5" s="59"/>
+      <c r="W5" s="59"/>
+      <c r="X5" s="59"/>
+      <c r="Y5" s="60"/>
+    </row>
+    <row r="6" spans="1:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="1"/>
       <c r="B6" s="2"/>
       <c r="C6" s="3" t="s">
@@ -12737,8 +12831,19 @@
       <c r="I6" s="65"/>
       <c r="J6" s="65"/>
       <c r="K6" s="66"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="O6" s="1"/>
+      <c r="P6" s="61"/>
+      <c r="Q6" s="62"/>
+      <c r="R6" s="62"/>
+      <c r="S6" s="62"/>
+      <c r="T6" s="62"/>
+      <c r="U6" s="62"/>
+      <c r="V6" s="62"/>
+      <c r="W6" s="62"/>
+      <c r="X6" s="62"/>
+      <c r="Y6" s="63"/>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
         <v>4</v>
       </c>
@@ -12778,8 +12883,25 @@
       <c r="M7" s="49" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="O7" s="1"/>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="R7" s="68" t="s">
+        <v>2</v>
+      </c>
+      <c r="S7" s="69"/>
+      <c r="T7" s="69"/>
+      <c r="U7" s="70"/>
+      <c r="V7" s="68" t="s">
+        <v>3</v>
+      </c>
+      <c r="W7" s="69"/>
+      <c r="X7" s="69"/>
+      <c r="Y7" s="70"/>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A8" s="27"/>
       <c r="B8" s="10" t="s">
         <v>60</v>
@@ -12814,8 +12936,47 @@
       <c r="M8" s="53">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="O8" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="P8" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q8" s="38" t="s">
+        <v>6</v>
+      </c>
+      <c r="R8" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S8" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="T8" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="U8" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="V8" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="W8" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="X8" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y8" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>59</v>
+      </c>
+      <c r="AA8" s="49" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A9" s="27"/>
       <c r="B9" s="10" t="s">
         <v>11</v>
@@ -12856,8 +13017,46 @@
       <c r="M9" s="53">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="O9" s="27"/>
+      <c r="P9" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q9" s="12"/>
+      <c r="R9" s="12">
+        <v>20</v>
+      </c>
+      <c r="S9" s="12">
+        <v>20</v>
+      </c>
+      <c r="T9" s="12">
+        <v>0</v>
+      </c>
+      <c r="U9" s="28">
+        <f>SUM(R9:T9)/20</f>
+        <v>2</v>
+      </c>
+      <c r="V9" s="12">
+        <v>155</v>
+      </c>
+      <c r="W9" s="12">
+        <v>50</v>
+      </c>
+      <c r="X9" s="12">
+        <v>115</v>
+      </c>
+      <c r="Y9" s="28">
+        <f>SUM(V9:X9)/20</f>
+        <v>16</v>
+      </c>
+      <c r="Z9">
+        <f>SUM(Q9:T9,V9,W9,X9)/40</f>
+        <v>9</v>
+      </c>
+      <c r="AA9" s="49">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
         <v>71</v>
@@ -12898,8 +13097,42 @@
       <c r="M10" s="53">
         <v>10</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="O10" s="27"/>
+      <c r="P10" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q10" s="12">
+        <v>152</v>
+      </c>
+      <c r="R10" s="12">
+        <v>15</v>
+      </c>
+      <c r="S10" s="12">
+        <v>15</v>
+      </c>
+      <c r="T10" s="12">
+        <v>0</v>
+      </c>
+      <c r="U10" s="28">
+        <f t="shared" ref="U10:U13" si="3">SUM(R10:T10)/20</f>
+        <v>1.5</v>
+      </c>
+      <c r="V10" s="12"/>
+      <c r="W10" s="12"/>
+      <c r="X10" s="12"/>
+      <c r="Y10" s="28">
+        <f t="shared" ref="Y10:Y13" si="4">SUM(V10:X10)/20</f>
+        <v>0</v>
+      </c>
+      <c r="Z10">
+        <f t="shared" ref="Z10:Z13" si="5">SUM(Q10:T10,V10,W10,X10)/40</f>
+        <v>4.55</v>
+      </c>
+      <c r="AA10" s="49">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
         <v>16</v>
@@ -12940,8 +13173,48 @@
       <c r="M11" s="53">
         <v>20</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="O11" s="27"/>
+      <c r="P11" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q11" s="12">
+        <v>260</v>
+      </c>
+      <c r="R11" s="12">
+        <v>96</v>
+      </c>
+      <c r="S11" s="12">
+        <v>96</v>
+      </c>
+      <c r="T11" s="12">
+        <v>0</v>
+      </c>
+      <c r="U11" s="28">
+        <f t="shared" si="3"/>
+        <v>9.6</v>
+      </c>
+      <c r="V11" s="12">
+        <v>81</v>
+      </c>
+      <c r="W11" s="12">
+        <v>76</v>
+      </c>
+      <c r="X11" s="12">
+        <v>103</v>
+      </c>
+      <c r="Y11" s="28">
+        <f t="shared" si="4"/>
+        <v>13</v>
+      </c>
+      <c r="Z11">
+        <f t="shared" si="5"/>
+        <v>17.8</v>
+      </c>
+      <c r="AA11" s="49">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
       <c r="B12" s="11" t="s">
         <v>9</v>
@@ -12982,8 +13255,46 @@
       <c r="M12" s="53">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="O12" s="11"/>
+      <c r="P12" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q12" s="12"/>
+      <c r="R12" s="12">
+        <v>30</v>
+      </c>
+      <c r="S12" s="12">
+        <v>30</v>
+      </c>
+      <c r="T12" s="12">
+        <v>0</v>
+      </c>
+      <c r="U12" s="28">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="V12" s="12">
+        <v>10</v>
+      </c>
+      <c r="W12" s="12">
+        <v>10</v>
+      </c>
+      <c r="X12" s="12">
+        <v>30</v>
+      </c>
+      <c r="Y12" s="28">
+        <f t="shared" si="4"/>
+        <v>2.5</v>
+      </c>
+      <c r="Z12">
+        <f t="shared" si="5"/>
+        <v>2.75</v>
+      </c>
+      <c r="AA12" s="42">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
       <c r="B13" s="11"/>
       <c r="C13" s="12"/>
@@ -12997,52 +13308,84 @@
       <c r="I13" s="12"/>
       <c r="J13" s="12"/>
       <c r="K13" s="12"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="O13" s="11"/>
+      <c r="P13" s="11"/>
+      <c r="Q13" s="12"/>
+      <c r="R13" s="12"/>
+      <c r="S13" s="12"/>
+      <c r="T13" s="12"/>
+      <c r="U13" s="28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V13" s="12"/>
+      <c r="W13" s="12"/>
+      <c r="X13" s="12"/>
+      <c r="Y13" s="28">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Z13">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:K14" si="3">SUM(C8:C13)</f>
+        <f t="shared" ref="C14:K14" si="6">SUM(C8:C13)</f>
         <v>798</v>
       </c>
       <c r="D14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>217</v>
       </c>
       <c r="E14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>197</v>
       </c>
       <c r="F14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="G14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>20.7</v>
       </c>
       <c r="H14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>329</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>197</v>
       </c>
       <c r="J14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>343</v>
       </c>
       <c r="K14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>43.45</v>
       </c>
       <c r="L14" s="36">
         <f>C14+D14+E14+F14+H14+I14+J14</f>
         <v>2081</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="O14" s="11"/>
+      <c r="P14" s="11"/>
+      <c r="Q14" s="12"/>
+      <c r="R14" s="12"/>
+      <c r="S14" s="12"/>
+      <c r="T14" s="12"/>
+      <c r="U14" s="12"/>
+      <c r="V14" s="12"/>
+      <c r="W14" s="12"/>
+      <c r="X14" s="12"/>
+      <c r="Y14" s="12"/>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="13"/>
       <c r="B15" s="10" t="s">
         <v>40</v>
@@ -13053,29 +13396,71 @@
         <v>10.85</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:J15" si="4">E14/20</f>
+        <f t="shared" ref="E15:J15" si="7">E14/20</f>
         <v>9.85</v>
       </c>
       <c r="F15" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>16.45</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>9.85</v>
       </c>
       <c r="J15" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>17.149999999999999</v>
       </c>
       <c r="K15" s="13"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="O15" s="13"/>
+      <c r="P15" s="10"/>
+      <c r="Q15" s="14">
+        <f t="shared" ref="Q15:Y15" si="8">SUM(Q9:Q14)</f>
+        <v>412</v>
+      </c>
+      <c r="R15" s="14">
+        <f t="shared" si="8"/>
+        <v>161</v>
+      </c>
+      <c r="S15" s="14">
+        <f t="shared" si="8"/>
+        <v>161</v>
+      </c>
+      <c r="T15" s="14">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="14">
+        <f t="shared" si="8"/>
+        <v>16.100000000000001</v>
+      </c>
+      <c r="V15" s="14">
+        <f t="shared" si="8"/>
+        <v>246</v>
+      </c>
+      <c r="W15" s="14">
+        <f t="shared" si="8"/>
+        <v>136</v>
+      </c>
+      <c r="X15" s="14">
+        <f t="shared" si="8"/>
+        <v>248</v>
+      </c>
+      <c r="Y15" s="14">
+        <f t="shared" si="8"/>
+        <v>31.5</v>
+      </c>
+      <c r="Z15" s="36">
+        <f>Q15+R15+S15+T15+V15+W15+X15</f>
+        <v>1364</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="13"/>
       <c r="B16" s="10" t="s">
         <v>39</v>
@@ -13085,33 +13470,64 @@
         <v>798</v>
       </c>
       <c r="D16" s="37">
-        <f t="shared" ref="D16:J16" si="5">D15+D14</f>
+        <f t="shared" ref="D16:J16" si="9">D15+D14</f>
         <v>227.85</v>
       </c>
       <c r="E16" s="37">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>206.85</v>
       </c>
       <c r="F16" s="37">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="G16" s="37"/>
       <c r="H16" s="37">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>345.45</v>
       </c>
       <c r="I16" s="37">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>206.85</v>
       </c>
       <c r="J16" s="37">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>360.15</v>
       </c>
       <c r="K16" s="37"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="O16" s="13"/>
+      <c r="P16" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q16" s="13"/>
+      <c r="R16" s="13">
+        <f>R15/20</f>
+        <v>8.0500000000000007</v>
+      </c>
+      <c r="S16" s="13">
+        <f t="shared" ref="S16:T16" si="10">S15/20</f>
+        <v>8.0500000000000007</v>
+      </c>
+      <c r="T16" s="13">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="13"/>
+      <c r="V16" s="13">
+        <f t="shared" ref="V16:X16" si="11">V15/20</f>
+        <v>12.3</v>
+      </c>
+      <c r="W16" s="13">
+        <f t="shared" si="11"/>
+        <v>6.8</v>
+      </c>
+      <c r="X16" s="13">
+        <f t="shared" si="11"/>
+        <v>12.4</v>
+      </c>
+      <c r="Y16" s="13"/>
+    </row>
+    <row r="17" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A17" s="13"/>
       <c r="B17" s="40" t="s">
         <v>41</v>
@@ -13121,28 +13537,28 @@
         <v>19.95</v>
       </c>
       <c r="D17" s="37">
-        <f t="shared" ref="D17:J17" si="6">D14/40</f>
+        <f t="shared" ref="D17:J17" si="12">D14/40</f>
         <v>5.4249999999999998</v>
       </c>
       <c r="E17" s="37">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>4.9249999999999998</v>
       </c>
       <c r="F17" s="37">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="G17" s="37"/>
       <c r="H17" s="37">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>8.2249999999999996</v>
       </c>
       <c r="I17" s="37">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>4.9249999999999998</v>
       </c>
       <c r="J17" s="37">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>8.5749999999999993</v>
       </c>
       <c r="K17" s="37"/>
@@ -13150,11 +13566,83 @@
         <f>SUM(C17:J17)</f>
         <v>52.024999999999991</v>
       </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="O17" s="13"/>
+      <c r="P17" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q17" s="37">
+        <f>Q16+Q15</f>
+        <v>412</v>
+      </c>
+      <c r="R17" s="37">
+        <f t="shared" ref="R17:T17" si="13">R16+R15</f>
+        <v>169.05</v>
+      </c>
+      <c r="S17" s="37">
+        <f t="shared" si="13"/>
+        <v>169.05</v>
+      </c>
+      <c r="T17" s="37">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="U17" s="37"/>
+      <c r="V17" s="37">
+        <f t="shared" ref="V17:X17" si="14">V16+V15</f>
+        <v>258.3</v>
+      </c>
+      <c r="W17" s="37">
+        <f t="shared" si="14"/>
+        <v>142.80000000000001</v>
+      </c>
+      <c r="X17" s="37">
+        <f t="shared" si="14"/>
+        <v>260.39999999999998</v>
+      </c>
+      <c r="Y17" s="37"/>
+    </row>
+    <row r="18" spans="1:26" x14ac:dyDescent="0.35">
       <c r="C18" s="32"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="O18" s="13"/>
+      <c r="P18" s="40" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q18" s="37">
+        <f>Q15/40</f>
+        <v>10.3</v>
+      </c>
+      <c r="R18" s="37">
+        <f t="shared" ref="R18:T18" si="15">R15/40</f>
+        <v>4.0250000000000004</v>
+      </c>
+      <c r="S18" s="37">
+        <f t="shared" si="15"/>
+        <v>4.0250000000000004</v>
+      </c>
+      <c r="T18" s="37">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="37"/>
+      <c r="V18" s="37">
+        <f t="shared" ref="V18:X18" si="16">V15/40</f>
+        <v>6.15</v>
+      </c>
+      <c r="W18" s="37">
+        <f t="shared" si="16"/>
+        <v>3.4</v>
+      </c>
+      <c r="X18" s="37">
+        <f t="shared" si="16"/>
+        <v>6.2</v>
+      </c>
+      <c r="Y18" s="37"/>
+      <c r="Z18" s="36">
+        <f>SUM(Q18:X18)</f>
+        <v>34.1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="26"/>
@@ -13168,7 +13656,11 @@
       <c r="K19" s="26"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="7">
+    <mergeCell ref="R7:U7"/>
+    <mergeCell ref="V7:Y7"/>
+    <mergeCell ref="P3:Y6"/>
+    <mergeCell ref="Q2:R2"/>
     <mergeCell ref="B2:K5"/>
     <mergeCell ref="D6:G6"/>
     <mergeCell ref="H6:K6"/>
